--- a/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
+++ b/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
@@ -8460,12 +8460,12 @@
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>`FST-409`</t>
+          <t>`STI-403`</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
-          <t>Manajemen Sains &amp; Riset Op</t>
+          <t>Pengantar NLP &amp; IR</t>
         </is>
       </c>
       <c r="D49" s="22" t="inlineStr">
@@ -8474,22 +8474,22 @@
         </is>
       </c>
       <c r="E49" s="20" t="inlineStr"/>
-      <c r="F49" s="20" t="inlineStr">
-        <is>
-          <t>**R**</t>
-        </is>
-      </c>
+      <c r="F49" s="20" t="inlineStr"/>
       <c r="G49" s="20" t="inlineStr"/>
       <c r="H49" s="20" t="inlineStr"/>
-      <c r="I49" s="20" t="inlineStr">
+      <c r="I49" s="20" t="inlineStr"/>
+      <c r="J49" s="20" t="inlineStr">
         <is>
           <t>**R**</t>
         </is>
       </c>
-      <c r="J49" s="20" t="inlineStr"/>
       <c r="K49" s="20" t="inlineStr"/>
       <c r="L49" s="20" t="inlineStr"/>
-      <c r="M49" s="20" t="inlineStr"/>
+      <c r="M49" s="20" t="inlineStr">
+        <is>
+          <t>**R**</t>
+        </is>
+      </c>
       <c r="N49" s="20" t="inlineStr"/>
       <c r="O49" s="20" t="inlineStr"/>
       <c r="P49" s="20" t="inlineStr"/>
@@ -8497,12 +8497,12 @@
       <c r="R49" s="20" t="inlineStr"/>
       <c r="S49" s="20" t="inlineStr">
         <is>
-          <t>PL-1, PL-4</t>
+          <t>PL-1</t>
         </is>
       </c>
       <c r="T49" s="20" t="inlineStr">
         <is>
-          <t>PEO-1, PEO-2</t>
+          <t>PEO-1, PEO-3</t>
         </is>
       </c>
       <c r="U49" s="20" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="C137" s="20" t="inlineStr">
         <is>
-          <t>`STI-102`, `STI-103`, `STI-201`, `STI-202`, `FST-408`, `FST-409`</t>
+          <t>`STI-102`, `STI-103`, `STI-201`, `STI-202`, `FST-408`</t>
         </is>
       </c>
       <c r="D137" s="22" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="E137" s="20" t="inlineStr">
         <is>
-          <t>7 MK</t>
+          <t>6 MK</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="C143" s="20" t="inlineStr">
         <is>
-          <t>`STI-302`, `STI-601`, `STA-03`, `STA-05`</t>
+          <t>`STI-302`, `STI-403`, `STI-601`, `STA-03`, `STA-05`</t>
         </is>
       </c>
       <c r="D143" s="20" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="E143" s="20" t="inlineStr">
         <is>
-          <t>6 MK</t>
+          <t>7 MK</t>
         </is>
       </c>
       <c r="F143" s="20" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="C151" s="20" t="inlineStr">
         <is>
-          <t>`STI-302`, `STI-401`, `STI-501`, `STI-601`</t>
+          <t>`STI-302`, `STI-401`, `STI-403`, `STI-501`, `STI-601`</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="E151" s="20" t="inlineStr">
         <is>
-          <t>8 MK</t>
+          <t>9 MK</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
@@ -14441,12 +14441,12 @@
       </c>
       <c r="B196" s="20" t="inlineStr">
         <is>
-          <t>`FST-409`</t>
+          <t>`STI-403`</t>
         </is>
       </c>
       <c r="C196" s="20" t="inlineStr">
         <is>
-          <t>Manajemen Sains &amp; Riset Op</t>
+          <t>Pengantar NLP &amp; IR</t>
         </is>
       </c>
       <c r="D196" s="22" t="inlineStr">
@@ -14456,22 +14456,22 @@
       </c>
       <c r="E196" s="20" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F196" s="20" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="G196" s="20" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="H196" s="20" t="inlineStr">
         <is>
-          <t>**50%**</t>
+          <t>**65%**</t>
         </is>
       </c>
       <c r="I196" s="20" t="inlineStr">
@@ -15794,17 +15794,17 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>14 MK</t>
+          <t>13 MK</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>38 SKS</t>
+          <t>36 SKS</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -15816,17 +15816,17 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>27 MK</t>
+          <t>28 MK</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>77 SKS</t>
+          <t>79 SKS</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>AI/ML, Cloud &amp; Keamanan</t>
+          <t>AI/ML, NLP, Cloud &amp; Keamanan</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>Machine Learning, DW/BI, Web Back, Cloud</t>
+          <t>ML, NLP/IR, DW/BI, Web Back, Cloud, Probstat</t>
         </is>
       </c>
     </row>
@@ -16175,7 +16175,7 @@
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>**Standar Sarjana Terapan Komputasi**</t>
+          <t>**Standar Sarjana S1 Komputasi**</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17298,7 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="15" t="inlineStr">
         <is>
-          <t>SEMESTER 4 (21 SKS) — Penguatan Core AI/ML, DW &amp; Cloud</t>
+          <t>SEMESTER 4 (21 SKS) — Penguatan Core AI/ML, NLP, DW &amp; Cloud</t>
         </is>
       </c>
       <c r="B63" s="16" t="n"/>
@@ -17390,17 +17390,17 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>`STI-402`</t>
+          <t>`STI-403`</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Business Intelligence</t>
+          <t>Pengantar NLP &amp; Information Retrieval</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
@@ -17415,7 +17415,7 @@
       </c>
       <c r="G66" s="20" t="inlineStr">
         <is>
-          <t>`FST-207`</t>
+          <t>`STI-302`</t>
         </is>
       </c>
     </row>
@@ -17427,12 +17427,12 @@
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t>`STI-407`</t>
+          <t>`STI-402`</t>
         </is>
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t>Web Back End Development</t>
+          <t>Data Warehouse &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="D67" s="21" t="inlineStr">
@@ -17452,7 +17452,7 @@
       </c>
       <c r="G67" s="19" t="inlineStr">
         <is>
-          <t>`FST-207`, `STI-306`</t>
+          <t>`FST-207`</t>
         </is>
       </c>
     </row>
@@ -17464,12 +17464,12 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>`STI-404`</t>
+          <t>`STI-407`</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>Komputasi Awan (Cloud Computing)</t>
+          <t>Web Back End Development</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
@@ -17479,7 +17479,7 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
@@ -17489,7 +17489,7 @@
       </c>
       <c r="G68" s="20" t="inlineStr">
         <is>
-          <t>`STI-307`, `STI-305`</t>
+          <t>`FST-207`, `STI-306`</t>
         </is>
       </c>
     </row>
@@ -17501,17 +17501,17 @@
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t>`STI-405`</t>
+          <t>`STI-404`</t>
         </is>
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t>Dasar Keamanan Informasi</t>
+          <t>Komputasi Awan (Cloud Computing)</t>
         </is>
       </c>
       <c r="D69" s="21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`STI-307`, `STI-305`</t>
         </is>
       </c>
     </row>
@@ -17538,17 +17538,17 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>`FST-408`</t>
+          <t>`STI-405`</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>Probabilitas dan Statistika</t>
+          <t>Dasar Keamanan Informasi</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E70" s="20" t="inlineStr">
@@ -17558,12 +17558,12 @@
       </c>
       <c r="F70" s="20" t="inlineStr">
         <is>
-          <t>FSTI</t>
+          <t>Core STI</t>
         </is>
       </c>
       <c r="G70" s="20" t="inlineStr">
         <is>
-          <t>`STI-102`</t>
+          <t>`STI-307`</t>
         </is>
       </c>
     </row>
@@ -17575,17 +17575,17 @@
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t>`FST-409`</t>
+          <t>`FST-408`</t>
         </is>
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t>Manajemen Sains &amp; Riset Operasi</t>
+          <t>Probabilitas dan Statistika</t>
         </is>
       </c>
       <c r="D71" s="21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -17600,7 +17600,7 @@
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`STI-102`</t>
         </is>
       </c>
     </row>
@@ -19087,7 +19087,7 @@
       </c>
       <c r="F120" s="20" t="inlineStr">
         <is>
-          <t>Tahap Penguatan Core AI/ML, DW &amp; Cloud</t>
+          <t>Tahap Penguatan Core AI/ML, NLP &amp; Cloud</t>
         </is>
       </c>
     </row>

--- a/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
+++ b/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
@@ -6297,7 +6297,7 @@
     <col width="28.75" customWidth="1" min="6" max="6"/>
     <col width="37.95" customWidth="1" min="7" max="7"/>
     <col width="37.95" customWidth="1" min="8" max="8"/>
-    <col width="25.3" customWidth="1" min="9" max="9"/>
+    <col width="32.2" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>Logika Informatika</t>
+          <t>Arsitektur &amp; Org. Sistem TI</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -6925,7 +6925,11 @@
         </is>
       </c>
       <c r="J21" s="19" t="inlineStr"/>
-      <c r="K21" s="19" t="inlineStr"/>
+      <c r="K21" s="19" t="inlineStr">
+        <is>
+          <t>**I**</t>
+        </is>
+      </c>
       <c r="L21" s="19" t="inlineStr"/>
       <c r="M21" s="19" t="inlineStr"/>
       <c r="N21" s="19" t="inlineStr"/>
@@ -7127,7 +7131,7 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>Matematika Diskrit</t>
+          <t>Matematika Diskrit &amp; Logika</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -7136,7 +7140,11 @@
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr"/>
-      <c r="F25" s="19" t="inlineStr"/>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>**I**</t>
+        </is>
+      </c>
       <c r="G25" s="19" t="inlineStr"/>
       <c r="H25" s="19" t="inlineStr"/>
       <c r="I25" s="19" t="inlineStr">
@@ -11983,7 +11991,7 @@
       </c>
       <c r="C130" s="19" t="inlineStr">
         <is>
-          <t>`STI-307`, `STI-404`, `STI-305`</t>
+          <t>`STI-103`, `STI-307`, `STI-404`, `STI-305`</t>
         </is>
       </c>
       <c r="D130" s="19" t="inlineStr">
@@ -11993,7 +12001,7 @@
       </c>
       <c r="E130" s="19" t="inlineStr">
         <is>
-          <t>6 MK</t>
+          <t>7 MK</t>
         </is>
       </c>
       <c r="F130" s="19" t="inlineStr">
@@ -12207,7 +12215,7 @@
       </c>
       <c r="C137" s="20" t="inlineStr">
         <is>
-          <t>`STI-102`, `STI-103`, `STI-201`, `STI-202`, `FST-408`</t>
+          <t>`STI-102`, `STI-201`, `STI-202`, `FST-408`</t>
         </is>
       </c>
       <c r="D137" s="22" t="inlineStr">
@@ -12217,7 +12225,7 @@
       </c>
       <c r="E137" s="20" t="inlineStr">
         <is>
-          <t>6 MK</t>
+          <t>5 MK</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
@@ -13271,7 +13279,7 @@
       </c>
       <c r="C171" s="19" t="inlineStr">
         <is>
-          <t>Logika Informatika</t>
+          <t>Arsitektur &amp; Org. Sistem TI</t>
         </is>
       </c>
       <c r="D171" s="21" t="inlineStr">
@@ -13301,7 +13309,7 @@
       </c>
       <c r="I171" s="19" t="inlineStr">
         <is>
-          <t>*MK Teori Dasar Sains*</t>
+          <t>*MK Teori Sistem &amp; Hardware*</t>
         </is>
       </c>
     </row>
@@ -13328,27 +13336,27 @@
       </c>
       <c r="E172" s="20" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G172" s="20" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="H172" s="20" t="inlineStr">
         <is>
-          <t>**60%**</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="I172" s="20" t="inlineStr">
         <is>
-          <t>✅ Patuh IKU 7</t>
+          <t>*MK Teori Dasar Sikap*</t>
         </is>
       </c>
     </row>
@@ -13375,27 +13383,27 @@
       </c>
       <c r="E173" s="19" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F173" s="19" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G173" s="19" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="H173" s="19" t="inlineStr">
         <is>
-          <t>**60%**</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="I173" s="19" t="inlineStr">
         <is>
-          <t>✅ Patuh IKU 7</t>
+          <t>*MK Teori Dasar Sikap*</t>
         </is>
       </c>
     </row>
@@ -13422,27 +13430,27 @@
       </c>
       <c r="E174" s="20" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F174" s="20" t="inlineStr">
+        <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F174" s="20" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
       <c r="G174" s="20" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="H174" s="20" t="inlineStr">
         <is>
-          <t>**60%**</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="I174" s="20" t="inlineStr">
         <is>
-          <t>✅ Patuh IKU 7</t>
+          <t>*MK Keterampilan Komunikasi*</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13467,7 @@
       </c>
       <c r="C175" s="19" t="inlineStr">
         <is>
-          <t>Matematika Diskrit</t>
+          <t>Matematika Diskrit &amp; Logika</t>
         </is>
       </c>
       <c r="D175" s="21" t="inlineStr">
@@ -16183,7 +16191,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>SEMESTER 1 (19 SKS) — Fondasi Sains, Algoritma &amp; MKWU</t>
+          <t>SEMESTER 1 (19 SKS) — Fondasi Sains, Algoritma, Arsitektur STI &amp; MKWU</t>
         </is>
       </c>
       <c r="B28" s="16" t="n"/>
@@ -16238,27 +16246,27 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>`STI-101`</t>
+          <t>`FST-101`</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>Algoritma dan Pemrograman</t>
+          <t>Dasar Teknologi Digital</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
@@ -16275,12 +16283,12 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>`STI-102`</t>
+          <t>`FST-102`</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>Kalkulus dan Aljabar Linier</t>
+          <t>Algoritma dan Pemrograman</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -16290,12 +16298,12 @@
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -16312,17 +16320,17 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>`STI-103`</t>
+          <t>`STI-101`</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>Logika Informatika dan Matematika Diskrit</t>
+          <t>Pengantar Sistem dan Teknologi Informasi</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
@@ -16349,17 +16357,17 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>`STI-104`</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>Pengantar Sistem dan Teknologi Informasi</t>
+          <t>`STI-102`</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>Kalkulus</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -16386,17 +16394,17 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>`MKU-101`</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>Agama I</t>
+          <t>`STI-103`</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>Arsitektur dan Organisasi Sistem Teknologi Informasi</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
@@ -16406,7 +16414,7 @@
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>MKWU</t>
+          <t>Core STI</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
@@ -16423,12 +16431,12 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>`MKU-102`</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
-        <is>
-          <t>Pancasila</t>
+          <t>`MKU-101`</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>Agama I</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -16460,12 +16468,12 @@
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>`MKU-103`</t>
+          <t>`MKU-102`</t>
         </is>
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>Pancasila</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -16497,12 +16505,12 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>`MKU-104`</t>
+          <t>`MKU-103`</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>Bahasa Inggris Komunikasi Saintifik</t>
+          <t>Bahasa Indonesia</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -16567,7 +16575,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>SEMESTER 2 (20 SKS) — Fondasi Data, Matdis, OOP &amp; Etika</t>
+          <t>SEMESTER 2 (20 SKS) — Fondasi Data, Matdis &amp; Logika, Aljabar &amp; Etika</t>
         </is>
       </c>
       <c r="B40" s="16" t="n"/>
@@ -16627,7 +16635,7 @@
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>Struktur Data dan Algoritma Lanjut</t>
+          <t>Matematika Diskrit dan Logika</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
@@ -16637,7 +16645,7 @@
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
@@ -16647,7 +16655,7 @@
       </c>
       <c r="G42" s="19" t="inlineStr">
         <is>
-          <t>`STI-101`</t>
+          <t>`STI-103`</t>
         </is>
       </c>
     </row>
@@ -16664,7 +16672,7 @@
       </c>
       <c r="C43" s="20" t="inlineStr">
         <is>
-          <t>Pemrograman Berorientasi Objek</t>
+          <t>Aljabar Linear dan Matriks</t>
         </is>
       </c>
       <c r="D43" s="22" t="inlineStr">
@@ -16674,7 +16682,7 @@
       </c>
       <c r="E43" s="20" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
@@ -16684,7 +16692,7 @@
       </c>
       <c r="G43" s="20" t="inlineStr">
         <is>
-          <t>`STI-101`</t>
+          <t>`STI-102`</t>
         </is>
       </c>
     </row>
@@ -16696,12 +16704,12 @@
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>`FST-207`</t>
+          <t>`FST-203`</t>
         </is>
       </c>
       <c r="C44" s="19" t="inlineStr">
         <is>
-          <t>Sistem Basis Data</t>
+          <t>Struktur Data dan Algoritma</t>
         </is>
       </c>
       <c r="D44" s="21" t="inlineStr">
@@ -16721,7 +16729,7 @@
       </c>
       <c r="G44" s="19" t="inlineStr">
         <is>
-          <t>`STI-101`</t>
+          <t>`FST-102`</t>
         </is>
       </c>
     </row>
@@ -16733,12 +16741,12 @@
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>`STI-203`</t>
+          <t>`FST-204`</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
-          <t>Matematika Diskrit Lanjut</t>
+          <t>Pengantar Kecerdasan Artifisial &amp; Data</t>
         </is>
       </c>
       <c r="D45" s="22" t="inlineStr">
@@ -16753,12 +16761,12 @@
       </c>
       <c r="F45" s="20" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G45" s="20" t="inlineStr">
         <is>
-          <t>`STI-103`</t>
+          <t>`FST-101`</t>
         </is>
       </c>
     </row>
@@ -16770,12 +16778,12 @@
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>`STI-204`</t>
+          <t>`FST-205`</t>
         </is>
       </c>
       <c r="C46" s="19" t="inlineStr">
         <is>
-          <t>Aljabar Linear Terapan &amp; Matriks</t>
+          <t>Basic English for IT</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -16790,12 +16798,12 @@
       </c>
       <c r="F46" s="19" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G46" s="19" t="inlineStr">
         <is>
-          <t>`STI-102`</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -16807,12 +16815,12 @@
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>`STI-205`</t>
+          <t>`FST-206`</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
         <is>
-          <t>Etika Profesi &amp; Hukum Siber</t>
+          <t>Etika Profesi &amp; Hukum Digital</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
@@ -16827,7 +16835,7 @@
       </c>
       <c r="F47" s="20" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G47" s="20" t="inlineStr">
@@ -16844,32 +16852,32 @@
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>`MKU-204`</t>
+          <t>`FST-207`</t>
         </is>
       </c>
       <c r="C48" s="19" t="inlineStr">
         <is>
-          <t>Kewirausahaan I</t>
+          <t>Sistem Basis Data</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F48" s="19" t="inlineStr">
         <is>
-          <t>MKWU</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G48" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`FST-102`</t>
         </is>
       </c>
     </row>
@@ -16881,17 +16889,17 @@
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>`FST-208`</t>
+          <t>`MKU-204`</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
-          <t>Statistika Dasar</t>
+          <t>Kewirausahaan I</t>
         </is>
       </c>
       <c r="D49" s="22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E49" s="20" t="inlineStr">
@@ -16901,12 +16909,12 @@
       </c>
       <c r="F49" s="20" t="inlineStr">
         <is>
-          <t>FSTI</t>
+          <t>MKWU</t>
         </is>
       </c>
       <c r="G49" s="20" t="inlineStr">
         <is>
-          <t>`STI-102`</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
+++ b/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
@@ -16959,7 +16959,7 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t>SEMESTER 3 (20 SKS) — Penguatan Core RPL, OS &amp; Jaringan Komputer</t>
+          <t>SEMESTER 3 (20 SKS) — Penguatan Core RPL, OS, Jarkom &amp; UI/UX</t>
         </is>
       </c>
       <c r="B52" s="16" t="n"/>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="G54" s="19" t="inlineStr">
         <is>
-          <t>`STI-104`, `FST-207`</t>
+          <t>`STI-101`, `FST-207`</t>
         </is>
       </c>
     </row>
@@ -17056,17 +17056,17 @@
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
-          <t>Kecerdasan Buatan (Artificial Intelligence)</t>
+          <t>Sistem Cerdas</t>
         </is>
       </c>
       <c r="D55" s="22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E55" s="20" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F55" s="20" t="inlineStr">
@@ -17076,7 +17076,7 @@
       </c>
       <c r="G55" s="20" t="inlineStr">
         <is>
-          <t>`STI-201`, `STI-202`</t>
+          <t>`STI-201`, `FST-204`</t>
         </is>
       </c>
     </row>
@@ -17093,7 +17093,7 @@
       </c>
       <c r="C56" s="19" t="inlineStr">
         <is>
-          <t>Desain Pengalaman Pengguna (UI/UX Design)</t>
+          <t>UI/UX Design &amp; Prototyping</t>
         </is>
       </c>
       <c r="D56" s="21" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="G56" s="19" t="inlineStr">
         <is>
-          <t>`STI-104`</t>
+          <t>`FST-101`</t>
         </is>
       </c>
     </row>
@@ -17150,7 +17150,7 @@
       </c>
       <c r="G57" s="20" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`FST-203`</t>
         </is>
       </c>
     </row>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="G58" s="19" t="inlineStr">
         <is>
-          <t>`STI-201`</t>
+          <t>`STI-103`</t>
         </is>
       </c>
     </row>
@@ -17204,12 +17204,12 @@
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>Pemrograman Web Front-End</t>
+          <t>Web Front End Development</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="G59" s="20" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`FST-102`</t>
         </is>
       </c>
     </row>
@@ -17261,7 +17261,7 @@
       </c>
       <c r="G60" s="19" t="inlineStr">
         <is>
-          <t>`STI-104`</t>
+          <t>`STI-103`</t>
         </is>
       </c>
     </row>

--- a/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
+++ b/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
@@ -3538,7 +3538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P96"/>
+  <dimension ref="A1:P99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -4427,7 +4427,7 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>4. MATRIKS SILANG CPL ↔ 19 BAHAN KAJIAN (BoK) IS2020 (APTIKOM v2.0)</t>
+          <t>4. MATRIKS SILANG CPL ↔ 21 BAHAN KAJIAN (BoK) IS2020 (APTIKOM v2.0)</t>
         </is>
       </c>
       <c r="B46" s="16" t="n"/>
@@ -5210,184 +5210,204 @@
       <c r="O66" s="19" t="inlineStr"/>
       <c r="P66" s="19" t="inlineStr"/>
     </row>
-    <row r="67"/>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="15" t="inlineStr">
-        <is>
-          <t>5. MATRIKS SILANG CPL ↔ 14 BAHAN KAJIAN UTAMA (BoK) IT2017 (APTIKOM)</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="n"/>
-      <c r="C68" s="16" t="n"/>
-      <c r="D68" s="16" t="n"/>
-      <c r="E68" s="16" t="n"/>
-      <c r="F68" s="16" t="n"/>
-      <c r="G68" s="16" t="n"/>
-      <c r="H68" s="16" t="n"/>
-      <c r="I68" s="16" t="n"/>
-      <c r="J68" s="16" t="n"/>
-      <c r="K68" s="16" t="n"/>
-      <c r="L68" s="16" t="n"/>
-      <c r="M68" s="16" t="n"/>
-      <c r="N68" s="16" t="n"/>
-      <c r="O68" s="16" t="n"/>
-      <c r="P68" s="17" t="n"/>
-    </row>
-    <row r="69" ht="26" customHeight="1">
-      <c r="A69" s="18" t="inlineStr">
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="20" t="inlineStr">
+        <is>
+          <t>**BK-IS20**</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>*Ethics, Use and Implications for Society*</t>
+        </is>
+      </c>
+      <c r="C67" s="22" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D67" s="22" t="inlineStr"/>
+      <c r="E67" s="20" t="inlineStr"/>
+      <c r="F67" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G67" s="20" t="inlineStr"/>
+      <c r="H67" s="20" t="inlineStr"/>
+      <c r="I67" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J67" s="20" t="inlineStr"/>
+      <c r="K67" s="20" t="inlineStr"/>
+      <c r="L67" s="20" t="inlineStr"/>
+      <c r="M67" s="20" t="inlineStr"/>
+      <c r="N67" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O67" s="20" t="inlineStr"/>
+      <c r="P67" s="20" t="inlineStr"/>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="19" t="inlineStr">
+        <is>
+          <t>**BK-IS21**</t>
+        </is>
+      </c>
+      <c r="B68" s="19" t="inlineStr">
+        <is>
+          <t>*Internship and Professional Practice*</t>
+        </is>
+      </c>
+      <c r="C68" s="21" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D68" s="21" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E68" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F68" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G68" s="19" t="inlineStr"/>
+      <c r="H68" s="19" t="inlineStr"/>
+      <c r="I68" s="19" t="inlineStr"/>
+      <c r="J68" s="19" t="inlineStr"/>
+      <c r="K68" s="19" t="inlineStr"/>
+      <c r="L68" s="19" t="inlineStr"/>
+      <c r="M68" s="19" t="inlineStr"/>
+      <c r="N68" s="19" t="inlineStr"/>
+      <c r="O68" s="19" t="inlineStr"/>
+      <c r="P68" s="19" t="inlineStr"/>
+    </row>
+    <row r="69"/>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>5. MATRIKS SILANG CPL ↔ 15 BAHAN KAJIAN UTAMA (BoK) IT2017 (APTIKOM)</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="n"/>
+      <c r="C70" s="16" t="n"/>
+      <c r="D70" s="16" t="n"/>
+      <c r="E70" s="16" t="n"/>
+      <c r="F70" s="16" t="n"/>
+      <c r="G70" s="16" t="n"/>
+      <c r="H70" s="16" t="n"/>
+      <c r="I70" s="16" t="n"/>
+      <c r="J70" s="16" t="n"/>
+      <c r="K70" s="16" t="n"/>
+      <c r="L70" s="16" t="n"/>
+      <c r="M70" s="16" t="n"/>
+      <c r="N70" s="16" t="n"/>
+      <c r="O70" s="16" t="n"/>
+      <c r="P70" s="17" t="n"/>
+    </row>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="18" t="inlineStr">
         <is>
           <t>Kode Bahan Kajian (BoK)</t>
         </is>
       </c>
-      <c r="B69" s="18" t="inlineStr">
+      <c r="B71" s="18" t="inlineStr">
         <is>
           <t>Nomenklatur Bahan Kajian Utama IT2017</t>
         </is>
       </c>
-      <c r="C69" s="18" t="inlineStr">
+      <c r="C71" s="18" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="D69" s="18" t="inlineStr">
+      <c r="D71" s="18" t="inlineStr">
         <is>
           <t>KU1</t>
         </is>
       </c>
-      <c r="E69" s="18" t="inlineStr">
+      <c r="E71" s="18" t="inlineStr">
         <is>
           <t>KU2</t>
         </is>
       </c>
-      <c r="F69" s="18" t="inlineStr">
+      <c r="F71" s="18" t="inlineStr">
         <is>
           <t>KU3</t>
         </is>
       </c>
-      <c r="G69" s="18" t="inlineStr">
+      <c r="G71" s="18" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H69" s="18" t="inlineStr">
+      <c r="H71" s="18" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I69" s="18" t="inlineStr">
+      <c r="I71" s="18" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J69" s="18" t="inlineStr">
+      <c r="J71" s="18" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="K69" s="18" t="inlineStr">
+      <c r="K71" s="18" t="inlineStr">
         <is>
           <t>KK1</t>
         </is>
       </c>
-      <c r="L69" s="18" t="inlineStr">
+      <c r="L71" s="18" t="inlineStr">
         <is>
           <t>KK2</t>
         </is>
       </c>
-      <c r="M69" s="18" t="inlineStr">
+      <c r="M71" s="18" t="inlineStr">
         <is>
           <t>KK3</t>
         </is>
       </c>
-      <c r="N69" s="18" t="inlineStr">
+      <c r="N71" s="18" t="inlineStr">
         <is>
           <t>KK4</t>
         </is>
       </c>
-      <c r="O69" s="18" t="inlineStr">
+      <c r="O71" s="18" t="inlineStr">
         <is>
           <t>KK5</t>
         </is>
       </c>
-      <c r="P69" s="18" t="inlineStr">
+      <c r="P71" s="18" t="inlineStr">
         <is>
           <t>KK6</t>
         </is>
       </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="19" t="inlineStr">
-        <is>
-          <t>**BK-IT01**</t>
-        </is>
-      </c>
-      <c r="B70" s="19" t="inlineStr">
-        <is>
-          <t>*Information Technology Fundamentals*</t>
-        </is>
-      </c>
-      <c r="C70" s="21" t="inlineStr"/>
-      <c r="D70" s="21" t="inlineStr"/>
-      <c r="E70" s="19" t="inlineStr"/>
-      <c r="F70" s="19" t="inlineStr"/>
-      <c r="G70" s="19" t="inlineStr"/>
-      <c r="H70" s="19" t="inlineStr"/>
-      <c r="I70" s="19" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J70" s="19" t="inlineStr"/>
-      <c r="K70" s="19" t="inlineStr"/>
-      <c r="L70" s="19" t="inlineStr"/>
-      <c r="M70" s="19" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="N70" s="19" t="inlineStr"/>
-      <c r="O70" s="19" t="inlineStr"/>
-      <c r="P70" s="19" t="inlineStr"/>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="20" t="inlineStr">
-        <is>
-          <t>**BK-IT02**</t>
-        </is>
-      </c>
-      <c r="B71" s="20" t="inlineStr">
-        <is>
-          <t>*Applied AI &amp; Intelligent Technologies*</t>
-        </is>
-      </c>
-      <c r="C71" s="22" t="inlineStr"/>
-      <c r="D71" s="22" t="inlineStr"/>
-      <c r="E71" s="20" t="inlineStr"/>
-      <c r="F71" s="20" t="inlineStr"/>
-      <c r="G71" s="20" t="inlineStr"/>
-      <c r="H71" s="20" t="inlineStr"/>
-      <c r="I71" s="20" t="inlineStr"/>
-      <c r="J71" s="20" t="inlineStr"/>
-      <c r="K71" s="20" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L71" s="20" t="inlineStr"/>
-      <c r="M71" s="20" t="inlineStr"/>
-      <c r="N71" s="20" t="inlineStr"/>
-      <c r="O71" s="20" t="inlineStr"/>
-      <c r="P71" s="20" t="inlineStr"/>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT03**</t>
+          <t>**BK-IT01**</t>
         </is>
       </c>
       <c r="B72" s="19" t="inlineStr">
         <is>
-          <t>*Networking &amp; Communications*</t>
+          <t>*Information Technology Fundamentals*</t>
         </is>
       </c>
       <c r="C72" s="21" t="inlineStr"/>
@@ -5416,12 +5436,12 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT04**</t>
+          <t>**BK-IT02**</t>
         </is>
       </c>
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>*Platform Technologies &amp; Web/Mobile*</t>
+          <t>*Applied AI &amp; Intelligent Technologies*</t>
         </is>
       </c>
       <c r="C73" s="22" t="inlineStr"/>
@@ -5431,31 +5451,27 @@
       <c r="G73" s="20" t="inlineStr"/>
       <c r="H73" s="20" t="inlineStr"/>
       <c r="I73" s="20" t="inlineStr"/>
-      <c r="J73" s="20" t="inlineStr">
+      <c r="J73" s="20" t="inlineStr"/>
+      <c r="K73" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="K73" s="20" t="inlineStr"/>
       <c r="L73" s="20" t="inlineStr"/>
       <c r="M73" s="20" t="inlineStr"/>
       <c r="N73" s="20" t="inlineStr"/>
-      <c r="O73" s="20" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="O73" s="20" t="inlineStr"/>
       <c r="P73" s="20" t="inlineStr"/>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT05**</t>
+          <t>**BK-IT03**</t>
         </is>
       </c>
       <c r="B74" s="19" t="inlineStr">
         <is>
-          <t>*Cloud Computing &amp; Virtualization*</t>
+          <t>*Networking &amp; Communications*</t>
         </is>
       </c>
       <c r="C74" s="21" t="inlineStr"/>
@@ -5484,12 +5500,12 @@
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT06**</t>
+          <t>**BK-IT04**</t>
         </is>
       </c>
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>*Cybersecurity Principles &amp; Defense*</t>
+          <t>*Platform Technologies &amp; Web/Mobile*</t>
         </is>
       </c>
       <c r="C75" s="22" t="inlineStr"/>
@@ -5498,36 +5514,32 @@
       <c r="F75" s="20" t="inlineStr"/>
       <c r="G75" s="20" t="inlineStr"/>
       <c r="H75" s="20" t="inlineStr"/>
-      <c r="I75" s="20" t="inlineStr">
+      <c r="I75" s="20" t="inlineStr"/>
+      <c r="J75" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="J75" s="20" t="inlineStr"/>
       <c r="K75" s="20" t="inlineStr"/>
       <c r="L75" s="20" t="inlineStr"/>
-      <c r="M75" s="20" t="inlineStr">
+      <c r="M75" s="20" t="inlineStr"/>
+      <c r="N75" s="20" t="inlineStr"/>
+      <c r="O75" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="N75" s="20" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O75" s="20" t="inlineStr"/>
       <c r="P75" s="20" t="inlineStr"/>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT07**</t>
+          <t>**BK-IT05**</t>
         </is>
       </c>
       <c r="B76" s="19" t="inlineStr">
         <is>
-          <t>*System Integration and Architecture*</t>
+          <t>*Cloud Computing &amp; Virtualization*</t>
         </is>
       </c>
       <c r="C76" s="21" t="inlineStr"/>
@@ -5550,22 +5562,18 @@
         </is>
       </c>
       <c r="N76" s="19" t="inlineStr"/>
-      <c r="O76" s="19" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="O76" s="19" t="inlineStr"/>
       <c r="P76" s="19" t="inlineStr"/>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT08**</t>
+          <t>**BK-IT06**</t>
         </is>
       </c>
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>*IT Service Management &amp; Governance*</t>
+          <t>*Cybersecurity Principles &amp; Defense*</t>
         </is>
       </c>
       <c r="C77" s="22" t="inlineStr"/>
@@ -5582,7 +5590,11 @@
       <c r="J77" s="20" t="inlineStr"/>
       <c r="K77" s="20" t="inlineStr"/>
       <c r="L77" s="20" t="inlineStr"/>
-      <c r="M77" s="20" t="inlineStr"/>
+      <c r="M77" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="N77" s="20" t="inlineStr">
         <is>
           <t>✅</t>
@@ -5594,12 +5606,12 @@
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT09**</t>
+          <t>**BK-IT07**</t>
         </is>
       </c>
       <c r="B78" s="19" t="inlineStr">
         <is>
-          <t>*Data Analytics &amp; Information Visualization*</t>
+          <t>*System Integration and Architecture*</t>
         </is>
       </c>
       <c r="C78" s="21" t="inlineStr"/>
@@ -5608,32 +5620,36 @@
       <c r="F78" s="19" t="inlineStr"/>
       <c r="G78" s="19" t="inlineStr"/>
       <c r="H78" s="19" t="inlineStr"/>
-      <c r="I78" s="19" t="inlineStr"/>
-      <c r="J78" s="19" t="inlineStr">
+      <c r="I78" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
+      <c r="J78" s="19" t="inlineStr"/>
       <c r="K78" s="19" t="inlineStr"/>
-      <c r="L78" s="19" t="inlineStr">
+      <c r="L78" s="19" t="inlineStr"/>
+      <c r="M78" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="M78" s="19" t="inlineStr"/>
       <c r="N78" s="19" t="inlineStr"/>
-      <c r="O78" s="19" t="inlineStr"/>
+      <c r="O78" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="P78" s="19" t="inlineStr"/>
     </row>
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT10**</t>
+          <t>**BK-IT08**</t>
         </is>
       </c>
       <c r="B79" s="20" t="inlineStr">
         <is>
-          <t>*User Experience &amp; Interaction Design*</t>
+          <t>*IT Service Management &amp; Governance*</t>
         </is>
       </c>
       <c r="C79" s="22" t="inlineStr"/>
@@ -5642,32 +5658,32 @@
       <c r="F79" s="20" t="inlineStr"/>
       <c r="G79" s="20" t="inlineStr"/>
       <c r="H79" s="20" t="inlineStr"/>
-      <c r="I79" s="20" t="inlineStr"/>
-      <c r="J79" s="20" t="inlineStr">
+      <c r="I79" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
+      <c r="J79" s="20" t="inlineStr"/>
       <c r="K79" s="20" t="inlineStr"/>
       <c r="L79" s="20" t="inlineStr"/>
       <c r="M79" s="20" t="inlineStr"/>
-      <c r="N79" s="20" t="inlineStr"/>
-      <c r="O79" s="20" t="inlineStr">
+      <c r="N79" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
+      <c r="O79" s="20" t="inlineStr"/>
       <c r="P79" s="20" t="inlineStr"/>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT11**</t>
+          <t>**BK-IT09**</t>
         </is>
       </c>
       <c r="B80" s="19" t="inlineStr">
         <is>
-          <t>*Software Development Practices*</t>
+          <t>*Data Analytics &amp; Information Visualization*</t>
         </is>
       </c>
       <c r="C80" s="21" t="inlineStr"/>
@@ -5683,25 +5699,25 @@
         </is>
       </c>
       <c r="K80" s="19" t="inlineStr"/>
-      <c r="L80" s="19" t="inlineStr"/>
+      <c r="L80" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="M80" s="19" t="inlineStr"/>
       <c r="N80" s="19" t="inlineStr"/>
-      <c r="O80" s="19" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="O80" s="19" t="inlineStr"/>
       <c r="P80" s="19" t="inlineStr"/>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT12**</t>
+          <t>**BK-IT10**</t>
         </is>
       </c>
       <c r="B81" s="20" t="inlineStr">
         <is>
-          <t>*IT Risk Management and Compliance*</t>
+          <t>*User Experience &amp; Interaction Design*</t>
         </is>
       </c>
       <c r="C81" s="22" t="inlineStr"/>
@@ -5711,27 +5727,31 @@
       <c r="G81" s="20" t="inlineStr"/>
       <c r="H81" s="20" t="inlineStr"/>
       <c r="I81" s="20" t="inlineStr"/>
-      <c r="J81" s="20" t="inlineStr"/>
+      <c r="J81" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="K81" s="20" t="inlineStr"/>
       <c r="L81" s="20" t="inlineStr"/>
       <c r="M81" s="20" t="inlineStr"/>
-      <c r="N81" s="20" t="inlineStr">
+      <c r="N81" s="20" t="inlineStr"/>
+      <c r="O81" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="O81" s="20" t="inlineStr"/>
       <c r="P81" s="20" t="inlineStr"/>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT13**</t>
+          <t>**BK-IT11**</t>
         </is>
       </c>
       <c r="B82" s="19" t="inlineStr">
         <is>
-          <t>*Technology Entrepreneurship*</t>
+          <t>*Software Development Practices*</t>
         </is>
       </c>
       <c r="C82" s="21" t="inlineStr"/>
@@ -5741,27 +5761,31 @@
       <c r="G82" s="19" t="inlineStr"/>
       <c r="H82" s="19" t="inlineStr"/>
       <c r="I82" s="19" t="inlineStr"/>
-      <c r="J82" s="19" t="inlineStr"/>
+      <c r="J82" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="K82" s="19" t="inlineStr"/>
       <c r="L82" s="19" t="inlineStr"/>
       <c r="M82" s="19" t="inlineStr"/>
       <c r="N82" s="19" t="inlineStr"/>
-      <c r="O82" s="19" t="inlineStr"/>
-      <c r="P82" s="19" t="inlineStr">
+      <c r="O82" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
+      <c r="P82" s="19" t="inlineStr"/>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT14**</t>
+          <t>**BK-IT12**</t>
         </is>
       </c>
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>*IoT and Embedded Smart Systems*</t>
+          <t>*IT Risk Management and Compliance*</t>
         </is>
       </c>
       <c r="C83" s="22" t="inlineStr"/>
@@ -5772,490 +5796,592 @@
       <c r="H83" s="20" t="inlineStr"/>
       <c r="I83" s="20" t="inlineStr"/>
       <c r="J83" s="20" t="inlineStr"/>
-      <c r="K83" s="20" t="inlineStr">
+      <c r="K83" s="20" t="inlineStr"/>
+      <c r="L83" s="20" t="inlineStr"/>
+      <c r="M83" s="20" t="inlineStr"/>
+      <c r="N83" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="L83" s="20" t="inlineStr"/>
-      <c r="M83" s="20" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="N83" s="20" t="inlineStr"/>
       <c r="O83" s="20" t="inlineStr"/>
       <c r="P83" s="20" t="inlineStr"/>
     </row>
-    <row r="84"/>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="15" t="inlineStr">
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="19" t="inlineStr">
+        <is>
+          <t>**BK-IT13**</t>
+        </is>
+      </c>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>*Technology Entrepreneurship*</t>
+        </is>
+      </c>
+      <c r="C84" s="21" t="inlineStr"/>
+      <c r="D84" s="21" t="inlineStr"/>
+      <c r="E84" s="19" t="inlineStr"/>
+      <c r="F84" s="19" t="inlineStr"/>
+      <c r="G84" s="19" t="inlineStr"/>
+      <c r="H84" s="19" t="inlineStr"/>
+      <c r="I84" s="19" t="inlineStr"/>
+      <c r="J84" s="19" t="inlineStr"/>
+      <c r="K84" s="19" t="inlineStr"/>
+      <c r="L84" s="19" t="inlineStr"/>
+      <c r="M84" s="19" t="inlineStr"/>
+      <c r="N84" s="19" t="inlineStr"/>
+      <c r="O84" s="19" t="inlineStr"/>
+      <c r="P84" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="20" t="inlineStr">
+        <is>
+          <t>**BK-IT14**</t>
+        </is>
+      </c>
+      <c r="B85" s="20" t="inlineStr">
+        <is>
+          <t>*IoT and Embedded Smart Systems*</t>
+        </is>
+      </c>
+      <c r="C85" s="22" t="inlineStr"/>
+      <c r="D85" s="22" t="inlineStr"/>
+      <c r="E85" s="20" t="inlineStr"/>
+      <c r="F85" s="20" t="inlineStr"/>
+      <c r="G85" s="20" t="inlineStr"/>
+      <c r="H85" s="20" t="inlineStr"/>
+      <c r="I85" s="20" t="inlineStr"/>
+      <c r="J85" s="20" t="inlineStr"/>
+      <c r="K85" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L85" s="20" t="inlineStr"/>
+      <c r="M85" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N85" s="20" t="inlineStr"/>
+      <c r="O85" s="20" t="inlineStr"/>
+      <c r="P85" s="20" t="inlineStr"/>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="19" t="inlineStr">
+        <is>
+          <t>**BK-IT15**</t>
+        </is>
+      </c>
+      <c r="B86" s="19" t="inlineStr">
+        <is>
+          <t>*Global Professional Practice*</t>
+        </is>
+      </c>
+      <c r="C86" s="21" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D86" s="21" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E86" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F86" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G86" s="19" t="inlineStr"/>
+      <c r="H86" s="19" t="inlineStr"/>
+      <c r="I86" s="19" t="inlineStr"/>
+      <c r="J86" s="19" t="inlineStr"/>
+      <c r="K86" s="19" t="inlineStr"/>
+      <c r="L86" s="19" t="inlineStr"/>
+      <c r="M86" s="19" t="inlineStr"/>
+      <c r="N86" s="19" t="inlineStr"/>
+      <c r="O86" s="19" t="inlineStr"/>
+      <c r="P86" s="19" t="inlineStr"/>
+    </row>
+    <row r="87"/>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="15" t="inlineStr">
         <is>
           <t>6. MATRIKS PEMETAAN CPL ↔ 4 PROFIL LULUSAN (PL)</t>
         </is>
       </c>
-      <c r="B85" s="16" t="n"/>
-      <c r="C85" s="16" t="n"/>
-      <c r="D85" s="16" t="n"/>
-      <c r="E85" s="16" t="n"/>
-      <c r="F85" s="16" t="n"/>
-      <c r="G85" s="16" t="n"/>
-      <c r="H85" s="16" t="n"/>
-      <c r="I85" s="16" t="n"/>
-      <c r="J85" s="16" t="n"/>
-      <c r="K85" s="16" t="n"/>
-      <c r="L85" s="16" t="n"/>
-      <c r="M85" s="16" t="n"/>
-      <c r="N85" s="16" t="n"/>
-      <c r="O85" s="16" t="n"/>
-      <c r="P85" s="17" t="n"/>
-    </row>
-    <row r="86" ht="26" customHeight="1">
-      <c r="A86" s="18" t="inlineStr">
+      <c r="B88" s="16" t="n"/>
+      <c r="C88" s="16" t="n"/>
+      <c r="D88" s="16" t="n"/>
+      <c r="E88" s="16" t="n"/>
+      <c r="F88" s="16" t="n"/>
+      <c r="G88" s="16" t="n"/>
+      <c r="H88" s="16" t="n"/>
+      <c r="I88" s="16" t="n"/>
+      <c r="J88" s="16" t="n"/>
+      <c r="K88" s="16" t="n"/>
+      <c r="L88" s="16" t="n"/>
+      <c r="M88" s="16" t="n"/>
+      <c r="N88" s="16" t="n"/>
+      <c r="O88" s="16" t="n"/>
+      <c r="P88" s="17" t="n"/>
+    </row>
+    <row r="89" ht="26" customHeight="1">
+      <c r="A89" s="18" t="inlineStr">
         <is>
           <t>Profil Lulusan SISTEKIN 2026</t>
         </is>
       </c>
-      <c r="B86" s="18" t="inlineStr">
+      <c r="B89" s="18" t="inlineStr">
         <is>
           <t>Peminatan Terkait</t>
         </is>
       </c>
-      <c r="C86" s="18" t="inlineStr">
+      <c r="C89" s="18" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="D86" s="18" t="inlineStr">
+      <c r="D89" s="18" t="inlineStr">
         <is>
           <t>KU1</t>
         </is>
       </c>
-      <c r="E86" s="18" t="inlineStr">
+      <c r="E89" s="18" t="inlineStr">
         <is>
           <t>KU2</t>
         </is>
       </c>
-      <c r="F86" s="18" t="inlineStr">
+      <c r="F89" s="18" t="inlineStr">
         <is>
           <t>KU3</t>
         </is>
       </c>
-      <c r="G86" s="18" t="inlineStr">
+      <c r="G89" s="18" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H86" s="18" t="inlineStr">
+      <c r="H89" s="18" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I86" s="18" t="inlineStr">
+      <c r="I89" s="18" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J86" s="18" t="inlineStr">
+      <c r="J89" s="18" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="K86" s="18" t="inlineStr">
+      <c r="K89" s="18" t="inlineStr">
         <is>
           <t>KK1</t>
         </is>
       </c>
-      <c r="L86" s="18" t="inlineStr">
+      <c r="L89" s="18" t="inlineStr">
         <is>
           <t>KK2</t>
         </is>
       </c>
-      <c r="M86" s="18" t="inlineStr">
+      <c r="M89" s="18" t="inlineStr">
         <is>
           <t>KK3</t>
         </is>
       </c>
-      <c r="N86" s="18" t="inlineStr">
+      <c r="N89" s="18" t="inlineStr">
         <is>
           <t>KK4</t>
         </is>
       </c>
-      <c r="O86" s="18" t="inlineStr">
+      <c r="O89" s="18" t="inlineStr">
         <is>
           <t>KK5</t>
         </is>
       </c>
-      <c r="P86" s="18" t="inlineStr">
+      <c r="P89" s="18" t="inlineStr">
         <is>
           <t>KK6</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="19" t="inlineStr">
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="19" t="inlineStr">
         <is>
           <t>**PL-1: Intelligent IS Developer &amp; AI Engineer**</t>
         </is>
       </c>
-      <c r="B87" s="21" t="inlineStr">
+      <c r="B90" s="21" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C87" s="21" t="inlineStr">
+      <c r="C90" s="21" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D87" s="21" t="inlineStr">
+      <c r="D90" s="21" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="E87" s="19" t="inlineStr">
+      <c r="E90" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="F87" s="19" t="inlineStr">
+      <c r="F90" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="G87" s="19" t="inlineStr">
+      <c r="G90" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="H87" s="19" t="inlineStr">
+      <c r="H90" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="I87" s="19" t="inlineStr"/>
-      <c r="J87" s="19" t="inlineStr">
+      <c r="I90" s="19" t="inlineStr"/>
+      <c r="J90" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="K87" s="19" t="inlineStr">
+      <c r="K90" s="19" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="L87" s="19" t="inlineStr">
+      <c r="L90" s="19" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="M87" s="19" t="inlineStr"/>
-      <c r="N87" s="19" t="inlineStr"/>
-      <c r="O87" s="19" t="inlineStr">
+      <c r="M90" s="19" t="inlineStr"/>
+      <c r="N90" s="19" t="inlineStr"/>
+      <c r="O90" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="P87" s="19" t="inlineStr"/>
-    </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="20" t="inlineStr">
+      <c r="P90" s="19" t="inlineStr"/>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="20" t="inlineStr">
         <is>
           <t>**PL-2: Cloud &amp; Cybersecurity Specialist**</t>
         </is>
       </c>
-      <c r="B88" s="22" t="inlineStr">
+      <c r="B91" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C88" s="22" t="inlineStr">
+      <c r="C91" s="22" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D88" s="22" t="inlineStr">
+      <c r="D91" s="22" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="E88" s="20" t="inlineStr">
+      <c r="E91" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="F88" s="20" t="inlineStr">
+      <c r="F91" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="G88" s="20" t="inlineStr">
+      <c r="G91" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="H88" s="20" t="inlineStr"/>
-      <c r="I88" s="20" t="inlineStr">
+      <c r="H91" s="20" t="inlineStr"/>
+      <c r="I91" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="J88" s="20" t="inlineStr"/>
-      <c r="K88" s="20" t="inlineStr"/>
-      <c r="L88" s="20" t="inlineStr"/>
-      <c r="M88" s="20" t="inlineStr">
+      <c r="J91" s="20" t="inlineStr"/>
+      <c r="K91" s="20" t="inlineStr"/>
+      <c r="L91" s="20" t="inlineStr"/>
+      <c r="M91" s="20" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="N88" s="20" t="inlineStr">
+      <c r="N91" s="20" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="O88" s="20" t="inlineStr"/>
-      <c r="P88" s="20" t="inlineStr"/>
-    </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="19" t="inlineStr">
+      <c r="O91" s="20" t="inlineStr"/>
+      <c r="P91" s="20" t="inlineStr"/>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="19" t="inlineStr">
         <is>
           <t>**PL-3: UI/UX &amp; Digital Platform Engineer**</t>
         </is>
       </c>
-      <c r="B89" s="21" t="inlineStr">
+      <c r="B92" s="21" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C89" s="21" t="inlineStr">
+      <c r="C92" s="21" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D89" s="21" t="inlineStr">
+      <c r="D92" s="21" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="E89" s="19" t="inlineStr">
+      <c r="E92" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="F89" s="19" t="inlineStr">
+      <c r="F92" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="G89" s="19" t="inlineStr"/>
-      <c r="H89" s="19" t="inlineStr">
+      <c r="G92" s="19" t="inlineStr"/>
+      <c r="H92" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="I89" s="19" t="inlineStr"/>
-      <c r="J89" s="19" t="inlineStr">
+      <c r="I92" s="19" t="inlineStr"/>
+      <c r="J92" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="K89" s="19" t="inlineStr"/>
-      <c r="L89" s="19" t="inlineStr"/>
-      <c r="M89" s="19" t="inlineStr"/>
-      <c r="N89" s="19" t="inlineStr"/>
-      <c r="O89" s="19" t="inlineStr">
+      <c r="K92" s="19" t="inlineStr"/>
+      <c r="L92" s="19" t="inlineStr"/>
+      <c r="M92" s="19" t="inlineStr"/>
+      <c r="N92" s="19" t="inlineStr"/>
+      <c r="O92" s="19" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="P89" s="19" t="inlineStr">
+      <c r="P92" s="19" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="20" t="inlineStr">
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="20" t="inlineStr">
         <is>
           <t>**PL-4: IT Project Manager &amp; Technopreneur**</t>
         </is>
       </c>
-      <c r="B90" s="20" t="inlineStr">
+      <c r="B93" s="20" t="inlineStr">
         <is>
           <t>P3 / P1 / P2</t>
         </is>
       </c>
-      <c r="C90" s="22" t="inlineStr">
+      <c r="C93" s="22" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D90" s="22" t="inlineStr">
+      <c r="D93" s="22" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="E90" s="20" t="inlineStr">
+      <c r="E93" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="F90" s="20" t="inlineStr">
+      <c r="F93" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="G90" s="20" t="inlineStr"/>
-      <c r="H90" s="20" t="inlineStr">
+      <c r="G93" s="20" t="inlineStr"/>
+      <c r="H93" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="I90" s="20" t="inlineStr">
+      <c r="I93" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="J90" s="20" t="inlineStr">
+      <c r="J93" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="K90" s="20" t="inlineStr">
+      <c r="K93" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="L90" s="20" t="inlineStr"/>
-      <c r="M90" s="20" t="inlineStr"/>
-      <c r="N90" s="20" t="inlineStr"/>
-      <c r="O90" s="20" t="inlineStr">
+      <c r="L93" s="20" t="inlineStr"/>
+      <c r="M93" s="20" t="inlineStr"/>
+      <c r="N93" s="20" t="inlineStr"/>
+      <c r="O93" s="20" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="P90" s="20" t="inlineStr">
+      <c r="P93" s="20" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
-    <row r="91"/>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="15" t="inlineStr">
+    <row r="94"/>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="15" t="inlineStr">
         <is>
           <t>7. MATRIKS PEMETAAN CPL ↔ 3 PROGRAM EDUCATIONAL OBJECTIVES (PEO)</t>
         </is>
       </c>
-      <c r="B92" s="16" t="n"/>
-      <c r="C92" s="16" t="n"/>
-      <c r="D92" s="16" t="n"/>
-      <c r="E92" s="16" t="n"/>
-      <c r="F92" s="17" t="n"/>
-    </row>
-    <row r="93" ht="26" customHeight="1">
-      <c r="A93" s="18" t="inlineStr">
+      <c r="B95" s="16" t="n"/>
+      <c r="C95" s="16" t="n"/>
+      <c r="D95" s="16" t="n"/>
+      <c r="E95" s="16" t="n"/>
+      <c r="F95" s="17" t="n"/>
+    </row>
+    <row r="96" ht="26" customHeight="1">
+      <c r="A96" s="18" t="inlineStr">
         <is>
           <t>Kode PEO</t>
         </is>
       </c>
-      <c r="B93" s="18" t="inlineStr">
+      <c r="B96" s="18" t="inlineStr">
         <is>
           <t>Nomenklatur Program Educational Objectives (3–5 Tahun)</t>
         </is>
       </c>
-      <c r="C93" s="18" t="inlineStr">
+      <c r="C96" s="18" t="inlineStr">
         <is>
           <t>CPL Sikap &amp; Umum</t>
         </is>
       </c>
-      <c r="D93" s="18" t="inlineStr">
+      <c r="D96" s="18" t="inlineStr">
         <is>
           <t>CPL Pengetahuan</t>
         </is>
       </c>
-      <c r="E93" s="18" t="inlineStr">
+      <c r="E96" s="18" t="inlineStr">
         <is>
           <t>CPL Keterampilan Khusus</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="19" t="inlineStr">
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="19" t="inlineStr">
         <is>
           <t>**PEO-1**</t>
         </is>
       </c>
-      <c r="B94" s="19" t="inlineStr">
+      <c r="B97" s="19" t="inlineStr">
         <is>
           <t>**PEO-1 — Professional Practice and Systems Integration**&lt;br/&gt;Lulusan menunjukkan keunggulan profesional dalam merancang, mengintegrasikan, dan mengelola sistem informasi cerdas, infrastruktur cloud, atau platform digital enterprise.</t>
         </is>
       </c>
-      <c r="C94" s="19" t="inlineStr">
+      <c r="C97" s="19" t="inlineStr">
         <is>
           <t>`S1`, `KU1`, `KU2`, `KU3`</t>
         </is>
       </c>
-      <c r="D94" s="19" t="inlineStr">
+      <c r="D97" s="19" t="inlineStr">
         <is>
           <t>`P1`, `P2`, `P3`, `P4`</t>
         </is>
       </c>
-      <c r="E94" s="19" t="inlineStr">
+      <c r="E97" s="19" t="inlineStr">
         <is>
           <t>`KK1`, `KK2`, `KK3`, `KK4`, `KK5`</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="20" t="inlineStr">
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="20" t="inlineStr">
         <is>
           <t>**PEO-2**</t>
         </is>
       </c>
-      <c r="B95" s="20" t="inlineStr">
+      <c r="B98" s="20" t="inlineStr">
         <is>
           <t>**PEO-2 — Digital Innovation and Technopreneurship**&lt;br/&gt;Lulusan mampu memimpin inovasi digital, menginisiasi usaha rintisan teknologi (*technopreneurship*), atau mengelola proyek transformasi digital yang memberikan dampak ekonomi dan sosial.</t>
         </is>
       </c>
-      <c r="C95" s="20" t="inlineStr">
+      <c r="C98" s="20" t="inlineStr">
         <is>
           <t>`S1`, `KU1`, `KU2`, `KU3`</t>
         </is>
       </c>
-      <c r="D95" s="20" t="inlineStr">
+      <c r="D98" s="20" t="inlineStr">
         <is>
           <t>`P2`, `P3`, `P4`</t>
         </is>
       </c>
-      <c r="E95" s="20" t="inlineStr">
+      <c r="E98" s="20" t="inlineStr">
         <is>
           <t>`KK6`, `KK5`, `KK1`</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="19" t="inlineStr">
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="19" t="inlineStr">
         <is>
           <t>**PEO-3**</t>
         </is>
       </c>
-      <c r="B96" s="19" t="inlineStr">
+      <c r="B99" s="19" t="inlineStr">
         <is>
           <t>**PEO-3 — Advanced Study, Research, and Lifelong Learning**&lt;br/&gt;Lulusan mampu melanjutkan studi ke jenjang pascasarjana, melakukan riset terapan di bidang sains komputasi/AI, serta adaptif mengembangkan diri sepanjang hayat.</t>
         </is>
       </c>
-      <c r="C96" s="19" t="inlineStr">
+      <c r="C99" s="19" t="inlineStr">
         <is>
           <t>`S1`, `KU1`, `KU2`, `KU3`</t>
         </is>
       </c>
-      <c r="D96" s="19" t="inlineStr">
+      <c r="D99" s="19" t="inlineStr">
         <is>
           <t>`P1`, `P2`, `P3`, `P4`</t>
         </is>
       </c>
-      <c r="E96" s="19" t="inlineStr">
+      <c r="E99" s="19" t="inlineStr">
         <is>
           <t>`KK1`, `KK2`, `KK3`, `KK4`, `KK5`, `KK6`</t>
         </is>
@@ -6264,16 +6390,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A85:P85"/>
-    <mergeCell ref="A92:F92"/>
     <mergeCell ref="A46:P46"/>
     <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A88:P88"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A70:P70"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A68:P68"/>
+    <mergeCell ref="A95:F95"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6286,7 +6412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U220"/>
+  <dimension ref="A1:U223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -11873,7 +11999,7 @@
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="15" t="inlineStr">
         <is>
-          <t>TABEL 6.1: PEMETAAN 19 BAHAN KAJIAN IS2020 (APTIKOM v2.0) ↔ MATA KULIAH</t>
+          <t>TABEL 6.1: PEMETAAN 21 BAHAN KAJIAN IS2020 (APTIKOM v2.0) ↔ MATA KULIAH</t>
         </is>
       </c>
       <c r="B126" s="16" t="n"/>
@@ -12522,139 +12648,139 @@
         </is>
       </c>
     </row>
-    <row r="147"/>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="15" t="inlineStr">
-        <is>
-          <t>TABEL 6.2: PEMETAAN 14 BAHAN KAJIAN UTAMA IT2017 (APTIKOM) ↔ MATA KULIAH</t>
-        </is>
-      </c>
-      <c r="B148" s="16" t="n"/>
-      <c r="C148" s="16" t="n"/>
-      <c r="D148" s="16" t="n"/>
-      <c r="E148" s="16" t="n"/>
-      <c r="F148" s="17" t="n"/>
-    </row>
-    <row r="149" ht="26" customHeight="1">
-      <c r="A149" s="18" t="inlineStr">
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" s="20" t="inlineStr">
+        <is>
+          <t>**BK-IS20**</t>
+        </is>
+      </c>
+      <c r="B147" s="20" t="inlineStr">
+        <is>
+          <t>*Ethics, Use and Implications for Society*</t>
+        </is>
+      </c>
+      <c r="C147" s="20" t="inlineStr">
+        <is>
+          <t>`FST-206`</t>
+        </is>
+      </c>
+      <c r="D147" s="20" t="inlineStr">
+        <is>
+          <t>`STI-405`, `STI-602`, `STB-04`</t>
+        </is>
+      </c>
+      <c r="E147" s="20" t="inlineStr">
+        <is>
+          <t>4 MK</t>
+        </is>
+      </c>
+      <c r="F147" s="20" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="19" t="inlineStr">
+        <is>
+          <t>**BK-IS21**</t>
+        </is>
+      </c>
+      <c r="B148" s="19" t="inlineStr">
+        <is>
+          <t>*Internship and Professional Practice*</t>
+        </is>
+      </c>
+      <c r="C148" s="19" t="inlineStr">
+        <is>
+          <t>`FST-612`</t>
+        </is>
+      </c>
+      <c r="D148" s="19" t="inlineStr">
+        <is>
+          <t>`MKU-507`, `FST-610`</t>
+        </is>
+      </c>
+      <c r="E148" s="19" t="inlineStr">
+        <is>
+          <t>3 MK</t>
+        </is>
+      </c>
+      <c r="F148" s="19" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="149"/>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="15" t="inlineStr">
+        <is>
+          <t>TABEL 6.2: PEMETAAN 15 BAHAN KAJIAN UTAMA IT2017 (APTIKOM) ↔ MATA KULIAH</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="n"/>
+      <c r="C150" s="16" t="n"/>
+      <c r="D150" s="16" t="n"/>
+      <c r="E150" s="16" t="n"/>
+      <c r="F150" s="17" t="n"/>
+    </row>
+    <row r="151" ht="26" customHeight="1">
+      <c r="A151" s="18" t="inlineStr">
         <is>
           <t>Kode BoK IT</t>
         </is>
       </c>
-      <c r="B149" s="18" t="inlineStr">
+      <c r="B151" s="18" t="inlineStr">
         <is>
           <t>Nomenklatur Bahan Kajian Utama IT2017</t>
         </is>
       </c>
-      <c r="C149" s="18" t="inlineStr">
+      <c r="C151" s="18" t="inlineStr">
         <is>
           <t>Mata Kuliah Pembina Primer (●)</t>
         </is>
       </c>
-      <c r="D149" s="18" t="inlineStr">
+      <c r="D151" s="18" t="inlineStr">
         <is>
           <t>Mata Kuliah Pembina Sekunder (○)</t>
         </is>
       </c>
-      <c r="E149" s="18" t="inlineStr">
+      <c r="E151" s="18" t="inlineStr">
         <is>
           <t>Total MK</t>
         </is>
       </c>
-      <c r="F149" s="18" t="inlineStr">
+      <c r="F151" s="18" t="inlineStr">
         <is>
           <t>Status Cakupan</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="16" customHeight="1">
-      <c r="A150" s="19" t="inlineStr">
-        <is>
-          <t>**BK-IT01**</t>
-        </is>
-      </c>
-      <c r="B150" s="19" t="inlineStr">
-        <is>
-          <t>*Information Technology Fundamentals*</t>
-        </is>
-      </c>
-      <c r="C150" s="19" t="inlineStr">
-        <is>
-          <t>`FST-101`, `STI-101`</t>
-        </is>
-      </c>
-      <c r="D150" s="19" t="inlineStr">
-        <is>
-          <t>`FST-204`</t>
-        </is>
-      </c>
-      <c r="E150" s="19" t="inlineStr">
-        <is>
-          <t>3 MK</t>
-        </is>
-      </c>
-      <c r="F150" s="19" t="inlineStr">
-        <is>
-          <t>✅ Sangat Kuat</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="16" customHeight="1">
-      <c r="A151" s="20" t="inlineStr">
-        <is>
-          <t>**BK-IT02**</t>
-        </is>
-      </c>
-      <c r="B151" s="20" t="inlineStr">
-        <is>
-          <t>*Applied AI &amp; Intelligent Technologies*</t>
-        </is>
-      </c>
-      <c r="C151" s="20" t="inlineStr">
-        <is>
-          <t>`STI-302`, `STI-401`, `STI-403`, `STI-501`, `STI-601`</t>
-        </is>
-      </c>
-      <c r="D151" s="20" t="inlineStr">
-        <is>
-          <t>`STA-03..06`</t>
-        </is>
-      </c>
-      <c r="E151" s="20" t="inlineStr">
-        <is>
-          <t>9 MK</t>
-        </is>
-      </c>
-      <c r="F151" s="20" t="inlineStr">
-        <is>
-          <t>✅ Sangat Kuat</t>
         </is>
       </c>
     </row>
     <row r="152" ht="16" customHeight="1">
       <c r="A152" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT03**</t>
+          <t>**BK-IT01**</t>
         </is>
       </c>
       <c r="B152" s="19" t="inlineStr">
         <is>
-          <t>*Networking &amp; Communications*</t>
+          <t>*Information Technology Fundamentals*</t>
         </is>
       </c>
       <c r="C152" s="19" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`FST-101`, `STI-101`</t>
         </is>
       </c>
       <c r="D152" s="19" t="inlineStr">
         <is>
-          <t>`STI-404`, `STI-504`, `STB-01`</t>
+          <t>`FST-204`</t>
         </is>
       </c>
       <c r="E152" s="19" t="inlineStr">
         <is>
-          <t>4 MK</t>
+          <t>3 MK</t>
         </is>
       </c>
       <c r="F152" s="19" t="inlineStr">
@@ -12666,27 +12792,27 @@
     <row r="153" ht="16" customHeight="1">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT04**</t>
+          <t>**BK-IT02**</t>
         </is>
       </c>
       <c r="B153" s="20" t="inlineStr">
         <is>
-          <t>*Platform Technologies &amp; Web/Mobile*</t>
+          <t>*Applied AI &amp; Intelligent Technologies*</t>
         </is>
       </c>
       <c r="C153" s="20" t="inlineStr">
         <is>
-          <t>`STI-306`, `STI-407`, `STI-505`, `STI-604`</t>
+          <t>`STI-302`, `STI-401`, `STI-403`, `STI-501`, `STI-601`</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>`STC-03..05`</t>
+          <t>`STA-03..06`</t>
         </is>
       </c>
       <c r="E153" s="20" t="inlineStr">
         <is>
-          <t>7 MK</t>
+          <t>9 MK</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
@@ -12698,22 +12824,22 @@
     <row r="154" ht="16" customHeight="1">
       <c r="A154" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT05**</t>
+          <t>**BK-IT03**</t>
         </is>
       </c>
       <c r="B154" s="19" t="inlineStr">
         <is>
-          <t>*Cloud Computing &amp; Virtualization*</t>
+          <t>*Networking &amp; Communications*</t>
         </is>
       </c>
       <c r="C154" s="19" t="inlineStr">
         <is>
-          <t>`STI-404`, `STB-02`</t>
+          <t>`STI-307`</t>
         </is>
       </c>
       <c r="D154" s="19" t="inlineStr">
         <is>
-          <t>`STI-305`, `STC-05`</t>
+          <t>`STI-404`, `STI-504`, `STB-01`</t>
         </is>
       </c>
       <c r="E154" s="19" t="inlineStr">
@@ -12730,27 +12856,27 @@
     <row r="155" ht="16" customHeight="1">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT06**</t>
+          <t>**BK-IT04**</t>
         </is>
       </c>
       <c r="B155" s="20" t="inlineStr">
         <is>
-          <t>*Cybersecurity Principles &amp; Defense*</t>
+          <t>*Platform Technologies &amp; Web/Mobile*</t>
         </is>
       </c>
       <c r="C155" s="20" t="inlineStr">
         <is>
-          <t>`STI-405`, `STI-603`, `STB-01`</t>
-        </is>
-      </c>
-      <c r="D155" s="22" t="inlineStr">
-        <is>
-          <t>`STB-03`</t>
+          <t>`STI-306`, `STI-407`, `STI-505`, `STI-604`</t>
+        </is>
+      </c>
+      <c r="D155" s="20" t="inlineStr">
+        <is>
+          <t>`STC-03..05`</t>
         </is>
       </c>
       <c r="E155" s="20" t="inlineStr">
         <is>
-          <t>4 MK</t>
+          <t>7 MK</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
@@ -12762,27 +12888,27 @@
     <row r="156" ht="16" customHeight="1">
       <c r="A156" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT07**</t>
+          <t>**BK-IT05**</t>
         </is>
       </c>
       <c r="B156" s="19" t="inlineStr">
         <is>
-          <t>*System Integration and Architecture*</t>
+          <t>*Cloud Computing &amp; Virtualization*</t>
         </is>
       </c>
       <c r="C156" s="19" t="inlineStr">
         <is>
-          <t>`STI-601`, `STI-604`, `FST-610`</t>
+          <t>`STI-404`, `STB-02`</t>
         </is>
       </c>
       <c r="D156" s="19" t="inlineStr">
         <is>
-          <t>`STB-06`, `STC-02`</t>
+          <t>`STI-305`, `STC-05`</t>
         </is>
       </c>
       <c r="E156" s="19" t="inlineStr">
         <is>
-          <t>5 MK</t>
+          <t>4 MK</t>
         </is>
       </c>
       <c r="F156" s="19" t="inlineStr">
@@ -12794,59 +12920,59 @@
     <row r="157" ht="16" customHeight="1">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT08**</t>
+          <t>**BK-IT06**</t>
         </is>
       </c>
       <c r="B157" s="20" t="inlineStr">
         <is>
-          <t>*IT Service Management &amp; Governance*</t>
+          <t>*Cybersecurity Principles &amp; Defense*</t>
         </is>
       </c>
       <c r="C157" s="20" t="inlineStr">
         <is>
-          <t>`STB-04`, `STB-05`</t>
-        </is>
-      </c>
-      <c r="D157" s="20" t="inlineStr">
-        <is>
-          <t>`STI-506`</t>
+          <t>`STI-405`, `STI-603`, `STB-01`</t>
+        </is>
+      </c>
+      <c r="D157" s="22" t="inlineStr">
+        <is>
+          <t>`STB-03`</t>
         </is>
       </c>
       <c r="E157" s="20" t="inlineStr">
         <is>
-          <t>3 MK</t>
+          <t>4 MK</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
         <is>
-          <t>✅ Terpenuhi</t>
+          <t>✅ Sangat Kuat</t>
         </is>
       </c>
     </row>
     <row r="158" ht="16" customHeight="1">
       <c r="A158" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT09**</t>
+          <t>**BK-IT07**</t>
         </is>
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
-          <t>*Data Analytics &amp; Information Visualization*</t>
+          <t>*System Integration and Architecture*</t>
         </is>
       </c>
       <c r="C158" s="19" t="inlineStr">
         <is>
-          <t>`STI-402`, `STI-503`</t>
+          <t>`STI-601`, `STI-604`, `FST-610`</t>
         </is>
       </c>
       <c r="D158" s="19" t="inlineStr">
         <is>
-          <t>`STA-01`, `STA-04`</t>
+          <t>`STB-06`, `STC-02`</t>
         </is>
       </c>
       <c r="E158" s="19" t="inlineStr">
         <is>
-          <t>4 MK</t>
+          <t>5 MK</t>
         </is>
       </c>
       <c r="F158" s="19" t="inlineStr">
@@ -12858,59 +12984,59 @@
     <row r="159" ht="16" customHeight="1">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT10**</t>
+          <t>**BK-IT08**</t>
         </is>
       </c>
       <c r="B159" s="20" t="inlineStr">
         <is>
-          <t>*User Experience &amp; Interaction Design*</t>
+          <t>*IT Service Management &amp; Governance*</t>
         </is>
       </c>
       <c r="C159" s="20" t="inlineStr">
         <is>
-          <t>`STI-303`, `STC-01`</t>
+          <t>`STB-04`, `STB-05`</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>`STI-306`, `STC-04`</t>
+          <t>`STI-506`</t>
         </is>
       </c>
       <c r="E159" s="20" t="inlineStr">
         <is>
-          <t>4 MK</t>
+          <t>3 MK</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
         <is>
-          <t>✅ Sangat Kuat</t>
+          <t>✅ Terpenuhi</t>
         </is>
       </c>
     </row>
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT11**</t>
+          <t>**BK-IT09**</t>
         </is>
       </c>
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>*Software Development Practices*</t>
+          <t>*Data Analytics &amp; Information Visualization*</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
         <is>
-          <t>`STI-304`, `STI-407`, `STI-604`</t>
+          <t>`STI-402`, `STI-503`</t>
         </is>
       </c>
       <c r="D160" s="19" t="inlineStr">
         <is>
-          <t>`FST-205`, `STC-05`</t>
+          <t>`STA-01`, `STA-04`</t>
         </is>
       </c>
       <c r="E160" s="19" t="inlineStr">
         <is>
-          <t>5 MK</t>
+          <t>4 MK</t>
         </is>
       </c>
       <c r="F160" s="19" t="inlineStr">
@@ -12922,59 +13048,59 @@
     <row r="161" ht="16" customHeight="1">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT12**</t>
+          <t>**BK-IT10**</t>
         </is>
       </c>
       <c r="B161" s="20" t="inlineStr">
         <is>
-          <t>*IT Risk Management and Compliance*</t>
+          <t>*User Experience &amp; Interaction Design*</t>
         </is>
       </c>
       <c r="C161" s="20" t="inlineStr">
         <is>
-          <t>`STB-03`, `STB-04`</t>
+          <t>`STI-303`, `STC-01`</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>`FST-206`</t>
+          <t>`STI-306`, `STC-04`</t>
         </is>
       </c>
       <c r="E161" s="20" t="inlineStr">
         <is>
-          <t>3 MK</t>
+          <t>4 MK</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
         <is>
-          <t>✅ Terpenuhi</t>
+          <t>✅ Sangat Kuat</t>
         </is>
       </c>
     </row>
     <row r="162" ht="16" customHeight="1">
       <c r="A162" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT13**</t>
+          <t>**BK-IT11**</t>
         </is>
       </c>
       <c r="B162" s="19" t="inlineStr">
         <is>
-          <t>*Technology Entrepreneurship*</t>
+          <t>*Software Development Practices*</t>
         </is>
       </c>
       <c r="C162" s="19" t="inlineStr">
         <is>
-          <t>`MKU-204`, `STI-701`, `FST-610`</t>
-        </is>
-      </c>
-      <c r="D162" s="21" t="inlineStr">
-        <is>
-          <t>`STC-06`</t>
+          <t>`STI-304`, `STI-407`, `STI-604`</t>
+        </is>
+      </c>
+      <c r="D162" s="19" t="inlineStr">
+        <is>
+          <t>`FST-205`, `STC-05`</t>
         </is>
       </c>
       <c r="E162" s="19" t="inlineStr">
         <is>
-          <t>4 MK</t>
+          <t>5 MK</t>
         </is>
       </c>
       <c r="F162" s="19" t="inlineStr">
@@ -12986,2631 +13112,2727 @@
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="20" t="inlineStr">
         <is>
+          <t>**BK-IT12**</t>
+        </is>
+      </c>
+      <c r="B163" s="20" t="inlineStr">
+        <is>
+          <t>*IT Risk Management and Compliance*</t>
+        </is>
+      </c>
+      <c r="C163" s="20" t="inlineStr">
+        <is>
+          <t>`STB-03`, `STB-04`</t>
+        </is>
+      </c>
+      <c r="D163" s="20" t="inlineStr">
+        <is>
+          <t>`FST-206`</t>
+        </is>
+      </c>
+      <c r="E163" s="20" t="inlineStr">
+        <is>
+          <t>3 MK</t>
+        </is>
+      </c>
+      <c r="F163" s="20" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="16" customHeight="1">
+      <c r="A164" s="19" t="inlineStr">
+        <is>
+          <t>**BK-IT13**</t>
+        </is>
+      </c>
+      <c r="B164" s="19" t="inlineStr">
+        <is>
+          <t>*Technology Entrepreneurship*</t>
+        </is>
+      </c>
+      <c r="C164" s="19" t="inlineStr">
+        <is>
+          <t>`MKU-204`, `STI-701`, `FST-610`</t>
+        </is>
+      </c>
+      <c r="D164" s="21" t="inlineStr">
+        <is>
+          <t>`STC-06`</t>
+        </is>
+      </c>
+      <c r="E164" s="19" t="inlineStr">
+        <is>
+          <t>4 MK</t>
+        </is>
+      </c>
+      <c r="F164" s="19" t="inlineStr">
+        <is>
+          <t>✅ Sangat Kuat</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="16" customHeight="1">
+      <c r="A165" s="20" t="inlineStr">
+        <is>
           <t>**BK-IT14**</t>
         </is>
       </c>
-      <c r="B163" s="20" t="inlineStr">
+      <c r="B165" s="20" t="inlineStr">
         <is>
           <t>*IoT and Embedded Smart Systems*</t>
         </is>
       </c>
-      <c r="C163" s="20" t="inlineStr">
+      <c r="C165" s="20" t="inlineStr">
         <is>
           <t>`STI-504`, `STA-06`</t>
         </is>
       </c>
-      <c r="D163" s="20" t="inlineStr">
+      <c r="D165" s="20" t="inlineStr">
         <is>
           <t>`STI-305`, `STI-307`</t>
         </is>
       </c>
-      <c r="E163" s="20" t="inlineStr">
+      <c r="E165" s="20" t="inlineStr">
         <is>
           <t>4 MK</t>
         </is>
       </c>
-      <c r="F163" s="20" t="inlineStr">
+      <c r="F165" s="20" t="inlineStr">
         <is>
           <t>✅ Sangat Kuat</t>
         </is>
       </c>
     </row>
-    <row r="164"/>
-    <row r="165" ht="20" customHeight="1">
-      <c r="A165" s="15" t="inlineStr">
+    <row r="166" ht="16" customHeight="1">
+      <c r="A166" s="19" t="inlineStr">
+        <is>
+          <t>**BK-IT15**</t>
+        </is>
+      </c>
+      <c r="B166" s="19" t="inlineStr">
+        <is>
+          <t>*Global Professional Practice*</t>
+        </is>
+      </c>
+      <c r="C166" s="19" t="inlineStr">
+        <is>
+          <t>`FST-205`, `FST-612`</t>
+        </is>
+      </c>
+      <c r="D166" s="19" t="inlineStr">
+        <is>
+          <t>`FST-206`, `MKU-507`</t>
+        </is>
+      </c>
+      <c r="E166" s="19" t="inlineStr">
+        <is>
+          <t>4 MK</t>
+        </is>
+      </c>
+      <c r="F166" s="19" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="167"/>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="15" t="inlineStr">
         <is>
           <t>7. MATRIKS KEPATUHAN IKU 7 &amp; METODE PEMBELAJARAN PARTISIPATIF PER MATA KULIAH</t>
         </is>
       </c>
-      <c r="B165" s="16" t="n"/>
-      <c r="C165" s="16" t="n"/>
-      <c r="D165" s="16" t="n"/>
-      <c r="E165" s="16" t="n"/>
-      <c r="F165" s="16" t="n"/>
-      <c r="G165" s="16" t="n"/>
-      <c r="H165" s="16" t="n"/>
-      <c r="I165" s="17" t="n"/>
-    </row>
-    <row r="166" ht="26" customHeight="1">
-      <c r="A166" s="18" t="inlineStr">
+      <c r="B168" s="16" t="n"/>
+      <c r="C168" s="16" t="n"/>
+      <c r="D168" s="16" t="n"/>
+      <c r="E168" s="16" t="n"/>
+      <c r="F168" s="16" t="n"/>
+      <c r="G168" s="16" t="n"/>
+      <c r="H168" s="16" t="n"/>
+      <c r="I168" s="17" t="n"/>
+    </row>
+    <row r="169" ht="26" customHeight="1">
+      <c r="A169" s="18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B166" s="18" t="inlineStr">
+      <c r="B169" s="18" t="inlineStr">
         <is>
           <t>Kode MK</t>
         </is>
       </c>
-      <c r="C166" s="18" t="inlineStr">
+      <c r="C169" s="18" t="inlineStr">
         <is>
           <t>Nama Mata Kuliah</t>
         </is>
       </c>
-      <c r="D166" s="18" t="inlineStr">
+      <c r="D169" s="18" t="inlineStr">
         <is>
           <t>SKS</t>
         </is>
       </c>
-      <c r="E166" s="18" t="inlineStr">
+      <c r="E169" s="18" t="inlineStr">
         <is>
           <t>Bobot Case Method (%)</t>
         </is>
       </c>
-      <c r="F166" s="18" t="inlineStr">
+      <c r="F169" s="18" t="inlineStr">
         <is>
           <t>Bobot Team-Based PjBL (%)</t>
         </is>
       </c>
-      <c r="G166" s="18" t="inlineStr">
+      <c r="G169" s="18" t="inlineStr">
         <is>
           <t>Bobot Evaluasi Kognitif / Lab (%)</t>
         </is>
       </c>
-      <c r="H166" s="18" t="inlineStr">
+      <c r="H169" s="18" t="inlineStr">
         <is>
           <t>**Total Bobot IKU 7 (CM + PjBL)**</t>
         </is>
       </c>
-      <c r="I166" s="18" t="inlineStr">
+      <c r="I169" s="18" t="inlineStr">
         <is>
           <t>Status Kepatuhan IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="16" customHeight="1">
-      <c r="A167" s="21" t="inlineStr">
+    <row r="170" ht="16" customHeight="1">
+      <c r="A170" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B167" s="19" t="inlineStr">
+      <c r="B170" s="19" t="inlineStr">
         <is>
           <t>`FST-101`</t>
         </is>
       </c>
-      <c r="C167" s="19" t="inlineStr">
+      <c r="C170" s="19" t="inlineStr">
         <is>
           <t>Dasar Teknologi Digital</t>
         </is>
       </c>
-      <c r="D167" s="21" t="inlineStr">
+      <c r="D170" s="21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E167" s="19" t="inlineStr">
+      <c r="E170" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F167" s="19" t="inlineStr">
+      <c r="F170" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G167" s="19" t="inlineStr">
+      <c r="G170" s="19" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H167" s="19" t="inlineStr">
+      <c r="H170" s="19" t="inlineStr">
         <is>
           <t>**50%**</t>
         </is>
       </c>
-      <c r="I167" s="19" t="inlineStr">
+      <c r="I170" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="16" customHeight="1">
-      <c r="A168" s="22" t="inlineStr">
+    <row r="171" ht="16" customHeight="1">
+      <c r="A171" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B168" s="20" t="inlineStr">
+      <c r="B171" s="20" t="inlineStr">
         <is>
           <t>`FST-102`</t>
         </is>
       </c>
-      <c r="C168" s="20" t="inlineStr">
+      <c r="C171" s="20" t="inlineStr">
         <is>
           <t>Algoritma &amp; Pemrograman</t>
         </is>
       </c>
-      <c r="D168" s="22" t="inlineStr">
+      <c r="D171" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E168" s="20" t="inlineStr">
+      <c r="E171" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F168" s="20" t="inlineStr">
+      <c r="F171" s="20" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G168" s="20" t="inlineStr">
+      <c r="G171" s="20" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="H168" s="20" t="inlineStr">
+      <c r="H171" s="20" t="inlineStr">
         <is>
           <t>**60%**</t>
         </is>
       </c>
-      <c r="I168" s="20" t="inlineStr">
+      <c r="I171" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="16" customHeight="1">
-      <c r="A169" s="21" t="inlineStr">
+    <row r="172" ht="16" customHeight="1">
+      <c r="A172" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B169" s="19" t="inlineStr">
+      <c r="B172" s="19" t="inlineStr">
         <is>
           <t>`STI-101`</t>
         </is>
       </c>
-      <c r="C169" s="19" t="inlineStr">
+      <c r="C172" s="19" t="inlineStr">
         <is>
           <t>Pengantar Sistem &amp; TI</t>
         </is>
       </c>
-      <c r="D169" s="21" t="inlineStr">
+      <c r="D172" s="21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E169" s="19" t="inlineStr">
+      <c r="E172" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F169" s="19" t="inlineStr">
+      <c r="F172" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="G169" s="19" t="inlineStr">
+      <c r="G172" s="19" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H169" s="19" t="inlineStr">
+      <c r="H172" s="19" t="inlineStr">
         <is>
           <t>**50%**</t>
         </is>
       </c>
-      <c r="I169" s="19" t="inlineStr">
+      <c r="I172" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="16" customHeight="1">
-      <c r="A170" s="22" t="inlineStr">
+    <row r="173" ht="16" customHeight="1">
+      <c r="A173" s="22" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B170" s="20" t="inlineStr">
+      <c r="B173" s="20" t="inlineStr">
         <is>
           <t>`STI-102`</t>
         </is>
       </c>
-      <c r="C170" s="22" t="inlineStr">
+      <c r="C173" s="22" t="inlineStr">
         <is>
           <t>Kalkulus</t>
         </is>
       </c>
-      <c r="D170" s="22" t="inlineStr">
+      <c r="D173" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E170" s="20" t="inlineStr">
+      <c r="E173" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F170" s="20" t="inlineStr">
+      <c r="F173" s="20" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G170" s="20" t="inlineStr">
+      <c r="G173" s="20" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="H170" s="20" t="inlineStr">
+      <c r="H173" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I170" s="20" t="inlineStr">
+      <c r="I173" s="20" t="inlineStr">
         <is>
           <t>*MK Teori Dasar Sains*</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="16" customHeight="1">
-      <c r="A171" s="21" t="inlineStr">
+    <row r="174" ht="16" customHeight="1">
+      <c r="A174" s="21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B171" s="19" t="inlineStr">
+      <c r="B174" s="19" t="inlineStr">
         <is>
           <t>`STI-103`</t>
         </is>
       </c>
-      <c r="C171" s="19" t="inlineStr">
+      <c r="C174" s="19" t="inlineStr">
         <is>
           <t>Arsitektur &amp; Org. Sistem TI</t>
         </is>
       </c>
-      <c r="D171" s="21" t="inlineStr">
+      <c r="D174" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E171" s="19" t="inlineStr">
+      <c r="E174" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F171" s="19" t="inlineStr">
+      <c r="F174" s="19" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G171" s="19" t="inlineStr">
+      <c r="G174" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="H171" s="19" t="inlineStr">
+      <c r="H174" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I171" s="19" t="inlineStr">
+      <c r="I174" s="19" t="inlineStr">
         <is>
           <t>*MK Teori Sistem &amp; Hardware*</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="16" customHeight="1">
-      <c r="A172" s="22" t="inlineStr">
+    <row r="175" ht="16" customHeight="1">
+      <c r="A175" s="22" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B172" s="20" t="inlineStr">
+      <c r="B175" s="20" t="inlineStr">
         <is>
           <t>`MKU-101`</t>
         </is>
       </c>
-      <c r="C172" s="22" t="inlineStr">
+      <c r="C175" s="22" t="inlineStr">
         <is>
           <t>Agama I</t>
         </is>
       </c>
-      <c r="D172" s="22" t="inlineStr">
+      <c r="D175" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E172" s="20" t="inlineStr">
+      <c r="E175" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F172" s="20" t="inlineStr">
+      <c r="F175" s="20" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G172" s="20" t="inlineStr">
+      <c r="G175" s="20" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="H172" s="20" t="inlineStr">
+      <c r="H175" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I172" s="20" t="inlineStr">
+      <c r="I175" s="20" t="inlineStr">
         <is>
           <t>*MK Teori Dasar Sikap*</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="16" customHeight="1">
-      <c r="A173" s="21" t="inlineStr">
+    <row r="176" ht="16" customHeight="1">
+      <c r="A176" s="21" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B173" s="19" t="inlineStr">
+      <c r="B176" s="19" t="inlineStr">
         <is>
           <t>`MKU-102`</t>
         </is>
       </c>
-      <c r="C173" s="19" t="inlineStr">
+      <c r="C176" s="19" t="inlineStr">
         <is>
           <t>Pancasila</t>
         </is>
       </c>
-      <c r="D173" s="21" t="inlineStr">
+      <c r="D176" s="21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E173" s="19" t="inlineStr">
+      <c r="E176" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F173" s="19" t="inlineStr">
+      <c r="F176" s="19" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G173" s="19" t="inlineStr">
+      <c r="G176" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="H173" s="19" t="inlineStr">
+      <c r="H176" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I173" s="19" t="inlineStr">
+      <c r="I176" s="19" t="inlineStr">
         <is>
           <t>*MK Teori Dasar Sikap*</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="16" customHeight="1">
-      <c r="A174" s="22" t="inlineStr">
+    <row r="177" ht="16" customHeight="1">
+      <c r="A177" s="22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B174" s="20" t="inlineStr">
+      <c r="B177" s="20" t="inlineStr">
         <is>
           <t>`MKU-103`</t>
         </is>
       </c>
-      <c r="C174" s="20" t="inlineStr">
+      <c r="C177" s="20" t="inlineStr">
         <is>
           <t>Bahasa Indonesia</t>
         </is>
       </c>
-      <c r="D174" s="22" t="inlineStr">
+      <c r="D177" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E174" s="20" t="inlineStr">
+      <c r="E177" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F174" s="20" t="inlineStr">
+      <c r="F177" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="G174" s="20" t="inlineStr">
+      <c r="G177" s="20" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H174" s="20" t="inlineStr">
+      <c r="H177" s="20" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="I174" s="20" t="inlineStr">
+      <c r="I177" s="20" t="inlineStr">
         <is>
           <t>*MK Keterampilan Komunikasi*</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="16" customHeight="1">
-      <c r="A175" s="21" t="inlineStr">
+    <row r="178" ht="16" customHeight="1">
+      <c r="A178" s="21" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B175" s="19" t="inlineStr">
+      <c r="B178" s="19" t="inlineStr">
         <is>
           <t>`STI-201`</t>
         </is>
       </c>
-      <c r="C175" s="19" t="inlineStr">
+      <c r="C178" s="19" t="inlineStr">
         <is>
           <t>Matematika Diskrit &amp; Logika</t>
         </is>
       </c>
-      <c r="D175" s="21" t="inlineStr">
+      <c r="D178" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E175" s="19" t="inlineStr">
+      <c r="E178" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F175" s="19" t="inlineStr">
+      <c r="F178" s="19" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G175" s="19" t="inlineStr">
+      <c r="G178" s="19" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="H175" s="19" t="inlineStr">
+      <c r="H178" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I175" s="19" t="inlineStr">
+      <c r="I178" s="19" t="inlineStr">
         <is>
           <t>*MK Teori Dasar Sains*</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="16" customHeight="1">
-      <c r="A176" s="22" t="inlineStr">
+    <row r="179" ht="16" customHeight="1">
+      <c r="A179" s="22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B176" s="20" t="inlineStr">
+      <c r="B179" s="20" t="inlineStr">
         <is>
           <t>`STI-202`</t>
         </is>
       </c>
-      <c r="C176" s="20" t="inlineStr">
+      <c r="C179" s="20" t="inlineStr">
         <is>
           <t>Aljabar Linear &amp; Matriks</t>
         </is>
       </c>
-      <c r="D176" s="22" t="inlineStr">
+      <c r="D179" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E176" s="20" t="inlineStr">
+      <c r="E179" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F176" s="20" t="inlineStr">
+      <c r="F179" s="20" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G176" s="20" t="inlineStr">
+      <c r="G179" s="20" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="H176" s="20" t="inlineStr">
+      <c r="H179" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I176" s="20" t="inlineStr">
+      <c r="I179" s="20" t="inlineStr">
         <is>
           <t>*MK Teori Dasar Sains*</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="16" customHeight="1">
-      <c r="A177" s="21" t="inlineStr">
+    <row r="180" ht="16" customHeight="1">
+      <c r="A180" s="21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B177" s="19" t="inlineStr">
+      <c r="B180" s="19" t="inlineStr">
         <is>
           <t>`FST-203`</t>
         </is>
       </c>
-      <c r="C177" s="19" t="inlineStr">
+      <c r="C180" s="19" t="inlineStr">
         <is>
           <t>Struktur Data &amp; Algoritma</t>
         </is>
       </c>
-      <c r="D177" s="21" t="inlineStr">
+      <c r="D180" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E177" s="19" t="inlineStr">
+      <c r="E180" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F177" s="19" t="inlineStr">
+      <c r="F180" s="19" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G177" s="19" t="inlineStr">
+      <c r="G180" s="19" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="H177" s="19" t="inlineStr">
+      <c r="H180" s="19" t="inlineStr">
         <is>
           <t>**60%**</t>
         </is>
       </c>
-      <c r="I177" s="19" t="inlineStr">
+      <c r="I180" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="16" customHeight="1">
-      <c r="A178" s="22" t="inlineStr">
+    <row r="181" ht="16" customHeight="1">
+      <c r="A181" s="22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B178" s="20" t="inlineStr">
+      <c r="B181" s="20" t="inlineStr">
         <is>
           <t>`FST-204`</t>
         </is>
       </c>
-      <c r="C178" s="20" t="inlineStr">
+      <c r="C181" s="20" t="inlineStr">
         <is>
           <t>Organisasi &amp; Arsitektur Kom</t>
         </is>
       </c>
-      <c r="D178" s="22" t="inlineStr">
+      <c r="D181" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E178" s="20" t="inlineStr">
+      <c r="E181" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F178" s="20" t="inlineStr">
+      <c r="F181" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G178" s="20" t="inlineStr">
+      <c r="G181" s="20" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H178" s="20" t="inlineStr">
+      <c r="H181" s="20" t="inlineStr">
         <is>
           <t>**50%**</t>
         </is>
       </c>
-      <c r="I178" s="20" t="inlineStr">
+      <c r="I181" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="16" customHeight="1">
-      <c r="A179" s="21" t="inlineStr">
+    <row r="182" ht="16" customHeight="1">
+      <c r="A182" s="21" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B179" s="19" t="inlineStr">
+      <c r="B182" s="19" t="inlineStr">
         <is>
           <t>`FST-205`</t>
         </is>
       </c>
-      <c r="C179" s="19" t="inlineStr">
+      <c r="C182" s="19" t="inlineStr">
         <is>
           <t>Pemrograman Lanjut (OOP)</t>
         </is>
       </c>
-      <c r="D179" s="21" t="inlineStr">
+      <c r="D182" s="21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E179" s="19" t="inlineStr">
+      <c r="E182" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F179" s="19" t="inlineStr">
+      <c r="F182" s="19" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G179" s="19" t="inlineStr">
+      <c r="G182" s="19" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="H179" s="19" t="inlineStr">
+      <c r="H182" s="19" t="inlineStr">
         <is>
           <t>**65%**</t>
         </is>
       </c>
-      <c r="I179" s="19" t="inlineStr">
+      <c r="I182" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="16" customHeight="1">
-      <c r="A180" s="22" t="inlineStr">
+    <row r="183" ht="16" customHeight="1">
+      <c r="A183" s="22" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B180" s="20" t="inlineStr">
+      <c r="B183" s="20" t="inlineStr">
         <is>
           <t>`FST-206`</t>
         </is>
       </c>
-      <c r="C180" s="20" t="inlineStr">
+      <c r="C183" s="20" t="inlineStr">
         <is>
           <t>Etika Profesi &amp; Hukum Dig.</t>
         </is>
       </c>
-      <c r="D180" s="22" t="inlineStr">
+      <c r="D183" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E180" s="20" t="inlineStr">
+      <c r="E183" s="20" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="F180" s="20" t="inlineStr">
+      <c r="F183" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="G180" s="20" t="inlineStr">
+      <c r="G183" s="20" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="H180" s="20" t="inlineStr">
+      <c r="H183" s="20" t="inlineStr">
         <is>
           <t>**60%**</t>
         </is>
       </c>
-      <c r="I180" s="20" t="inlineStr">
+      <c r="I183" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="16" customHeight="1">
-      <c r="A181" s="21" t="inlineStr">
+    <row r="184" ht="16" customHeight="1">
+      <c r="A184" s="21" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B181" s="19" t="inlineStr">
+      <c r="B184" s="19" t="inlineStr">
         <is>
           <t>`FST-207`</t>
         </is>
       </c>
-      <c r="C181" s="19" t="inlineStr">
+      <c r="C184" s="19" t="inlineStr">
         <is>
           <t>Sistem Basis Data</t>
         </is>
       </c>
-      <c r="D181" s="21" t="inlineStr">
+      <c r="D184" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E181" s="19" t="inlineStr">
+      <c r="E184" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F181" s="19" t="inlineStr">
+      <c r="F184" s="19" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G181" s="19" t="inlineStr">
+      <c r="G184" s="19" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="H181" s="19" t="inlineStr">
+      <c r="H184" s="19" t="inlineStr">
         <is>
           <t>**65%**</t>
         </is>
       </c>
-      <c r="I181" s="19" t="inlineStr">
+      <c r="I184" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="16" customHeight="1">
-      <c r="A182" s="22" t="inlineStr">
+    <row r="185" ht="16" customHeight="1">
+      <c r="A185" s="22" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B182" s="20" t="inlineStr">
+      <c r="B185" s="20" t="inlineStr">
         <is>
           <t>`MKU-204`</t>
         </is>
       </c>
-      <c r="C182" s="20" t="inlineStr">
+      <c r="C185" s="20" t="inlineStr">
         <is>
           <t>Kewirausahaan I</t>
         </is>
       </c>
-      <c r="D182" s="22" t="inlineStr">
+      <c r="D185" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E182" s="20" t="inlineStr">
+      <c r="E185" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F182" s="20" t="inlineStr">
+      <c r="F185" s="20" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G182" s="20" t="inlineStr">
+      <c r="G185" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H182" s="20" t="inlineStr">
+      <c r="H185" s="20" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I182" s="20" t="inlineStr">
+      <c r="I185" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="16" customHeight="1">
-      <c r="A183" s="21" t="inlineStr">
+    <row r="186" ht="16" customHeight="1">
+      <c r="A186" s="21" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B183" s="19" t="inlineStr">
+      <c r="B186" s="19" t="inlineStr">
         <is>
           <t>`STI-301`</t>
         </is>
       </c>
-      <c r="C183" s="19" t="inlineStr">
+      <c r="C186" s="19" t="inlineStr">
         <is>
           <t>Analisis &amp; Perancangan SI</t>
         </is>
       </c>
-      <c r="D183" s="21" t="inlineStr">
+      <c r="D186" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E183" s="19" t="inlineStr">
+      <c r="E186" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F183" s="19" t="inlineStr">
+      <c r="F186" s="19" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G183" s="19" t="inlineStr">
+      <c r="G186" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H183" s="19" t="inlineStr">
+      <c r="H186" s="19" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I183" s="19" t="inlineStr">
+      <c r="I186" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="16" customHeight="1">
-      <c r="A184" s="22" t="inlineStr">
+    <row r="187" ht="16" customHeight="1">
+      <c r="A187" s="22" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B184" s="20" t="inlineStr">
+      <c r="B187" s="20" t="inlineStr">
         <is>
           <t>`STI-302`</t>
         </is>
       </c>
-      <c r="C184" s="20" t="inlineStr">
+      <c r="C187" s="20" t="inlineStr">
         <is>
           <t>Sistem Cerdas</t>
         </is>
       </c>
-      <c r="D184" s="22" t="inlineStr">
+      <c r="D187" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E184" s="20" t="inlineStr">
+      <c r="E187" s="20" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="F184" s="20" t="inlineStr">
+      <c r="F187" s="20" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="G184" s="20" t="inlineStr">
+      <c r="G187" s="20" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="H184" s="20" t="inlineStr">
+      <c r="H187" s="20" t="inlineStr">
         <is>
           <t>**60%**</t>
         </is>
       </c>
-      <c r="I184" s="20" t="inlineStr">
+      <c r="I187" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="16" customHeight="1">
-      <c r="A185" s="21" t="inlineStr">
+    <row r="188" ht="16" customHeight="1">
+      <c r="A188" s="21" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B185" s="19" t="inlineStr">
+      <c r="B188" s="19" t="inlineStr">
         <is>
           <t>`STI-303`</t>
         </is>
       </c>
-      <c r="C185" s="19" t="inlineStr">
+      <c r="C188" s="19" t="inlineStr">
         <is>
           <t>UI/UX Design &amp; Prototyping</t>
         </is>
       </c>
-      <c r="D185" s="21" t="inlineStr">
+      <c r="D188" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E185" s="19" t="inlineStr">
+      <c r="E188" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F185" s="19" t="inlineStr">
+      <c r="F188" s="19" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="G185" s="19" t="inlineStr">
+      <c r="G188" s="19" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="H185" s="19" t="inlineStr">
+      <c r="H188" s="19" t="inlineStr">
         <is>
           <t>**75%**</t>
         </is>
       </c>
-      <c r="I185" s="19" t="inlineStr">
+      <c r="I188" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="16" customHeight="1">
-      <c r="A186" s="22" t="inlineStr">
+    <row r="189" ht="16" customHeight="1">
+      <c r="A189" s="22" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B186" s="20" t="inlineStr">
+      <c r="B189" s="20" t="inlineStr">
         <is>
           <t>`STI-304`</t>
         </is>
       </c>
-      <c r="C186" s="20" t="inlineStr">
+      <c r="C189" s="20" t="inlineStr">
         <is>
           <t>Rekayasa Perangkat Lunak</t>
         </is>
       </c>
-      <c r="D186" s="22" t="inlineStr">
+      <c r="D189" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E186" s="20" t="inlineStr">
+      <c r="E189" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F186" s="20" t="inlineStr">
+      <c r="F189" s="20" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="G186" s="20" t="inlineStr">
+      <c r="G189" s="20" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="H186" s="20" t="inlineStr">
+      <c r="H189" s="20" t="inlineStr">
         <is>
           <t>**75%**</t>
         </is>
       </c>
-      <c r="I186" s="20" t="inlineStr">
+      <c r="I189" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="16" customHeight="1">
-      <c r="A187" s="21" t="inlineStr">
+    <row r="190" ht="16" customHeight="1">
+      <c r="A190" s="21" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B187" s="19" t="inlineStr">
+      <c r="B190" s="19" t="inlineStr">
         <is>
           <t>`STI-305`</t>
         </is>
       </c>
-      <c r="C187" s="19" t="inlineStr">
+      <c r="C190" s="19" t="inlineStr">
         <is>
           <t>Sistem Operasi</t>
         </is>
       </c>
-      <c r="D187" s="21" t="inlineStr">
+      <c r="D190" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E187" s="19" t="inlineStr">
+      <c r="E190" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F187" s="19" t="inlineStr">
+      <c r="F190" s="19" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="G187" s="19" t="inlineStr">
+      <c r="G190" s="19" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="H187" s="19" t="inlineStr">
+      <c r="H190" s="19" t="inlineStr">
         <is>
           <t>**55%**</t>
         </is>
       </c>
-      <c r="I187" s="19" t="inlineStr">
+      <c r="I190" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="16" customHeight="1">
-      <c r="A188" s="22" t="inlineStr">
+    <row r="191" ht="16" customHeight="1">
+      <c r="A191" s="22" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B188" s="20" t="inlineStr">
+      <c r="B191" s="20" t="inlineStr">
         <is>
           <t>`STI-306`</t>
         </is>
       </c>
-      <c r="C188" s="20" t="inlineStr">
+      <c r="C191" s="20" t="inlineStr">
         <is>
           <t>Web Front End Development</t>
         </is>
       </c>
-      <c r="D188" s="22" t="inlineStr">
+      <c r="D191" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E188" s="20" t="inlineStr">
+      <c r="E191" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F188" s="20" t="inlineStr">
+      <c r="F191" s="20" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G188" s="20" t="inlineStr">
+      <c r="G191" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H188" s="20" t="inlineStr">
+      <c r="H191" s="20" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I188" s="20" t="inlineStr">
+      <c r="I191" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="16" customHeight="1">
-      <c r="A189" s="21" t="inlineStr">
+    <row r="192" ht="16" customHeight="1">
+      <c r="A192" s="21" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B189" s="19" t="inlineStr">
+      <c r="B192" s="19" t="inlineStr">
         <is>
           <t>`STI-307`</t>
         </is>
       </c>
-      <c r="C189" s="19" t="inlineStr">
+      <c r="C192" s="19" t="inlineStr">
         <is>
           <t>Jaringan Komputer</t>
         </is>
       </c>
-      <c r="D189" s="21" t="inlineStr">
+      <c r="D192" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E189" s="19" t="inlineStr">
+      <c r="E192" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F189" s="19" t="inlineStr">
+      <c r="F192" s="19" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="G189" s="19" t="inlineStr">
+      <c r="G192" s="19" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="H189" s="19" t="inlineStr">
+      <c r="H192" s="19" t="inlineStr">
         <is>
           <t>**55%**</t>
         </is>
       </c>
-      <c r="I189" s="19" t="inlineStr">
+      <c r="I192" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="16" customHeight="1">
-      <c r="A190" s="22" t="inlineStr">
+    <row r="193" ht="16" customHeight="1">
+      <c r="A193" s="22" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B190" s="20" t="inlineStr">
+      <c r="B193" s="20" t="inlineStr">
         <is>
           <t>`STI-401`</t>
         </is>
       </c>
-      <c r="C190" s="20" t="inlineStr">
+      <c r="C193" s="20" t="inlineStr">
         <is>
           <t>Machine Learning</t>
         </is>
       </c>
-      <c r="D190" s="22" t="inlineStr">
+      <c r="D193" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E190" s="20" t="inlineStr">
+      <c r="E193" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F190" s="20" t="inlineStr">
+      <c r="F193" s="20" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G190" s="20" t="inlineStr">
+      <c r="G193" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H190" s="20" t="inlineStr">
+      <c r="H193" s="20" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I190" s="20" t="inlineStr">
+      <c r="I193" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="16" customHeight="1">
-      <c r="A191" s="21" t="inlineStr">
+    <row r="194" ht="16" customHeight="1">
+      <c r="A194" s="21" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B191" s="19" t="inlineStr">
+      <c r="B194" s="19" t="inlineStr">
         <is>
           <t>`STI-402`</t>
         </is>
       </c>
-      <c r="C191" s="19" t="inlineStr">
+      <c r="C194" s="19" t="inlineStr">
         <is>
           <t>Data Warehouse &amp; BI</t>
         </is>
       </c>
-      <c r="D191" s="21" t="inlineStr">
+      <c r="D194" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E191" s="19" t="inlineStr">
+      <c r="E194" s="19" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="F191" s="19" t="inlineStr">
+      <c r="F194" s="19" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G191" s="19" t="inlineStr">
+      <c r="G194" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H191" s="19" t="inlineStr">
+      <c r="H194" s="19" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I191" s="19" t="inlineStr">
+      <c r="I194" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="16" customHeight="1">
-      <c r="A192" s="22" t="inlineStr">
+    <row r="195" ht="16" customHeight="1">
+      <c r="A195" s="22" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B192" s="20" t="inlineStr">
+      <c r="B195" s="20" t="inlineStr">
         <is>
           <t>`STI-407`</t>
         </is>
       </c>
-      <c r="C192" s="20" t="inlineStr">
+      <c r="C195" s="20" t="inlineStr">
         <is>
           <t>Web Back End Development</t>
         </is>
       </c>
-      <c r="D192" s="22" t="inlineStr">
+      <c r="D195" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E192" s="20" t="inlineStr">
+      <c r="E195" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F192" s="20" t="inlineStr">
+      <c r="F195" s="20" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G192" s="20" t="inlineStr">
+      <c r="G195" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H192" s="20" t="inlineStr">
+      <c r="H195" s="20" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I192" s="20" t="inlineStr">
+      <c r="I195" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="16" customHeight="1">
-      <c r="A193" s="21" t="inlineStr">
+    <row r="196" ht="16" customHeight="1">
+      <c r="A196" s="21" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B193" s="19" t="inlineStr">
+      <c r="B196" s="19" t="inlineStr">
         <is>
           <t>`STI-404`</t>
         </is>
       </c>
-      <c r="C193" s="19" t="inlineStr">
+      <c r="C196" s="19" t="inlineStr">
         <is>
           <t>Komputasi Awan (Cloud)</t>
         </is>
       </c>
-      <c r="D193" s="21" t="inlineStr">
+      <c r="D196" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E193" s="19" t="inlineStr">
+      <c r="E196" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F193" s="19" t="inlineStr">
+      <c r="F196" s="19" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G193" s="19" t="inlineStr">
+      <c r="G196" s="19" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="H193" s="19" t="inlineStr">
+      <c r="H196" s="19" t="inlineStr">
         <is>
           <t>**65%**</t>
         </is>
       </c>
-      <c r="I193" s="19" t="inlineStr">
+      <c r="I196" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="16" customHeight="1">
-      <c r="A194" s="22" t="inlineStr">
+    <row r="197" ht="16" customHeight="1">
+      <c r="A197" s="22" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B194" s="20" t="inlineStr">
+      <c r="B197" s="20" t="inlineStr">
         <is>
           <t>`STI-405`</t>
         </is>
       </c>
-      <c r="C194" s="20" t="inlineStr">
+      <c r="C197" s="20" t="inlineStr">
         <is>
           <t>Dasar Keamanan Informasi</t>
         </is>
       </c>
-      <c r="D194" s="22" t="inlineStr">
+      <c r="D197" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E194" s="20" t="inlineStr">
+      <c r="E197" s="20" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="F194" s="20" t="inlineStr">
+      <c r="F197" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G194" s="20" t="inlineStr">
+      <c r="G197" s="20" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="H194" s="20" t="inlineStr">
+      <c r="H197" s="20" t="inlineStr">
         <is>
           <t>**55%**</t>
         </is>
       </c>
-      <c r="I194" s="20" t="inlineStr">
+      <c r="I197" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="16" customHeight="1">
-      <c r="A195" s="21" t="inlineStr">
+    <row r="198" ht="16" customHeight="1">
+      <c r="A198" s="21" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B195" s="19" t="inlineStr">
+      <c r="B198" s="19" t="inlineStr">
         <is>
           <t>`FST-408`</t>
         </is>
       </c>
-      <c r="C195" s="19" t="inlineStr">
+      <c r="C198" s="19" t="inlineStr">
         <is>
           <t>Probabilitas &amp; Statistika</t>
         </is>
       </c>
-      <c r="D195" s="21" t="inlineStr">
+      <c r="D198" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E195" s="19" t="inlineStr">
+      <c r="E198" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F195" s="19" t="inlineStr">
+      <c r="F198" s="19" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="G195" s="19" t="inlineStr">
+      <c r="G198" s="19" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="H195" s="19" t="inlineStr">
+      <c r="H198" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I195" s="19" t="inlineStr">
+      <c r="I198" s="19" t="inlineStr">
         <is>
           <t>*MK Teori Dasar Sains*</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="16" customHeight="1">
-      <c r="A196" s="22" t="inlineStr">
+    <row r="199" ht="16" customHeight="1">
+      <c r="A199" s="22" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B196" s="20" t="inlineStr">
+      <c r="B199" s="20" t="inlineStr">
         <is>
           <t>`STI-403`</t>
         </is>
       </c>
-      <c r="C196" s="20" t="inlineStr">
+      <c r="C199" s="20" t="inlineStr">
         <is>
           <t>Pengantar NLP &amp; IR</t>
         </is>
       </c>
-      <c r="D196" s="22" t="inlineStr">
+      <c r="D199" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E196" s="20" t="inlineStr">
+      <c r="E199" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F196" s="20" t="inlineStr">
+      <c r="F199" s="20" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G196" s="20" t="inlineStr">
+      <c r="G199" s="20" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="H196" s="20" t="inlineStr">
+      <c r="H199" s="20" t="inlineStr">
         <is>
           <t>**65%**</t>
         </is>
       </c>
-      <c r="I196" s="20" t="inlineStr">
+      <c r="I199" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="16" customHeight="1">
-      <c r="A197" s="21" t="inlineStr">
+    <row r="200" ht="16" customHeight="1">
+      <c r="A200" s="21" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B197" s="19" t="inlineStr">
+      <c r="B200" s="19" t="inlineStr">
         <is>
           <t>`MKU-405`</t>
         </is>
       </c>
-      <c r="C197" s="19" t="inlineStr">
+      <c r="C200" s="19" t="inlineStr">
         <is>
           <t>Kewarganegaraan</t>
         </is>
       </c>
-      <c r="D197" s="21" t="inlineStr">
+      <c r="D200" s="21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E197" s="19" t="inlineStr">
+      <c r="E200" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F197" s="19" t="inlineStr">
+      <c r="F200" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G197" s="19" t="inlineStr">
+      <c r="G200" s="19" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="H197" s="19" t="inlineStr">
+      <c r="H200" s="19" t="inlineStr">
         <is>
           <t>**60%**</t>
         </is>
       </c>
-      <c r="I197" s="19" t="inlineStr">
+      <c r="I200" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="16" customHeight="1">
-      <c r="A198" s="22" t="inlineStr">
+    <row r="201" ht="16" customHeight="1">
+      <c r="A201" s="22" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B198" s="20" t="inlineStr">
+      <c r="B201" s="20" t="inlineStr">
         <is>
           <t>`STI-501`</t>
         </is>
       </c>
-      <c r="C198" s="20" t="inlineStr">
+      <c r="C201" s="20" t="inlineStr">
         <is>
           <t>Deep Learning &amp; Neural Net</t>
         </is>
       </c>
-      <c r="D198" s="22" t="inlineStr">
+      <c r="D201" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E198" s="20" t="inlineStr">
+      <c r="E201" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F198" s="20" t="inlineStr">
+      <c r="F201" s="20" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G198" s="20" t="inlineStr">
+      <c r="G201" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H198" s="20" t="inlineStr">
+      <c r="H201" s="20" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I198" s="20" t="inlineStr">
+      <c r="I201" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="16" customHeight="1">
-      <c r="A199" s="21" t="inlineStr">
+    <row r="202" ht="16" customHeight="1">
+      <c r="A202" s="21" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B199" s="19" t="inlineStr">
+      <c r="B202" s="19" t="inlineStr">
         <is>
           <t>`STI-503`</t>
         </is>
       </c>
-      <c r="C199" s="19" t="inlineStr">
+      <c r="C202" s="19" t="inlineStr">
         <is>
           <t>Data Mining &amp; Visualisasi</t>
         </is>
       </c>
-      <c r="D199" s="21" t="inlineStr">
+      <c r="D202" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E199" s="19" t="inlineStr">
+      <c r="E202" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F199" s="19" t="inlineStr">
+      <c r="F202" s="19" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G199" s="19" t="inlineStr">
+      <c r="G202" s="19" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="H199" s="19" t="inlineStr">
+      <c r="H202" s="19" t="inlineStr">
         <is>
           <t>**65%**</t>
         </is>
       </c>
-      <c r="I199" s="19" t="inlineStr">
+      <c r="I202" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="16" customHeight="1">
-      <c r="A200" s="22" t="inlineStr">
+    <row r="203" ht="16" customHeight="1">
+      <c r="A203" s="22" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B200" s="20" t="inlineStr">
+      <c r="B203" s="20" t="inlineStr">
         <is>
           <t>`STI-504`</t>
         </is>
       </c>
-      <c r="C200" s="20" t="inlineStr">
+      <c r="C203" s="20" t="inlineStr">
         <is>
           <t>Internet of Things (IoT)</t>
         </is>
       </c>
-      <c r="D200" s="22" t="inlineStr">
+      <c r="D203" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E200" s="20" t="inlineStr">
+      <c r="E203" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F200" s="20" t="inlineStr">
+      <c r="F203" s="20" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G200" s="20" t="inlineStr">
+      <c r="G203" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H200" s="20" t="inlineStr">
+      <c r="H203" s="20" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I200" s="20" t="inlineStr">
+      <c r="I203" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="16" customHeight="1">
-      <c r="A201" s="21" t="inlineStr">
+    <row r="204" ht="16" customHeight="1">
+      <c r="A204" s="21" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B201" s="19" t="inlineStr">
+      <c r="B204" s="19" t="inlineStr">
         <is>
           <t>`STI-505`</t>
         </is>
       </c>
-      <c r="C201" s="19" t="inlineStr">
+      <c r="C204" s="19" t="inlineStr">
         <is>
           <t>Pemrograman Mobile</t>
         </is>
       </c>
-      <c r="D201" s="21" t="inlineStr">
+      <c r="D204" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E201" s="19" t="inlineStr">
+      <c r="E204" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F201" s="19" t="inlineStr">
+      <c r="F204" s="19" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G201" s="19" t="inlineStr">
+      <c r="G204" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H201" s="19" t="inlineStr">
+      <c r="H204" s="19" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I201" s="19" t="inlineStr">
+      <c r="I204" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="16" customHeight="1">
-      <c r="A202" s="22" t="inlineStr">
+    <row r="205" ht="16" customHeight="1">
+      <c r="A205" s="22" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B202" s="20" t="inlineStr">
+      <c r="B205" s="20" t="inlineStr">
         <is>
           <t>`STI-506`</t>
         </is>
       </c>
-      <c r="C202" s="20" t="inlineStr">
+      <c r="C205" s="20" t="inlineStr">
         <is>
           <t>Manajemen Proyek TI</t>
         </is>
       </c>
-      <c r="D202" s="22" t="inlineStr">
+      <c r="D205" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E202" s="20" t="inlineStr">
+      <c r="E205" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F202" s="20" t="inlineStr">
+      <c r="F205" s="20" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="G202" s="20" t="inlineStr">
+      <c r="G205" s="20" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="H202" s="20" t="inlineStr">
+      <c r="H205" s="20" t="inlineStr">
         <is>
           <t>**75%**</t>
         </is>
       </c>
-      <c r="I202" s="20" t="inlineStr">
+      <c r="I205" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="16" customHeight="1">
-      <c r="A203" s="21" t="inlineStr">
+    <row r="206" ht="16" customHeight="1">
+      <c r="A206" s="21" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B203" s="19" t="inlineStr">
+      <c r="B206" s="19" t="inlineStr">
         <is>
           <t>`MKU-507`</t>
         </is>
       </c>
-      <c r="C203" s="19" t="inlineStr">
+      <c r="C206" s="19" t="inlineStr">
         <is>
           <t>KPM (Kuliah Pengabdian Kepada Masyarakat)</t>
         </is>
       </c>
-      <c r="D203" s="21" t="inlineStr">
+      <c r="D206" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E203" s="19" t="inlineStr">
+      <c r="E206" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F203" s="19" t="inlineStr">
+      <c r="F206" s="19" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="G203" s="19" t="inlineStr">
+      <c r="G206" s="19" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="H203" s="19" t="inlineStr">
+      <c r="H206" s="19" t="inlineStr">
         <is>
           <t>**90%**</t>
         </is>
       </c>
-      <c r="I203" s="19" t="inlineStr">
+      <c r="I206" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="16" customHeight="1">
-      <c r="A204" s="22" t="inlineStr">
+    <row r="207" ht="16" customHeight="1">
+      <c r="A207" s="22" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B204" s="20" t="inlineStr">
+      <c r="B207" s="20" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C204" s="20" t="inlineStr">
+      <c r="C207" s="20" t="inlineStr">
         <is>
           <t>MK Pilihan Peminatan 1</t>
         </is>
       </c>
-      <c r="D204" s="22" t="inlineStr">
+      <c r="D207" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E204" s="20" t="inlineStr">
+      <c r="E207" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F204" s="20" t="inlineStr">
+      <c r="F207" s="20" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G204" s="20" t="inlineStr">
+      <c r="G207" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H204" s="20" t="inlineStr">
+      <c r="H207" s="20" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I204" s="20" t="inlineStr">
+      <c r="I207" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="16" customHeight="1">
-      <c r="A205" s="21" t="inlineStr">
+    <row r="208" ht="16" customHeight="1">
+      <c r="A208" s="21" t="inlineStr">
         <is>
           <t>38.B</t>
         </is>
       </c>
-      <c r="B205" s="19" t="inlineStr">
+      <c r="B208" s="19" t="inlineStr">
         <is>
           <t>`MKU-508`</t>
         </is>
       </c>
-      <c r="C205" s="19" t="inlineStr">
+      <c r="C208" s="19" t="inlineStr">
         <is>
           <t>Kewirausahaan II</t>
         </is>
       </c>
-      <c r="D205" s="21" t="inlineStr">
+      <c r="D208" s="21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E205" s="19" t="inlineStr">
+      <c r="E208" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F205" s="19" t="inlineStr">
+      <c r="F208" s="19" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G205" s="19" t="inlineStr">
+      <c r="G208" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H205" s="19" t="inlineStr">
+      <c r="H208" s="19" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I205" s="19" t="inlineStr">
+      <c r="I208" s="19" t="inlineStr">
         <is>
           <t>*MKWU 0 SKS (Sem 5)*</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="16" customHeight="1">
-      <c r="A206" s="22" t="inlineStr">
+    <row r="209" ht="16" customHeight="1">
+      <c r="A209" s="22" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B206" s="20" t="inlineStr">
+      <c r="B209" s="20" t="inlineStr">
         <is>
           <t>`STI-601`</t>
         </is>
       </c>
-      <c r="C206" s="20" t="inlineStr">
+      <c r="C209" s="20" t="inlineStr">
         <is>
           <t>Integrasi Layanan Cerdas AI</t>
         </is>
       </c>
-      <c r="D206" s="22" t="inlineStr">
+      <c r="D209" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E206" s="20" t="inlineStr">
+      <c r="E209" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F206" s="20" t="inlineStr">
+      <c r="F209" s="20" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="G206" s="20" t="inlineStr">
+      <c r="G209" s="20" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="H206" s="20" t="inlineStr">
+      <c r="H209" s="20" t="inlineStr">
         <is>
           <t>**75%**</t>
         </is>
       </c>
-      <c r="I206" s="20" t="inlineStr">
+      <c r="I209" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="16" customHeight="1">
-      <c r="A207" s="21" t="inlineStr">
+    <row r="210" ht="16" customHeight="1">
+      <c r="A210" s="21" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B207" s="19" t="inlineStr">
+      <c r="B210" s="19" t="inlineStr">
         <is>
           <t>`STI-602`</t>
         </is>
       </c>
-      <c r="C207" s="19" t="inlineStr">
+      <c r="C210" s="19" t="inlineStr">
         <is>
           <t>Smart City &amp; Pem. Digital</t>
         </is>
       </c>
-      <c r="D207" s="21" t="inlineStr">
+      <c r="D210" s="21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E207" s="19" t="inlineStr">
+      <c r="E210" s="19" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="F207" s="19" t="inlineStr">
+      <c r="F210" s="19" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="G207" s="19" t="inlineStr">
+      <c r="G210" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H207" s="19" t="inlineStr">
+      <c r="H210" s="19" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I207" s="19" t="inlineStr">
+      <c r="I210" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="16" customHeight="1">
-      <c r="A208" s="22" t="inlineStr">
+    <row r="211" ht="16" customHeight="1">
+      <c r="A211" s="22" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B208" s="20" t="inlineStr">
+      <c r="B211" s="20" t="inlineStr">
         <is>
           <t>`STI-603`</t>
         </is>
       </c>
-      <c r="C208" s="20" t="inlineStr">
+      <c r="C211" s="20" t="inlineStr">
         <is>
           <t>Keamanan Informasi Lanjut</t>
         </is>
       </c>
-      <c r="D208" s="22" t="inlineStr">
+      <c r="D211" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E208" s="20" t="inlineStr">
+      <c r="E211" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F208" s="20" t="inlineStr">
+      <c r="F211" s="20" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G208" s="20" t="inlineStr">
+      <c r="G211" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H208" s="20" t="inlineStr">
+      <c r="H211" s="20" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I208" s="20" t="inlineStr">
+      <c r="I211" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="16" customHeight="1">
-      <c r="A209" s="21" t="inlineStr">
+    <row r="212" ht="16" customHeight="1">
+      <c r="A212" s="21" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="B209" s="19" t="inlineStr">
+      <c r="B212" s="19" t="inlineStr">
         <is>
           <t>`STI-604`</t>
         </is>
       </c>
-      <c r="C209" s="19" t="inlineStr">
+      <c r="C212" s="19" t="inlineStr">
         <is>
           <t>Digital Platform Engineering</t>
         </is>
       </c>
-      <c r="D209" s="21" t="inlineStr">
+      <c r="D212" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E209" s="19" t="inlineStr">
+      <c r="E212" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F209" s="19" t="inlineStr">
+      <c r="F212" s="19" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="G209" s="19" t="inlineStr">
+      <c r="G212" s="19" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="H209" s="19" t="inlineStr">
+      <c r="H212" s="19" t="inlineStr">
         <is>
           <t>**75%**</t>
         </is>
       </c>
-      <c r="I209" s="19" t="inlineStr">
+      <c r="I212" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="16" customHeight="1">
-      <c r="A210" s="22" t="inlineStr">
+    <row r="213" ht="16" customHeight="1">
+      <c r="A213" s="22" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="B210" s="20" t="inlineStr">
+      <c r="B213" s="20" t="inlineStr">
         <is>
           <t>`FST-611`</t>
         </is>
       </c>
-      <c r="C210" s="20" t="inlineStr">
+      <c r="C213" s="20" t="inlineStr">
         <is>
           <t>Metodologi Penelitian</t>
         </is>
       </c>
-      <c r="D210" s="22" t="inlineStr">
+      <c r="D213" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E210" s="20" t="inlineStr">
+      <c r="E213" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F210" s="20" t="inlineStr">
+      <c r="F213" s="20" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="G210" s="20" t="inlineStr">
+      <c r="G213" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H210" s="20" t="inlineStr">
+      <c r="H213" s="20" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I210" s="20" t="inlineStr">
+      <c r="I213" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="16" customHeight="1">
-      <c r="A211" s="21" t="inlineStr">
+    <row r="214" ht="16" customHeight="1">
+      <c r="A214" s="21" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="B211" s="19" t="inlineStr">
+      <c r="B214" s="19" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C211" s="19" t="inlineStr">
+      <c r="C214" s="19" t="inlineStr">
         <is>
           <t>MK Pilihan Peminatan 2</t>
         </is>
       </c>
-      <c r="D211" s="21" t="inlineStr">
+      <c r="D214" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E211" s="19" t="inlineStr">
+      <c r="E214" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F211" s="19" t="inlineStr">
+      <c r="F214" s="19" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G211" s="19" t="inlineStr">
+      <c r="G214" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H211" s="19" t="inlineStr">
+      <c r="H214" s="19" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I211" s="19" t="inlineStr">
+      <c r="I214" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="16" customHeight="1">
-      <c r="A212" s="22" t="inlineStr">
+    <row r="215" ht="16" customHeight="1">
+      <c r="A215" s="22" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="B212" s="20" t="inlineStr">
+      <c r="B215" s="20" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C212" s="20" t="inlineStr">
+      <c r="C215" s="20" t="inlineStr">
         <is>
           <t>MK Pilihan Peminatan 3</t>
         </is>
       </c>
-      <c r="D212" s="22" t="inlineStr">
+      <c r="D215" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E212" s="20" t="inlineStr">
+      <c r="E215" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F212" s="20" t="inlineStr">
+      <c r="F215" s="20" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G212" s="20" t="inlineStr">
+      <c r="G215" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H212" s="20" t="inlineStr">
+      <c r="H215" s="20" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I212" s="20" t="inlineStr">
+      <c r="I215" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="16" customHeight="1">
-      <c r="A213" s="21" t="inlineStr">
+    <row r="216" ht="16" customHeight="1">
+      <c r="A216" s="21" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="B213" s="19" t="inlineStr">
+      <c r="B216" s="19" t="inlineStr">
         <is>
           <t>`STI-701`</t>
         </is>
       </c>
-      <c r="C213" s="19" t="inlineStr">
+      <c r="C216" s="19" t="inlineStr">
         <is>
           <t>Inovasi &amp; Startup Digital</t>
         </is>
       </c>
-      <c r="D213" s="21" t="inlineStr">
+      <c r="D216" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E213" s="19" t="inlineStr">
+      <c r="E216" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F213" s="19" t="inlineStr">
+      <c r="F216" s="19" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="G213" s="19" t="inlineStr">
+      <c r="G216" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="H213" s="19" t="inlineStr">
+      <c r="H216" s="19" t="inlineStr">
         <is>
           <t>**80%**</t>
         </is>
       </c>
-      <c r="I213" s="19" t="inlineStr">
+      <c r="I216" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="16" customHeight="1">
-      <c r="A214" s="22" t="inlineStr">
+    <row r="217" ht="16" customHeight="1">
+      <c r="A217" s="22" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="B214" s="20" t="inlineStr">
+      <c r="B217" s="20" t="inlineStr">
         <is>
           <t>`FST-610`</t>
         </is>
       </c>
-      <c r="C214" s="20" t="inlineStr">
+      <c r="C217" s="20" t="inlineStr">
         <is>
           <t>Capstone Project FSTI</t>
         </is>
       </c>
-      <c r="D214" s="22" t="inlineStr">
+      <c r="D217" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E214" s="20" t="inlineStr">
+      <c r="E217" s="20" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F214" s="20" t="inlineStr">
+      <c r="F217" s="20" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="G214" s="20" t="inlineStr">
+      <c r="G217" s="20" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="H214" s="20" t="inlineStr">
+      <c r="H217" s="20" t="inlineStr">
         <is>
           <t>**85%**</t>
         </is>
       </c>
-      <c r="I214" s="20" t="inlineStr">
+      <c r="I217" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="16" customHeight="1">
-      <c r="A215" s="21" t="inlineStr">
+    <row r="218" ht="16" customHeight="1">
+      <c r="A218" s="21" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="B215" s="19" t="inlineStr">
+      <c r="B218" s="19" t="inlineStr">
         <is>
           <t>`FST-612`</t>
         </is>
       </c>
-      <c r="C215" s="19" t="inlineStr">
+      <c r="C218" s="19" t="inlineStr">
         <is>
           <t>Praktik Kerja Lapangan(PKL)</t>
         </is>
       </c>
-      <c r="D215" s="21" t="inlineStr">
+      <c r="D218" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E215" s="19" t="inlineStr">
+      <c r="E218" s="19" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F215" s="19" t="inlineStr">
+      <c r="F218" s="19" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="G215" s="19" t="inlineStr">
+      <c r="G218" s="19" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="H215" s="19" t="inlineStr">
+      <c r="H218" s="19" t="inlineStr">
         <is>
           <t>**85%**</t>
         </is>
       </c>
-      <c r="I215" s="19" t="inlineStr">
+      <c r="I218" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="16" customHeight="1">
-      <c r="A216" s="22" t="inlineStr">
+    <row r="219" ht="16" customHeight="1">
+      <c r="A219" s="22" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="B216" s="20" t="inlineStr">
+      <c r="B219" s="20" t="inlineStr">
         <is>
           <t>`FST-613`</t>
         </is>
       </c>
-      <c r="C216" s="20" t="inlineStr">
+      <c r="C219" s="20" t="inlineStr">
         <is>
           <t>Pra-Skripsi / Sempro</t>
         </is>
       </c>
-      <c r="D216" s="22" t="inlineStr">
+      <c r="D219" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E216" s="20" t="inlineStr">
+      <c r="E219" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="F216" s="20" t="inlineStr">
+      <c r="F219" s="20" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G216" s="20" t="inlineStr">
+      <c r="G219" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="H216" s="20" t="inlineStr">
+      <c r="H219" s="20" t="inlineStr">
         <is>
           <t>**80%**</t>
         </is>
       </c>
-      <c r="I216" s="20" t="inlineStr">
+      <c r="I219" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="16" customHeight="1">
-      <c r="A217" s="21" t="inlineStr">
+    <row r="220" ht="16" customHeight="1">
+      <c r="A220" s="21" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="B217" s="19" t="inlineStr">
+      <c r="B220" s="19" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C217" s="19" t="inlineStr">
+      <c r="C220" s="19" t="inlineStr">
         <is>
           <t>MK Pilihan Peminatan 4</t>
         </is>
       </c>
-      <c r="D217" s="21" t="inlineStr">
+      <c r="D220" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E217" s="19" t="inlineStr">
+      <c r="E220" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F217" s="19" t="inlineStr">
+      <c r="F220" s="19" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G217" s="19" t="inlineStr">
+      <c r="G220" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H217" s="19" t="inlineStr">
+      <c r="H220" s="19" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I217" s="19" t="inlineStr">
+      <c r="I220" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="16" customHeight="1">
-      <c r="A218" s="22" t="inlineStr">
+    <row r="221" ht="16" customHeight="1">
+      <c r="A221" s="22" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="B218" s="20" t="inlineStr">
+      <c r="B221" s="20" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C218" s="20" t="inlineStr">
+      <c r="C221" s="20" t="inlineStr">
         <is>
           <t>MK Pilihan Peminatan 5</t>
         </is>
       </c>
-      <c r="D218" s="22" t="inlineStr">
+      <c r="D221" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E218" s="20" t="inlineStr">
+      <c r="E221" s="20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F218" s="20" t="inlineStr">
+      <c r="F221" s="20" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G218" s="20" t="inlineStr">
+      <c r="G221" s="20" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H218" s="20" t="inlineStr">
+      <c r="H221" s="20" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I218" s="20" t="inlineStr">
+      <c r="I221" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="16" customHeight="1">
-      <c r="A219" s="21" t="inlineStr">
+    <row r="222" ht="16" customHeight="1">
+      <c r="A222" s="21" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="B219" s="19" t="inlineStr">
+      <c r="B222" s="19" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C219" s="19" t="inlineStr">
+      <c r="C222" s="19" t="inlineStr">
         <is>
           <t>MK Pilihan Peminatan 6</t>
         </is>
       </c>
-      <c r="D219" s="21" t="inlineStr">
+      <c r="D222" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E219" s="19" t="inlineStr">
+      <c r="E222" s="19" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="F219" s="19" t="inlineStr">
+      <c r="F222" s="19" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G219" s="19" t="inlineStr">
+      <c r="G222" s="19" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="H219" s="19" t="inlineStr">
+      <c r="H222" s="19" t="inlineStr">
         <is>
           <t>**70%**</t>
         </is>
       </c>
-      <c r="I219" s="19" t="inlineStr">
+      <c r="I222" s="19" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="16" customHeight="1">
-      <c r="A220" s="22" t="inlineStr">
+    <row r="223" ht="16" customHeight="1">
+      <c r="A223" s="22" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="B220" s="20" t="inlineStr">
+      <c r="B223" s="20" t="inlineStr">
         <is>
           <t>`FST-714`</t>
         </is>
       </c>
-      <c r="C220" s="20" t="inlineStr">
+      <c r="C223" s="20" t="inlineStr">
         <is>
           <t>Skripsi / Tugas Akhir</t>
         </is>
       </c>
-      <c r="D220" s="22" t="inlineStr">
+      <c r="D223" s="22" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E220" s="20" t="inlineStr">
+      <c r="E223" s="20" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F220" s="20" t="inlineStr">
+      <c r="F223" s="20" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="G220" s="20" t="inlineStr">
+      <c r="G223" s="20" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="H220" s="20" t="inlineStr">
+      <c r="H223" s="20" t="inlineStr">
         <is>
           <t>**90%**</t>
         </is>
       </c>
-      <c r="I220" s="20" t="inlineStr">
+      <c r="I223" s="20" t="inlineStr">
         <is>
           <t>✅ Patuh IKU 7</t>
         </is>
@@ -15623,16 +15845,16 @@
     <mergeCell ref="A34:U34"/>
     <mergeCell ref="A82:I82"/>
     <mergeCell ref="A109:F109"/>
-    <mergeCell ref="A165:I165"/>
     <mergeCell ref="A15:U15"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A150:F150"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A71:U71"/>
     <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A168:I168"/>
     <mergeCell ref="A91:I91"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A100:I100"/>
-    <mergeCell ref="A148:F148"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20262,7 +20484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -20793,7 +21015,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2. MATRIKS SILANG CPL ↔ 19 BAHAN KAJIAN (BoK) IS2020 (APTIKOM v2.0)</t>
+          <t>2. MATRIKS SILANG CPL ↔ 21 BAHAN KAJIAN (BoK) IS2020 (APTIKOM v2.0)</t>
         </is>
       </c>
       <c r="B20" s="16" t="n"/>
@@ -21588,184 +21810,204 @@
       <c r="O40" s="19" t="inlineStr"/>
       <c r="P40" s="19" t="inlineStr"/>
     </row>
-    <row r="41"/>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>3. MATRIKS SILANG CPL ↔ 14 BAHAN KAJIAN UTAMA (BoK) IT2017 (APTIKOM)</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-      <c r="G42" s="16" t="n"/>
-      <c r="H42" s="16" t="n"/>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n"/>
-      <c r="M42" s="16" t="n"/>
-      <c r="N42" s="16" t="n"/>
-      <c r="O42" s="16" t="n"/>
-      <c r="P42" s="17" t="n"/>
-    </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="18" t="inlineStr">
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>**BK-IS20**</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>Ethics, Use and Implications for Society</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr"/>
+      <c r="E41" s="20" t="inlineStr"/>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr"/>
+      <c r="H41" s="20" t="inlineStr"/>
+      <c r="I41" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J41" s="20" t="inlineStr"/>
+      <c r="K41" s="20" t="inlineStr"/>
+      <c r="L41" s="20" t="inlineStr"/>
+      <c r="M41" s="20" t="inlineStr"/>
+      <c r="N41" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O41" s="20" t="inlineStr"/>
+      <c r="P41" s="20" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>**BK-IS21**</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>Internship and Professional Practice</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G42" s="19" t="inlineStr"/>
+      <c r="H42" s="19" t="inlineStr"/>
+      <c r="I42" s="19" t="inlineStr"/>
+      <c r="J42" s="19" t="inlineStr"/>
+      <c r="K42" s="19" t="inlineStr"/>
+      <c r="L42" s="19" t="inlineStr"/>
+      <c r="M42" s="19" t="inlineStr"/>
+      <c r="N42" s="19" t="inlineStr"/>
+      <c r="O42" s="19" t="inlineStr"/>
+      <c r="P42" s="19" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>3. MATRIKS SILANG CPL ↔ 15 BAHAN KAJIAN UTAMA (BoK) IT2017 (APTIKOM)</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
+      <c r="G44" s="16" t="n"/>
+      <c r="H44" s="16" t="n"/>
+      <c r="I44" s="16" t="n"/>
+      <c r="J44" s="16" t="n"/>
+      <c r="K44" s="16" t="n"/>
+      <c r="L44" s="16" t="n"/>
+      <c r="M44" s="16" t="n"/>
+      <c r="N44" s="16" t="n"/>
+      <c r="O44" s="16" t="n"/>
+      <c r="P44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>Kode BK</t>
         </is>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B45" s="18" t="inlineStr">
         <is>
           <t>Nama Bahan Kajian Utama IT2017</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C45" s="18" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="D43" s="18" t="inlineStr">
+      <c r="D45" s="18" t="inlineStr">
         <is>
           <t>KU1</t>
         </is>
       </c>
-      <c r="E43" s="18" t="inlineStr">
+      <c r="E45" s="18" t="inlineStr">
         <is>
           <t>KU2</t>
         </is>
       </c>
-      <c r="F43" s="18" t="inlineStr">
+      <c r="F45" s="18" t="inlineStr">
         <is>
           <t>KU3</t>
         </is>
       </c>
-      <c r="G43" s="18" t="inlineStr">
+      <c r="G45" s="18" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H43" s="18" t="inlineStr">
+      <c r="H45" s="18" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I43" s="18" t="inlineStr">
+      <c r="I45" s="18" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J43" s="18" t="inlineStr">
+      <c r="J45" s="18" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="K43" s="18" t="inlineStr">
+      <c r="K45" s="18" t="inlineStr">
         <is>
           <t>KK1</t>
         </is>
       </c>
-      <c r="L43" s="18" t="inlineStr">
+      <c r="L45" s="18" t="inlineStr">
         <is>
           <t>KK2</t>
         </is>
       </c>
-      <c r="M43" s="18" t="inlineStr">
+      <c r="M45" s="18" t="inlineStr">
         <is>
           <t>KK3</t>
         </is>
       </c>
-      <c r="N43" s="18" t="inlineStr">
+      <c r="N45" s="18" t="inlineStr">
         <is>
           <t>KK4</t>
         </is>
       </c>
-      <c r="O43" s="18" t="inlineStr">
+      <c r="O45" s="18" t="inlineStr">
         <is>
           <t>KK5</t>
         </is>
       </c>
-      <c r="P43" s="18" t="inlineStr">
+      <c r="P45" s="18" t="inlineStr">
         <is>
           <t>KK6</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>**BK-IT01**</t>
-        </is>
-      </c>
-      <c r="B44" s="19" t="inlineStr">
-        <is>
-          <t>Information Technology Fundamentals</t>
-        </is>
-      </c>
-      <c r="C44" s="21" t="inlineStr"/>
-      <c r="D44" s="21" t="inlineStr"/>
-      <c r="E44" s="19" t="inlineStr"/>
-      <c r="F44" s="19" t="inlineStr"/>
-      <c r="G44" s="19" t="inlineStr"/>
-      <c r="H44" s="19" t="inlineStr"/>
-      <c r="I44" s="19" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J44" s="19" t="inlineStr"/>
-      <c r="K44" s="19" t="inlineStr"/>
-      <c r="L44" s="19" t="inlineStr"/>
-      <c r="M44" s="19" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="N44" s="19" t="inlineStr"/>
-      <c r="O44" s="19" t="inlineStr"/>
-      <c r="P44" s="19" t="inlineStr"/>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>**BK-IT02**</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>Applied AI &amp; Intelligent Technologies</t>
-        </is>
-      </c>
-      <c r="C45" s="22" t="inlineStr"/>
-      <c r="D45" s="22" t="inlineStr"/>
-      <c r="E45" s="20" t="inlineStr"/>
-      <c r="F45" s="20" t="inlineStr"/>
-      <c r="G45" s="20" t="inlineStr"/>
-      <c r="H45" s="20" t="inlineStr"/>
-      <c r="I45" s="20" t="inlineStr"/>
-      <c r="J45" s="20" t="inlineStr"/>
-      <c r="K45" s="20" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="L45" s="20" t="inlineStr"/>
-      <c r="M45" s="20" t="inlineStr"/>
-      <c r="N45" s="20" t="inlineStr"/>
-      <c r="O45" s="20" t="inlineStr"/>
-      <c r="P45" s="20" t="inlineStr"/>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT03**</t>
+          <t>**BK-IT01**</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>Networking &amp; Communications</t>
+          <t>Information Technology Fundamentals</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr"/>
@@ -21794,12 +22036,12 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT04**</t>
+          <t>**BK-IT02**</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>Platform Technologies &amp; Web/Mobile</t>
+          <t>Applied AI &amp; Intelligent Technologies</t>
         </is>
       </c>
       <c r="C47" s="22" t="inlineStr"/>
@@ -21809,31 +22051,27 @@
       <c r="G47" s="20" t="inlineStr"/>
       <c r="H47" s="20" t="inlineStr"/>
       <c r="I47" s="20" t="inlineStr"/>
-      <c r="J47" s="20" t="inlineStr">
+      <c r="J47" s="20" t="inlineStr"/>
+      <c r="K47" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="K47" s="20" t="inlineStr"/>
       <c r="L47" s="20" t="inlineStr"/>
       <c r="M47" s="20" t="inlineStr"/>
       <c r="N47" s="20" t="inlineStr"/>
-      <c r="O47" s="20" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="O47" s="20" t="inlineStr"/>
       <c r="P47" s="20" t="inlineStr"/>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT05**</t>
+          <t>**BK-IT03**</t>
         </is>
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>Cloud Computing &amp; Virtualization</t>
+          <t>Networking &amp; Communications</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr"/>
@@ -21862,12 +22100,12 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT06**</t>
+          <t>**BK-IT04**</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>Cybersecurity Principles &amp; Defense</t>
+          <t>Platform Technologies &amp; Web/Mobile</t>
         </is>
       </c>
       <c r="C49" s="22" t="inlineStr"/>
@@ -21876,36 +22114,32 @@
       <c r="F49" s="20" t="inlineStr"/>
       <c r="G49" s="20" t="inlineStr"/>
       <c r="H49" s="20" t="inlineStr"/>
-      <c r="I49" s="20" t="inlineStr">
+      <c r="I49" s="20" t="inlineStr"/>
+      <c r="J49" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="J49" s="20" t="inlineStr"/>
       <c r="K49" s="20" t="inlineStr"/>
       <c r="L49" s="20" t="inlineStr"/>
-      <c r="M49" s="20" t="inlineStr">
+      <c r="M49" s="20" t="inlineStr"/>
+      <c r="N49" s="20" t="inlineStr"/>
+      <c r="O49" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="N49" s="20" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O49" s="20" t="inlineStr"/>
       <c r="P49" s="20" t="inlineStr"/>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT07**</t>
+          <t>**BK-IT05**</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>System Integration and Architecture</t>
+          <t>Cloud Computing &amp; Virtualization</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr"/>
@@ -21928,22 +22162,18 @@
         </is>
       </c>
       <c r="N50" s="19" t="inlineStr"/>
-      <c r="O50" s="19" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="O50" s="19" t="inlineStr"/>
       <c r="P50" s="19" t="inlineStr"/>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT08**</t>
+          <t>**BK-IT06**</t>
         </is>
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>IT Service Management &amp; Governance</t>
+          <t>Cybersecurity Principles &amp; Defense</t>
         </is>
       </c>
       <c r="C51" s="22" t="inlineStr"/>
@@ -21960,7 +22190,11 @@
       <c r="J51" s="20" t="inlineStr"/>
       <c r="K51" s="20" t="inlineStr"/>
       <c r="L51" s="20" t="inlineStr"/>
-      <c r="M51" s="20" t="inlineStr"/>
+      <c r="M51" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
           <t>✅</t>
@@ -21972,12 +22206,12 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT09**</t>
+          <t>**BK-IT07**</t>
         </is>
       </c>
       <c r="B52" s="19" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Information Visualization</t>
+          <t>System Integration and Architecture</t>
         </is>
       </c>
       <c r="C52" s="21" t="inlineStr"/>
@@ -21986,32 +22220,36 @@
       <c r="F52" s="19" t="inlineStr"/>
       <c r="G52" s="19" t="inlineStr"/>
       <c r="H52" s="19" t="inlineStr"/>
-      <c r="I52" s="19" t="inlineStr"/>
-      <c r="J52" s="19" t="inlineStr">
+      <c r="I52" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
+      <c r="J52" s="19" t="inlineStr"/>
       <c r="K52" s="19" t="inlineStr"/>
-      <c r="L52" s="19" t="inlineStr">
+      <c r="L52" s="19" t="inlineStr"/>
+      <c r="M52" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="M52" s="19" t="inlineStr"/>
       <c r="N52" s="19" t="inlineStr"/>
-      <c r="O52" s="19" t="inlineStr"/>
+      <c r="O52" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="P52" s="19" t="inlineStr"/>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT10**</t>
+          <t>**BK-IT08**</t>
         </is>
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>User Experience &amp; Interaction Design</t>
+          <t>IT Service Management &amp; Governance</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr"/>
@@ -22020,32 +22258,32 @@
       <c r="F53" s="20" t="inlineStr"/>
       <c r="G53" s="20" t="inlineStr"/>
       <c r="H53" s="20" t="inlineStr"/>
-      <c r="I53" s="20" t="inlineStr"/>
-      <c r="J53" s="20" t="inlineStr">
+      <c r="I53" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
+      <c r="J53" s="20" t="inlineStr"/>
       <c r="K53" s="20" t="inlineStr"/>
       <c r="L53" s="20" t="inlineStr"/>
       <c r="M53" s="20" t="inlineStr"/>
-      <c r="N53" s="20" t="inlineStr"/>
-      <c r="O53" s="20" t="inlineStr">
+      <c r="N53" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
+      <c r="O53" s="20" t="inlineStr"/>
       <c r="P53" s="20" t="inlineStr"/>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT11**</t>
+          <t>**BK-IT09**</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>Software Development Practices</t>
+          <t>Data Analytics &amp; Information Visualization</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr"/>
@@ -22061,25 +22299,25 @@
         </is>
       </c>
       <c r="K54" s="19" t="inlineStr"/>
-      <c r="L54" s="19" t="inlineStr"/>
+      <c r="L54" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="M54" s="19" t="inlineStr"/>
       <c r="N54" s="19" t="inlineStr"/>
-      <c r="O54" s="19" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="O54" s="19" t="inlineStr"/>
       <c r="P54" s="19" t="inlineStr"/>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT12**</t>
+          <t>**BK-IT10**</t>
         </is>
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>IT Risk Management and Compliance</t>
+          <t>User Experience &amp; Interaction Design</t>
         </is>
       </c>
       <c r="C55" s="22" t="inlineStr"/>
@@ -22089,27 +22327,31 @@
       <c r="G55" s="20" t="inlineStr"/>
       <c r="H55" s="20" t="inlineStr"/>
       <c r="I55" s="20" t="inlineStr"/>
-      <c r="J55" s="20" t="inlineStr"/>
+      <c r="J55" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="K55" s="20" t="inlineStr"/>
       <c r="L55" s="20" t="inlineStr"/>
       <c r="M55" s="20" t="inlineStr"/>
-      <c r="N55" s="20" t="inlineStr">
+      <c r="N55" s="20" t="inlineStr"/>
+      <c r="O55" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="O55" s="20" t="inlineStr"/>
       <c r="P55" s="20" t="inlineStr"/>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>**BK-IT13**</t>
+          <t>**BK-IT11**</t>
         </is>
       </c>
       <c r="B56" s="19" t="inlineStr">
         <is>
-          <t>Technology Entrepreneurship</t>
+          <t>Software Development Practices</t>
         </is>
       </c>
       <c r="C56" s="21" t="inlineStr"/>
@@ -22119,27 +22361,31 @@
       <c r="G56" s="19" t="inlineStr"/>
       <c r="H56" s="19" t="inlineStr"/>
       <c r="I56" s="19" t="inlineStr"/>
-      <c r="J56" s="19" t="inlineStr"/>
+      <c r="J56" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="K56" s="19" t="inlineStr"/>
       <c r="L56" s="19" t="inlineStr"/>
       <c r="M56" s="19" t="inlineStr"/>
       <c r="N56" s="19" t="inlineStr"/>
-      <c r="O56" s="19" t="inlineStr"/>
-      <c r="P56" s="19" t="inlineStr">
+      <c r="O56" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
+      <c r="P56" s="19" t="inlineStr"/>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="20" t="inlineStr">
         <is>
-          <t>**BK-IT14**</t>
+          <t>**BK-IT12**</t>
         </is>
       </c>
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>IoT and Embedded Smart Systems</t>
+          <t>IT Risk Management and Compliance</t>
         </is>
       </c>
       <c r="C57" s="22" t="inlineStr"/>
@@ -22150,741 +22396,843 @@
       <c r="H57" s="20" t="inlineStr"/>
       <c r="I57" s="20" t="inlineStr"/>
       <c r="J57" s="20" t="inlineStr"/>
-      <c r="K57" s="20" t="inlineStr">
+      <c r="K57" s="20" t="inlineStr"/>
+      <c r="L57" s="20" t="inlineStr"/>
+      <c r="M57" s="20" t="inlineStr"/>
+      <c r="N57" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="L57" s="20" t="inlineStr"/>
-      <c r="M57" s="20" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="N57" s="20" t="inlineStr"/>
       <c r="O57" s="20" t="inlineStr"/>
       <c r="P57" s="20" t="inlineStr"/>
     </row>
-    <row r="58"/>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="15" t="inlineStr">
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>**BK-IT13**</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>Technology Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C58" s="21" t="inlineStr"/>
+      <c r="D58" s="21" t="inlineStr"/>
+      <c r="E58" s="19" t="inlineStr"/>
+      <c r="F58" s="19" t="inlineStr"/>
+      <c r="G58" s="19" t="inlineStr"/>
+      <c r="H58" s="19" t="inlineStr"/>
+      <c r="I58" s="19" t="inlineStr"/>
+      <c r="J58" s="19" t="inlineStr"/>
+      <c r="K58" s="19" t="inlineStr"/>
+      <c r="L58" s="19" t="inlineStr"/>
+      <c r="M58" s="19" t="inlineStr"/>
+      <c r="N58" s="19" t="inlineStr"/>
+      <c r="O58" s="19" t="inlineStr"/>
+      <c r="P58" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>**BK-IT14**</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>IoT and Embedded Smart Systems</t>
+        </is>
+      </c>
+      <c r="C59" s="22" t="inlineStr"/>
+      <c r="D59" s="22" t="inlineStr"/>
+      <c r="E59" s="20" t="inlineStr"/>
+      <c r="F59" s="20" t="inlineStr"/>
+      <c r="G59" s="20" t="inlineStr"/>
+      <c r="H59" s="20" t="inlineStr"/>
+      <c r="I59" s="20" t="inlineStr"/>
+      <c r="J59" s="20" t="inlineStr"/>
+      <c r="K59" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="L59" s="20" t="inlineStr"/>
+      <c r="M59" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N59" s="20" t="inlineStr"/>
+      <c r="O59" s="20" t="inlineStr"/>
+      <c r="P59" s="20" t="inlineStr"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>**BK-IT15**</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>Global Professional Practice</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D60" s="21" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F60" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G60" s="19" t="inlineStr"/>
+      <c r="H60" s="19" t="inlineStr"/>
+      <c r="I60" s="19" t="inlineStr"/>
+      <c r="J60" s="19" t="inlineStr"/>
+      <c r="K60" s="19" t="inlineStr"/>
+      <c r="L60" s="19" t="inlineStr"/>
+      <c r="M60" s="19" t="inlineStr"/>
+      <c r="N60" s="19" t="inlineStr"/>
+      <c r="O60" s="19" t="inlineStr"/>
+      <c r="P60" s="19" t="inlineStr"/>
+    </row>
+    <row r="61"/>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>4. MATRIKS PEMETAAN CPL ↔ 4 PROFIL LULUSAN (PL)</t>
         </is>
       </c>
-      <c r="B59" s="16" t="n"/>
-      <c r="C59" s="16" t="n"/>
-      <c r="D59" s="16" t="n"/>
-      <c r="E59" s="16" t="n"/>
-      <c r="F59" s="16" t="n"/>
-      <c r="G59" s="16" t="n"/>
-      <c r="H59" s="16" t="n"/>
-      <c r="I59" s="16" t="n"/>
-      <c r="J59" s="16" t="n"/>
-      <c r="K59" s="16" t="n"/>
-      <c r="L59" s="16" t="n"/>
-      <c r="M59" s="16" t="n"/>
-      <c r="N59" s="16" t="n"/>
-      <c r="O59" s="16" t="n"/>
-      <c r="P59" s="17" t="n"/>
-    </row>
-    <row r="60" ht="26" customHeight="1">
-      <c r="A60" s="18" t="inlineStr">
+      <c r="B62" s="16" t="n"/>
+      <c r="C62" s="16" t="n"/>
+      <c r="D62" s="16" t="n"/>
+      <c r="E62" s="16" t="n"/>
+      <c r="F62" s="16" t="n"/>
+      <c r="G62" s="16" t="n"/>
+      <c r="H62" s="16" t="n"/>
+      <c r="I62" s="16" t="n"/>
+      <c r="J62" s="16" t="n"/>
+      <c r="K62" s="16" t="n"/>
+      <c r="L62" s="16" t="n"/>
+      <c r="M62" s="16" t="n"/>
+      <c r="N62" s="16" t="n"/>
+      <c r="O62" s="16" t="n"/>
+      <c r="P62" s="17" t="n"/>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="18" t="inlineStr">
         <is>
           <t>Profil Lulusan</t>
         </is>
       </c>
-      <c r="B60" s="18" t="inlineStr">
+      <c r="B63" s="18" t="inlineStr">
         <is>
           <t>Peminatan Terkait</t>
         </is>
       </c>
-      <c r="C60" s="18" t="inlineStr">
+      <c r="C63" s="18" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="D60" s="18" t="inlineStr">
+      <c r="D63" s="18" t="inlineStr">
         <is>
           <t>KU1</t>
         </is>
       </c>
-      <c r="E60" s="18" t="inlineStr">
+      <c r="E63" s="18" t="inlineStr">
         <is>
           <t>KU2</t>
         </is>
       </c>
-      <c r="F60" s="18" t="inlineStr">
+      <c r="F63" s="18" t="inlineStr">
         <is>
           <t>KU3</t>
         </is>
       </c>
-      <c r="G60" s="18" t="inlineStr">
+      <c r="G63" s="18" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H60" s="18" t="inlineStr">
+      <c r="H63" s="18" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I60" s="18" t="inlineStr">
+      <c r="I63" s="18" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J60" s="18" t="inlineStr">
+      <c r="J63" s="18" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="K60" s="18" t="inlineStr">
+      <c r="K63" s="18" t="inlineStr">
         <is>
           <t>KK1</t>
         </is>
       </c>
-      <c r="L60" s="18" t="inlineStr">
+      <c r="L63" s="18" t="inlineStr">
         <is>
           <t>KK2</t>
         </is>
       </c>
-      <c r="M60" s="18" t="inlineStr">
+      <c r="M63" s="18" t="inlineStr">
         <is>
           <t>KK3</t>
         </is>
       </c>
-      <c r="N60" s="18" t="inlineStr">
+      <c r="N63" s="18" t="inlineStr">
         <is>
           <t>KK4</t>
         </is>
       </c>
-      <c r="O60" s="18" t="inlineStr">
+      <c r="O63" s="18" t="inlineStr">
         <is>
           <t>KK5</t>
         </is>
       </c>
-      <c r="P60" s="18" t="inlineStr">
+      <c r="P63" s="18" t="inlineStr">
         <is>
           <t>KK6</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>**PL-1: Intelligent IS Developer &amp; AI Engineer**</t>
         </is>
       </c>
-      <c r="B61" s="21" t="inlineStr">
+      <c r="B64" s="21" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C61" s="21" t="inlineStr">
+      <c r="C64" s="21" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D61" s="21" t="inlineStr">
+      <c r="D64" s="21" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="E61" s="19" t="inlineStr">
+      <c r="E64" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="F61" s="19" t="inlineStr">
+      <c r="F64" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="G61" s="19" t="inlineStr">
+      <c r="G64" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="H61" s="19" t="inlineStr">
+      <c r="H64" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="I61" s="19" t="inlineStr"/>
-      <c r="J61" s="19" t="inlineStr">
+      <c r="I64" s="19" t="inlineStr"/>
+      <c r="J64" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="K61" s="19" t="inlineStr">
+      <c r="K64" s="19" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="L61" s="19" t="inlineStr">
+      <c r="L64" s="19" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="M61" s="19" t="inlineStr"/>
-      <c r="N61" s="19" t="inlineStr"/>
-      <c r="O61" s="19" t="inlineStr">
+      <c r="M64" s="19" t="inlineStr"/>
+      <c r="N64" s="19" t="inlineStr"/>
+      <c r="O64" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="P61" s="19" t="inlineStr"/>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="20" t="inlineStr">
+      <c r="P64" s="19" t="inlineStr"/>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="20" t="inlineStr">
         <is>
           <t>**PL-2: Cloud Infrastructure &amp; Cybersecurity Specialist**</t>
         </is>
       </c>
-      <c r="B62" s="22" t="inlineStr">
+      <c r="B65" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C62" s="22" t="inlineStr">
+      <c r="C65" s="22" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D62" s="22" t="inlineStr">
+      <c r="D65" s="22" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="E62" s="20" t="inlineStr">
+      <c r="E65" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="F62" s="20" t="inlineStr">
+      <c r="F65" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="G62" s="20" t="inlineStr">
+      <c r="G65" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="H62" s="20" t="inlineStr"/>
-      <c r="I62" s="20" t="inlineStr">
+      <c r="H65" s="20" t="inlineStr"/>
+      <c r="I65" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="J62" s="20" t="inlineStr"/>
-      <c r="K62" s="20" t="inlineStr"/>
-      <c r="L62" s="20" t="inlineStr"/>
-      <c r="M62" s="20" t="inlineStr">
+      <c r="J65" s="20" t="inlineStr"/>
+      <c r="K65" s="20" t="inlineStr"/>
+      <c r="L65" s="20" t="inlineStr"/>
+      <c r="M65" s="20" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="N62" s="20" t="inlineStr">
+      <c r="N65" s="20" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="O62" s="20" t="inlineStr"/>
-      <c r="P62" s="20" t="inlineStr"/>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="19" t="inlineStr">
+      <c r="O65" s="20" t="inlineStr"/>
+      <c r="P65" s="20" t="inlineStr"/>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>**PL-3: UI/UX Designer &amp; Digital Platform Engineer**</t>
         </is>
       </c>
-      <c r="B63" s="21" t="inlineStr">
+      <c r="B66" s="21" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C63" s="21" t="inlineStr">
+      <c r="C66" s="21" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D63" s="21" t="inlineStr">
+      <c r="D66" s="21" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="E63" s="19" t="inlineStr">
+      <c r="E66" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr">
+      <c r="F66" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="G63" s="19" t="inlineStr"/>
-      <c r="H63" s="19" t="inlineStr">
+      <c r="G66" s="19" t="inlineStr"/>
+      <c r="H66" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="I63" s="19" t="inlineStr"/>
-      <c r="J63" s="19" t="inlineStr">
+      <c r="I66" s="19" t="inlineStr"/>
+      <c r="J66" s="19" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="K63" s="19" t="inlineStr"/>
-      <c r="L63" s="19" t="inlineStr"/>
-      <c r="M63" s="19" t="inlineStr"/>
-      <c r="N63" s="19" t="inlineStr"/>
-      <c r="O63" s="19" t="inlineStr">
+      <c r="K66" s="19" t="inlineStr"/>
+      <c r="L66" s="19" t="inlineStr"/>
+      <c r="M66" s="19" t="inlineStr"/>
+      <c r="N66" s="19" t="inlineStr"/>
+      <c r="O66" s="19" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="P63" s="19" t="inlineStr">
+      <c r="P66" s="19" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="20" t="inlineStr">
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="20" t="inlineStr">
         <is>
           <t>**PL-4: Digital Technopreneur &amp; IT Product Innovator**</t>
         </is>
       </c>
-      <c r="B64" s="20" t="inlineStr">
+      <c r="B67" s="20" t="inlineStr">
         <is>
           <t>P3 / P1 / P2</t>
         </is>
       </c>
-      <c r="C64" s="22" t="inlineStr">
+      <c r="C67" s="22" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D64" s="22" t="inlineStr">
+      <c r="D67" s="22" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="E64" s="20" t="inlineStr">
+      <c r="E67" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="F64" s="20" t="inlineStr">
+      <c r="F67" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="G64" s="20" t="inlineStr"/>
-      <c r="H64" s="20" t="inlineStr">
+      <c r="G67" s="20" t="inlineStr"/>
+      <c r="H67" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="I64" s="20" t="inlineStr">
+      <c r="I67" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="J64" s="20" t="inlineStr">
+      <c r="J67" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="K64" s="20" t="inlineStr">
+      <c r="K67" s="20" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="L64" s="20" t="inlineStr"/>
-      <c r="M64" s="20" t="inlineStr"/>
-      <c r="N64" s="20" t="inlineStr"/>
-      <c r="O64" s="20" t="inlineStr">
+      <c r="L67" s="20" t="inlineStr"/>
+      <c r="M67" s="20" t="inlineStr"/>
+      <c r="N67" s="20" t="inlineStr"/>
+      <c r="O67" s="20" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="P64" s="20" t="inlineStr">
+      <c r="P67" s="20" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
-    <row r="65"/>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="15" t="inlineStr">
+    <row r="68"/>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="15" t="inlineStr">
         <is>
           <t>5. MATRIKS PEMETAAN CPL ↔ 3 JALUR PEMINATAN</t>
         </is>
       </c>
-      <c r="B66" s="16" t="n"/>
-      <c r="C66" s="16" t="n"/>
-      <c r="D66" s="16" t="n"/>
-      <c r="E66" s="16" t="n"/>
-      <c r="F66" s="16" t="n"/>
-      <c r="G66" s="16" t="n"/>
-      <c r="H66" s="16" t="n"/>
-      <c r="I66" s="16" t="n"/>
-      <c r="J66" s="16" t="n"/>
-      <c r="K66" s="16" t="n"/>
-      <c r="L66" s="16" t="n"/>
-      <c r="M66" s="16" t="n"/>
-      <c r="N66" s="16" t="n"/>
-      <c r="O66" s="16" t="n"/>
-      <c r="P66" s="17" t="n"/>
-    </row>
-    <row r="67" ht="26" customHeight="1">
-      <c r="A67" s="18" t="inlineStr">
+      <c r="B69" s="16" t="n"/>
+      <c r="C69" s="16" t="n"/>
+      <c r="D69" s="16" t="n"/>
+      <c r="E69" s="16" t="n"/>
+      <c r="F69" s="16" t="n"/>
+      <c r="G69" s="16" t="n"/>
+      <c r="H69" s="16" t="n"/>
+      <c r="I69" s="16" t="n"/>
+      <c r="J69" s="16" t="n"/>
+      <c r="K69" s="16" t="n"/>
+      <c r="L69" s="16" t="n"/>
+      <c r="M69" s="16" t="n"/>
+      <c r="N69" s="16" t="n"/>
+      <c r="O69" s="16" t="n"/>
+      <c r="P69" s="17" t="n"/>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="18" t="inlineStr">
         <is>
           <t>Kode Peminatan</t>
         </is>
       </c>
-      <c r="B67" s="18" t="inlineStr">
+      <c r="B70" s="18" t="inlineStr">
         <is>
           <t>Nomenklatur Jalur Peminatan</t>
         </is>
       </c>
-      <c r="C67" s="18" t="inlineStr">
+      <c r="C70" s="18" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="D67" s="18" t="inlineStr">
+      <c r="D70" s="18" t="inlineStr">
         <is>
           <t>KU1</t>
         </is>
       </c>
-      <c r="E67" s="18" t="inlineStr">
+      <c r="E70" s="18" t="inlineStr">
         <is>
           <t>KU2</t>
         </is>
       </c>
-      <c r="F67" s="18" t="inlineStr">
+      <c r="F70" s="18" t="inlineStr">
         <is>
           <t>KU3</t>
         </is>
       </c>
-      <c r="G67" s="18" t="inlineStr">
+      <c r="G70" s="18" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H67" s="18" t="inlineStr">
+      <c r="H70" s="18" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I67" s="18" t="inlineStr">
+      <c r="I70" s="18" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J67" s="18" t="inlineStr">
+      <c r="J70" s="18" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="K67" s="18" t="inlineStr">
+      <c r="K70" s="18" t="inlineStr">
         <is>
           <t>KK1</t>
         </is>
       </c>
-      <c r="L67" s="18" t="inlineStr">
+      <c r="L70" s="18" t="inlineStr">
         <is>
           <t>KK2</t>
         </is>
       </c>
-      <c r="M67" s="18" t="inlineStr">
+      <c r="M70" s="18" t="inlineStr">
         <is>
           <t>KK3</t>
         </is>
       </c>
-      <c r="N67" s="18" t="inlineStr">
+      <c r="N70" s="18" t="inlineStr">
         <is>
           <t>KK4</t>
         </is>
       </c>
-      <c r="O67" s="18" t="inlineStr">
+      <c r="O70" s="18" t="inlineStr">
         <is>
           <t>KK5</t>
         </is>
       </c>
-      <c r="P67" s="18" t="inlineStr">
+      <c r="P70" s="18" t="inlineStr">
         <is>
           <t>KK6</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="21" t="inlineStr">
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="21" t="inlineStr">
         <is>
           <t>**P1**</t>
         </is>
       </c>
-      <c r="B68" s="19" t="inlineStr">
+      <c r="B71" s="19" t="inlineStr">
         <is>
           <t>Integrated Smart Systems</t>
         </is>
       </c>
-      <c r="C68" s="21" t="inlineStr">
+      <c r="C71" s="21" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D68" s="21" t="inlineStr">
+      <c r="D71" s="21" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="E68" s="19" t="inlineStr">
+      <c r="E71" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="F68" s="19" t="inlineStr">
+      <c r="F71" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="G68" s="19" t="inlineStr">
+      <c r="G71" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="H68" s="19" t="inlineStr">
+      <c r="H71" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="I68" s="19" t="inlineStr"/>
-      <c r="J68" s="19" t="inlineStr">
+      <c r="I71" s="19" t="inlineStr"/>
+      <c r="J71" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="K68" s="19" t="inlineStr">
+      <c r="K71" s="19" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="L68" s="19" t="inlineStr">
+      <c r="L71" s="19" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="M68" s="19" t="inlineStr"/>
-      <c r="N68" s="19" t="inlineStr"/>
-      <c r="O68" s="19" t="inlineStr"/>
-      <c r="P68" s="19" t="inlineStr"/>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="22" t="inlineStr">
+      <c r="M71" s="19" t="inlineStr"/>
+      <c r="N71" s="19" t="inlineStr"/>
+      <c r="O71" s="19" t="inlineStr"/>
+      <c r="P71" s="19" t="inlineStr"/>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="22" t="inlineStr">
         <is>
           <t>**P2**</t>
         </is>
       </c>
-      <c r="B69" s="20" t="inlineStr">
+      <c r="B72" s="20" t="inlineStr">
         <is>
           <t>Cloud Infrastructure &amp; Cybersecurity</t>
         </is>
       </c>
-      <c r="C69" s="22" t="inlineStr">
+      <c r="C72" s="22" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D69" s="22" t="inlineStr">
+      <c r="D72" s="22" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="E69" s="20" t="inlineStr">
+      <c r="E72" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="F69" s="20" t="inlineStr">
+      <c r="F72" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="G69" s="20" t="inlineStr">
+      <c r="G72" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="H69" s="20" t="inlineStr"/>
-      <c r="I69" s="20" t="inlineStr">
+      <c r="H72" s="20" t="inlineStr"/>
+      <c r="I72" s="20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="J69" s="20" t="inlineStr"/>
-      <c r="K69" s="20" t="inlineStr"/>
-      <c r="L69" s="20" t="inlineStr"/>
-      <c r="M69" s="20" t="inlineStr">
+      <c r="J72" s="20" t="inlineStr"/>
+      <c r="K72" s="20" t="inlineStr"/>
+      <c r="L72" s="20" t="inlineStr"/>
+      <c r="M72" s="20" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="N69" s="20" t="inlineStr">
+      <c r="N72" s="20" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="O69" s="20" t="inlineStr"/>
-      <c r="P69" s="20" t="inlineStr"/>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="21" t="inlineStr">
+      <c r="O72" s="20" t="inlineStr"/>
+      <c r="P72" s="20" t="inlineStr"/>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="21" t="inlineStr">
         <is>
           <t>**P3**</t>
         </is>
       </c>
-      <c r="B70" s="19" t="inlineStr">
+      <c r="B73" s="19" t="inlineStr">
         <is>
           <t>Digital Platform Engineering</t>
         </is>
       </c>
-      <c r="C70" s="21" t="inlineStr">
+      <c r="C73" s="21" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="D70" s="21" t="inlineStr">
+      <c r="D73" s="21" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="E70" s="19" t="inlineStr">
+      <c r="E73" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="F70" s="19" t="inlineStr">
+      <c r="F73" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="G70" s="19" t="inlineStr">
+      <c r="G73" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="H70" s="19" t="inlineStr">
+      <c r="H73" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="I70" s="19" t="inlineStr"/>
-      <c r="J70" s="19" t="inlineStr">
+      <c r="I73" s="19" t="inlineStr"/>
+      <c r="J73" s="19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="K70" s="19" t="inlineStr"/>
-      <c r="L70" s="19" t="inlineStr"/>
-      <c r="M70" s="19" t="inlineStr"/>
-      <c r="N70" s="19" t="inlineStr"/>
-      <c r="O70" s="19" t="inlineStr">
+      <c r="K73" s="19" t="inlineStr"/>
+      <c r="L73" s="19" t="inlineStr"/>
+      <c r="M73" s="19" t="inlineStr"/>
+      <c r="N73" s="19" t="inlineStr"/>
+      <c r="O73" s="19" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="P70" s="19" t="inlineStr">
+      <c r="P73" s="19" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="15" t="inlineStr">
+    <row r="74"/>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="15" t="inlineStr">
         <is>
           <t>6. MATRIKS KESELARASAN CPL ↔ VISI KEILMUAN VMTS 2045</t>
         </is>
       </c>
-      <c r="B72" s="16" t="n"/>
-      <c r="C72" s="16" t="n"/>
-      <c r="D72" s="16" t="n"/>
-      <c r="E72" s="16" t="n"/>
-      <c r="F72" s="17" t="n"/>
-    </row>
-    <row r="73" ht="26" customHeight="1">
-      <c r="A73" s="18" t="inlineStr">
+      <c r="B75" s="16" t="n"/>
+      <c r="C75" s="16" t="n"/>
+      <c r="D75" s="16" t="n"/>
+      <c r="E75" s="16" t="n"/>
+      <c r="F75" s="17" t="n"/>
+    </row>
+    <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="18" t="inlineStr">
         <is>
           <t>Elemen Kunci VMTS SISTEKIN 2045</t>
         </is>
       </c>
-      <c r="B73" s="18" t="inlineStr">
+      <c r="B76" s="18" t="inlineStr">
         <is>
           <t>CPL yang Selaras &amp; Mengakomodasi</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="19" t="inlineStr">
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>*"Sistem dan teknologi informasi cerdas"*</t>
         </is>
       </c>
-      <c r="B74" s="19" t="inlineStr">
+      <c r="B77" s="19" t="inlineStr">
         <is>
           <t>`P1`, `P2`, `KK1`, `KK2`</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="20" t="inlineStr">
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="20" t="inlineStr">
         <is>
           <t>*"Terintegrasi kecerdasan artifisial"*</t>
         </is>
       </c>
-      <c r="B75" s="20" t="inlineStr">
+      <c r="B78" s="20" t="inlineStr">
         <is>
           <t>`P1`, `P2`, `KK1`, `KK2`, `KK3`</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="19" t="inlineStr">
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="19" t="inlineStr">
         <is>
           <t>*"Technopreneurship berbasis kebutuhan masyarakat"*</t>
         </is>
       </c>
-      <c r="B76" s="19" t="inlineStr">
+      <c r="B79" s="19" t="inlineStr">
         <is>
           <t>`P2`, `KK5`, `KK6`</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="20" t="inlineStr">
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>*"Bermutu, mandiri, dan bermartabat"*</t>
         </is>
       </c>
-      <c r="B77" s="20" t="inlineStr">
+      <c r="B80" s="20" t="inlineStr">
         <is>
           <t>`S1`, `KU1`, `KU3`, `P3`, `KK4`</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="19" t="inlineStr">
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>*"Berwawasan global"*</t>
         </is>
       </c>
-      <c r="B78" s="19" t="inlineStr">
+      <c r="B81" s="19" t="inlineStr">
         <is>
           <t>`KU2`, `P3`, `KK3`, `KK5`</t>
         </is>
@@ -22893,13 +23241,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A42:P42"/>
-    <mergeCell ref="A66:P66"/>
+    <mergeCell ref="A44:P44"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A69:P69"/>
+    <mergeCell ref="A62:P62"/>
     <mergeCell ref="A20:P20"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A59:P59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
+++ b/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
@@ -7252,7 +7252,7 @@
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>`STI-201`</t>
+          <t>`STI-204`</t>
         </is>
       </c>
       <c r="C25" s="19" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`STI-205`</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>`STI-301`</t>
+          <t>`STI-306`</t>
         </is>
       </c>
       <c r="C36" s="19" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>`STI-302`</t>
+          <t>`STI-307`</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>`STI-303`</t>
+          <t>`STI-308`</t>
         </is>
       </c>
       <c r="C38" s="19" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>`STI-304`</t>
+          <t>`STI-309`</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>`STI-305`</t>
+          <t>`STI-310`</t>
         </is>
       </c>
       <c r="C40" s="19" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>`STI-306`</t>
+          <t>`STI-311`</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`STI-312`</t>
         </is>
       </c>
       <c r="C42" s="19" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>`STI-401`</t>
+          <t>`STI-413`</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>`STI-402`</t>
+          <t>`STI-415`</t>
         </is>
       </c>
       <c r="C44" s="19" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>`STI-407`</t>
+          <t>`STI-416`</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>`STI-404`</t>
+          <t>`STI-417`</t>
         </is>
       </c>
       <c r="C46" s="19" t="inlineStr">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>`STI-405`</t>
+          <t>`STI-418`</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>`STI-403`</t>
+          <t>`STI-414`</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
-          <t>`STI-501`</t>
+          <t>`STI-519`</t>
         </is>
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t>Deep Learning &amp; Neural Net</t>
+          <t>Keamanan Informasi Lanjut</t>
         </is>
       </c>
       <c r="D55" s="21" t="inlineStr">
@@ -8917,35 +8917,39 @@
       <c r="H55" s="19" t="inlineStr"/>
       <c r="I55" s="19" t="inlineStr"/>
       <c r="J55" s="19" t="inlineStr"/>
-      <c r="K55" s="19" t="inlineStr"/>
+      <c r="K55" s="19" t="inlineStr">
+        <is>
+          <t>**M**</t>
+        </is>
+      </c>
       <c r="L55" s="19" t="inlineStr"/>
-      <c r="M55" s="19" t="inlineStr">
-        <is>
-          <t>**R**</t>
-        </is>
-      </c>
-      <c r="N55" s="19" t="inlineStr">
-        <is>
-          <t>**R**</t>
-        </is>
-      </c>
-      <c r="O55" s="19" t="inlineStr"/>
-      <c r="P55" s="19" t="inlineStr"/>
+      <c r="M55" s="19" t="inlineStr"/>
+      <c r="N55" s="19" t="inlineStr"/>
+      <c r="O55" s="19" t="inlineStr">
+        <is>
+          <t>**M**</t>
+        </is>
+      </c>
+      <c r="P55" s="19" t="inlineStr">
+        <is>
+          <t>**M**</t>
+        </is>
+      </c>
       <c r="Q55" s="19" t="inlineStr"/>
       <c r="R55" s="19" t="inlineStr"/>
       <c r="S55" s="19" t="inlineStr">
         <is>
-          <t>PL-1</t>
+          <t>PL-2</t>
         </is>
       </c>
       <c r="T55" s="19" t="inlineStr">
         <is>
-          <t>PEO-1, PEO-3</t>
+          <t>PEO-1</t>
         </is>
       </c>
       <c r="U55" s="19" t="inlineStr">
         <is>
-          <t>**R**</t>
+          <t>**M**</t>
         </is>
       </c>
     </row>
@@ -8957,7 +8961,7 @@
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>`STI-503`</t>
+          <t>`STI-520`</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
@@ -9016,7 +9020,7 @@
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>`STI-504`</t>
+          <t>`STI-521`</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">
@@ -9075,7 +9079,7 @@
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>`STI-505`</t>
+          <t>`STI-522`</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr">
@@ -9134,7 +9138,7 @@
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t>`STI-506`</t>
+          <t>`STI-523`</t>
         </is>
       </c>
       <c r="C59" s="19" t="inlineStr">
@@ -9378,7 +9382,7 @@
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>`STI-601`</t>
+          <t>`STI-624`</t>
         </is>
       </c>
       <c r="C63" s="19" t="inlineStr">
@@ -9437,7 +9441,7 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>`STI-602`</t>
+          <t>`STI-625`</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
@@ -9496,12 +9500,12 @@
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>`STI-603`</t>
+          <t>`STI-626`</t>
         </is>
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t>Keamanan Informasi Lanjut</t>
+          <t>Deep Learning &amp; Neural Net</t>
         </is>
       </c>
       <c r="D65" s="21" t="inlineStr">
@@ -9515,39 +9519,35 @@
       <c r="H65" s="19" t="inlineStr"/>
       <c r="I65" s="19" t="inlineStr"/>
       <c r="J65" s="19" t="inlineStr"/>
-      <c r="K65" s="19" t="inlineStr">
-        <is>
-          <t>**M**</t>
-        </is>
-      </c>
+      <c r="K65" s="19" t="inlineStr"/>
       <c r="L65" s="19" t="inlineStr"/>
-      <c r="M65" s="19" t="inlineStr"/>
-      <c r="N65" s="19" t="inlineStr"/>
-      <c r="O65" s="19" t="inlineStr">
-        <is>
-          <t>**M**</t>
-        </is>
-      </c>
-      <c r="P65" s="19" t="inlineStr">
-        <is>
-          <t>**M**</t>
-        </is>
-      </c>
+      <c r="M65" s="19" t="inlineStr">
+        <is>
+          <t>**R**</t>
+        </is>
+      </c>
+      <c r="N65" s="19" t="inlineStr">
+        <is>
+          <t>**R**</t>
+        </is>
+      </c>
+      <c r="O65" s="19" t="inlineStr"/>
+      <c r="P65" s="19" t="inlineStr"/>
       <c r="Q65" s="19" t="inlineStr"/>
       <c r="R65" s="19" t="inlineStr"/>
       <c r="S65" s="19" t="inlineStr">
         <is>
-          <t>PL-2</t>
+          <t>PL-1</t>
         </is>
       </c>
       <c r="T65" s="19" t="inlineStr">
         <is>
-          <t>PEO-1</t>
+          <t>PEO-1, PEO-3</t>
         </is>
       </c>
       <c r="U65" s="19" t="inlineStr">
         <is>
-          <t>**M**</t>
+          <t>**R**</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>`STI-604`</t>
+          <t>`STI-627`</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="B73" s="19" t="inlineStr">
         <is>
-          <t>`STI-701`</t>
+          <t>`STI-728`</t>
         </is>
       </c>
       <c r="C73" s="19" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D128" s="19" t="inlineStr">
         <is>
-          <t>`STI-301`</t>
+          <t>`STI-306`</t>
         </is>
       </c>
       <c r="E128" s="19" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="C129" s="20" t="inlineStr">
         <is>
-          <t>`FST-207`, `STI-402`, `STI-503`</t>
+          <t>`FST-207`, `STI-415`, `STI-520`</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
@@ -12117,12 +12117,12 @@
       </c>
       <c r="C130" s="19" t="inlineStr">
         <is>
-          <t>`STI-103`, `STI-307`, `STI-404`, `STI-305`</t>
+          <t>`STI-103`, `STI-312`, `STI-417`, `STI-310`</t>
         </is>
       </c>
       <c r="D130" s="19" t="inlineStr">
         <is>
-          <t>`STB-01`, `STB-02`, `STI-504`</t>
+          <t>`STB-01`, `STB-02`, `STI-521`</t>
         </is>
       </c>
       <c r="E130" s="19" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="D131" s="20" t="inlineStr">
         <is>
-          <t>`STI-301`, `STI-604`</t>
+          <t>`STI-306`, `STI-627`</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="D132" s="19" t="inlineStr">
         <is>
-          <t>`STI-506`, `STB-03`</t>
+          <t>`STI-523`, `STB-03`</t>
         </is>
       </c>
       <c r="E132" s="19" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="C133" s="20" t="inlineStr">
         <is>
-          <t>`STI-405`, `STI-603`, `STB-01`, `STB-03`</t>
+          <t>`STI-418`, `STI-519`, `STB-01`, `STB-03`</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="C134" s="19" t="inlineStr">
         <is>
-          <t>`STI-301`, `STI-304`</t>
+          <t>`STI-306`, `STI-309`</t>
         </is>
       </c>
       <c r="D134" s="19" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="C135" s="20" t="inlineStr">
         <is>
-          <t>`STI-506`, `STC-06`</t>
+          <t>`STI-523`, `STC-06`</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
@@ -12314,7 +12314,7 @@
       </c>
       <c r="D136" s="19" t="inlineStr">
         <is>
-          <t>`STI-301`, `STI-602`</t>
+          <t>`STI-306`, `STI-625`</t>
         </is>
       </c>
       <c r="E136" s="19" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="C137" s="20" t="inlineStr">
         <is>
-          <t>`STI-102`, `STI-201`, `STI-202`, `FST-408`</t>
+          <t>`STI-102`, `STI-204`, `STI-205`, `FST-408`</t>
         </is>
       </c>
       <c r="D137" s="22" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="D138" s="19" t="inlineStr">
         <is>
-          <t>`STI-306`, `STI-407`</t>
+          <t>`STI-311`, `STI-416`</t>
         </is>
       </c>
       <c r="E138" s="19" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="C139" s="20" t="inlineStr">
         <is>
-          <t>`STI-306`, `STI-407`, `STI-505`, `STI-604`</t>
+          <t>`STI-311`, `STI-416`, `STI-522`, `STI-627`</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="C140" s="19" t="inlineStr">
         <is>
-          <t>`STI-402`, `STI-503`, `STA-01`</t>
+          <t>`STI-415`, `STI-520`, `STA-01`</t>
         </is>
       </c>
       <c r="D140" s="19" t="inlineStr">
         <is>
-          <t>`STI-401`, `STA-04`</t>
+          <t>`STI-413`, `STA-04`</t>
         </is>
       </c>
       <c r="E140" s="19" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C142" s="19" t="inlineStr">
         <is>
-          <t>`MKU-204`, `STI-701`, `FST-610`</t>
+          <t>`MKU-204`, `STI-728`, `FST-610`</t>
         </is>
       </c>
       <c r="D142" s="21" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="C143" s="20" t="inlineStr">
         <is>
-          <t>`STI-302`, `STI-403`, `STI-601`, `STA-03`, `STA-05`</t>
+          <t>`STI-307`, `STI-414`, `STI-624`, `STA-03`, `STA-05`</t>
         </is>
       </c>
       <c r="D143" s="20" t="inlineStr">
         <is>
-          <t>`STI-401`, `STA-06`</t>
+          <t>`STI-413`, `STA-06`</t>
         </is>
       </c>
       <c r="E143" s="20" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="C144" s="19" t="inlineStr">
         <is>
-          <t>`STI-303`, `STC-01`</t>
+          <t>`STI-308`, `STC-01`</t>
         </is>
       </c>
       <c r="D144" s="19" t="inlineStr">
         <is>
-          <t>`STI-306`, `STI-505`</t>
+          <t>`STI-311`, `STI-522`</t>
         </is>
       </c>
       <c r="E144" s="19" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="C145" s="20" t="inlineStr">
         <is>
-          <t>`STI-401`, `STI-501`, `STA-04`</t>
+          <t>`STI-413`, `STI-626`, `STA-04`</t>
         </is>
       </c>
       <c r="D145" s="20" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="C146" s="19" t="inlineStr">
         <is>
-          <t>`STI-404`, `STB-02`</t>
+          <t>`STI-417`, `STB-02`</t>
         </is>
       </c>
       <c r="D146" s="19" t="inlineStr">
         <is>
-          <t>`STI-604`, `STC-05`</t>
+          <t>`STI-627`, `STC-05`</t>
         </is>
       </c>
       <c r="E146" s="19" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="D147" s="20" t="inlineStr">
         <is>
-          <t>`STI-405`, `STI-602`, `STB-04`</t>
+          <t>`STI-418`, `STI-625`, `STB-04`</t>
         </is>
       </c>
       <c r="E147" s="20" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="C153" s="20" t="inlineStr">
         <is>
-          <t>`STI-302`, `STI-401`, `STI-403`, `STI-501`, `STI-601`</t>
+          <t>`STI-307`, `STI-413`, `STI-414`, `STI-626`, `STI-624`</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
@@ -12834,12 +12834,12 @@
       </c>
       <c r="C154" s="19" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`STI-312`</t>
         </is>
       </c>
       <c r="D154" s="19" t="inlineStr">
         <is>
-          <t>`STI-404`, `STI-504`, `STB-01`</t>
+          <t>`STI-417`, `STI-521`, `STB-01`</t>
         </is>
       </c>
       <c r="E154" s="19" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="C155" s="20" t="inlineStr">
         <is>
-          <t>`STI-306`, `STI-407`, `STI-505`, `STI-604`</t>
+          <t>`STI-311`, `STI-416`, `STI-522`, `STI-627`</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="C156" s="19" t="inlineStr">
         <is>
-          <t>`STI-404`, `STB-02`</t>
+          <t>`STI-417`, `STB-02`</t>
         </is>
       </c>
       <c r="D156" s="19" t="inlineStr">
         <is>
-          <t>`STI-305`, `STC-05`</t>
+          <t>`STI-310`, `STC-05`</t>
         </is>
       </c>
       <c r="E156" s="19" t="inlineStr">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="C157" s="20" t="inlineStr">
         <is>
-          <t>`STI-405`, `STI-603`, `STB-01`</t>
+          <t>`STI-418`, `STI-519`, `STB-01`</t>
         </is>
       </c>
       <c r="D157" s="22" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="C158" s="19" t="inlineStr">
         <is>
-          <t>`STI-601`, `STI-604`, `FST-610`</t>
+          <t>`STI-624`, `STI-627`, `FST-610`</t>
         </is>
       </c>
       <c r="D158" s="19" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>`STI-506`</t>
+          <t>`STI-523`</t>
         </is>
       </c>
       <c r="E159" s="20" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="C160" s="19" t="inlineStr">
         <is>
-          <t>`STI-402`, `STI-503`</t>
+          <t>`STI-415`, `STI-520`</t>
         </is>
       </c>
       <c r="D160" s="19" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="C161" s="20" t="inlineStr">
         <is>
-          <t>`STI-303`, `STC-01`</t>
+          <t>`STI-308`, `STC-01`</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>`STI-306`, `STC-04`</t>
+          <t>`STI-311`, `STC-04`</t>
         </is>
       </c>
       <c r="E161" s="20" t="inlineStr">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="C162" s="19" t="inlineStr">
         <is>
-          <t>`STI-304`, `STI-407`, `STI-604`</t>
+          <t>`STI-309`, `STI-416`, `STI-627`</t>
         </is>
       </c>
       <c r="D162" s="19" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="C164" s="19" t="inlineStr">
         <is>
-          <t>`MKU-204`, `STI-701`, `FST-610`</t>
+          <t>`MKU-204`, `STI-728`, `FST-610`</t>
         </is>
       </c>
       <c r="D164" s="21" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="C165" s="20" t="inlineStr">
         <is>
-          <t>`STI-504`, `STA-06`</t>
+          <t>`STI-521`, `STA-06`</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
         <is>
-          <t>`STI-305`, `STI-307`</t>
+          <t>`STI-310`, `STI-312`</t>
         </is>
       </c>
       <c r="E165" s="20" t="inlineStr">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="B178" s="19" t="inlineStr">
         <is>
-          <t>`STI-201`</t>
+          <t>`STI-204`</t>
         </is>
       </c>
       <c r="C178" s="19" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="B179" s="20" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`STI-205`</t>
         </is>
       </c>
       <c r="C179" s="20" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="B186" s="19" t="inlineStr">
         <is>
-          <t>`STI-301`</t>
+          <t>`STI-306`</t>
         </is>
       </c>
       <c r="C186" s="19" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="B187" s="20" t="inlineStr">
         <is>
-          <t>`STI-302`</t>
+          <t>`STI-307`</t>
         </is>
       </c>
       <c r="C187" s="20" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="B188" s="19" t="inlineStr">
         <is>
-          <t>`STI-303`</t>
+          <t>`STI-308`</t>
         </is>
       </c>
       <c r="C188" s="19" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="B189" s="20" t="inlineStr">
         <is>
-          <t>`STI-304`</t>
+          <t>`STI-309`</t>
         </is>
       </c>
       <c r="C189" s="20" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="B190" s="19" t="inlineStr">
         <is>
-          <t>`STI-305`</t>
+          <t>`STI-310`</t>
         </is>
       </c>
       <c r="C190" s="19" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="B191" s="20" t="inlineStr">
         <is>
-          <t>`STI-306`</t>
+          <t>`STI-311`</t>
         </is>
       </c>
       <c r="C191" s="20" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="B192" s="19" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`STI-312`</t>
         </is>
       </c>
       <c r="C192" s="19" t="inlineStr">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="B193" s="20" t="inlineStr">
         <is>
-          <t>`STI-401`</t>
+          <t>`STI-413`</t>
         </is>
       </c>
       <c r="C193" s="20" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="B194" s="19" t="inlineStr">
         <is>
-          <t>`STI-402`</t>
+          <t>`STI-415`</t>
         </is>
       </c>
       <c r="C194" s="19" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="B195" s="20" t="inlineStr">
         <is>
-          <t>`STI-407`</t>
+          <t>`STI-416`</t>
         </is>
       </c>
       <c r="C195" s="20" t="inlineStr">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="B196" s="19" t="inlineStr">
         <is>
-          <t>`STI-404`</t>
+          <t>`STI-417`</t>
         </is>
       </c>
       <c r="C196" s="19" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="B197" s="20" t="inlineStr">
         <is>
-          <t>`STI-405`</t>
+          <t>`STI-418`</t>
         </is>
       </c>
       <c r="C197" s="20" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B199" s="20" t="inlineStr">
         <is>
-          <t>`STI-403`</t>
+          <t>`STI-414`</t>
         </is>
       </c>
       <c r="C199" s="20" t="inlineStr">
@@ -14765,12 +14765,12 @@
       </c>
       <c r="B201" s="20" t="inlineStr">
         <is>
-          <t>`STI-501`</t>
+          <t>`STI-519`</t>
         </is>
       </c>
       <c r="C201" s="20" t="inlineStr">
         <is>
-          <t>Deep Learning &amp; Neural Net</t>
+          <t>Keamanan Informasi Lanjut</t>
         </is>
       </c>
       <c r="D201" s="22" t="inlineStr">
@@ -14780,12 +14780,12 @@
       </c>
       <c r="E201" s="20" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="F201" s="20" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="G201" s="20" t="inlineStr">
@@ -14812,7 +14812,7 @@
       </c>
       <c r="B202" s="19" t="inlineStr">
         <is>
-          <t>`STI-503`</t>
+          <t>`STI-520`</t>
         </is>
       </c>
       <c r="C202" s="19" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="B203" s="20" t="inlineStr">
         <is>
-          <t>`STI-504`</t>
+          <t>`STI-521`</t>
         </is>
       </c>
       <c r="C203" s="20" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="B204" s="19" t="inlineStr">
         <is>
-          <t>`STI-505`</t>
+          <t>`STI-522`</t>
         </is>
       </c>
       <c r="C204" s="19" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="B205" s="20" t="inlineStr">
         <is>
-          <t>`STI-506`</t>
+          <t>`STI-523`</t>
         </is>
       </c>
       <c r="C205" s="20" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="B209" s="20" t="inlineStr">
         <is>
-          <t>`STI-601`</t>
+          <t>`STI-624`</t>
         </is>
       </c>
       <c r="C209" s="20" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="B210" s="19" t="inlineStr">
         <is>
-          <t>`STI-602`</t>
+          <t>`STI-625`</t>
         </is>
       </c>
       <c r="C210" s="19" t="inlineStr">
@@ -15235,12 +15235,12 @@
       </c>
       <c r="B211" s="20" t="inlineStr">
         <is>
-          <t>`STI-603`</t>
+          <t>`STI-626`</t>
         </is>
       </c>
       <c r="C211" s="20" t="inlineStr">
         <is>
-          <t>Keamanan Informasi Lanjut</t>
+          <t>Deep Learning &amp; Neural Net</t>
         </is>
       </c>
       <c r="D211" s="22" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="E211" s="20" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="F211" s="20" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="G211" s="20" t="inlineStr">
@@ -15282,7 +15282,7 @@
       </c>
       <c r="B212" s="19" t="inlineStr">
         <is>
-          <t>`STI-604`</t>
+          <t>`STI-627`</t>
         </is>
       </c>
       <c r="C212" s="19" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="B216" s="19" t="inlineStr">
         <is>
-          <t>`STI-701`</t>
+          <t>`STI-728`</t>
         </is>
       </c>
       <c r="C216" s="19" t="inlineStr">
@@ -15867,7 +15867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -15877,6 +15877,7 @@
     <col width="50.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="35.65" customWidth="1" min="7" max="7"/>
+    <col width="47.15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -16130,255 +16131,392 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>SEBARAN 8 SEMESTER KURIKULUM SISTEKIN</t>
+          <t>1.1 KELOMPOK MATA KULIAH WAJIB UMUM (MKWU) (8 MK / 13 SKS)</t>
         </is>
       </c>
       <c r="B16" s="16" t="n"/>
       <c r="C16" s="16" t="n"/>
       <c r="D16" s="16" t="n"/>
       <c r="E16" s="16" t="n"/>
-      <c r="F16" s="17" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="17" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
           <t>Semester</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>Fokus Pembelajaran</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>Jml MK</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>Jml SKS</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>Karakteristik Kurikulum</t>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>Catatan / Kebijakan</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 1**</t>
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Fondasi Sains &amp; MKWU</t>
+          <t>`MKU-101`</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>8 MK</t>
+          <t>Agama I</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>19 SKS</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>Sains, Algoritma Dasar, Logika, Agama</t>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>Sem 1</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="inlineStr">
+        <is>
+          <t>Wajib Nasional SN-Dikti</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 2**</t>
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>Data, Matdis &amp; Etika</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>8 MK</t>
+          <t>`MKU-102`</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>Pancasila</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>20 SKS</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>Struktur Data, Basis Data, Matdis, Etika</t>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>Sem 1</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>Wajib Nasional SN-Dikti</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 3**</t>
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>RPL, UI/UX &amp; Infra</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>7 MK</t>
+          <t>`MKU-103`</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>Bahasa Indonesia</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>20 SKS</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>APSI, RPL, Web Front, Jarkom, OS, Cerdas</t>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>Sem 1</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
+        <is>
+          <t>Wajib Nasional SN-Dikti</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 4**</t>
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>AI/ML, NLP, Cloud &amp; Keamanan</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>8 MK</t>
+          <t>`MKU-204`</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>Kewirausahaan I</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>21 SKS</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>ML, NLP/IR, DW/BI, Web Back, Cloud, Probstat</t>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>Sem 2</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>Muatan Unggulan Universitas</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 5**</t>
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>Deep Learning &amp; IoT</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>7 MK</t>
+          <t>`MKU-405`</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>Kewarganegaraan</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>21 SKS</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>Deep Learning, IoT, Mobile, KPM, Peminatan 1</t>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>Sem 4</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
+        <is>
+          <t>Wajib Nasional SN-Dikti</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 6**</t>
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>AI Integrasi &amp; Platform</t>
+          <t>`MKU-406`</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>7 MK</t>
+          <t>Agama II</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>19 SKS</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>Smart AI, Smart City, Platform, Metopel</t>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>Sem 4</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>Muatan Khusus Kebijakan UWG</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 7**</t>
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>Capstone, PKL &amp; Sempro</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>7 MK</t>
+          <t>`MKU-507`</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>Kuliah Pengabdian Kepada Masyarakat (KPM)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>20 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>Startup, Capstone FSTI, PKL, Pra-Skripsi</t>
+          <t>Praktik</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>Sem 5</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>$\ge 80\text{ SKS}$</t>
+        </is>
+      </c>
+      <c r="H24" s="19" t="inlineStr">
+        <is>
+          <t>Wajib Universitas / MBKM</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 8**</t>
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>Skripsi Mandiri</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>1 MK</t>
+          <t>`MKU-508`</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>Kewirausahaan II</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
         <is>
-          <t>6 SKS</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>Skripsi Murni / 4 Opsi Non-Skripsi</t>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>Sem 5</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>Muatan Khusus Kebijakan UWG</t>
         </is>
       </c>
     </row>
@@ -16388,24 +16526,39 @@
           <t>**TOTAL**</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>**Paket Lulus Tepat Waktu**</t>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>**55 MK**</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>**146 SKS**</t>
+          <t>**8 Mata Kuliah Wajib Umum**</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>**13**</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>**Standar Sarjana S1 Komputasi**</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>**8,9% Beban Kurikulum**</t>
+        </is>
+      </c>
+      <c r="H26" s="19" t="inlineStr">
+        <is>
+          <t>**6 Berbobot SKS + 2 Khusus UWG (0 SKS)**</t>
         </is>
       </c>
     </row>
@@ -16413,7 +16566,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>SEMESTER 1 (19 SKS) — Fondasi Sains, Algoritma, Arsitektur STI &amp; MKWU</t>
+          <t>1.2 KELOMPOK MATA KULIAH WAJIB FAKULTAS (FSTI) (13 MK / 36 SKS)</t>
         </is>
       </c>
       <c r="B28" s="16" t="n"/>
@@ -16451,7 +16604,7 @@
       </c>
       <c r="F29" s="18" t="inlineStr">
         <is>
-          <t>Kategori</t>
+          <t>Semester</t>
         </is>
       </c>
       <c r="G29" s="18" t="inlineStr">
@@ -16488,7 +16641,7 @@
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>FSTI</t>
+          <t>Sem 1</t>
         </is>
       </c>
       <c r="G30" s="19" t="inlineStr">
@@ -16525,7 +16678,7 @@
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>FSTI</t>
+          <t>Sem 1</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -16542,32 +16695,32 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>`STI-101`</t>
+          <t>`FST-203`</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>Pengantar Sistem dan Teknologi Informasi</t>
+          <t>Struktur Data dan Algoritma</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 2</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`FST-102`</t>
         </is>
       </c>
     </row>
@@ -16579,17 +16732,17 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>`STI-102`</t>
-        </is>
-      </c>
-      <c r="C33" s="22" t="inlineStr">
-        <is>
-          <t>Kalkulus</t>
+          <t>`FST-204`</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>Pengantar Kecerdasan Artifisial &amp; Data</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -16599,12 +16752,12 @@
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 2</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`FST-101`</t>
         </is>
       </c>
     </row>
@@ -16616,17 +16769,17 @@
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>`STI-103`</t>
+          <t>`FST-205`</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>Arsitektur dan Organisasi Sistem Teknologi Informasi</t>
+          <t>Basic English for IT</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
@@ -16636,7 +16789,7 @@
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 2</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
@@ -16653,12 +16806,12 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>`MKU-101`</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="inlineStr">
-        <is>
-          <t>Agama I</t>
+          <t>`FST-206`</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>Etika Profesi &amp; Hukum Digital</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -16673,7 +16826,7 @@
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
-          <t>MKWU</t>
+          <t>Sem 2</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -16690,32 +16843,32 @@
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>`MKU-102`</t>
+          <t>`FST-207`</t>
         </is>
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>Pancasila</t>
+          <t>Sistem Basis Data</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F36" s="19" t="inlineStr">
         <is>
-          <t>MKWU</t>
+          <t>Sem 2</t>
         </is>
       </c>
       <c r="G36" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`FST-102`</t>
         </is>
       </c>
     </row>
@@ -16727,868 +16880,988 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>`MKU-103`</t>
+          <t>`FST-408`</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>Probabilitas dan Statistika</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>Sem 4</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>`STI-102`</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>`FST-611`</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>Metodologi Penelitian</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E38" s="19" t="inlineStr">
         <is>
           <t>Teori</t>
         </is>
       </c>
-      <c r="F37" s="20" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G37" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 1 (8 MK)**</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>**19**</t>
-        </is>
-      </c>
-      <c r="E38" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sem 6</t>
         </is>
       </c>
       <c r="G38" s="19" t="inlineStr">
         <is>
-          <t>**Kumulatif: 19 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 2 (20 SKS) — Fondasi Data, Matdis &amp; Logika, Aljabar &amp; Etika</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
-      <c r="G40" s="17" t="n"/>
-    </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D41" s="18" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E41" s="18" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F41" s="18" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G41" s="18" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
+          <t>$\ge 76\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>`FST-610`</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>Capstone Project FSTI</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>Proyek</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>`STI-523`, $\ge 100\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>`FST-612`</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>Praktik Kerja Lapangan (PKL)</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>Magang</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>$\ge 100\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>`FST-613`</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>Pra-Skripsi / Seminar Proposal</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>Seminar</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>`FST-611`, $\ge 100\text{ SKS}$</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="21" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>`FST-714`</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>Skripsi / Tugas Akhir</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>Mandiri</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
+        <is>
+          <t>Sem 8</t>
+        </is>
+      </c>
+      <c r="G42" s="19" t="inlineStr">
+        <is>
+          <t>`FST-613`, $\ge 120\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>**TOTAL**</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>**13 Mata Kuliah Wajib Fakultas**</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>**36**</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>**24,7% Beban Kurikulum**</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>1.3 KELOMPOK MATA KULIAH INTI PROGRAM STUDI (CORE STI) (28 MK / 79 SKS)</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="16" t="n"/>
+      <c r="F45" s="16" t="n"/>
+      <c r="G45" s="17" t="n"/>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>`STI-101`</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>Pengantar Sistem dan Teknologi Informasi</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F47" s="19" t="inlineStr">
+        <is>
+          <t>Sem 1</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>`STI-102`</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>Kalkulus</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>Sem 1</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>`STI-103`</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>Arsitektur dan Organisasi Sistem Teknologi Informasi</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F49" s="19" t="inlineStr">
+        <is>
+          <t>Sem 1</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>`STI-204`</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>Matematika Diskrit dan Logika</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>Sem 2</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="inlineStr">
+        <is>
+          <t>`STI-103`</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>`STI-205`</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>Aljabar Linear dan Matriks</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F51" s="19" t="inlineStr">
+        <is>
+          <t>Sem 2</t>
+        </is>
+      </c>
+      <c r="G51" s="19" t="inlineStr">
+        <is>
+          <t>`STI-102`</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>`STI-306`</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>Analisis dan Perancangan Sistem Informasi</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>Sem 3</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>`STI-101`, `FST-207`</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>`STI-307`</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>Sistem Cerdas</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="inlineStr">
+        <is>
+          <t>Sem 3</t>
+        </is>
+      </c>
+      <c r="G53" s="19" t="inlineStr">
+        <is>
+          <t>`STI-204`, `FST-204`</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>`STI-308`</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>UI/UX Design &amp; Prototyping</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>Sem 3</t>
+        </is>
+      </c>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>`FST-101`</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>`STI-201`</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>Matematika Diskrit dan Logika</t>
-        </is>
-      </c>
-      <c r="D42" s="21" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>`STI-309`</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="inlineStr">
+        <is>
+          <t>Rekayasa Perangkat Lunak</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E42" s="19" t="inlineStr">
+      <c r="E55" s="19" t="inlineStr">
         <is>
           <t>Teori</t>
         </is>
       </c>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G42" s="19" t="inlineStr">
+      <c r="F55" s="19" t="inlineStr">
+        <is>
+          <t>Sem 3</t>
+        </is>
+      </c>
+      <c r="G55" s="19" t="inlineStr">
+        <is>
+          <t>`FST-203`</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>`STI-310`</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>Sistem Operasi</t>
+        </is>
+      </c>
+      <c r="D56" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E56" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>Sem 3</t>
+        </is>
+      </c>
+      <c r="G56" s="20" t="inlineStr">
         <is>
           <t>`STI-103`</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="inlineStr">
-        <is>
-          <t>`STI-202`</t>
-        </is>
-      </c>
-      <c r="C43" s="20" t="inlineStr">
-        <is>
-          <t>Aljabar Linear dan Matriks</t>
-        </is>
-      </c>
-      <c r="D43" s="22" t="inlineStr">
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>`STI-311`</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>Web Front End Development</t>
+        </is>
+      </c>
+      <c r="D57" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E43" s="20" t="inlineStr">
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F57" s="19" t="inlineStr">
+        <is>
+          <t>Sem 3</t>
+        </is>
+      </c>
+      <c r="G57" s="19" t="inlineStr">
+        <is>
+          <t>`FST-102`</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>`STI-312`</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>Jaringan Komputer</t>
+        </is>
+      </c>
+      <c r="D58" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F58" s="20" t="inlineStr">
+        <is>
+          <t>Sem 3</t>
+        </is>
+      </c>
+      <c r="G58" s="20" t="inlineStr">
+        <is>
+          <t>`STI-103`</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="21" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>`STI-413`</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="D59" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E59" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F59" s="19" t="inlineStr">
+        <is>
+          <t>Sem 4</t>
+        </is>
+      </c>
+      <c r="G59" s="19" t="inlineStr">
+        <is>
+          <t>`STI-205`, `STI-307`</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>`STI-414`</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>Pengantar NLP &amp; Information Retrieval</t>
+        </is>
+      </c>
+      <c r="D60" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E60" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F60" s="20" t="inlineStr">
+        <is>
+          <t>Sem 4</t>
+        </is>
+      </c>
+      <c r="G60" s="20" t="inlineStr">
+        <is>
+          <t>`STI-307`</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>`STI-415`</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>Data Warehouse &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="D61" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F61" s="19" t="inlineStr">
+        <is>
+          <t>Sem 4</t>
+        </is>
+      </c>
+      <c r="G61" s="19" t="inlineStr">
+        <is>
+          <t>`FST-207`</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>`STI-416`</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>Web Back End Development</t>
+        </is>
+      </c>
+      <c r="D62" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E62" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>Sem 4</t>
+        </is>
+      </c>
+      <c r="G62" s="20" t="inlineStr">
+        <is>
+          <t>`FST-207`, `STI-311`</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>`STI-417`</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>Komputasi Awan (Cloud Computing)</t>
+        </is>
+      </c>
+      <c r="D63" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
         <is>
           <t>Teori</t>
         </is>
       </c>
-      <c r="F43" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G43" s="20" t="inlineStr">
-        <is>
-          <t>`STI-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B44" s="19" t="inlineStr">
-        <is>
-          <t>`FST-203`</t>
-        </is>
-      </c>
-      <c r="C44" s="19" t="inlineStr">
-        <is>
-          <t>Struktur Data dan Algoritma</t>
-        </is>
-      </c>
-      <c r="D44" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E44" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F44" s="19" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G44" s="19" t="inlineStr">
-        <is>
-          <t>`FST-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>`FST-204`</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
-        <is>
-          <t>Pengantar Kecerdasan Artifisial &amp; Data</t>
-        </is>
-      </c>
-      <c r="D45" s="22" t="inlineStr">
+      <c r="F63" s="19" t="inlineStr">
+        <is>
+          <t>Sem 4</t>
+        </is>
+      </c>
+      <c r="G63" s="19" t="inlineStr">
+        <is>
+          <t>`STI-312`, `STI-310`</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>`STI-418`</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>Dasar Keamanan Informasi</t>
+        </is>
+      </c>
+      <c r="D64" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E45" s="20" t="inlineStr">
+      <c r="E64" s="20" t="inlineStr">
         <is>
           <t>Teori</t>
         </is>
       </c>
-      <c r="F45" s="20" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G45" s="20" t="inlineStr">
-        <is>
-          <t>`FST-101`</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="21" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B46" s="19" t="inlineStr">
-        <is>
-          <t>`FST-205`</t>
-        </is>
-      </c>
-      <c r="C46" s="19" t="inlineStr">
-        <is>
-          <t>Basic English for IT</t>
-        </is>
-      </c>
-      <c r="D46" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E46" s="19" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F46" s="19" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G46" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="22" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="inlineStr">
-        <is>
-          <t>`FST-206`</t>
-        </is>
-      </c>
-      <c r="C47" s="20" t="inlineStr">
-        <is>
-          <t>Etika Profesi &amp; Hukum Digital</t>
-        </is>
-      </c>
-      <c r="D47" s="22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E47" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F47" s="20" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G47" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B48" s="19" t="inlineStr">
-        <is>
-          <t>`FST-207`</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="inlineStr">
-        <is>
-          <t>Sistem Basis Data</t>
-        </is>
-      </c>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E48" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F48" s="19" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G48" s="19" t="inlineStr">
-        <is>
-          <t>`FST-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="22" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
-        <is>
-          <t>`MKU-204`</t>
-        </is>
-      </c>
-      <c r="C49" s="20" t="inlineStr">
-        <is>
-          <t>Kewirausahaan I</t>
-        </is>
-      </c>
-      <c r="D49" s="22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E49" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F49" s="20" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G49" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="19" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B50" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 2 (8 MK)**</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>**20**</t>
-        </is>
-      </c>
-      <c r="E50" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="19" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 39 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 3 (20 SKS) — Penguatan Core RPL, OS, Jarkom &amp; UI/UX</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n"/>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
-      <c r="G52" s="17" t="n"/>
-    </row>
-    <row r="53" ht="26" customHeight="1">
-      <c r="A53" s="18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B53" s="18" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D53" s="18" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E53" s="18" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F53" s="18" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G53" s="18" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="21" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B54" s="19" t="inlineStr">
-        <is>
-          <t>`STI-301`</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="inlineStr">
-        <is>
-          <t>Analisis dan Perancangan Sistem Informasi</t>
-        </is>
-      </c>
-      <c r="D54" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E54" s="19" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F54" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G54" s="19" t="inlineStr">
-        <is>
-          <t>`STI-101`, `FST-207`</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="22" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B55" s="20" t="inlineStr">
-        <is>
-          <t>`STI-302`</t>
-        </is>
-      </c>
-      <c r="C55" s="20" t="inlineStr">
-        <is>
-          <t>Sistem Cerdas</t>
-        </is>
-      </c>
-      <c r="D55" s="22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E55" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G55" s="20" t="inlineStr">
-        <is>
-          <t>`STI-201`, `FST-204`</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="21" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B56" s="19" t="inlineStr">
-        <is>
-          <t>`STI-303`</t>
-        </is>
-      </c>
-      <c r="C56" s="19" t="inlineStr">
-        <is>
-          <t>UI/UX Design &amp; Prototyping</t>
-        </is>
-      </c>
-      <c r="D56" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E56" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F56" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G56" s="19" t="inlineStr">
-        <is>
-          <t>`FST-101`</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B57" s="20" t="inlineStr">
-        <is>
-          <t>`STI-304`</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="inlineStr">
-        <is>
-          <t>Rekayasa Perangkat Lunak</t>
-        </is>
-      </c>
-      <c r="D57" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E57" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F57" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G57" s="20" t="inlineStr">
-        <is>
-          <t>`FST-203`</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="21" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B58" s="19" t="inlineStr">
-        <is>
-          <t>`STI-305`</t>
-        </is>
-      </c>
-      <c r="C58" s="19" t="inlineStr">
-        <is>
-          <t>Sistem Operasi</t>
-        </is>
-      </c>
-      <c r="D58" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E58" s="19" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F58" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G58" s="19" t="inlineStr">
-        <is>
-          <t>`STI-103`</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B59" s="20" t="inlineStr">
-        <is>
-          <t>`STI-306`</t>
-        </is>
-      </c>
-      <c r="C59" s="20" t="inlineStr">
-        <is>
-          <t>Web Front End Development</t>
-        </is>
-      </c>
-      <c r="D59" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E59" s="20" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F59" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G59" s="20" t="inlineStr">
-        <is>
-          <t>`FST-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="21" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B60" s="19" t="inlineStr">
-        <is>
-          <t>`STI-307`</t>
-        </is>
-      </c>
-      <c r="C60" s="19" t="inlineStr">
-        <is>
-          <t>Jaringan Komputer</t>
-        </is>
-      </c>
-      <c r="D60" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E60" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F60" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G60" s="19" t="inlineStr">
-        <is>
-          <t>`STI-103`</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="20" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B61" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C61" s="20" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 3 (7 MK)**</t>
-        </is>
-      </c>
-      <c r="D61" s="22" t="inlineStr">
-        <is>
-          <t>**20**</t>
-        </is>
-      </c>
-      <c r="E61" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F61" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="20" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 59 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="62"/>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 4 (21 SKS) — Penguatan Core AI/ML, NLP, DW &amp; Cloud</t>
-        </is>
-      </c>
-      <c r="B63" s="16" t="n"/>
-      <c r="C63" s="16" t="n"/>
-      <c r="D63" s="16" t="n"/>
-      <c r="E63" s="16" t="n"/>
-      <c r="F63" s="16" t="n"/>
-      <c r="G63" s="17" t="n"/>
-    </row>
-    <row r="64" ht="26" customHeight="1">
-      <c r="A64" s="18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B64" s="18" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D64" s="18" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E64" s="18" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F64" s="18" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G64" s="18" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>Sem 4</t>
+        </is>
+      </c>
+      <c r="G64" s="20" t="inlineStr">
+        <is>
+          <t>`STI-312`</t>
         </is>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>`STI-401`</t>
+          <t>`STI-519`</t>
         </is>
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Keamanan Informasi Lanjut</t>
         </is>
       </c>
       <c r="D65" s="21" t="inlineStr">
@@ -17598,39 +17871,39 @@
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F65" s="19" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 5</t>
         </is>
       </c>
       <c r="G65" s="19" t="inlineStr">
         <is>
-          <t>`STI-202`, `STI-302`</t>
+          <t>`STI-418`</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>`STI-403`</t>
+          <t>`STI-520`</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>Pengantar NLP &amp; Information Retrieval</t>
+          <t>Data Mining &amp; Visualisasi Data</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
@@ -17640,29 +17913,29 @@
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 5</t>
         </is>
       </c>
       <c r="G66" s="20" t="inlineStr">
         <is>
-          <t>`STI-302`</t>
+          <t>`STI-413`, `STI-415`</t>
         </is>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t>`STI-402`</t>
+          <t>`STI-521`</t>
         </is>
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t>Data Warehouse &amp; Business Intelligence</t>
+          <t>Internet of Things (IoT)</t>
         </is>
       </c>
       <c r="D67" s="21" t="inlineStr">
@@ -17677,29 +17950,29 @@
       </c>
       <c r="F67" s="19" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 5</t>
         </is>
       </c>
       <c r="G67" s="19" t="inlineStr">
         <is>
-          <t>`FST-207`</t>
+          <t>`STI-312`, `STI-310`</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="22" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>`STI-407`</t>
+          <t>`STI-522`</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>Web Back End Development</t>
+          <t>Pemrograman Aplikasi Mobile</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
@@ -17714,29 +17987,29 @@
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 5</t>
         </is>
       </c>
       <c r="G68" s="20" t="inlineStr">
         <is>
-          <t>`FST-207`, `STI-306`</t>
+          <t>`STI-311`, `STI-416`</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t>`STI-404`</t>
+          <t>`STI-523`</t>
         </is>
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t>Komputasi Awan (Cloud Computing)</t>
+          <t>Manajemen Proyek TI</t>
         </is>
       </c>
       <c r="D69" s="21" t="inlineStr">
@@ -17751,71 +18024,71 @@
       </c>
       <c r="F69" s="19" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 5</t>
         </is>
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
-          <t>`STI-307`, `STI-305`</t>
+          <t>`STI-306`, `STI-309`</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>`STI-405`</t>
+          <t>`STI-624`</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>Dasar Keamanan Informasi</t>
+          <t>Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F70" s="20" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 6</t>
         </is>
       </c>
       <c r="G70" s="20" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`STI-413`, `STI-416`</t>
         </is>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t>`FST-408`</t>
+          <t>`STI-625`</t>
         </is>
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t>Probabilitas dan Statistika</t>
+          <t>Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="D71" s="21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -17825,996 +18098,895 @@
       </c>
       <c r="F71" s="19" t="inlineStr">
         <is>
-          <t>FSTI</t>
+          <t>Sem 6</t>
         </is>
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
-          <t>`STI-102`</t>
+          <t>`STI-521`</t>
         </is>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>`MKU-405`</t>
+          <t>`STI-626`</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>Kewarganegaraan</t>
+          <t>Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
         <is>
-          <t>MKWU</t>
+          <t>Sem 6</t>
         </is>
       </c>
       <c r="G72" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`STI-413`</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="21" t="inlineStr">
         <is>
-          <t>31.B</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B73" s="19" t="inlineStr">
         <is>
-          <t>`MKU-406`</t>
-        </is>
-      </c>
-      <c r="C73" s="21" t="inlineStr">
-        <is>
-          <t>Agama II</t>
+          <t>`STI-627`</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>Digital Platform Engineering</t>
         </is>
       </c>
       <c r="D73" s="21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F73" s="19" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G73" s="19" t="inlineStr">
+        <is>
+          <t>`STI-416`</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="22" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>`STI-728`</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="inlineStr">
+        <is>
+          <t>Inovasi Teknologi dan Startup Digital</t>
+        </is>
+      </c>
+      <c r="D74" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G74" s="20" t="inlineStr">
+        <is>
+          <t>`STI-627`, `MKU-204`</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>**TOTAL**</t>
+        </is>
+      </c>
+      <c r="B75" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>**28 Mata Kuliah Inti Program Studi**</t>
+        </is>
+      </c>
+      <c r="D75" s="21" t="inlineStr">
+        <is>
+          <t>**79**</t>
+        </is>
+      </c>
+      <c r="E75" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="19" t="inlineStr">
+        <is>
+          <t>**54,1% Beban Kurikulum**</t>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t>SEBARAN 8 SEMESTER KURIKULUM SISTEKIN</t>
+        </is>
+      </c>
+      <c r="B77" s="16" t="n"/>
+      <c r="C77" s="16" t="n"/>
+      <c r="D77" s="16" t="n"/>
+      <c r="E77" s="16" t="n"/>
+      <c r="F77" s="17" t="n"/>
+    </row>
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>Fokus Pembelajaran</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>Jml MK</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>Jml SKS</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>Karakteristik Kurikulum</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 1**</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>Fondasi Sains &amp; MKWU</t>
+        </is>
+      </c>
+      <c r="C79" s="21" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="D79" s="21" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="E79" s="19" t="inlineStr">
+        <is>
+          <t>Sains, Algoritma Dasar, Logika, Agama</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 2**</t>
+        </is>
+      </c>
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>Data, Matdis &amp; Etika</t>
+        </is>
+      </c>
+      <c r="C80" s="22" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="D80" s="22" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="E80" s="20" t="inlineStr">
+        <is>
+          <t>Struktur Data, Basis Data, Matdis, Etika</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 3**</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>RPL, UI/UX &amp; Infra</t>
+        </is>
+      </c>
+      <c r="C81" s="21" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="D81" s="21" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="inlineStr">
+        <is>
+          <t>APSI, RPL, Web Front, Jarkom, OS, Cerdas</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 4**</t>
+        </is>
+      </c>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>AI/ML, NLP, Cloud &amp; Keamanan</t>
+        </is>
+      </c>
+      <c r="C82" s="22" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="D82" s="22" t="inlineStr">
+        <is>
+          <t>21 SKS</t>
+        </is>
+      </c>
+      <c r="E82" s="20" t="inlineStr">
+        <is>
+          <t>ML, NLP/IR, DW/BI, Web Back, Cloud, Probstat</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 5**</t>
+        </is>
+      </c>
+      <c r="B83" s="19" t="inlineStr">
+        <is>
+          <t>Deep Learning &amp; IoT</t>
+        </is>
+      </c>
+      <c r="C83" s="21" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>21 SKS</t>
+        </is>
+      </c>
+      <c r="E83" s="19" t="inlineStr">
+        <is>
+          <t>Deep Learning, IoT, Mobile, KPM, Peminatan 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 6**</t>
+        </is>
+      </c>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>AI Integrasi &amp; Platform</t>
+        </is>
+      </c>
+      <c r="C84" s="22" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="D84" s="22" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="E84" s="20" t="inlineStr">
+        <is>
+          <t>Smart AI, Smart City, Platform, Metopel</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 7**</t>
+        </is>
+      </c>
+      <c r="B85" s="19" t="inlineStr">
+        <is>
+          <t>Capstone, PKL &amp; Sempro</t>
+        </is>
+      </c>
+      <c r="C85" s="21" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="D85" s="21" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="E85" s="19" t="inlineStr">
+        <is>
+          <t>Startup, Capstone FSTI, PKL, Pra-Skripsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 8**</t>
+        </is>
+      </c>
+      <c r="B86" s="20" t="inlineStr">
+        <is>
+          <t>Skripsi Mandiri</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>1 MK</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="inlineStr">
+        <is>
+          <t>6 SKS</t>
+        </is>
+      </c>
+      <c r="E86" s="20" t="inlineStr">
+        <is>
+          <t>Skripsi Murni / 4 Opsi Non-Skripsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
+          <t>**TOTAL**</t>
+        </is>
+      </c>
+      <c r="B87" s="19" t="inlineStr">
+        <is>
+          <t>**Paket Lulus Tepat Waktu**</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>**55 MK**</t>
+        </is>
+      </c>
+      <c r="D87" s="19" t="inlineStr">
+        <is>
+          <t>**146 SKS**</t>
+        </is>
+      </c>
+      <c r="E87" s="19" t="inlineStr">
+        <is>
+          <t>**Standar Sarjana S1 Komputasi**</t>
+        </is>
+      </c>
+    </row>
+    <row r="88"/>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 1 (19 SKS) — Fondasi Sains, Algoritma, Arsitektur STI &amp; MKWU</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="n"/>
+      <c r="C89" s="16" t="n"/>
+      <c r="D89" s="16" t="n"/>
+      <c r="E89" s="16" t="n"/>
+      <c r="F89" s="16" t="n"/>
+      <c r="G89" s="17" t="n"/>
+    </row>
+    <row r="90" ht="26" customHeight="1">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G90" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t>`FST-101`</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
+        <is>
+          <t>Dasar Teknologi Digital</t>
+        </is>
+      </c>
+      <c r="D91" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E91" s="19" t="inlineStr">
+        <is>
           <t>Teori</t>
         </is>
       </c>
-      <c r="F73" s="19" t="inlineStr">
+      <c r="F91" s="19" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G91" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B92" s="20" t="inlineStr">
+        <is>
+          <t>`FST-102`</t>
+        </is>
+      </c>
+      <c r="C92" s="20" t="inlineStr">
+        <is>
+          <t>Algoritma dan Pemrograman</t>
+        </is>
+      </c>
+      <c r="D92" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E92" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F92" s="20" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G92" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>`STI-101`</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t>Pengantar Sistem dan Teknologi Informasi</t>
+        </is>
+      </c>
+      <c r="D93" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F93" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G93" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B94" s="20" t="inlineStr">
+        <is>
+          <t>`STI-102`</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="inlineStr">
+        <is>
+          <t>Kalkulus</t>
+        </is>
+      </c>
+      <c r="D94" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E94" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F94" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G94" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B95" s="19" t="inlineStr">
+        <is>
+          <t>`STI-103`</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="inlineStr">
+        <is>
+          <t>Arsitektur dan Organisasi Sistem Teknologi Informasi</t>
+        </is>
+      </c>
+      <c r="D95" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F95" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G95" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B96" s="20" t="inlineStr">
+        <is>
+          <t>`MKU-101`</t>
+        </is>
+      </c>
+      <c r="C96" s="22" t="inlineStr">
+        <is>
+          <t>Agama I</t>
+        </is>
+      </c>
+      <c r="D96" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E96" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F96" s="20" t="inlineStr">
         <is>
           <t>MKWU</t>
         </is>
       </c>
-      <c r="G73" s="19" t="inlineStr">
-        <is>
-          <t>— (Kebijakan UWG, Sem 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="20" t="inlineStr">
+      <c r="G96" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B97" s="19" t="inlineStr">
+        <is>
+          <t>`MKU-102`</t>
+        </is>
+      </c>
+      <c r="C97" s="19" t="inlineStr">
+        <is>
+          <t>Pancasila</t>
+        </is>
+      </c>
+      <c r="D97" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F97" s="19" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G97" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B98" s="20" t="inlineStr">
+        <is>
+          <t>`MKU-103`</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="inlineStr">
+        <is>
+          <t>Bahasa Indonesia</t>
+        </is>
+      </c>
+      <c r="D98" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F98" s="20" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G98" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="19" t="inlineStr">
         <is>
           <t>**SUBTOTAL**</t>
         </is>
       </c>
-      <c r="B74" s="22" t="inlineStr">
+      <c r="B99" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C74" s="20" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 4 (8 MK + 1 MK 0 SKS)**</t>
-        </is>
-      </c>
-      <c r="D74" s="22" t="inlineStr">
-        <is>
-          <t>**21**</t>
-        </is>
-      </c>
-      <c r="E74" s="20" t="inlineStr">
+      <c r="C99" s="19" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 1 (8 MK)**</t>
+        </is>
+      </c>
+      <c r="D99" s="21" t="inlineStr">
+        <is>
+          <t>**19**</t>
+        </is>
+      </c>
+      <c r="E99" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F74" s="20" t="inlineStr">
+      <c r="F99" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G74" s="20" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 80 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 5 (21 SKS) — Tahap Spesialisasi Deep Learning, IoT &amp; Peminatan 1</t>
-        </is>
-      </c>
-      <c r="B76" s="16" t="n"/>
-      <c r="C76" s="16" t="n"/>
-      <c r="D76" s="16" t="n"/>
-      <c r="E76" s="16" t="n"/>
-      <c r="F76" s="16" t="n"/>
-      <c r="G76" s="17" t="n"/>
-    </row>
-    <row r="77" ht="26" customHeight="1">
-      <c r="A77" s="18" t="inlineStr">
+      <c r="G99" s="19" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 19 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 2 (20 SKS) — Fondasi Data, Matdis &amp; Logika, Aljabar &amp; Etika</t>
+        </is>
+      </c>
+      <c r="B101" s="16" t="n"/>
+      <c r="C101" s="16" t="n"/>
+      <c r="D101" s="16" t="n"/>
+      <c r="E101" s="16" t="n"/>
+      <c r="F101" s="16" t="n"/>
+      <c r="G101" s="17" t="n"/>
+    </row>
+    <row r="102" ht="26" customHeight="1">
+      <c r="A102" s="18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B77" s="18" t="inlineStr">
+      <c r="B102" s="18" t="inlineStr">
         <is>
           <t>Kode MK</t>
         </is>
       </c>
-      <c r="C77" s="18" t="inlineStr">
+      <c r="C102" s="18" t="inlineStr">
         <is>
           <t>Nama Mata Kuliah</t>
         </is>
       </c>
-      <c r="D77" s="18" t="inlineStr">
+      <c r="D102" s="18" t="inlineStr">
         <is>
           <t>SKS</t>
         </is>
       </c>
-      <c r="E77" s="18" t="inlineStr">
+      <c r="E102" s="18" t="inlineStr">
         <is>
           <t>Tipe</t>
         </is>
       </c>
-      <c r="F77" s="18" t="inlineStr">
+      <c r="F102" s="18" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="G77" s="18" t="inlineStr">
+      <c r="G102" s="18" t="inlineStr">
         <is>
           <t>Prasyarat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="21" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B78" s="19" t="inlineStr">
-        <is>
-          <t>`STI-501`</t>
-        </is>
-      </c>
-      <c r="C78" s="19" t="inlineStr">
-        <is>
-          <t>Deep Learning &amp; Neural Networks</t>
-        </is>
-      </c>
-      <c r="D78" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E78" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F78" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G78" s="19" t="inlineStr">
-        <is>
-          <t>`STI-401`</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="22" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B79" s="20" t="inlineStr">
-        <is>
-          <t>`STI-503`</t>
-        </is>
-      </c>
-      <c r="C79" s="20" t="inlineStr">
-        <is>
-          <t>Data Mining &amp; Visualisasi Data</t>
-        </is>
-      </c>
-      <c r="D79" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E79" s="20" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F79" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G79" s="20" t="inlineStr">
-        <is>
-          <t>`STI-401`, `STI-402`</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="21" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B80" s="19" t="inlineStr">
-        <is>
-          <t>`STI-504`</t>
-        </is>
-      </c>
-      <c r="C80" s="19" t="inlineStr">
-        <is>
-          <t>Internet of Things (IoT)</t>
-        </is>
-      </c>
-      <c r="D80" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E80" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F80" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G80" s="19" t="inlineStr">
-        <is>
-          <t>`STI-307`, `STI-305`</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="22" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B81" s="20" t="inlineStr">
-        <is>
-          <t>`STI-505`</t>
-        </is>
-      </c>
-      <c r="C81" s="20" t="inlineStr">
-        <is>
-          <t>Pemrograman Aplikasi Mobile</t>
-        </is>
-      </c>
-      <c r="D81" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E81" s="20" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F81" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G81" s="20" t="inlineStr">
-        <is>
-          <t>`STI-306`, `STI-407`</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="21" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B82" s="19" t="inlineStr">
-        <is>
-          <t>`STI-506`</t>
-        </is>
-      </c>
-      <c r="C82" s="19" t="inlineStr">
-        <is>
-          <t>Manajemen Proyek TI</t>
-        </is>
-      </c>
-      <c r="D82" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E82" s="19" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F82" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G82" s="19" t="inlineStr">
-        <is>
-          <t>`STI-301`, `STI-304`</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="22" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B83" s="20" t="inlineStr">
-        <is>
-          <t>`MKU-507`</t>
-        </is>
-      </c>
-      <c r="C83" s="20" t="inlineStr">
-        <is>
-          <t>Kuliah Pengabdian Kepada Masyarakat (KPM)</t>
-        </is>
-      </c>
-      <c r="D83" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E83" s="20" t="inlineStr">
-        <is>
-          <t>Praktik</t>
-        </is>
-      </c>
-      <c r="F83" s="20" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G83" s="20" t="inlineStr">
-        <is>
-          <t>$\ge 80\text{ SKS}$</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="21" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B84" s="19" t="inlineStr">
-        <is>
-          <t>`STA/B/C`</t>
-        </is>
-      </c>
-      <c r="C84" s="19" t="inlineStr">
-        <is>
-          <t>**MK Pilihan Peminatan 1**</t>
-        </is>
-      </c>
-      <c r="D84" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E84" s="19" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F84" s="19" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G84" s="19" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="22" t="inlineStr">
-        <is>
-          <t>38.B</t>
-        </is>
-      </c>
-      <c r="B85" s="20" t="inlineStr">
-        <is>
-          <t>`MKU-508`</t>
-        </is>
-      </c>
-      <c r="C85" s="20" t="inlineStr">
-        <is>
-          <t>Kewirausahaan II</t>
-        </is>
-      </c>
-      <c r="D85" s="22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E85" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F85" s="20" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G85" s="20" t="inlineStr">
-        <is>
-          <t>— (Kebijakan UWG, Sem 5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="19" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B86" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C86" s="19" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 5 (7 MK + 1 MK 0 SKS)**</t>
-        </is>
-      </c>
-      <c r="D86" s="21" t="inlineStr">
-        <is>
-          <t>**21**</t>
-        </is>
-      </c>
-      <c r="E86" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F86" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G86" s="19" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 101 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="87"/>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 6 (19 SKS) — Tahap Spesialisasi MBKM &amp; Platform Engineering</t>
-        </is>
-      </c>
-      <c r="B88" s="16" t="n"/>
-      <c r="C88" s="16" t="n"/>
-      <c r="D88" s="16" t="n"/>
-      <c r="E88" s="16" t="n"/>
-      <c r="F88" s="16" t="n"/>
-      <c r="G88" s="17" t="n"/>
-    </row>
-    <row r="89" ht="26" customHeight="1">
-      <c r="A89" s="18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B89" s="18" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D89" s="18" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E89" s="18" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F89" s="18" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G89" s="18" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="21" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B90" s="19" t="inlineStr">
-        <is>
-          <t>`STI-601`</t>
-        </is>
-      </c>
-      <c r="C90" s="19" t="inlineStr">
-        <is>
-          <t>Integrasi Layanan Cerdas Berbasis AI</t>
-        </is>
-      </c>
-      <c r="D90" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E90" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F90" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G90" s="19" t="inlineStr">
-        <is>
-          <t>`STI-501`, `STI-407`</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="22" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B91" s="20" t="inlineStr">
-        <is>
-          <t>`STI-602`</t>
-        </is>
-      </c>
-      <c r="C91" s="20" t="inlineStr">
-        <is>
-          <t>Smart City &amp; Pemerintahan Digital</t>
-        </is>
-      </c>
-      <c r="D91" s="22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E91" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F91" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G91" s="20" t="inlineStr">
-        <is>
-          <t>`STI-504`</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="21" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B92" s="19" t="inlineStr">
-        <is>
-          <t>`STI-603`</t>
-        </is>
-      </c>
-      <c r="C92" s="19" t="inlineStr">
-        <is>
-          <t>Keamanan Informasi Lanjut</t>
-        </is>
-      </c>
-      <c r="D92" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E92" s="19" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F92" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G92" s="19" t="inlineStr">
-        <is>
-          <t>`STI-405`</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="22" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B93" s="20" t="inlineStr">
-        <is>
-          <t>`STI-604`</t>
-        </is>
-      </c>
-      <c r="C93" s="20" t="inlineStr">
-        <is>
-          <t>Digital Platform Engineering</t>
-        </is>
-      </c>
-      <c r="D93" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E93" s="20" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F93" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G93" s="20" t="inlineStr">
-        <is>
-          <t>`STI-407`</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="21" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B94" s="19" t="inlineStr">
-        <is>
-          <t>`FST-611`</t>
-        </is>
-      </c>
-      <c r="C94" s="19" t="inlineStr">
-        <is>
-          <t>Metodologi Penelitian</t>
-        </is>
-      </c>
-      <c r="D94" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E94" s="19" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F94" s="19" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G94" s="19" t="inlineStr">
-        <is>
-          <t>$\ge 76\text{ SKS}$</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="22" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B95" s="20" t="inlineStr">
-        <is>
-          <t>`STA/B/C`</t>
-        </is>
-      </c>
-      <c r="C95" s="20" t="inlineStr">
-        <is>
-          <t>**MK Pilihan Peminatan 2**</t>
-        </is>
-      </c>
-      <c r="D95" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E95" s="20" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F95" s="20" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G95" s="20" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="21" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B96" s="19" t="inlineStr">
-        <is>
-          <t>`STA/B/C`</t>
-        </is>
-      </c>
-      <c r="C96" s="19" t="inlineStr">
-        <is>
-          <t>**MK Pilihan Peminatan 3**</t>
-        </is>
-      </c>
-      <c r="D96" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E96" s="19" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F96" s="19" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G96" s="19" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="20" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B97" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C97" s="20" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 6 (7 MK)**</t>
-        </is>
-      </c>
-      <c r="D97" s="22" t="inlineStr">
-        <is>
-          <t>**19**</t>
-        </is>
-      </c>
-      <c r="E97" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F97" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G97" s="20" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 120 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="98"/>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 7 (20 SKS) — Tahap Integrasi Capstone, PKL &amp; Pra-Skripsi</t>
-        </is>
-      </c>
-      <c r="B99" s="16" t="n"/>
-      <c r="C99" s="16" t="n"/>
-      <c r="D99" s="16" t="n"/>
-      <c r="E99" s="16" t="n"/>
-      <c r="F99" s="16" t="n"/>
-      <c r="G99" s="17" t="n"/>
-    </row>
-    <row r="100" ht="26" customHeight="1">
-      <c r="A100" s="18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B100" s="18" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C100" s="18" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D100" s="18" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E100" s="18" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F100" s="18" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G100" s="18" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="21" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B101" s="19" t="inlineStr">
-        <is>
-          <t>`STI-701`</t>
-        </is>
-      </c>
-      <c r="C101" s="19" t="inlineStr">
-        <is>
-          <t>Inovasi Teknologi dan Startup Digital</t>
-        </is>
-      </c>
-      <c r="D101" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E101" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F101" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G101" s="19" t="inlineStr">
-        <is>
-          <t>`STI-604`, `MKU-204`</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="22" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B102" s="20" t="inlineStr">
-        <is>
-          <t>`FST-610`</t>
-        </is>
-      </c>
-      <c r="C102" s="20" t="inlineStr">
-        <is>
-          <t>Capstone Project FSTI</t>
-        </is>
-      </c>
-      <c r="D102" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E102" s="20" t="inlineStr">
-        <is>
-          <t>Proyek</t>
-        </is>
-      </c>
-      <c r="F102" s="20" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G102" s="20" t="inlineStr">
-        <is>
-          <t>`STI-506`, $\ge 100\text{ SKS}$</t>
         </is>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="21" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B103" s="19" t="inlineStr">
         <is>
-          <t>`FST-612`</t>
+          <t>`STI-204`</t>
         </is>
       </c>
       <c r="C103" s="19" t="inlineStr">
         <is>
-          <t>Praktik Kerja Lapangan (PKL)</t>
+          <t>Matematika Diskrit dan Logika</t>
         </is>
       </c>
       <c r="D103" s="21" t="inlineStr">
@@ -18824,71 +18996,71 @@
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t>Magang</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F103" s="19" t="inlineStr">
         <is>
-          <t>FSTI</t>
+          <t>Core STI</t>
         </is>
       </c>
       <c r="G103" s="19" t="inlineStr">
         <is>
-          <t>$\ge 100\text{ SKS}$</t>
+          <t>`STI-103`</t>
         </is>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="22" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>`FST-613`</t>
+          <t>`STI-205`</t>
         </is>
       </c>
       <c r="C104" s="20" t="inlineStr">
         <is>
-          <t>Pra-Skripsi / Seminar Proposal</t>
+          <t>Aljabar Linear dan Matriks</t>
         </is>
       </c>
       <c r="D104" s="22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Seminar</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F104" s="20" t="inlineStr">
         <is>
-          <t>FSTI</t>
+          <t>Core STI</t>
         </is>
       </c>
       <c r="G104" s="20" t="inlineStr">
         <is>
-          <t>`FST-611`, $\ge 100\text{ SKS}$</t>
+          <t>`STI-102`</t>
         </is>
       </c>
     </row>
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B105" s="19" t="inlineStr">
         <is>
-          <t>`STA/B/C`</t>
+          <t>`FST-203`</t>
         </is>
       </c>
       <c r="C105" s="19" t="inlineStr">
         <is>
-          <t>**MK Pilihan Peminatan 4**</t>
+          <t>Struktur Data dan Algoritma</t>
         </is>
       </c>
       <c r="D105" s="21" t="inlineStr">
@@ -18898,685 +19070,2645 @@
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t>Elektif</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F105" s="19" t="inlineStr">
         <is>
-          <t>Peminatan</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G105" s="19" t="inlineStr">
         <is>
-          <t>Prasyarat Peminatan</t>
+          <t>`FST-102`</t>
         </is>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="22" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B106" s="20" t="inlineStr">
         <is>
-          <t>`STA/B/C`</t>
+          <t>`FST-204`</t>
         </is>
       </c>
       <c r="C106" s="20" t="inlineStr">
         <is>
-          <t>**MK Pilihan Peminatan 5**</t>
+          <t>Pengantar Kecerdasan Artifisial &amp; Data</t>
         </is>
       </c>
       <c r="D106" s="22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Elektif</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
         <is>
-          <t>Peminatan</t>
+          <t>FSTI</t>
         </is>
       </c>
       <c r="G106" s="20" t="inlineStr">
         <is>
-          <t>Prasyarat Peminatan</t>
+          <t>`FST-101`</t>
         </is>
       </c>
     </row>
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="21" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B107" s="19" t="inlineStr">
         <is>
-          <t>`STA/B/C`</t>
+          <t>`FST-205`</t>
         </is>
       </c>
       <c r="C107" s="19" t="inlineStr">
         <is>
-          <t>**MK Pilihan Peminatan 6**</t>
+          <t>Basic English for IT</t>
         </is>
       </c>
       <c r="D107" s="21" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E107" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F107" s="19" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G107" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="22" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>`FST-206`</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>Etika Profesi &amp; Hukum Digital</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F108" s="20" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G108" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t>`FST-207`</t>
+        </is>
+      </c>
+      <c r="C109" s="19" t="inlineStr">
+        <is>
+          <t>Sistem Basis Data</t>
+        </is>
+      </c>
+      <c r="D109" s="21" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E107" s="19" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F107" s="19" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G107" s="19" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="20" t="inlineStr">
+      <c r="E109" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F109" s="19" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G109" s="19" t="inlineStr">
+        <is>
+          <t>`FST-102`</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="16" customHeight="1">
+      <c r="A110" s="22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B110" s="20" t="inlineStr">
+        <is>
+          <t>`MKU-204`</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="inlineStr">
+        <is>
+          <t>Kewirausahaan I</t>
+        </is>
+      </c>
+      <c r="D110" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E110" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F110" s="20" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G110" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="19" t="inlineStr">
         <is>
           <t>**SUBTOTAL**</t>
         </is>
       </c>
-      <c r="B108" s="22" t="inlineStr">
+      <c r="B111" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C108" s="20" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 7 (7 MK)**</t>
-        </is>
-      </c>
-      <c r="D108" s="22" t="inlineStr">
+      <c r="C111" s="19" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 2 (8 MK)**</t>
+        </is>
+      </c>
+      <c r="D111" s="21" t="inlineStr">
         <is>
           <t>**20**</t>
         </is>
       </c>
-      <c r="E108" s="20" t="inlineStr">
+      <c r="E111" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F108" s="20" t="inlineStr">
+      <c r="F111" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G108" s="20" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 140 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="109"/>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 8 (6 SKS) — Tahap Penyelesaian Skripsi / Non-Skripsi</t>
-        </is>
-      </c>
-      <c r="B110" s="16" t="n"/>
-      <c r="C110" s="16" t="n"/>
-      <c r="D110" s="16" t="n"/>
-      <c r="E110" s="16" t="n"/>
-      <c r="F110" s="16" t="n"/>
-      <c r="G110" s="17" t="n"/>
-    </row>
-    <row r="111" ht="26" customHeight="1">
-      <c r="A111" s="18" t="inlineStr">
+      <c r="G111" s="19" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 39 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="112"/>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 3 (20 SKS) — Penguatan Core RPL, OS, Jarkom &amp; UI/UX</t>
+        </is>
+      </c>
+      <c r="B113" s="16" t="n"/>
+      <c r="C113" s="16" t="n"/>
+      <c r="D113" s="16" t="n"/>
+      <c r="E113" s="16" t="n"/>
+      <c r="F113" s="16" t="n"/>
+      <c r="G113" s="17" t="n"/>
+    </row>
+    <row r="114" ht="26" customHeight="1">
+      <c r="A114" s="18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B111" s="18" t="inlineStr">
+      <c r="B114" s="18" t="inlineStr">
         <is>
           <t>Kode MK</t>
         </is>
       </c>
-      <c r="C111" s="18" t="inlineStr">
+      <c r="C114" s="18" t="inlineStr">
         <is>
           <t>Nama Mata Kuliah</t>
         </is>
       </c>
-      <c r="D111" s="18" t="inlineStr">
+      <c r="D114" s="18" t="inlineStr">
         <is>
           <t>SKS</t>
         </is>
       </c>
-      <c r="E111" s="18" t="inlineStr">
+      <c r="E114" s="18" t="inlineStr">
         <is>
           <t>Tipe</t>
         </is>
       </c>
-      <c r="F111" s="18" t="inlineStr">
+      <c r="F114" s="18" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="G111" s="18" t="inlineStr">
+      <c r="G114" s="18" t="inlineStr">
         <is>
           <t>Prasyarat</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="21" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B112" s="19" t="inlineStr">
-        <is>
-          <t>`FST-714`</t>
-        </is>
-      </c>
-      <c r="C112" s="19" t="inlineStr">
-        <is>
-          <t>Skripsi / Tugas Akhir</t>
-        </is>
-      </c>
-      <c r="D112" s="21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E112" s="19" t="inlineStr">
-        <is>
-          <t>Mandiri</t>
-        </is>
-      </c>
-      <c r="F112" s="19" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G112" s="19" t="inlineStr">
-        <is>
-          <t>`FST-613`, $\ge 120\text{ SKS}$</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="20" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B113" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C113" s="20" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 8 (1 MK)**</t>
-        </is>
-      </c>
-      <c r="D113" s="22" t="inlineStr">
-        <is>
-          <t>**6**</t>
-        </is>
-      </c>
-      <c r="E113" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F113" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G113" s="20" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 146 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="114"/>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="15" t="inlineStr">
-        <is>
-          <t>3.1 REKAPITULASI &amp; MATRIKS KALKULASI SKS AKUMULATIF SEMESTER 1 – 8</t>
-        </is>
-      </c>
-      <c r="B115" s="16" t="n"/>
-      <c r="C115" s="16" t="n"/>
-      <c r="D115" s="16" t="n"/>
-      <c r="E115" s="16" t="n"/>
-      <c r="F115" s="17" t="n"/>
-    </row>
-    <row r="116" ht="26" customHeight="1">
-      <c r="A116" s="18" t="inlineStr">
-        <is>
-          <t>Semester</t>
-        </is>
-      </c>
-      <c r="B116" s="18" t="inlineStr">
-        <is>
-          <t>Jumlah MK</t>
-        </is>
-      </c>
-      <c r="C116" s="18" t="inlineStr">
-        <is>
-          <t>Beban SKS</t>
-        </is>
-      </c>
-      <c r="D116" s="18" t="inlineStr">
-        <is>
-          <t>SKS Kumulatif</t>
-        </is>
-      </c>
-      <c r="E116" s="18" t="inlineStr">
-        <is>
-          <t>Persentase</t>
-        </is>
-      </c>
-      <c r="F116" s="18" t="inlineStr">
-        <is>
-          <t>Tahapan Akademik &amp; Karakteristik</t>
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B115" s="19" t="inlineStr">
+        <is>
+          <t>`STI-306`</t>
+        </is>
+      </c>
+      <c r="C115" s="19" t="inlineStr">
+        <is>
+          <t>Analisis dan Perancangan Sistem Informasi</t>
+        </is>
+      </c>
+      <c r="D115" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E115" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F115" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G115" s="19" t="inlineStr">
+        <is>
+          <t>`STI-101`, `FST-207`</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="16" customHeight="1">
+      <c r="A116" s="22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B116" s="20" t="inlineStr">
+        <is>
+          <t>`STI-307`</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="inlineStr">
+        <is>
+          <t>Sistem Cerdas</t>
+        </is>
+      </c>
+      <c r="D116" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E116" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F116" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G116" s="20" t="inlineStr">
+        <is>
+          <t>`STI-204`, `FST-204`</t>
         </is>
       </c>
     </row>
     <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 1**</t>
-        </is>
-      </c>
-      <c r="B117" s="21" t="inlineStr">
-        <is>
-          <t>8 MK</t>
-        </is>
-      </c>
-      <c r="C117" s="21" t="inlineStr">
-        <is>
-          <t>19 SKS</t>
+      <c r="A117" s="21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B117" s="19" t="inlineStr">
+        <is>
+          <t>`STI-308`</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t>UI/UX Design &amp; Prototyping</t>
         </is>
       </c>
       <c r="D117" s="21" t="inlineStr">
         <is>
-          <t>19 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F117" s="19" t="inlineStr">
         <is>
-          <t>Tahap Fondasi Sains, Algoritma &amp; Logika</t>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G117" s="19" t="inlineStr">
+        <is>
+          <t>`FST-101`</t>
         </is>
       </c>
     </row>
     <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 2**</t>
-        </is>
-      </c>
-      <c r="B118" s="22" t="inlineStr">
-        <is>
-          <t>8 MK</t>
-        </is>
-      </c>
-      <c r="C118" s="22" t="inlineStr">
-        <is>
-          <t>20 SKS</t>
+      <c r="A118" s="22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>`STI-309`</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="inlineStr">
+        <is>
+          <t>Rekayasa Perangkat Lunak</t>
         </is>
       </c>
       <c r="D118" s="22" t="inlineStr">
         <is>
-          <t>39 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F118" s="20" t="inlineStr">
         <is>
-          <t>Tahap Fondasi Data, Matdis &amp; OOP</t>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G118" s="20" t="inlineStr">
+        <is>
+          <t>`FST-203`</t>
         </is>
       </c>
     </row>
     <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 3**</t>
-        </is>
-      </c>
-      <c r="B119" s="21" t="inlineStr">
-        <is>
-          <t>7 MK</t>
-        </is>
-      </c>
-      <c r="C119" s="21" t="inlineStr">
-        <is>
-          <t>20 SKS</t>
+      <c r="A119" s="21" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B119" s="19" t="inlineStr">
+        <is>
+          <t>`STI-310`</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="inlineStr">
+        <is>
+          <t>Sistem Operasi</t>
         </is>
       </c>
       <c r="D119" s="21" t="inlineStr">
         <is>
-          <t>59 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F119" s="19" t="inlineStr">
         <is>
-          <t>Tahap Penguatan Core RPL, OS &amp; Jaringan</t>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G119" s="19" t="inlineStr">
+        <is>
+          <t>`STI-103`</t>
         </is>
       </c>
     </row>
     <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 4**</t>
-        </is>
-      </c>
-      <c r="B120" s="22" t="inlineStr">
-        <is>
-          <t>8 MK</t>
-        </is>
-      </c>
-      <c r="C120" s="22" t="inlineStr">
-        <is>
-          <t>21 SKS</t>
+      <c r="A120" s="22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B120" s="20" t="inlineStr">
+        <is>
+          <t>`STI-311`</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="inlineStr">
+        <is>
+          <t>Web Front End Development</t>
         </is>
       </c>
       <c r="D120" s="22" t="inlineStr">
         <is>
-          <t>80 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F120" s="20" t="inlineStr">
         <is>
-          <t>Tahap Penguatan Core AI/ML, NLP &amp; Cloud</t>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G120" s="20" t="inlineStr">
+        <is>
+          <t>`FST-102`</t>
         </is>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 5**</t>
-        </is>
-      </c>
-      <c r="B121" s="21" t="inlineStr">
-        <is>
-          <t>7 MK</t>
-        </is>
-      </c>
-      <c r="C121" s="21" t="inlineStr">
-        <is>
-          <t>21 SKS</t>
+      <c r="A121" s="21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B121" s="19" t="inlineStr">
+        <is>
+          <t>`STI-312`</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="inlineStr">
+        <is>
+          <t>Jaringan Komputer</t>
         </is>
       </c>
       <c r="D121" s="21" t="inlineStr">
         <is>
-          <t>101 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E121" s="19" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F121" s="19" t="inlineStr">
         <is>
-          <t>Tahap Spesialisasi Deep Learning &amp; IoT</t>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G121" s="19" t="inlineStr">
+        <is>
+          <t>`STI-103`</t>
         </is>
       </c>
     </row>
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="20" t="inlineStr">
         <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B122" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 3 (7 MK)**</t>
+        </is>
+      </c>
+      <c r="D122" s="22" t="inlineStr">
+        <is>
+          <t>**20**</t>
+        </is>
+      </c>
+      <c r="E122" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F122" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G122" s="20" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 59 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="123"/>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 4 (21 SKS) — Penguatan Core AI/ML, NLP, DW &amp; Cloud</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="n"/>
+      <c r="C124" s="16" t="n"/>
+      <c r="D124" s="16" t="n"/>
+      <c r="E124" s="16" t="n"/>
+      <c r="F124" s="16" t="n"/>
+      <c r="G124" s="17" t="n"/>
+    </row>
+    <row r="125" ht="26" customHeight="1">
+      <c r="A125" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B125" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C125" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D125" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E125" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F125" s="18" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G125" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="16" customHeight="1">
+      <c r="A126" s="21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B126" s="19" t="inlineStr">
+        <is>
+          <t>`STI-413`</t>
+        </is>
+      </c>
+      <c r="C126" s="19" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="D126" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E126" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F126" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G126" s="19" t="inlineStr">
+        <is>
+          <t>`STI-205`, `STI-307`</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B127" s="20" t="inlineStr">
+        <is>
+          <t>`STI-414`</t>
+        </is>
+      </c>
+      <c r="C127" s="20" t="inlineStr">
+        <is>
+          <t>Pengantar NLP &amp; Information Retrieval</t>
+        </is>
+      </c>
+      <c r="D127" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E127" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F127" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G127" s="20" t="inlineStr">
+        <is>
+          <t>`STI-307`</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="21" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B128" s="19" t="inlineStr">
+        <is>
+          <t>`STI-415`</t>
+        </is>
+      </c>
+      <c r="C128" s="19" t="inlineStr">
+        <is>
+          <t>Data Warehouse &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="D128" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E128" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F128" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G128" s="19" t="inlineStr">
+        <is>
+          <t>`FST-207`</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="16" customHeight="1">
+      <c r="A129" s="22" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B129" s="20" t="inlineStr">
+        <is>
+          <t>`STI-416`</t>
+        </is>
+      </c>
+      <c r="C129" s="20" t="inlineStr">
+        <is>
+          <t>Web Back End Development</t>
+        </is>
+      </c>
+      <c r="D129" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E129" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F129" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G129" s="20" t="inlineStr">
+        <is>
+          <t>`FST-207`, `STI-311`</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="A130" s="21" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B130" s="19" t="inlineStr">
+        <is>
+          <t>`STI-417`</t>
+        </is>
+      </c>
+      <c r="C130" s="19" t="inlineStr">
+        <is>
+          <t>Komputasi Awan (Cloud Computing)</t>
+        </is>
+      </c>
+      <c r="D130" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E130" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F130" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G130" s="19" t="inlineStr">
+        <is>
+          <t>`STI-312`, `STI-310`</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="16" customHeight="1">
+      <c r="A131" s="22" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B131" s="20" t="inlineStr">
+        <is>
+          <t>`STI-418`</t>
+        </is>
+      </c>
+      <c r="C131" s="20" t="inlineStr">
+        <is>
+          <t>Dasar Keamanan Informasi</t>
+        </is>
+      </c>
+      <c r="D131" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E131" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F131" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G131" s="20" t="inlineStr">
+        <is>
+          <t>`STI-312`</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="16" customHeight="1">
+      <c r="A132" s="21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B132" s="19" t="inlineStr">
+        <is>
+          <t>`FST-408`</t>
+        </is>
+      </c>
+      <c r="C132" s="19" t="inlineStr">
+        <is>
+          <t>Probabilitas dan Statistika</t>
+        </is>
+      </c>
+      <c r="D132" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E132" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F132" s="19" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G132" s="19" t="inlineStr">
+        <is>
+          <t>`STI-102`</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="22" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B133" s="20" t="inlineStr">
+        <is>
+          <t>`MKU-405`</t>
+        </is>
+      </c>
+      <c r="C133" s="20" t="inlineStr">
+        <is>
+          <t>Kewarganegaraan</t>
+        </is>
+      </c>
+      <c r="D133" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E133" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F133" s="20" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G133" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="16" customHeight="1">
+      <c r="A134" s="21" t="inlineStr">
+        <is>
+          <t>31.B</t>
+        </is>
+      </c>
+      <c r="B134" s="19" t="inlineStr">
+        <is>
+          <t>`MKU-406`</t>
+        </is>
+      </c>
+      <c r="C134" s="21" t="inlineStr">
+        <is>
+          <t>Agama II</t>
+        </is>
+      </c>
+      <c r="D134" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E134" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F134" s="19" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G134" s="19" t="inlineStr">
+        <is>
+          <t>— (Kebijakan UWG, Sem 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="16" customHeight="1">
+      <c r="A135" s="20" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B135" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C135" s="20" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 4 (8 MK + 1 MK 0 SKS)**</t>
+        </is>
+      </c>
+      <c r="D135" s="22" t="inlineStr">
+        <is>
+          <t>**21**</t>
+        </is>
+      </c>
+      <c r="E135" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F135" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G135" s="20" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 80 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="136"/>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 5 (21 SKS) — Tahap Spesialisasi Deep Learning, IoT &amp; Peminatan 1</t>
+        </is>
+      </c>
+      <c r="B137" s="16" t="n"/>
+      <c r="C137" s="16" t="n"/>
+      <c r="D137" s="16" t="n"/>
+      <c r="E137" s="16" t="n"/>
+      <c r="F137" s="16" t="n"/>
+      <c r="G137" s="17" t="n"/>
+    </row>
+    <row r="138" ht="26" customHeight="1">
+      <c r="A138" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D138" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F138" s="18" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G138" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="16" customHeight="1">
+      <c r="A139" s="21" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B139" s="19" t="inlineStr">
+        <is>
+          <t>`STI-519`</t>
+        </is>
+      </c>
+      <c r="C139" s="19" t="inlineStr">
+        <is>
+          <t>Keamanan Informasi Lanjut</t>
+        </is>
+      </c>
+      <c r="D139" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E139" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F139" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G139" s="19" t="inlineStr">
+        <is>
+          <t>`STI-418`</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" s="22" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B140" s="20" t="inlineStr">
+        <is>
+          <t>`STI-520`</t>
+        </is>
+      </c>
+      <c r="C140" s="20" t="inlineStr">
+        <is>
+          <t>Data Mining &amp; Visualisasi Data</t>
+        </is>
+      </c>
+      <c r="D140" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E140" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F140" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G140" s="20" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-415`</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="21" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B141" s="19" t="inlineStr">
+        <is>
+          <t>`STI-521`</t>
+        </is>
+      </c>
+      <c r="C141" s="19" t="inlineStr">
+        <is>
+          <t>Internet of Things (IoT)</t>
+        </is>
+      </c>
+      <c r="D141" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E141" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F141" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G141" s="19" t="inlineStr">
+        <is>
+          <t>`STI-312`, `STI-310`</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="16" customHeight="1">
+      <c r="A142" s="22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B142" s="20" t="inlineStr">
+        <is>
+          <t>`STI-522`</t>
+        </is>
+      </c>
+      <c r="C142" s="20" t="inlineStr">
+        <is>
+          <t>Pemrograman Aplikasi Mobile</t>
+        </is>
+      </c>
+      <c r="D142" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E142" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F142" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G142" s="20" t="inlineStr">
+        <is>
+          <t>`STI-311`, `STI-416`</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="16" customHeight="1">
+      <c r="A143" s="21" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B143" s="19" t="inlineStr">
+        <is>
+          <t>`STI-523`</t>
+        </is>
+      </c>
+      <c r="C143" s="19" t="inlineStr">
+        <is>
+          <t>Manajemen Proyek TI</t>
+        </is>
+      </c>
+      <c r="D143" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E143" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F143" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G143" s="19" t="inlineStr">
+        <is>
+          <t>`STI-306`, `STI-309`</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="22" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B144" s="20" t="inlineStr">
+        <is>
+          <t>`MKU-507`</t>
+        </is>
+      </c>
+      <c r="C144" s="20" t="inlineStr">
+        <is>
+          <t>Kuliah Pengabdian Kepada Masyarakat (KPM)</t>
+        </is>
+      </c>
+      <c r="D144" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E144" s="20" t="inlineStr">
+        <is>
+          <t>Praktik</t>
+        </is>
+      </c>
+      <c r="F144" s="20" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G144" s="20" t="inlineStr">
+        <is>
+          <t>$\ge 80\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="21" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B145" s="19" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C145" s="19" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 1**</t>
+        </is>
+      </c>
+      <c r="D145" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E145" s="19" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F145" s="19" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G145" s="19" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="16" customHeight="1">
+      <c r="A146" s="22" t="inlineStr">
+        <is>
+          <t>38.B</t>
+        </is>
+      </c>
+      <c r="B146" s="20" t="inlineStr">
+        <is>
+          <t>`MKU-508`</t>
+        </is>
+      </c>
+      <c r="C146" s="20" t="inlineStr">
+        <is>
+          <t>Kewirausahaan II</t>
+        </is>
+      </c>
+      <c r="D146" s="22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E146" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F146" s="20" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G146" s="20" t="inlineStr">
+        <is>
+          <t>— (Kebijakan UWG, Sem 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" s="19" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B147" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C147" s="19" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 5 (7 MK + 1 MK 0 SKS)**</t>
+        </is>
+      </c>
+      <c r="D147" s="21" t="inlineStr">
+        <is>
+          <t>**21**</t>
+        </is>
+      </c>
+      <c r="E147" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F147" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G147" s="19" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 101 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="148"/>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 6 (19 SKS) — Tahap Spesialisasi MBKM &amp; Platform Engineering</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="n"/>
+      <c r="C149" s="16" t="n"/>
+      <c r="D149" s="16" t="n"/>
+      <c r="E149" s="16" t="n"/>
+      <c r="F149" s="16" t="n"/>
+      <c r="G149" s="17" t="n"/>
+    </row>
+    <row r="150" ht="26" customHeight="1">
+      <c r="A150" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B150" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D150" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E150" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F150" s="18" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G150" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="21" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B151" s="19" t="inlineStr">
+        <is>
+          <t>`STI-624`</t>
+        </is>
+      </c>
+      <c r="C151" s="19" t="inlineStr">
+        <is>
+          <t>Integrasi Layanan Cerdas Berbasis AI</t>
+        </is>
+      </c>
+      <c r="D151" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E151" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F151" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G151" s="19" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-416`</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="16" customHeight="1">
+      <c r="A152" s="22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B152" s="20" t="inlineStr">
+        <is>
+          <t>`STI-625`</t>
+        </is>
+      </c>
+      <c r="C152" s="20" t="inlineStr">
+        <is>
+          <t>Smart City &amp; Pemerintahan Digital</t>
+        </is>
+      </c>
+      <c r="D152" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E152" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F152" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G152" s="20" t="inlineStr">
+        <is>
+          <t>`STI-521`</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="21" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B153" s="19" t="inlineStr">
+        <is>
+          <t>`STI-626`</t>
+        </is>
+      </c>
+      <c r="C153" s="19" t="inlineStr">
+        <is>
+          <t>Deep Learning &amp; Neural Networks</t>
+        </is>
+      </c>
+      <c r="D153" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E153" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F153" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G153" s="19" t="inlineStr">
+        <is>
+          <t>`STI-413`</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" s="22" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B154" s="20" t="inlineStr">
+        <is>
+          <t>`STI-627`</t>
+        </is>
+      </c>
+      <c r="C154" s="20" t="inlineStr">
+        <is>
+          <t>Digital Platform Engineering</t>
+        </is>
+      </c>
+      <c r="D154" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E154" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F154" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G154" s="20" t="inlineStr">
+        <is>
+          <t>`STI-416`</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="21" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B155" s="19" t="inlineStr">
+        <is>
+          <t>`FST-611`</t>
+        </is>
+      </c>
+      <c r="C155" s="19" t="inlineStr">
+        <is>
+          <t>Metodologi Penelitian</t>
+        </is>
+      </c>
+      <c r="D155" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E155" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F155" s="19" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G155" s="19" t="inlineStr">
+        <is>
+          <t>$\ge 76\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="22" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B156" s="20" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C156" s="20" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 2**</t>
+        </is>
+      </c>
+      <c r="D156" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E156" s="20" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F156" s="20" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G156" s="20" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="21" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B157" s="19" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C157" s="19" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 3**</t>
+        </is>
+      </c>
+      <c r="D157" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E157" s="19" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F157" s="19" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G157" s="19" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="20" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B158" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C158" s="20" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 6 (7 MK)**</t>
+        </is>
+      </c>
+      <c r="D158" s="22" t="inlineStr">
+        <is>
+          <t>**19**</t>
+        </is>
+      </c>
+      <c r="E158" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F158" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G158" s="20" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 120 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="159"/>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 7 (20 SKS) — Tahap Integrasi Capstone, PKL &amp; Pra-Skripsi</t>
+        </is>
+      </c>
+      <c r="B160" s="16" t="n"/>
+      <c r="C160" s="16" t="n"/>
+      <c r="D160" s="16" t="n"/>
+      <c r="E160" s="16" t="n"/>
+      <c r="F160" s="16" t="n"/>
+      <c r="G160" s="17" t="n"/>
+    </row>
+    <row r="161" ht="26" customHeight="1">
+      <c r="A161" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B161" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D161" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E161" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F161" s="18" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G161" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="16" customHeight="1">
+      <c r="A162" s="21" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B162" s="19" t="inlineStr">
+        <is>
+          <t>`STI-728`</t>
+        </is>
+      </c>
+      <c r="C162" s="19" t="inlineStr">
+        <is>
+          <t>Inovasi Teknologi dan Startup Digital</t>
+        </is>
+      </c>
+      <c r="D162" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E162" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F162" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G162" s="19" t="inlineStr">
+        <is>
+          <t>`STI-627`, `MKU-204`</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="16" customHeight="1">
+      <c r="A163" s="22" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B163" s="20" t="inlineStr">
+        <is>
+          <t>`FST-610`</t>
+        </is>
+      </c>
+      <c r="C163" s="20" t="inlineStr">
+        <is>
+          <t>Capstone Project FSTI</t>
+        </is>
+      </c>
+      <c r="D163" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E163" s="20" t="inlineStr">
+        <is>
+          <t>Proyek</t>
+        </is>
+      </c>
+      <c r="F163" s="20" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G163" s="20" t="inlineStr">
+        <is>
+          <t>`STI-523`, $\ge 100\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="16" customHeight="1">
+      <c r="A164" s="21" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B164" s="19" t="inlineStr">
+        <is>
+          <t>`FST-612`</t>
+        </is>
+      </c>
+      <c r="C164" s="19" t="inlineStr">
+        <is>
+          <t>Praktik Kerja Lapangan (PKL)</t>
+        </is>
+      </c>
+      <c r="D164" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E164" s="19" t="inlineStr">
+        <is>
+          <t>Magang</t>
+        </is>
+      </c>
+      <c r="F164" s="19" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G164" s="19" t="inlineStr">
+        <is>
+          <t>$\ge 100\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="16" customHeight="1">
+      <c r="A165" s="22" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B165" s="20" t="inlineStr">
+        <is>
+          <t>`FST-613`</t>
+        </is>
+      </c>
+      <c r="C165" s="20" t="inlineStr">
+        <is>
+          <t>Pra-Skripsi / Seminar Proposal</t>
+        </is>
+      </c>
+      <c r="D165" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E165" s="20" t="inlineStr">
+        <is>
+          <t>Seminar</t>
+        </is>
+      </c>
+      <c r="F165" s="20" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G165" s="20" t="inlineStr">
+        <is>
+          <t>`FST-611`, $\ge 100\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="16" customHeight="1">
+      <c r="A166" s="21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B166" s="19" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C166" s="19" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 4**</t>
+        </is>
+      </c>
+      <c r="D166" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E166" s="19" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F166" s="19" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G166" s="19" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="16" customHeight="1">
+      <c r="A167" s="22" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B167" s="20" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C167" s="20" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 5**</t>
+        </is>
+      </c>
+      <c r="D167" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E167" s="20" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F167" s="20" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G167" s="20" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="16" customHeight="1">
+      <c r="A168" s="21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B168" s="19" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C168" s="19" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 6**</t>
+        </is>
+      </c>
+      <c r="D168" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E168" s="19" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F168" s="19" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G168" s="19" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="16" customHeight="1">
+      <c r="A169" s="20" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B169" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C169" s="20" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 7 (7 MK)**</t>
+        </is>
+      </c>
+      <c r="D169" s="22" t="inlineStr">
+        <is>
+          <t>**20**</t>
+        </is>
+      </c>
+      <c r="E169" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F169" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G169" s="20" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 140 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="170"/>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 8 (6 SKS) — Tahap Penyelesaian Skripsi / Non-Skripsi</t>
+        </is>
+      </c>
+      <c r="B171" s="16" t="n"/>
+      <c r="C171" s="16" t="n"/>
+      <c r="D171" s="16" t="n"/>
+      <c r="E171" s="16" t="n"/>
+      <c r="F171" s="16" t="n"/>
+      <c r="G171" s="17" t="n"/>
+    </row>
+    <row r="172" ht="26" customHeight="1">
+      <c r="A172" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B172" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D172" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E172" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F172" s="18" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G172" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="16" customHeight="1">
+      <c r="A173" s="21" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B173" s="19" t="inlineStr">
+        <is>
+          <t>`FST-714`</t>
+        </is>
+      </c>
+      <c r="C173" s="19" t="inlineStr">
+        <is>
+          <t>Skripsi / Tugas Akhir</t>
+        </is>
+      </c>
+      <c r="D173" s="21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E173" s="19" t="inlineStr">
+        <is>
+          <t>Mandiri</t>
+        </is>
+      </c>
+      <c r="F173" s="19" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G173" s="19" t="inlineStr">
+        <is>
+          <t>`FST-613`, $\ge 120\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="16" customHeight="1">
+      <c r="A174" s="20" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B174" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C174" s="20" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 8 (1 MK)**</t>
+        </is>
+      </c>
+      <c r="D174" s="22" t="inlineStr">
+        <is>
+          <t>**6**</t>
+        </is>
+      </c>
+      <c r="E174" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F174" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G174" s="20" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 146 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="175"/>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="15" t="inlineStr">
+        <is>
+          <t>3.1 REKAPITULASI &amp; MATRIKS KALKULASI SKS AKUMULATIF SEMESTER 1 – 8</t>
+        </is>
+      </c>
+      <c r="B176" s="16" t="n"/>
+      <c r="C176" s="16" t="n"/>
+      <c r="D176" s="16" t="n"/>
+      <c r="E176" s="16" t="n"/>
+      <c r="F176" s="17" t="n"/>
+    </row>
+    <row r="177" ht="26" customHeight="1">
+      <c r="A177" s="18" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="B177" s="18" t="inlineStr">
+        <is>
+          <t>Jumlah MK</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="inlineStr">
+        <is>
+          <t>Beban SKS</t>
+        </is>
+      </c>
+      <c r="D177" s="18" t="inlineStr">
+        <is>
+          <t>SKS Kumulatif</t>
+        </is>
+      </c>
+      <c r="E177" s="18" t="inlineStr">
+        <is>
+          <t>Persentase</t>
+        </is>
+      </c>
+      <c r="F177" s="18" t="inlineStr">
+        <is>
+          <t>Tahapan Akademik &amp; Karakteristik</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="16" customHeight="1">
+      <c r="A178" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 1**</t>
+        </is>
+      </c>
+      <c r="B178" s="21" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="C178" s="21" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="D178" s="21" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="E178" s="19" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="F178" s="19" t="inlineStr">
+        <is>
+          <t>Tahap Fondasi Sains, Algoritma &amp; Logika</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="16" customHeight="1">
+      <c r="A179" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 2**</t>
+        </is>
+      </c>
+      <c r="B179" s="22" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="C179" s="22" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="D179" s="22" t="inlineStr">
+        <is>
+          <t>39 SKS</t>
+        </is>
+      </c>
+      <c r="E179" s="20" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="F179" s="20" t="inlineStr">
+        <is>
+          <t>Tahap Fondasi Data, Matdis &amp; OOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="16" customHeight="1">
+      <c r="A180" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 3**</t>
+        </is>
+      </c>
+      <c r="B180" s="21" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="C180" s="21" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="D180" s="21" t="inlineStr">
+        <is>
+          <t>59 SKS</t>
+        </is>
+      </c>
+      <c r="E180" s="19" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="F180" s="19" t="inlineStr">
+        <is>
+          <t>Tahap Penguatan Core RPL, OS &amp; Jaringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="16" customHeight="1">
+      <c r="A181" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 4**</t>
+        </is>
+      </c>
+      <c r="B181" s="22" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="C181" s="22" t="inlineStr">
+        <is>
+          <t>21 SKS</t>
+        </is>
+      </c>
+      <c r="D181" s="22" t="inlineStr">
+        <is>
+          <t>80 SKS</t>
+        </is>
+      </c>
+      <c r="E181" s="20" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="F181" s="20" t="inlineStr">
+        <is>
+          <t>Tahap Penguatan Core AI/ML, NLP &amp; Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="16" customHeight="1">
+      <c r="A182" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 5**</t>
+        </is>
+      </c>
+      <c r="B182" s="21" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="C182" s="21" t="inlineStr">
+        <is>
+          <t>21 SKS</t>
+        </is>
+      </c>
+      <c r="D182" s="21" t="inlineStr">
+        <is>
+          <t>101 SKS</t>
+        </is>
+      </c>
+      <c r="E182" s="19" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="F182" s="19" t="inlineStr">
+        <is>
+          <t>Tahap Spesialisasi Deep Learning &amp; IoT</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="16" customHeight="1">
+      <c r="A183" s="20" t="inlineStr">
+        <is>
           <t>**Sem 6**</t>
         </is>
       </c>
-      <c r="B122" s="22" t="inlineStr">
+      <c r="B183" s="22" t="inlineStr">
         <is>
           <t>7 MK</t>
         </is>
       </c>
-      <c r="C122" s="22" t="inlineStr">
+      <c r="C183" s="22" t="inlineStr">
         <is>
           <t>19 SKS</t>
         </is>
       </c>
-      <c r="D122" s="22" t="inlineStr">
+      <c r="D183" s="22" t="inlineStr">
         <is>
           <t>120 SKS</t>
         </is>
       </c>
-      <c r="E122" s="20" t="inlineStr">
+      <c r="E183" s="20" t="inlineStr">
         <is>
           <t>13,0%</t>
         </is>
       </c>
-      <c r="F122" s="20" t="inlineStr">
+      <c r="F183" s="20" t="inlineStr">
         <is>
           <t>Tahap Spesialisasi MBKM &amp; Platform Eng</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="19" t="inlineStr">
+    <row r="184" ht="16" customHeight="1">
+      <c r="A184" s="19" t="inlineStr">
         <is>
           <t>**Sem 7**</t>
         </is>
       </c>
-      <c r="B123" s="21" t="inlineStr">
+      <c r="B184" s="21" t="inlineStr">
         <is>
           <t>7 MK</t>
         </is>
       </c>
-      <c r="C123" s="21" t="inlineStr">
+      <c r="C184" s="21" t="inlineStr">
         <is>
           <t>20 SKS</t>
         </is>
       </c>
-      <c r="D123" s="21" t="inlineStr">
+      <c r="D184" s="21" t="inlineStr">
         <is>
           <t>140 SKS</t>
         </is>
       </c>
-      <c r="E123" s="19" t="inlineStr">
+      <c r="E184" s="19" t="inlineStr">
         <is>
           <t>13,7%</t>
         </is>
       </c>
-      <c r="F123" s="19" t="inlineStr">
+      <c r="F184" s="19" t="inlineStr">
         <is>
           <t>Tahap Integrasi Capstone, PKL &amp; Sempro</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="20" t="inlineStr">
+    <row r="185" ht="16" customHeight="1">
+      <c r="A185" s="20" t="inlineStr">
         <is>
           <t>**Sem 8**</t>
         </is>
       </c>
-      <c r="B124" s="22" t="inlineStr">
+      <c r="B185" s="22" t="inlineStr">
         <is>
           <t>1 MK</t>
         </is>
       </c>
-      <c r="C124" s="22" t="inlineStr">
+      <c r="C185" s="22" t="inlineStr">
         <is>
           <t>6 SKS</t>
         </is>
       </c>
-      <c r="D124" s="22" t="inlineStr">
+      <c r="D185" s="22" t="inlineStr">
         <is>
           <t>146 SKS</t>
         </is>
       </c>
-      <c r="E124" s="20" t="inlineStr">
+      <c r="E185" s="20" t="inlineStr">
         <is>
           <t>4,1%</t>
         </is>
       </c>
-      <c r="F124" s="20" t="inlineStr">
+      <c r="F185" s="20" t="inlineStr">
         <is>
           <t>Tahap Penyelesaian Skripsi / Non-Skripsi</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="16" customHeight="1">
-      <c r="A125" s="19" t="inlineStr">
+    <row r="186" ht="16" customHeight="1">
+      <c r="A186" s="19" t="inlineStr">
         <is>
           <t>**TOTAL**</t>
         </is>
       </c>
-      <c r="B125" s="19" t="inlineStr">
+      <c r="B186" s="19" t="inlineStr">
         <is>
           <t>**55 MK**</t>
         </is>
       </c>
-      <c r="C125" s="19" t="inlineStr">
+      <c r="C186" s="19" t="inlineStr">
         <is>
           <t>**146 SKS**</t>
         </is>
       </c>
-      <c r="D125" s="19" t="inlineStr">
+      <c r="D186" s="19" t="inlineStr">
         <is>
           <t>**146 SKS**</t>
         </is>
       </c>
-      <c r="E125" s="19" t="inlineStr">
+      <c r="E186" s="19" t="inlineStr">
         <is>
           <t>**100,0%**</t>
         </is>
       </c>
-      <c r="F125" s="19" t="inlineStr">
+      <c r="F186" s="19" t="inlineStr">
         <is>
           <t>**Paket Lulus Tepat Waktu (4 Tahun)**</t>
         </is>
       </c>
     </row>
-    <row r="126"/>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="15" t="inlineStr">
+    <row r="187"/>
+    <row r="188" ht="20" customHeight="1">
+      <c r="A188" s="15" t="inlineStr">
         <is>
           <t>3 PEMINATAN SPESIALISASI KEAHLIAN SISTEKIN</t>
         </is>
       </c>
-      <c r="B127" s="16" t="n"/>
-      <c r="C127" s="16" t="n"/>
-      <c r="D127" s="16" t="n"/>
-      <c r="E127" s="16" t="n"/>
-      <c r="F127" s="17" t="n"/>
-    </row>
-    <row r="128" ht="26" customHeight="1">
-      <c r="A128" s="18" t="inlineStr">
+      <c r="B188" s="16" t="n"/>
+      <c r="C188" s="16" t="n"/>
+      <c r="D188" s="16" t="n"/>
+      <c r="E188" s="16" t="n"/>
+      <c r="F188" s="17" t="n"/>
+    </row>
+    <row r="189" ht="26" customHeight="1">
+      <c r="A189" s="18" t="inlineStr">
         <is>
           <t>Peminatan</t>
         </is>
       </c>
-      <c r="B128" s="18" t="inlineStr">
+      <c r="B189" s="18" t="inlineStr">
         <is>
           <t>Basis Profil (PL)</t>
         </is>
       </c>
-      <c r="C128" s="18" t="inlineStr">
+      <c r="C189" s="18" t="inlineStr">
         <is>
           <t>Mata Kuliah Pilihan (@ 3 SKS)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="19" t="inlineStr">
+    <row r="190" ht="16" customHeight="1">
+      <c r="A190" s="19" t="inlineStr">
         <is>
           <t>**P1: Integrated Smart Systems** *(Flagship)*</t>
         </is>
       </c>
-      <c r="B129" s="19" t="inlineStr">
+      <c r="B190" s="19" t="inlineStr">
         <is>
           <t>**PL-1:** Intelligent IS &amp; Data/AI Engineer</t>
         </is>
       </c>
-      <c r="C129" s="19" t="inlineStr">
+      <c r="C190" s="19" t="inlineStr">
         <is>
           <t>1. `STA-01` Decision Support Systems (+P, Sem 5)&lt;br&gt;2. `STA-02` Computational Methods &amp; Numerics (+P, Sem 6)&lt;br&gt;3. `STA-03` Intelligent Agent Systems (+P, Sem 6)&lt;br&gt;4. `STA-04` MLOps and AI Pipeline (+P, Sem 7)&lt;br&gt;5. `STA-05` Conversational AI &amp; Assistant (+P, Sem 7)&lt;br&gt;6. `STA-06` Smart Surveillance &amp; IoT Analytics (+P, Sem 7)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="20" t="inlineStr">
+    <row r="191" ht="16" customHeight="1">
+      <c r="A191" s="20" t="inlineStr">
         <is>
           <t>**P2: Cloud Infrastructure &amp; Cybersecurity** *(Volume)*</t>
         </is>
       </c>
-      <c r="B130" s="20" t="inlineStr">
+      <c r="B191" s="20" t="inlineStr">
         <is>
           <t>**PL-2:** Cloud, Cyber &amp; Smart Systems Integrator</t>
         </is>
       </c>
-      <c r="C130" s="20" t="inlineStr">
+      <c r="C191" s="20" t="inlineStr">
         <is>
           <t>1. `STB-01` Network Security &amp; Digital Forensics (+P, Sem 5)&lt;br&gt;2. `STB-02` Cloud Architecture &amp; DevOps (+P, Sem 6)&lt;br&gt;3. `STB-03` Cybersecurity Risk Management (Teori, Sem 6)&lt;br&gt;4. `STB-04` IT Governance &amp; Compliance COBIT 2019 (Teori, Sem 7)&lt;br&gt;5. `STB-05` IT Service Management ITIL 4 (Teori, Sem 7)&lt;br&gt;6. `STB-06` Enterprise Architecture TOGAF (Teori, Sem 7)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="19" t="inlineStr">
+    <row r="192" ht="16" customHeight="1">
+      <c r="A192" s="19" t="inlineStr">
         <is>
           <t>**P3: Digital Platform Engineering** *(Niche &amp; Techno)*</t>
         </is>
       </c>
-      <c r="B131" s="19" t="inlineStr">
+      <c r="B192" s="19" t="inlineStr">
         <is>
           <t>**PL-3:** UI/UX Designer &amp; Platform Engineer</t>
         </is>
       </c>
-      <c r="C131" s="19" t="inlineStr">
+      <c r="C192" s="19" t="inlineStr">
         <is>
           <t>1. `STC-01` UX Research &amp; Design (+P, Sem 5)&lt;br&gt;2. `STC-02` Rekayasa &amp; Otomasi Proses Bisnis (+P, Sem 6)&lt;br&gt;3. `STC-03` Rekayasa Aplikasi Industri Vertikal (+P, Sem 6)&lt;br&gt;4. `STC-04` Immersive Media &amp; XR Development (+P, Sem 7)&lt;br&gt;5. `STC-05` SaaS Architecture &amp; Multi-Tenancy (+P, Sem 7)&lt;br&gt;6. `STC-06` Digital Product Management (Teori, Sem 7)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A99:G99"/>
+  <mergeCells count="18">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A88:G88"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A110:G110"/>
-    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A89:G89"/>
+    <mergeCell ref="A149:G149"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A127:F127"/>
-    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A176:F176"/>
+    <mergeCell ref="A101:G101"/>
+    <mergeCell ref="A171:G171"/>
+    <mergeCell ref="A137:G137"/>
+    <mergeCell ref="A160:G160"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A113:G113"/>
+    <mergeCell ref="A77:F77"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A28:G28"/>
   </mergeCells>
@@ -19679,7 +21811,7 @@
       <c r="B6" s="21" t="inlineStr"/>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>• STI-601 Integrasi AI (3)</t>
+          <t>• STI-624 Integrasi AI (3)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -19689,7 +21821,7 @@
       <c r="B7" s="22" t="inlineStr"/>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>• STI-604 Platform Eng (3)</t>
+          <t>• STI-627 Platform Eng (3)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr"/>
@@ -19699,7 +21831,7 @@
       <c r="B8" s="21" t="inlineStr"/>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>• STI-602 Smart City (3)</t>
+          <t>• STI-625 Smart City (3)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr"/>
@@ -19709,7 +21841,7 @@
       <c r="B9" s="22" t="inlineStr"/>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>• STI-603 Keamanan Lanjut (3)</t>
+          <t>• STI-519 Keamanan Lanjut (3)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr"/>
@@ -19779,7 +21911,7 @@
       <c r="B14" s="21" t="inlineStr"/>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>• STI-701 Startup Digital (3)</t>
+          <t>• STI-728 Startup Digital (3)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr"/>

--- a/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
+++ b/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
@@ -15874,8 +15874,8 @@
     <col width="56.34999999999999" customWidth="1" min="2" max="2"/>
     <col width="69" customWidth="1" min="3" max="3"/>
     <col width="40.25" customWidth="1" min="4" max="4"/>
-    <col width="50.59999999999999" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="69" customWidth="1" min="5" max="5"/>
+    <col width="54.05" customWidth="1" min="6" max="6"/>
     <col width="35.65" customWidth="1" min="7" max="7"/>
     <col width="47.15" customWidth="1" min="8" max="8"/>
   </cols>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="B83" s="19" t="inlineStr">
         <is>
-          <t>Deep Learning &amp; IoT</t>
+          <t>Keamanan Lanjut &amp; IoT</t>
         </is>
       </c>
       <c r="C83" s="21" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>Deep Learning, IoT, Mobile, KPM, Peminatan 1</t>
+          <t>Keamanan Lanjut, Data Mining, IoT, Mobile, KPM, Peminatan 1</t>
         </is>
       </c>
     </row>
@@ -18438,7 +18438,7 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>AI Integrasi &amp; Platform</t>
+          <t>Deep Learning &amp; Platform</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Smart AI, Smart City, Platform, Metopel</t>
+          <t>Integrasi AI, Smart City, Deep Learning, Platform Eng, Metopen</t>
         </is>
       </c>
     </row>
@@ -20078,7 +20078,7 @@
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="15" t="inlineStr">
         <is>
-          <t>SEMESTER 5 (21 SKS) — Tahap Spesialisasi Deep Learning, IoT &amp; Peminatan 1</t>
+          <t>SEMESTER 5 (21 SKS) — Tahap Spesialisasi Keamanan Lanjut, IoT &amp; Peminatan 1</t>
         </is>
       </c>
       <c r="B137" s="16" t="n"/>
@@ -20462,7 +20462,7 @@
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="15" t="inlineStr">
         <is>
-          <t>SEMESTER 6 (19 SKS) — Tahap Spesialisasi MBKM &amp; Platform Engineering</t>
+          <t>SEMESTER 6 (19 SKS) — Tahap Spesialisasi Deep Learning, Platform Engineering &amp; MBKM</t>
         </is>
       </c>
       <c r="B149" s="16" t="n"/>
@@ -21478,7 +21478,7 @@
       </c>
       <c r="F182" s="19" t="inlineStr">
         <is>
-          <t>Tahap Spesialisasi Deep Learning &amp; IoT</t>
+          <t>Tahap Spesialisasi Keamanan Lanjut &amp; IoT</t>
         </is>
       </c>
     </row>
@@ -21510,7 +21510,7 @@
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>Tahap Spesialisasi MBKM &amp; Platform Eng</t>
+          <t>Tahap Spesialisasi Deep Learning &amp; Platform Eng</t>
         </is>
       </c>
     </row>
@@ -21831,7 +21831,7 @@
       <c r="B8" s="21" t="inlineStr"/>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>• STI-625 Smart City (3)</t>
+          <t>• STI-625 Smart City (2)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr"/>

--- a/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
+++ b/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
@@ -15867,7 +15867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -15876,8 +15876,8 @@
     <col width="40.25" customWidth="1" min="4" max="4"/>
     <col width="69" customWidth="1" min="5" max="5"/>
     <col width="54.05" customWidth="1" min="6" max="6"/>
-    <col width="35.65" customWidth="1" min="7" max="7"/>
-    <col width="47.15" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="54.05" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -18259,387 +18259,619 @@
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t>SEBARAN 8 SEMESTER KURIKULUM SISTEKIN</t>
+          <t>1.4 KELOMPOK MATA KULIAH PILIHAN PEMINATAN (ELEKTIF) (18 MK DITAWARKAN / 18 SKS DITEMPUH)</t>
         </is>
       </c>
       <c r="B77" s="16" t="n"/>
       <c r="C77" s="16" t="n"/>
       <c r="D77" s="16" t="n"/>
       <c r="E77" s="16" t="n"/>
-      <c r="F77" s="17" t="n"/>
+      <c r="F77" s="16" t="n"/>
+      <c r="G77" s="16" t="n"/>
+      <c r="H77" s="17" t="n"/>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
           <t>Semester</t>
         </is>
       </c>
-      <c r="B78" s="18" t="inlineStr">
-        <is>
-          <t>Fokus Pembelajaran</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="inlineStr">
-        <is>
-          <t>Jml MK</t>
-        </is>
-      </c>
-      <c r="D78" s="18" t="inlineStr">
-        <is>
-          <t>Jml SKS</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="inlineStr">
-        <is>
-          <t>Karakteristik Kurikulum</t>
+      <c r="G78" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+      <c r="H78" s="18" t="inlineStr">
+        <is>
+          <t>Jalur Peminatan</t>
         </is>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 1**</t>
-        </is>
-      </c>
-      <c r="B79" s="19" t="inlineStr">
-        <is>
-          <t>Fondasi Sains &amp; MKWU</t>
-        </is>
-      </c>
-      <c r="C79" s="21" t="inlineStr">
-        <is>
-          <t>8 MK</t>
+      <c r="A79" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B79" s="21" t="inlineStr">
+        <is>
+          <t>`STA-01`</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>Decision Support Systems</t>
         </is>
       </c>
       <c r="D79" s="21" t="inlineStr">
         <is>
-          <t>19 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>Sains, Algoritma Dasar, Logika, Agama</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F79" s="19" t="inlineStr">
+        <is>
+          <t>Sem 5</t>
+        </is>
+      </c>
+      <c r="G79" s="19" t="inlineStr">
+        <is>
+          <t>`STI-307`</t>
+        </is>
+      </c>
+      <c r="H79" s="19" t="inlineStr">
+        <is>
+          <t>P1: Integrated Smart Systems</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 2**</t>
-        </is>
-      </c>
-      <c r="B80" s="20" t="inlineStr">
-        <is>
-          <t>Data, Matdis &amp; Etika</t>
-        </is>
-      </c>
-      <c r="C80" s="22" t="inlineStr">
-        <is>
-          <t>8 MK</t>
+      <c r="A80" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>`STA-02`</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr">
+        <is>
+          <t>Computational Methods and Numerics</t>
         </is>
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t>20 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Struktur Data, Basis Data, Matdis, Etika</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F80" s="20" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G80" s="20" t="inlineStr">
+        <is>
+          <t>`STI-102`, `STI-205`</t>
+        </is>
+      </c>
+      <c r="H80" s="20" t="inlineStr">
+        <is>
+          <t>P1: Integrated Smart Systems</t>
         </is>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 3**</t>
-        </is>
-      </c>
-      <c r="B81" s="19" t="inlineStr">
-        <is>
-          <t>RPL, UI/UX &amp; Infra</t>
-        </is>
-      </c>
-      <c r="C81" s="21" t="inlineStr">
-        <is>
-          <t>7 MK</t>
+      <c r="A81" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B81" s="21" t="inlineStr">
+        <is>
+          <t>`STA-03`</t>
+        </is>
+      </c>
+      <c r="C81" s="19" t="inlineStr">
+        <is>
+          <t>Intelligent Agent Systems</t>
         </is>
       </c>
       <c r="D81" s="21" t="inlineStr">
         <is>
-          <t>20 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>APSI, RPL, Web Front, Jarkom, OS, Cerdas</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F81" s="19" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G81" s="19" t="inlineStr">
+        <is>
+          <t>`STI-307`</t>
+        </is>
+      </c>
+      <c r="H81" s="19" t="inlineStr">
+        <is>
+          <t>P1: Integrated Smart Systems</t>
         </is>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 4**</t>
-        </is>
-      </c>
-      <c r="B82" s="20" t="inlineStr">
-        <is>
-          <t>AI/ML, NLP, Cloud &amp; Keamanan</t>
-        </is>
-      </c>
-      <c r="C82" s="22" t="inlineStr">
-        <is>
-          <t>8 MK</t>
+      <c r="A82" s="22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B82" s="22" t="inlineStr">
+        <is>
+          <t>`STA-04`</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>MLOps and AI Pipeline</t>
         </is>
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t>21 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>ML, NLP/IR, DW/BI, Web Back, Cloud, Probstat</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F82" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G82" s="20" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-624`</t>
+        </is>
+      </c>
+      <c r="H82" s="20" t="inlineStr">
+        <is>
+          <t>P1: Integrated Smart Systems</t>
         </is>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 5**</t>
-        </is>
-      </c>
-      <c r="B83" s="19" t="inlineStr">
-        <is>
-          <t>Keamanan Lanjut &amp; IoT</t>
-        </is>
-      </c>
-      <c r="C83" s="21" t="inlineStr">
-        <is>
-          <t>7 MK</t>
+      <c r="A83" s="21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B83" s="21" t="inlineStr">
+        <is>
+          <t>`STA-05`</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="inlineStr">
+        <is>
+          <t>Conversational AI and Intelligent Assistant</t>
         </is>
       </c>
       <c r="D83" s="21" t="inlineStr">
         <is>
-          <t>21 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>Keamanan Lanjut, Data Mining, IoT, Mobile, KPM, Peminatan 1</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F83" s="19" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G83" s="19" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-416`</t>
+        </is>
+      </c>
+      <c r="H83" s="19" t="inlineStr">
+        <is>
+          <t>P1: Integrated Smart Systems</t>
         </is>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 6**</t>
-        </is>
-      </c>
-      <c r="B84" s="20" t="inlineStr">
-        <is>
-          <t>Deep Learning &amp; Platform</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="inlineStr">
-        <is>
-          <t>7 MK</t>
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="inlineStr">
+        <is>
+          <t>`STA-06`</t>
+        </is>
+      </c>
+      <c r="C84" s="20" t="inlineStr">
+        <is>
+          <t>Smart Surveillance and IoT Analytics</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>19 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Integrasi AI, Smart City, Deep Learning, Platform Eng, Metopen</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F84" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G84" s="20" t="inlineStr">
+        <is>
+          <t>`STI-626`, `STI-521`</t>
+        </is>
+      </c>
+      <c r="H84" s="20" t="inlineStr">
+        <is>
+          <t>P1: Integrated Smart Systems</t>
         </is>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 7**</t>
-        </is>
-      </c>
-      <c r="B85" s="19" t="inlineStr">
-        <is>
-          <t>Capstone, PKL &amp; Sempro</t>
-        </is>
-      </c>
-      <c r="C85" s="21" t="inlineStr">
-        <is>
-          <t>7 MK</t>
+      <c r="A85" s="21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B85" s="21" t="inlineStr">
+        <is>
+          <t>`STB-01`</t>
+        </is>
+      </c>
+      <c r="C85" s="19" t="inlineStr">
+        <is>
+          <t>Network Security and Digital Forensics</t>
         </is>
       </c>
       <c r="D85" s="21" t="inlineStr">
         <is>
-          <t>20 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>Startup, Capstone FSTI, PKL, Pra-Skripsi</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F85" s="19" t="inlineStr">
+        <is>
+          <t>Sem 5</t>
+        </is>
+      </c>
+      <c r="G85" s="19" t="inlineStr">
+        <is>
+          <t>`STI-312`, `STI-418`</t>
+        </is>
+      </c>
+      <c r="H85" s="19" t="inlineStr">
+        <is>
+          <t>P2: Cloud Infra &amp; Cybersecurity</t>
         </is>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 8**</t>
-        </is>
-      </c>
-      <c r="B86" s="20" t="inlineStr">
-        <is>
-          <t>Skripsi Mandiri</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="inlineStr">
-        <is>
-          <t>1 MK</t>
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>`STB-02`</t>
+        </is>
+      </c>
+      <c r="C86" s="20" t="inlineStr">
+        <is>
+          <t>Cloud Architecture &amp; DevOps</t>
         </is>
       </c>
       <c r="D86" s="22" t="inlineStr">
         <is>
-          <t>6 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Skripsi Murni / 4 Opsi Non-Skripsi</t>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F86" s="20" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G86" s="20" t="inlineStr">
+        <is>
+          <t>`STI-417`</t>
+        </is>
+      </c>
+      <c r="H86" s="20" t="inlineStr">
+        <is>
+          <t>P2: Cloud Infra &amp; Cybersecurity</t>
         </is>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="19" t="inlineStr">
-        <is>
-          <t>**TOTAL**</t>
-        </is>
-      </c>
-      <c r="B87" s="19" t="inlineStr">
-        <is>
-          <t>**Paket Lulus Tepat Waktu**</t>
+      <c r="A87" s="21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B87" s="21" t="inlineStr">
+        <is>
+          <t>`STB-03`</t>
         </is>
       </c>
       <c r="C87" s="19" t="inlineStr">
         <is>
-          <t>**55 MK**</t>
-        </is>
-      </c>
-      <c r="D87" s="19" t="inlineStr">
-        <is>
-          <t>**146 SKS**</t>
+          <t>Cybersecurity Risk Management</t>
+        </is>
+      </c>
+      <c r="D87" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>**Standar Sarjana S1 Komputasi**</t>
-        </is>
-      </c>
-    </row>
-    <row r="88"/>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 1 (19 SKS) — Fondasi Sains, Algoritma, Arsitektur STI &amp; MKWU</t>
-        </is>
-      </c>
-      <c r="B89" s="16" t="n"/>
-      <c r="C89" s="16" t="n"/>
-      <c r="D89" s="16" t="n"/>
-      <c r="E89" s="16" t="n"/>
-      <c r="F89" s="16" t="n"/>
-      <c r="G89" s="17" t="n"/>
-    </row>
-    <row r="90" ht="26" customHeight="1">
-      <c r="A90" s="18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B90" s="18" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C90" s="18" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D90" s="18" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E90" s="18" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F90" s="18" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G90" s="18" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F87" s="19" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G87" s="19" t="inlineStr">
+        <is>
+          <t>`STI-418`</t>
+        </is>
+      </c>
+      <c r="H87" s="19" t="inlineStr">
+        <is>
+          <t>P2: Cloud Infra &amp; Cybersecurity</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="inlineStr">
+        <is>
+          <t>`STB-04`</t>
+        </is>
+      </c>
+      <c r="C88" s="20" t="inlineStr">
+        <is>
+          <t>IT Governance &amp; Compliance (COBIT 2019)</t>
+        </is>
+      </c>
+      <c r="D88" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E88" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F88" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G88" s="20" t="inlineStr">
+        <is>
+          <t>`STI-101`</t>
+        </is>
+      </c>
+      <c r="H88" s="20" t="inlineStr">
+        <is>
+          <t>P2: Cloud Infra &amp; Cybersecurity</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B89" s="21" t="inlineStr">
+        <is>
+          <t>`STB-05`</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t>IT Service Management (ITIL 4)</t>
+        </is>
+      </c>
+      <c r="D89" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E89" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F89" s="19" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G89" s="19" t="inlineStr">
+        <is>
+          <t>`STI-101`</t>
+        </is>
+      </c>
+      <c r="H89" s="19" t="inlineStr">
+        <is>
+          <t>P2: Cloud Infra &amp; Cybersecurity</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>`STB-06`</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="inlineStr">
+        <is>
+          <t>Enterprise Architecture (TOGAF)</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E90" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F90" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G90" s="20" t="inlineStr">
+        <is>
+          <t>`STI-306`</t>
+        </is>
+      </c>
+      <c r="H90" s="20" t="inlineStr">
+        <is>
+          <t>P2: Cloud Infra &amp; Cybersecurity</t>
         </is>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B91" s="19" t="inlineStr">
-        <is>
-          <t>`FST-101`</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B91" s="21" t="inlineStr">
+        <is>
+          <t>`STC-01`</t>
         </is>
       </c>
       <c r="C91" s="19" t="inlineStr">
         <is>
-          <t>Dasar Teknologi Digital</t>
+          <t>User Experience Research &amp; Design</t>
         </is>
       </c>
       <c r="D91" s="21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F91" s="19" t="inlineStr">
         <is>
-          <t>FSTI</t>
+          <t>Sem 5</t>
         </is>
       </c>
       <c r="G91" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`STI-308`</t>
+        </is>
+      </c>
+      <c r="H91" s="19" t="inlineStr">
+        <is>
+          <t>P3: Digital Platform Engineering</t>
         </is>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B92" s="20" t="inlineStr">
-        <is>
-          <t>`FST-102`</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="inlineStr">
+        <is>
+          <t>`STC-02`</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>Algoritma dan Pemrograman</t>
+          <t>Rekayasa &amp; Otomasi Proses Bisnis (BPA)</t>
         </is>
       </c>
       <c r="D92" s="22" t="inlineStr">
@@ -18654,66 +18886,76 @@
       </c>
       <c r="F92" s="20" t="inlineStr">
         <is>
-          <t>FSTI</t>
+          <t>Sem 6</t>
         </is>
       </c>
       <c r="G92" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`STI-306`</t>
+        </is>
+      </c>
+      <c r="H92" s="20" t="inlineStr">
+        <is>
+          <t>P3: Digital Platform Engineering</t>
         </is>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="21" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B93" s="21" t="inlineStr">
+        <is>
+          <t>`STC-03`</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t>Rekayasa Aplikasi Industri Vertikal (FinTech &amp; EdTech)</t>
+        </is>
+      </c>
+      <c r="D93" s="21" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B93" s="19" t="inlineStr">
-        <is>
-          <t>`STI-101`</t>
-        </is>
-      </c>
-      <c r="C93" s="19" t="inlineStr">
-        <is>
-          <t>Pengantar Sistem dan Teknologi Informasi</t>
-        </is>
-      </c>
-      <c r="D93" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F93" s="19" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 6</t>
         </is>
       </c>
       <c r="G93" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`STI-416`</t>
+        </is>
+      </c>
+      <c r="H93" s="19" t="inlineStr">
+        <is>
+          <t>P3: Digital Platform Engineering</t>
         </is>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="22" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B94" s="20" t="inlineStr">
-        <is>
-          <t>`STI-102`</t>
-        </is>
-      </c>
-      <c r="C94" s="22" t="inlineStr">
-        <is>
-          <t>Kalkulus</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B94" s="22" t="inlineStr">
+        <is>
+          <t>`STC-04`</t>
+        </is>
+      </c>
+      <c r="C94" s="20" t="inlineStr">
+        <is>
+          <t>Immersive Media &amp; XR Development</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
@@ -18723,34 +18965,39 @@
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 7</t>
         </is>
       </c>
       <c r="G94" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`STI-311`</t>
+        </is>
+      </c>
+      <c r="H94" s="20" t="inlineStr">
+        <is>
+          <t>P3: Digital Platform Engineering</t>
         </is>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B95" s="19" t="inlineStr">
-        <is>
-          <t>`STI-103`</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B95" s="21" t="inlineStr">
+        <is>
+          <t>`STC-05`</t>
         </is>
       </c>
       <c r="C95" s="19" t="inlineStr">
         <is>
-          <t>Arsitektur dan Organisasi Sistem Teknologi Informasi</t>
+          <t>SaaS Architecture &amp; Multi-Tenancy</t>
         </is>
       </c>
       <c r="D95" s="21" t="inlineStr">
@@ -18760,622 +19007,536 @@
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F95" s="19" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>Sem 7</t>
         </is>
       </c>
       <c r="G95" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>`STI-416`</t>
+        </is>
+      </c>
+      <c r="H95" s="19" t="inlineStr">
+        <is>
+          <t>P3: Digital Platform Engineering</t>
         </is>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="22" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B96" s="20" t="inlineStr">
-        <is>
-          <t>`MKU-101`</t>
-        </is>
-      </c>
-      <c r="C96" s="22" t="inlineStr">
-        <is>
-          <t>Agama I</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B96" s="22" t="inlineStr">
+        <is>
+          <t>`STC-06`</t>
+        </is>
+      </c>
+      <c r="C96" s="20" t="inlineStr">
+        <is>
+          <t>Digital Product Management &amp; Agile Practices</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E96" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F96" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G96" s="20" t="inlineStr">
+        <is>
+          <t>`STI-523`</t>
+        </is>
+      </c>
+      <c r="H96" s="20" t="inlineStr">
+        <is>
+          <t>P3: Digital Platform Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="19" t="inlineStr">
+        <is>
+          <t>**TOTAL**</t>
+        </is>
+      </c>
+      <c r="B97" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C97" s="19" t="inlineStr">
+        <is>
+          <t>**18 Mata Kuliah Pilihan Ditawarkan (Portofolio SIAKAD)**</t>
+        </is>
+      </c>
+      <c r="D97" s="21" t="inlineStr">
+        <is>
+          <t>**54**</t>
+        </is>
+      </c>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="19" t="inlineStr">
+        <is>
+          <t>**Ditempuh 6 MK (18 SKS) per Mahasiswa**</t>
+        </is>
+      </c>
+      <c r="H97" s="19" t="inlineStr">
+        <is>
+          <t>**3 Jalur Peminatan Seimbang**</t>
+        </is>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>SEBARAN 8 SEMESTER KURIKULUM SISTEKIN</t>
+        </is>
+      </c>
+      <c r="B99" s="16" t="n"/>
+      <c r="C99" s="16" t="n"/>
+      <c r="D99" s="16" t="n"/>
+      <c r="E99" s="16" t="n"/>
+      <c r="F99" s="17" t="n"/>
+    </row>
+    <row r="100" ht="26" customHeight="1">
+      <c r="A100" s="18" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="inlineStr">
+        <is>
+          <t>Fokus Pembelajaran</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>Jml MK</t>
+        </is>
+      </c>
+      <c r="D100" s="18" t="inlineStr">
+        <is>
+          <t>Jml SKS</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
+        <is>
+          <t>Karakteristik Kurikulum</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 1**</t>
+        </is>
+      </c>
+      <c r="B101" s="19" t="inlineStr">
+        <is>
+          <t>Fondasi Sains &amp; MKWU</t>
+        </is>
+      </c>
+      <c r="C101" s="21" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="D101" s="21" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="E101" s="19" t="inlineStr">
+        <is>
+          <t>Sains, Algoritma Dasar, Logika, Agama</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 2**</t>
+        </is>
+      </c>
+      <c r="B102" s="20" t="inlineStr">
+        <is>
+          <t>Data, Matdis &amp; Etika</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="E102" s="20" t="inlineStr">
+        <is>
+          <t>Struktur Data, Basis Data, Matdis, Etika</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 3**</t>
+        </is>
+      </c>
+      <c r="B103" s="19" t="inlineStr">
+        <is>
+          <t>RPL, UI/UX &amp; Infra</t>
+        </is>
+      </c>
+      <c r="C103" s="21" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="D103" s="21" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="E103" s="19" t="inlineStr">
+        <is>
+          <t>APSI, RPL, Web Front, Jarkom, OS, Cerdas</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 4**</t>
+        </is>
+      </c>
+      <c r="B104" s="20" t="inlineStr">
+        <is>
+          <t>AI/ML, NLP, Cloud &amp; Keamanan</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="inlineStr">
+        <is>
+          <t>21 SKS</t>
+        </is>
+      </c>
+      <c r="E104" s="20" t="inlineStr">
+        <is>
+          <t>ML, NLP/IR, DW/BI, Web Back, Cloud, Probstat</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 5**</t>
+        </is>
+      </c>
+      <c r="B105" s="19" t="inlineStr">
+        <is>
+          <t>Keamanan Lanjut &amp; IoT</t>
+        </is>
+      </c>
+      <c r="C105" s="21" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="D105" s="21" t="inlineStr">
+        <is>
+          <t>21 SKS</t>
+        </is>
+      </c>
+      <c r="E105" s="19" t="inlineStr">
+        <is>
+          <t>Keamanan Lanjut, Data Mining, IoT, Mobile, KPM, Peminatan 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 6**</t>
+        </is>
+      </c>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t>Deep Learning &amp; Platform</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="E106" s="20" t="inlineStr">
+        <is>
+          <t>Integrasi AI, Smart City, Deep Learning, Platform Eng, Metopen</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="16" customHeight="1">
+      <c r="A107" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 7**</t>
+        </is>
+      </c>
+      <c r="B107" s="19" t="inlineStr">
+        <is>
+          <t>Capstone, PKL &amp; Sempro</t>
+        </is>
+      </c>
+      <c r="C107" s="21" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="D107" s="21" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="E107" s="19" t="inlineStr">
+        <is>
+          <t>Startup, Capstone FSTI, PKL, Pra-Skripsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 8**</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>Skripsi Mandiri</t>
+        </is>
+      </c>
+      <c r="C108" s="22" t="inlineStr">
+        <is>
+          <t>1 MK</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="inlineStr">
+        <is>
+          <t>6 SKS</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>Skripsi Murni / 4 Opsi Non-Skripsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t>**TOTAL**</t>
+        </is>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t>**Paket Lulus Tepat Waktu**</t>
+        </is>
+      </c>
+      <c r="C109" s="19" t="inlineStr">
+        <is>
+          <t>**55 MK**</t>
+        </is>
+      </c>
+      <c r="D109" s="19" t="inlineStr">
+        <is>
+          <t>**146 SKS**</t>
+        </is>
+      </c>
+      <c r="E109" s="19" t="inlineStr">
+        <is>
+          <t>**Standar Sarjana S1 Komputasi**</t>
+        </is>
+      </c>
+    </row>
+    <row r="110"/>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 1 (19 SKS) — Fondasi Sains, Algoritma, Arsitektur STI &amp; MKWU</t>
+        </is>
+      </c>
+      <c r="B111" s="16" t="n"/>
+      <c r="C111" s="16" t="n"/>
+      <c r="D111" s="16" t="n"/>
+      <c r="E111" s="16" t="n"/>
+      <c r="F111" s="16" t="n"/>
+      <c r="G111" s="17" t="n"/>
+    </row>
+    <row r="112" ht="26" customHeight="1">
+      <c r="A112" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B112" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D112" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E112" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F112" s="18" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G112" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B113" s="19" t="inlineStr">
+        <is>
+          <t>`FST-101`</t>
+        </is>
+      </c>
+      <c r="C113" s="19" t="inlineStr">
+        <is>
+          <t>Dasar Teknologi Digital</t>
+        </is>
+      </c>
+      <c r="D113" s="21" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E96" s="20" t="inlineStr">
+      <c r="E113" s="19" t="inlineStr">
         <is>
           <t>Teori</t>
         </is>
       </c>
-      <c r="F96" s="20" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G96" s="20" t="inlineStr">
+      <c r="F113" s="19" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G113" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="21" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B97" s="19" t="inlineStr">
-        <is>
-          <t>`MKU-102`</t>
-        </is>
-      </c>
-      <c r="C97" s="19" t="inlineStr">
-        <is>
-          <t>Pancasila</t>
-        </is>
-      </c>
-      <c r="D97" s="21" t="inlineStr">
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E97" s="19" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F97" s="19" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G97" s="19" t="inlineStr">
+      <c r="B114" s="20" t="inlineStr">
+        <is>
+          <t>`FST-102`</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="inlineStr">
+        <is>
+          <t>Algoritma dan Pemrograman</t>
+        </is>
+      </c>
+      <c r="D114" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E114" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F114" s="20" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G114" s="20" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B98" s="20" t="inlineStr">
-        <is>
-          <t>`MKU-103`</t>
-        </is>
-      </c>
-      <c r="C98" s="20" t="inlineStr">
-        <is>
-          <t>Bahasa Indonesia</t>
-        </is>
-      </c>
-      <c r="D98" s="22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E98" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F98" s="20" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G98" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="19" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B99" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C99" s="19" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 1 (8 MK)**</t>
-        </is>
-      </c>
-      <c r="D99" s="21" t="inlineStr">
-        <is>
-          <t>**19**</t>
-        </is>
-      </c>
-      <c r="E99" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F99" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="19" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 19 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="100"/>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 2 (20 SKS) — Fondasi Data, Matdis &amp; Logika, Aljabar &amp; Etika</t>
-        </is>
-      </c>
-      <c r="B101" s="16" t="n"/>
-      <c r="C101" s="16" t="n"/>
-      <c r="D101" s="16" t="n"/>
-      <c r="E101" s="16" t="n"/>
-      <c r="F101" s="16" t="n"/>
-      <c r="G101" s="17" t="n"/>
-    </row>
-    <row r="102" ht="26" customHeight="1">
-      <c r="A102" s="18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B102" s="18" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C102" s="18" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D102" s="18" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E102" s="18" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F102" s="18" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G102" s="18" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B103" s="19" t="inlineStr">
-        <is>
-          <t>`STI-204`</t>
-        </is>
-      </c>
-      <c r="C103" s="19" t="inlineStr">
-        <is>
-          <t>Matematika Diskrit dan Logika</t>
-        </is>
-      </c>
-      <c r="D103" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E103" s="19" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F103" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G103" s="19" t="inlineStr">
-        <is>
-          <t>`STI-103`</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B104" s="20" t="inlineStr">
-        <is>
-          <t>`STI-205`</t>
-        </is>
-      </c>
-      <c r="C104" s="20" t="inlineStr">
-        <is>
-          <t>Aljabar Linear dan Matriks</t>
-        </is>
-      </c>
-      <c r="D104" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E104" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F104" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G104" s="20" t="inlineStr">
-        <is>
-          <t>`STI-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B105" s="19" t="inlineStr">
-        <is>
-          <t>`FST-203`</t>
-        </is>
-      </c>
-      <c r="C105" s="19" t="inlineStr">
-        <is>
-          <t>Struktur Data dan Algoritma</t>
-        </is>
-      </c>
-      <c r="D105" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E105" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F105" s="19" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G105" s="19" t="inlineStr">
-        <is>
-          <t>`FST-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B106" s="20" t="inlineStr">
-        <is>
-          <t>`FST-204`</t>
-        </is>
-      </c>
-      <c r="C106" s="20" t="inlineStr">
-        <is>
-          <t>Pengantar Kecerdasan Artifisial &amp; Data</t>
-        </is>
-      </c>
-      <c r="D106" s="22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E106" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F106" s="20" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G106" s="20" t="inlineStr">
-        <is>
-          <t>`FST-101`</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="21" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B107" s="19" t="inlineStr">
-        <is>
-          <t>`FST-205`</t>
-        </is>
-      </c>
-      <c r="C107" s="19" t="inlineStr">
-        <is>
-          <t>Basic English for IT</t>
-        </is>
-      </c>
-      <c r="D107" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E107" s="19" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F107" s="19" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G107" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="22" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B108" s="20" t="inlineStr">
-        <is>
-          <t>`FST-206`</t>
-        </is>
-      </c>
-      <c r="C108" s="20" t="inlineStr">
-        <is>
-          <t>Etika Profesi &amp; Hukum Digital</t>
-        </is>
-      </c>
-      <c r="D108" s="22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E108" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F108" s="20" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G108" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B109" s="19" t="inlineStr">
-        <is>
-          <t>`FST-207`</t>
-        </is>
-      </c>
-      <c r="C109" s="19" t="inlineStr">
-        <is>
-          <t>Sistem Basis Data</t>
-        </is>
-      </c>
-      <c r="D109" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E109" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F109" s="19" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G109" s="19" t="inlineStr">
-        <is>
-          <t>`FST-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="22" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B110" s="20" t="inlineStr">
-        <is>
-          <t>`MKU-204`</t>
-        </is>
-      </c>
-      <c r="C110" s="20" t="inlineStr">
-        <is>
-          <t>Kewirausahaan I</t>
-        </is>
-      </c>
-      <c r="D110" s="22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E110" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F110" s="20" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G110" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="16" customHeight="1">
-      <c r="A111" s="19" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B111" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C111" s="19" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 2 (8 MK)**</t>
-        </is>
-      </c>
-      <c r="D111" s="21" t="inlineStr">
-        <is>
-          <t>**20**</t>
-        </is>
-      </c>
-      <c r="E111" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F111" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G111" s="19" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 39 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="112"/>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 3 (20 SKS) — Penguatan Core RPL, OS, Jarkom &amp; UI/UX</t>
-        </is>
-      </c>
-      <c r="B113" s="16" t="n"/>
-      <c r="C113" s="16" t="n"/>
-      <c r="D113" s="16" t="n"/>
-      <c r="E113" s="16" t="n"/>
-      <c r="F113" s="16" t="n"/>
-      <c r="G113" s="17" t="n"/>
-    </row>
-    <row r="114" ht="26" customHeight="1">
-      <c r="A114" s="18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B114" s="18" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C114" s="18" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D114" s="18" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E114" s="18" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F114" s="18" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G114" s="18" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
         </is>
       </c>
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B115" s="19" t="inlineStr">
         <is>
-          <t>`STI-306`</t>
+          <t>`STI-101`</t>
         </is>
       </c>
       <c r="C115" s="19" t="inlineStr">
         <is>
-          <t>Analisis dan Perancangan Sistem Informasi</t>
+          <t>Pengantar Sistem dan Teknologi Informasi</t>
         </is>
       </c>
       <c r="D115" s="21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E115" s="19" t="inlineStr">
@@ -19390,29 +19551,29 @@
       </c>
       <c r="G115" s="19" t="inlineStr">
         <is>
-          <t>`STI-101`, `FST-207`</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B116" s="20" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
-        </is>
-      </c>
-      <c r="C116" s="20" t="inlineStr">
-        <is>
-          <t>Sistem Cerdas</t>
+          <t>`STI-102`</t>
+        </is>
+      </c>
+      <c r="C116" s="22" t="inlineStr">
+        <is>
+          <t>Kalkulus</t>
         </is>
       </c>
       <c r="D116" s="22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
@@ -19427,24 +19588,24 @@
       </c>
       <c r="G116" s="20" t="inlineStr">
         <is>
-          <t>`STI-204`, `FST-204`</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="117" ht="16" customHeight="1">
       <c r="A117" s="21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B117" s="19" t="inlineStr">
         <is>
-          <t>`STI-308`</t>
+          <t>`STI-103`</t>
         </is>
       </c>
       <c r="C117" s="19" t="inlineStr">
         <is>
-          <t>UI/UX Design &amp; Prototyping</t>
+          <t>Arsitektur dan Organisasi Sistem Teknologi Informasi</t>
         </is>
       </c>
       <c r="D117" s="21" t="inlineStr">
@@ -19454,7 +19615,7 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F117" s="19" t="inlineStr">
@@ -19464,29 +19625,29 @@
       </c>
       <c r="G117" s="19" t="inlineStr">
         <is>
-          <t>`FST-101`</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>`STI-309`</t>
-        </is>
-      </c>
-      <c r="C118" s="20" t="inlineStr">
-        <is>
-          <t>Rekayasa Perangkat Lunak</t>
+          <t>`MKU-101`</t>
+        </is>
+      </c>
+      <c r="C118" s="22" t="inlineStr">
+        <is>
+          <t>Agama I</t>
         </is>
       </c>
       <c r="D118" s="22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
@@ -19496,34 +19657,34 @@
       </c>
       <c r="F118" s="20" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>MKWU</t>
         </is>
       </c>
       <c r="G118" s="20" t="inlineStr">
         <is>
-          <t>`FST-203`</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B119" s="19" t="inlineStr">
         <is>
-          <t>`STI-310`</t>
+          <t>`MKU-102`</t>
         </is>
       </c>
       <c r="C119" s="19" t="inlineStr">
         <is>
-          <t>Sistem Operasi</t>
+          <t>Pancasila</t>
         </is>
       </c>
       <c r="D119" s="21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E119" s="19" t="inlineStr">
@@ -19533,612 +19694,612 @@
       </c>
       <c r="F119" s="19" t="inlineStr">
         <is>
-          <t>Core STI</t>
+          <t>MKWU</t>
         </is>
       </c>
       <c r="G119" s="19" t="inlineStr">
         <is>
-          <t>`STI-103`</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B120" s="20" t="inlineStr">
         <is>
-          <t>`STI-311`</t>
+          <t>`MKU-103`</t>
         </is>
       </c>
       <c r="C120" s="20" t="inlineStr">
         <is>
-          <t>Web Front End Development</t>
+          <t>Bahasa Indonesia</t>
         </is>
       </c>
       <c r="D120" s="22" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E120" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F120" s="20" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G120" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" s="19" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B121" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 1 (8 MK)**</t>
+        </is>
+      </c>
+      <c r="D121" s="21" t="inlineStr">
+        <is>
+          <t>**19**</t>
+        </is>
+      </c>
+      <c r="E121" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F121" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G121" s="19" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 19 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="122"/>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 2 (20 SKS) — Fondasi Data, Matdis &amp; Logika, Aljabar &amp; Etika</t>
+        </is>
+      </c>
+      <c r="B123" s="16" t="n"/>
+      <c r="C123" s="16" t="n"/>
+      <c r="D123" s="16" t="n"/>
+      <c r="E123" s="16" t="n"/>
+      <c r="F123" s="16" t="n"/>
+      <c r="G123" s="17" t="n"/>
+    </row>
+    <row r="124" ht="26" customHeight="1">
+      <c r="A124" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B124" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C124" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D124" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E124" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F124" s="18" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G124" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="16" customHeight="1">
+      <c r="A125" s="21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B125" s="19" t="inlineStr">
+        <is>
+          <t>`STI-204`</t>
+        </is>
+      </c>
+      <c r="C125" s="19" t="inlineStr">
+        <is>
+          <t>Matematika Diskrit dan Logika</t>
+        </is>
+      </c>
+      <c r="D125" s="21" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E120" s="20" t="inlineStr">
+      <c r="E125" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F125" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G125" s="19" t="inlineStr">
+        <is>
+          <t>`STI-103`</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="16" customHeight="1">
+      <c r="A126" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B126" s="20" t="inlineStr">
+        <is>
+          <t>`STI-205`</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="inlineStr">
+        <is>
+          <t>Aljabar Linear dan Matriks</t>
+        </is>
+      </c>
+      <c r="D126" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E126" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F126" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G126" s="20" t="inlineStr">
+        <is>
+          <t>`STI-102`</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B127" s="19" t="inlineStr">
+        <is>
+          <t>`FST-203`</t>
+        </is>
+      </c>
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t>Struktur Data dan Algoritma</t>
+        </is>
+      </c>
+      <c r="D127" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E127" s="19" t="inlineStr">
         <is>
           <t>+P</t>
         </is>
       </c>
-      <c r="F120" s="20" t="inlineStr">
+      <c r="F127" s="19" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G127" s="19" t="inlineStr">
+        <is>
+          <t>`FST-102`</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B128" s="20" t="inlineStr">
+        <is>
+          <t>`FST-204`</t>
+        </is>
+      </c>
+      <c r="C128" s="20" t="inlineStr">
+        <is>
+          <t>Pengantar Kecerdasan Artifisial &amp; Data</t>
+        </is>
+      </c>
+      <c r="D128" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E128" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F128" s="20" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G128" s="20" t="inlineStr">
+        <is>
+          <t>`FST-101`</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="16" customHeight="1">
+      <c r="A129" s="21" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B129" s="19" t="inlineStr">
+        <is>
+          <t>`FST-205`</t>
+        </is>
+      </c>
+      <c r="C129" s="19" t="inlineStr">
+        <is>
+          <t>Basic English for IT</t>
+        </is>
+      </c>
+      <c r="D129" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E129" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F129" s="19" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G129" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="A130" s="22" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B130" s="20" t="inlineStr">
+        <is>
+          <t>`FST-206`</t>
+        </is>
+      </c>
+      <c r="C130" s="20" t="inlineStr">
+        <is>
+          <t>Etika Profesi &amp; Hukum Digital</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E130" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F130" s="20" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G130" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="16" customHeight="1">
+      <c r="A131" s="21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B131" s="19" t="inlineStr">
+        <is>
+          <t>`FST-207`</t>
+        </is>
+      </c>
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t>Sistem Basis Data</t>
+        </is>
+      </c>
+      <c r="D131" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E131" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F131" s="19" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G131" s="19" t="inlineStr">
+        <is>
+          <t>`FST-102`</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="16" customHeight="1">
+      <c r="A132" s="22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>`MKU-204`</t>
+        </is>
+      </c>
+      <c r="C132" s="20" t="inlineStr">
+        <is>
+          <t>Kewirausahaan I</t>
+        </is>
+      </c>
+      <c r="D132" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F132" s="20" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G132" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="19" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B133" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C133" s="19" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 2 (8 MK)**</t>
+        </is>
+      </c>
+      <c r="D133" s="21" t="inlineStr">
+        <is>
+          <t>**20**</t>
+        </is>
+      </c>
+      <c r="E133" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F133" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G133" s="19" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 39 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="134"/>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 3 (20 SKS) — Penguatan Core RPL, OS, Jarkom &amp; UI/UX</t>
+        </is>
+      </c>
+      <c r="B135" s="16" t="n"/>
+      <c r="C135" s="16" t="n"/>
+      <c r="D135" s="16" t="n"/>
+      <c r="E135" s="16" t="n"/>
+      <c r="F135" s="16" t="n"/>
+      <c r="G135" s="17" t="n"/>
+    </row>
+    <row r="136" ht="26" customHeight="1">
+      <c r="A136" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B136" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D136" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E136" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F136" s="18" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G136" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B137" s="19" t="inlineStr">
+        <is>
+          <t>`STI-306`</t>
+        </is>
+      </c>
+      <c r="C137" s="19" t="inlineStr">
+        <is>
+          <t>Analisis dan Perancangan Sistem Informasi</t>
+        </is>
+      </c>
+      <c r="D137" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E137" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F137" s="19" t="inlineStr">
         <is>
           <t>Core STI</t>
         </is>
       </c>
-      <c r="G120" s="20" t="inlineStr">
-        <is>
-          <t>`FST-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="21" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B121" s="19" t="inlineStr">
-        <is>
-          <t>`STI-312`</t>
-        </is>
-      </c>
-      <c r="C121" s="19" t="inlineStr">
-        <is>
-          <t>Jaringan Komputer</t>
-        </is>
-      </c>
-      <c r="D121" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E121" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F121" s="19" t="inlineStr">
+      <c r="G137" s="19" t="inlineStr">
+        <is>
+          <t>`STI-101`, `FST-207`</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B138" s="20" t="inlineStr">
+        <is>
+          <t>`STI-307`</t>
+        </is>
+      </c>
+      <c r="C138" s="20" t="inlineStr">
+        <is>
+          <t>Sistem Cerdas</t>
+        </is>
+      </c>
+      <c r="D138" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E138" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F138" s="20" t="inlineStr">
         <is>
           <t>Core STI</t>
         </is>
       </c>
-      <c r="G121" s="19" t="inlineStr">
-        <is>
-          <t>`STI-103`</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="20" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B122" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C122" s="20" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 3 (7 MK)**</t>
-        </is>
-      </c>
-      <c r="D122" s="22" t="inlineStr">
-        <is>
-          <t>**20**</t>
-        </is>
-      </c>
-      <c r="E122" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F122" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G122" s="20" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 59 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="123"/>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 4 (21 SKS) — Penguatan Core AI/ML, NLP, DW &amp; Cloud</t>
-        </is>
-      </c>
-      <c r="B124" s="16" t="n"/>
-      <c r="C124" s="16" t="n"/>
-      <c r="D124" s="16" t="n"/>
-      <c r="E124" s="16" t="n"/>
-      <c r="F124" s="16" t="n"/>
-      <c r="G124" s="17" t="n"/>
-    </row>
-    <row r="125" ht="26" customHeight="1">
-      <c r="A125" s="18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B125" s="18" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C125" s="18" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D125" s="18" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E125" s="18" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F125" s="18" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G125" s="18" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="16" customHeight="1">
-      <c r="A126" s="21" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B126" s="19" t="inlineStr">
-        <is>
-          <t>`STI-413`</t>
-        </is>
-      </c>
-      <c r="C126" s="19" t="inlineStr">
-        <is>
-          <t>Machine Learning</t>
-        </is>
-      </c>
-      <c r="D126" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E126" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F126" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G126" s="19" t="inlineStr">
-        <is>
-          <t>`STI-205`, `STI-307`</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="22" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B127" s="20" t="inlineStr">
-        <is>
-          <t>`STI-414`</t>
-        </is>
-      </c>
-      <c r="C127" s="20" t="inlineStr">
-        <is>
-          <t>Pengantar NLP &amp; Information Retrieval</t>
-        </is>
-      </c>
-      <c r="D127" s="22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E127" s="20" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F127" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G127" s="20" t="inlineStr">
-        <is>
-          <t>`STI-307`</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="21" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B128" s="19" t="inlineStr">
-        <is>
-          <t>`STI-415`</t>
-        </is>
-      </c>
-      <c r="C128" s="19" t="inlineStr">
-        <is>
-          <t>Data Warehouse &amp; Business Intelligence</t>
-        </is>
-      </c>
-      <c r="D128" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E128" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F128" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G128" s="19" t="inlineStr">
-        <is>
-          <t>`FST-207`</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="22" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B129" s="20" t="inlineStr">
-        <is>
-          <t>`STI-416`</t>
-        </is>
-      </c>
-      <c r="C129" s="20" t="inlineStr">
-        <is>
-          <t>Web Back End Development</t>
-        </is>
-      </c>
-      <c r="D129" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E129" s="20" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F129" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G129" s="20" t="inlineStr">
-        <is>
-          <t>`FST-207`, `STI-311`</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="21" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B130" s="19" t="inlineStr">
-        <is>
-          <t>`STI-417`</t>
-        </is>
-      </c>
-      <c r="C130" s="19" t="inlineStr">
-        <is>
-          <t>Komputasi Awan (Cloud Computing)</t>
-        </is>
-      </c>
-      <c r="D130" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E130" s="19" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F130" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G130" s="19" t="inlineStr">
-        <is>
-          <t>`STI-312`, `STI-310`</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="22" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B131" s="20" t="inlineStr">
-        <is>
-          <t>`STI-418`</t>
-        </is>
-      </c>
-      <c r="C131" s="20" t="inlineStr">
-        <is>
-          <t>Dasar Keamanan Informasi</t>
-        </is>
-      </c>
-      <c r="D131" s="22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E131" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F131" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G131" s="20" t="inlineStr">
-        <is>
-          <t>`STI-312`</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B132" s="19" t="inlineStr">
-        <is>
-          <t>`FST-408`</t>
-        </is>
-      </c>
-      <c r="C132" s="19" t="inlineStr">
-        <is>
-          <t>Probabilitas dan Statistika</t>
-        </is>
-      </c>
-      <c r="D132" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E132" s="19" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F132" s="19" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G132" s="19" t="inlineStr">
-        <is>
-          <t>`STI-102`</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="22" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B133" s="20" t="inlineStr">
-        <is>
-          <t>`MKU-405`</t>
-        </is>
-      </c>
-      <c r="C133" s="20" t="inlineStr">
-        <is>
-          <t>Kewarganegaraan</t>
-        </is>
-      </c>
-      <c r="D133" s="22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E133" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F133" s="20" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G133" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="16" customHeight="1">
-      <c r="A134" s="21" t="inlineStr">
-        <is>
-          <t>31.B</t>
-        </is>
-      </c>
-      <c r="B134" s="19" t="inlineStr">
-        <is>
-          <t>`MKU-406`</t>
-        </is>
-      </c>
-      <c r="C134" s="21" t="inlineStr">
-        <is>
-          <t>Agama II</t>
-        </is>
-      </c>
-      <c r="D134" s="21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E134" s="19" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F134" s="19" t="inlineStr">
-        <is>
-          <t>MKWU</t>
-        </is>
-      </c>
-      <c r="G134" s="19" t="inlineStr">
-        <is>
-          <t>— (Kebijakan UWG, Sem 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="20" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B135" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C135" s="20" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 4 (8 MK + 1 MK 0 SKS)**</t>
-        </is>
-      </c>
-      <c r="D135" s="22" t="inlineStr">
-        <is>
-          <t>**21**</t>
-        </is>
-      </c>
-      <c r="E135" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F135" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G135" s="20" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 80 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="136"/>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 5 (21 SKS) — Tahap Spesialisasi Keamanan Lanjut, IoT &amp; Peminatan 1</t>
-        </is>
-      </c>
-      <c r="B137" s="16" t="n"/>
-      <c r="C137" s="16" t="n"/>
-      <c r="D137" s="16" t="n"/>
-      <c r="E137" s="16" t="n"/>
-      <c r="F137" s="16" t="n"/>
-      <c r="G137" s="17" t="n"/>
-    </row>
-    <row r="138" ht="26" customHeight="1">
-      <c r="A138" s="18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B138" s="18" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C138" s="18" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D138" s="18" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E138" s="18" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F138" s="18" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G138" s="18" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
+      <c r="G138" s="20" t="inlineStr">
+        <is>
+          <t>`STI-204`, `FST-204`</t>
         </is>
       </c>
     </row>
     <row r="139" ht="16" customHeight="1">
       <c r="A139" s="21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B139" s="19" t="inlineStr">
         <is>
-          <t>`STI-519`</t>
+          <t>`STI-308`</t>
         </is>
       </c>
       <c r="C139" s="19" t="inlineStr">
         <is>
-          <t>Keamanan Informasi Lanjut</t>
+          <t>UI/UX Design &amp; Prototyping</t>
         </is>
       </c>
       <c r="D139" s="21" t="inlineStr">
@@ -20148,7 +20309,7 @@
       </c>
       <c r="E139" s="19" t="inlineStr">
         <is>
-          <t>Teori</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F139" s="19" t="inlineStr">
@@ -20158,24 +20319,24 @@
       </c>
       <c r="G139" s="19" t="inlineStr">
         <is>
-          <t>`STI-418`</t>
+          <t>`FST-101`</t>
         </is>
       </c>
     </row>
     <row r="140" ht="16" customHeight="1">
       <c r="A140" s="22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B140" s="20" t="inlineStr">
         <is>
-          <t>`STI-520`</t>
+          <t>`STI-309`</t>
         </is>
       </c>
       <c r="C140" s="20" t="inlineStr">
         <is>
-          <t>Data Mining &amp; Visualisasi Data</t>
+          <t>Rekayasa Perangkat Lunak</t>
         </is>
       </c>
       <c r="D140" s="22" t="inlineStr">
@@ -20185,7 +20346,7 @@
       </c>
       <c r="E140" s="20" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
@@ -20195,24 +20356,24 @@
       </c>
       <c r="G140" s="20" t="inlineStr">
         <is>
-          <t>`STI-413`, `STI-415`</t>
+          <t>`FST-203`</t>
         </is>
       </c>
     </row>
     <row r="141" ht="16" customHeight="1">
       <c r="A141" s="21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B141" s="19" t="inlineStr">
         <is>
-          <t>`STI-521`</t>
+          <t>`STI-310`</t>
         </is>
       </c>
       <c r="C141" s="19" t="inlineStr">
         <is>
-          <t>Internet of Things (IoT)</t>
+          <t>Sistem Operasi</t>
         </is>
       </c>
       <c r="D141" s="21" t="inlineStr">
@@ -20222,7 +20383,7 @@
       </c>
       <c r="E141" s="19" t="inlineStr">
         <is>
-          <t>+P</t>
+          <t>Teori</t>
         </is>
       </c>
       <c r="F141" s="19" t="inlineStr">
@@ -20232,24 +20393,24 @@
       </c>
       <c r="G141" s="19" t="inlineStr">
         <is>
-          <t>`STI-312`, `STI-310`</t>
+          <t>`STI-103`</t>
         </is>
       </c>
     </row>
     <row r="142" ht="16" customHeight="1">
       <c r="A142" s="22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B142" s="20" t="inlineStr">
         <is>
-          <t>`STI-522`</t>
+          <t>`STI-311`</t>
         </is>
       </c>
       <c r="C142" s="20" t="inlineStr">
         <is>
-          <t>Pemrograman Aplikasi Mobile</t>
+          <t>Web Front End Development</t>
         </is>
       </c>
       <c r="D142" s="22" t="inlineStr">
@@ -20269,886 +20430,886 @@
       </c>
       <c r="G142" s="20" t="inlineStr">
         <is>
-          <t>`STI-311`, `STI-416`</t>
+          <t>`FST-102`</t>
         </is>
       </c>
     </row>
     <row r="143" ht="16" customHeight="1">
       <c r="A143" s="21" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B143" s="19" t="inlineStr">
+        <is>
+          <t>`STI-312`</t>
+        </is>
+      </c>
+      <c r="C143" s="19" t="inlineStr">
+        <is>
+          <t>Jaringan Komputer</t>
+        </is>
+      </c>
+      <c r="D143" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E143" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F143" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G143" s="19" t="inlineStr">
+        <is>
+          <t>`STI-103`</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="20" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B144" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C144" s="20" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 3 (7 MK)**</t>
+        </is>
+      </c>
+      <c r="D144" s="22" t="inlineStr">
+        <is>
+          <t>**20**</t>
+        </is>
+      </c>
+      <c r="E144" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F144" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G144" s="20" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 59 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="145"/>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 4 (21 SKS) — Penguatan Core AI/ML, NLP, DW &amp; Cloud</t>
+        </is>
+      </c>
+      <c r="B146" s="16" t="n"/>
+      <c r="C146" s="16" t="n"/>
+      <c r="D146" s="16" t="n"/>
+      <c r="E146" s="16" t="n"/>
+      <c r="F146" s="16" t="n"/>
+      <c r="G146" s="17" t="n"/>
+    </row>
+    <row r="147" ht="26" customHeight="1">
+      <c r="A147" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B147" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D147" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E147" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F147" s="18" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G147" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B148" s="19" t="inlineStr">
+        <is>
+          <t>`STI-413`</t>
+        </is>
+      </c>
+      <c r="C148" s="19" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="D148" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E148" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F148" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G148" s="19" t="inlineStr">
+        <is>
+          <t>`STI-205`, `STI-307`</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B149" s="20" t="inlineStr">
+        <is>
+          <t>`STI-414`</t>
+        </is>
+      </c>
+      <c r="C149" s="20" t="inlineStr">
+        <is>
+          <t>Pengantar NLP &amp; Information Retrieval</t>
+        </is>
+      </c>
+      <c r="D149" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E149" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F149" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G149" s="20" t="inlineStr">
+        <is>
+          <t>`STI-307`</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="21" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B150" s="19" t="inlineStr">
+        <is>
+          <t>`STI-415`</t>
+        </is>
+      </c>
+      <c r="C150" s="19" t="inlineStr">
+        <is>
+          <t>Data Warehouse &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="D150" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E150" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F150" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G150" s="19" t="inlineStr">
+        <is>
+          <t>`FST-207`</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="22" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B151" s="20" t="inlineStr">
+        <is>
+          <t>`STI-416`</t>
+        </is>
+      </c>
+      <c r="C151" s="20" t="inlineStr">
+        <is>
+          <t>Web Back End Development</t>
+        </is>
+      </c>
+      <c r="D151" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E151" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F151" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G151" s="20" t="inlineStr">
+        <is>
+          <t>`FST-207`, `STI-311`</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="16" customHeight="1">
+      <c r="A152" s="21" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B152" s="19" t="inlineStr">
+        <is>
+          <t>`STI-417`</t>
+        </is>
+      </c>
+      <c r="C152" s="19" t="inlineStr">
+        <is>
+          <t>Komputasi Awan (Cloud Computing)</t>
+        </is>
+      </c>
+      <c r="D152" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E152" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F152" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G152" s="19" t="inlineStr">
+        <is>
+          <t>`STI-312`, `STI-310`</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="22" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B153" s="20" t="inlineStr">
+        <is>
+          <t>`STI-418`</t>
+        </is>
+      </c>
+      <c r="C153" s="20" t="inlineStr">
+        <is>
+          <t>Dasar Keamanan Informasi</t>
+        </is>
+      </c>
+      <c r="D153" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E153" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F153" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G153" s="20" t="inlineStr">
+        <is>
+          <t>`STI-312`</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" s="21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B154" s="19" t="inlineStr">
+        <is>
+          <t>`FST-408`</t>
+        </is>
+      </c>
+      <c r="C154" s="19" t="inlineStr">
+        <is>
+          <t>Probabilitas dan Statistika</t>
+        </is>
+      </c>
+      <c r="D154" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E154" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F154" s="19" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G154" s="19" t="inlineStr">
+        <is>
+          <t>`STI-102`</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="22" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B155" s="20" t="inlineStr">
+        <is>
+          <t>`MKU-405`</t>
+        </is>
+      </c>
+      <c r="C155" s="20" t="inlineStr">
+        <is>
+          <t>Kewarganegaraan</t>
+        </is>
+      </c>
+      <c r="D155" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E155" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F155" s="20" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G155" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="21" t="inlineStr">
+        <is>
+          <t>31.B</t>
+        </is>
+      </c>
+      <c r="B156" s="19" t="inlineStr">
+        <is>
+          <t>`MKU-406`</t>
+        </is>
+      </c>
+      <c r="C156" s="21" t="inlineStr">
+        <is>
+          <t>Agama II</t>
+        </is>
+      </c>
+      <c r="D156" s="21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E156" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F156" s="19" t="inlineStr">
+        <is>
+          <t>MKWU</t>
+        </is>
+      </c>
+      <c r="G156" s="19" t="inlineStr">
+        <is>
+          <t>— (Kebijakan UWG, Sem 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="20" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B157" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C157" s="20" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 4 (8 MK + 1 MK 0 SKS)**</t>
+        </is>
+      </c>
+      <c r="D157" s="22" t="inlineStr">
+        <is>
+          <t>**21**</t>
+        </is>
+      </c>
+      <c r="E157" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F157" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G157" s="20" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 80 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="158"/>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 5 (21 SKS) — Tahap Spesialisasi Keamanan Lanjut, IoT &amp; Peminatan 1</t>
+        </is>
+      </c>
+      <c r="B159" s="16" t="n"/>
+      <c r="C159" s="16" t="n"/>
+      <c r="D159" s="16" t="n"/>
+      <c r="E159" s="16" t="n"/>
+      <c r="F159" s="16" t="n"/>
+      <c r="G159" s="17" t="n"/>
+    </row>
+    <row r="160" ht="26" customHeight="1">
+      <c r="A160" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B160" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D160" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E160" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F160" s="18" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G160" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="16" customHeight="1">
+      <c r="A161" s="21" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B161" s="19" t="inlineStr">
+        <is>
+          <t>`STI-519`</t>
+        </is>
+      </c>
+      <c r="C161" s="19" t="inlineStr">
+        <is>
+          <t>Keamanan Informasi Lanjut</t>
+        </is>
+      </c>
+      <c r="D161" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E161" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F161" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G161" s="19" t="inlineStr">
+        <is>
+          <t>`STI-418`</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="16" customHeight="1">
+      <c r="A162" s="22" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B162" s="20" t="inlineStr">
+        <is>
+          <t>`STI-520`</t>
+        </is>
+      </c>
+      <c r="C162" s="20" t="inlineStr">
+        <is>
+          <t>Data Mining &amp; Visualisasi Data</t>
+        </is>
+      </c>
+      <c r="D162" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E162" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F162" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G162" s="20" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-415`</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="16" customHeight="1">
+      <c r="A163" s="21" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B163" s="19" t="inlineStr">
+        <is>
+          <t>`STI-521`</t>
+        </is>
+      </c>
+      <c r="C163" s="19" t="inlineStr">
+        <is>
+          <t>Internet of Things (IoT)</t>
+        </is>
+      </c>
+      <c r="D163" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E163" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F163" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G163" s="19" t="inlineStr">
+        <is>
+          <t>`STI-312`, `STI-310`</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="16" customHeight="1">
+      <c r="A164" s="22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B164" s="20" t="inlineStr">
+        <is>
+          <t>`STI-522`</t>
+        </is>
+      </c>
+      <c r="C164" s="20" t="inlineStr">
+        <is>
+          <t>Pemrograman Aplikasi Mobile</t>
+        </is>
+      </c>
+      <c r="D164" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E164" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F164" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G164" s="20" t="inlineStr">
+        <is>
+          <t>`STI-311`, `STI-416`</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="16" customHeight="1">
+      <c r="A165" s="21" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B143" s="19" t="inlineStr">
+      <c r="B165" s="19" t="inlineStr">
         <is>
           <t>`STI-523`</t>
         </is>
       </c>
-      <c r="C143" s="19" t="inlineStr">
+      <c r="C165" s="19" t="inlineStr">
         <is>
           <t>Manajemen Proyek TI</t>
         </is>
       </c>
-      <c r="D143" s="21" t="inlineStr">
+      <c r="D165" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E143" s="19" t="inlineStr">
+      <c r="E165" s="19" t="inlineStr">
         <is>
           <t>Teori</t>
         </is>
       </c>
-      <c r="F143" s="19" t="inlineStr">
+      <c r="F165" s="19" t="inlineStr">
         <is>
           <t>Core STI</t>
         </is>
       </c>
-      <c r="G143" s="19" t="inlineStr">
+      <c r="G165" s="19" t="inlineStr">
         <is>
           <t>`STI-306`, `STI-309`</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="22" t="inlineStr">
+    <row r="166" ht="16" customHeight="1">
+      <c r="A166" s="22" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B144" s="20" t="inlineStr">
+      <c r="B166" s="20" t="inlineStr">
         <is>
           <t>`MKU-507`</t>
         </is>
       </c>
-      <c r="C144" s="20" t="inlineStr">
+      <c r="C166" s="20" t="inlineStr">
         <is>
           <t>Kuliah Pengabdian Kepada Masyarakat (KPM)</t>
         </is>
       </c>
-      <c r="D144" s="22" t="inlineStr">
+      <c r="D166" s="22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E144" s="20" t="inlineStr">
+      <c r="E166" s="20" t="inlineStr">
         <is>
           <t>Praktik</t>
         </is>
       </c>
-      <c r="F144" s="20" t="inlineStr">
+      <c r="F166" s="20" t="inlineStr">
         <is>
           <t>MKWU</t>
         </is>
       </c>
-      <c r="G144" s="20" t="inlineStr">
+      <c r="G166" s="20" t="inlineStr">
         <is>
           <t>$\ge 80\text{ SKS}$</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="16" customHeight="1">
-      <c r="A145" s="21" t="inlineStr">
+    <row r="167" ht="16" customHeight="1">
+      <c r="A167" s="21" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B145" s="19" t="inlineStr">
+      <c r="B167" s="19" t="inlineStr">
         <is>
           <t>`STA/B/C`</t>
         </is>
       </c>
-      <c r="C145" s="19" t="inlineStr">
+      <c r="C167" s="19" t="inlineStr">
         <is>
           <t>**MK Pilihan Peminatan 1**</t>
         </is>
       </c>
-      <c r="D145" s="21" t="inlineStr">
+      <c r="D167" s="21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E145" s="19" t="inlineStr">
+      <c r="E167" s="19" t="inlineStr">
         <is>
           <t>Elektif</t>
         </is>
       </c>
-      <c r="F145" s="19" t="inlineStr">
+      <c r="F167" s="19" t="inlineStr">
         <is>
           <t>Peminatan</t>
         </is>
       </c>
-      <c r="G145" s="19" t="inlineStr">
+      <c r="G167" s="19" t="inlineStr">
         <is>
           <t>Prasyarat Peminatan</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="22" t="inlineStr">
+    <row r="168" ht="16" customHeight="1">
+      <c r="A168" s="22" t="inlineStr">
         <is>
           <t>38.B</t>
         </is>
       </c>
-      <c r="B146" s="20" t="inlineStr">
+      <c r="B168" s="20" t="inlineStr">
         <is>
           <t>`MKU-508`</t>
         </is>
       </c>
-      <c r="C146" s="20" t="inlineStr">
+      <c r="C168" s="20" t="inlineStr">
         <is>
           <t>Kewirausahaan II</t>
         </is>
       </c>
-      <c r="D146" s="22" t="inlineStr">
+      <c r="D168" s="22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E146" s="20" t="inlineStr">
+      <c r="E168" s="20" t="inlineStr">
         <is>
           <t>Teori</t>
         </is>
       </c>
-      <c r="F146" s="20" t="inlineStr">
+      <c r="F168" s="20" t="inlineStr">
         <is>
           <t>MKWU</t>
         </is>
       </c>
-      <c r="G146" s="20" t="inlineStr">
+      <c r="G168" s="20" t="inlineStr">
         <is>
           <t>— (Kebijakan UWG, Sem 5)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="16" customHeight="1">
-      <c r="A147" s="19" t="inlineStr">
+    <row r="169" ht="16" customHeight="1">
+      <c r="A169" s="19" t="inlineStr">
         <is>
           <t>**SUBTOTAL**</t>
         </is>
       </c>
-      <c r="B147" s="21" t="inlineStr">
+      <c r="B169" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C147" s="19" t="inlineStr">
+      <c r="C169" s="19" t="inlineStr">
         <is>
           <t>**Total SKS Semester 5 (7 MK + 1 MK 0 SKS)**</t>
         </is>
       </c>
-      <c r="D147" s="21" t="inlineStr">
+      <c r="D169" s="21" t="inlineStr">
         <is>
           <t>**21**</t>
         </is>
       </c>
-      <c r="E147" s="19" t="inlineStr">
+      <c r="E169" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F147" s="19" t="inlineStr">
+      <c r="F169" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G147" s="19" t="inlineStr">
+      <c r="G169" s="19" t="inlineStr">
         <is>
           <t>**Kumulatif: 101 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="148"/>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 6 (19 SKS) — Tahap Spesialisasi Deep Learning, Platform Engineering &amp; MBKM</t>
-        </is>
-      </c>
-      <c r="B149" s="16" t="n"/>
-      <c r="C149" s="16" t="n"/>
-      <c r="D149" s="16" t="n"/>
-      <c r="E149" s="16" t="n"/>
-      <c r="F149" s="16" t="n"/>
-      <c r="G149" s="17" t="n"/>
-    </row>
-    <row r="150" ht="26" customHeight="1">
-      <c r="A150" s="18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B150" s="18" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C150" s="18" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D150" s="18" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E150" s="18" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F150" s="18" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G150" s="18" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="16" customHeight="1">
-      <c r="A151" s="21" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B151" s="19" t="inlineStr">
-        <is>
-          <t>`STI-624`</t>
-        </is>
-      </c>
-      <c r="C151" s="19" t="inlineStr">
-        <is>
-          <t>Integrasi Layanan Cerdas Berbasis AI</t>
-        </is>
-      </c>
-      <c r="D151" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E151" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F151" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G151" s="19" t="inlineStr">
-        <is>
-          <t>`STI-413`, `STI-416`</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="16" customHeight="1">
-      <c r="A152" s="22" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B152" s="20" t="inlineStr">
-        <is>
-          <t>`STI-625`</t>
-        </is>
-      </c>
-      <c r="C152" s="20" t="inlineStr">
-        <is>
-          <t>Smart City &amp; Pemerintahan Digital</t>
-        </is>
-      </c>
-      <c r="D152" s="22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E152" s="20" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F152" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G152" s="20" t="inlineStr">
-        <is>
-          <t>`STI-521`</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="16" customHeight="1">
-      <c r="A153" s="21" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B153" s="19" t="inlineStr">
-        <is>
-          <t>`STI-626`</t>
-        </is>
-      </c>
-      <c r="C153" s="19" t="inlineStr">
-        <is>
-          <t>Deep Learning &amp; Neural Networks</t>
-        </is>
-      </c>
-      <c r="D153" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E153" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F153" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G153" s="19" t="inlineStr">
-        <is>
-          <t>`STI-413`</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="22" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B154" s="20" t="inlineStr">
-        <is>
-          <t>`STI-627`</t>
-        </is>
-      </c>
-      <c r="C154" s="20" t="inlineStr">
-        <is>
-          <t>Digital Platform Engineering</t>
-        </is>
-      </c>
-      <c r="D154" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E154" s="20" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F154" s="20" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G154" s="20" t="inlineStr">
-        <is>
-          <t>`STI-416`</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="16" customHeight="1">
-      <c r="A155" s="21" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B155" s="19" t="inlineStr">
-        <is>
-          <t>`FST-611`</t>
-        </is>
-      </c>
-      <c r="C155" s="19" t="inlineStr">
-        <is>
-          <t>Metodologi Penelitian</t>
-        </is>
-      </c>
-      <c r="D155" s="21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E155" s="19" t="inlineStr">
-        <is>
-          <t>Teori</t>
-        </is>
-      </c>
-      <c r="F155" s="19" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G155" s="19" t="inlineStr">
-        <is>
-          <t>$\ge 76\text{ SKS}$</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="16" customHeight="1">
-      <c r="A156" s="22" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B156" s="20" t="inlineStr">
-        <is>
-          <t>`STA/B/C`</t>
-        </is>
-      </c>
-      <c r="C156" s="20" t="inlineStr">
-        <is>
-          <t>**MK Pilihan Peminatan 2**</t>
-        </is>
-      </c>
-      <c r="D156" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E156" s="20" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F156" s="20" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G156" s="20" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="16" customHeight="1">
-      <c r="A157" s="21" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B157" s="19" t="inlineStr">
-        <is>
-          <t>`STA/B/C`</t>
-        </is>
-      </c>
-      <c r="C157" s="19" t="inlineStr">
-        <is>
-          <t>**MK Pilihan Peminatan 3**</t>
-        </is>
-      </c>
-      <c r="D157" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E157" s="19" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F157" s="19" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G157" s="19" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="16" customHeight="1">
-      <c r="A158" s="20" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B158" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C158" s="20" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 6 (7 MK)**</t>
-        </is>
-      </c>
-      <c r="D158" s="22" t="inlineStr">
-        <is>
-          <t>**19**</t>
-        </is>
-      </c>
-      <c r="E158" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F158" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G158" s="20" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 120 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="159"/>
-    <row r="160" ht="20" customHeight="1">
-      <c r="A160" s="15" t="inlineStr">
-        <is>
-          <t>SEMESTER 7 (20 SKS) — Tahap Integrasi Capstone, PKL &amp; Pra-Skripsi</t>
-        </is>
-      </c>
-      <c r="B160" s="16" t="n"/>
-      <c r="C160" s="16" t="n"/>
-      <c r="D160" s="16" t="n"/>
-      <c r="E160" s="16" t="n"/>
-      <c r="F160" s="16" t="n"/>
-      <c r="G160" s="17" t="n"/>
-    </row>
-    <row r="161" ht="26" customHeight="1">
-      <c r="A161" s="18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B161" s="18" t="inlineStr">
-        <is>
-          <t>Kode MK</t>
-        </is>
-      </c>
-      <c r="C161" s="18" t="inlineStr">
-        <is>
-          <t>Nama Mata Kuliah</t>
-        </is>
-      </c>
-      <c r="D161" s="18" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
-      <c r="E161" s="18" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="F161" s="18" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="G161" s="18" t="inlineStr">
-        <is>
-          <t>Prasyarat</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="16" customHeight="1">
-      <c r="A162" s="21" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B162" s="19" t="inlineStr">
-        <is>
-          <t>`STI-728`</t>
-        </is>
-      </c>
-      <c r="C162" s="19" t="inlineStr">
-        <is>
-          <t>Inovasi Teknologi dan Startup Digital</t>
-        </is>
-      </c>
-      <c r="D162" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E162" s="19" t="inlineStr">
-        <is>
-          <t>+P</t>
-        </is>
-      </c>
-      <c r="F162" s="19" t="inlineStr">
-        <is>
-          <t>Core STI</t>
-        </is>
-      </c>
-      <c r="G162" s="19" t="inlineStr">
-        <is>
-          <t>`STI-627`, `MKU-204`</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="16" customHeight="1">
-      <c r="A163" s="22" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B163" s="20" t="inlineStr">
-        <is>
-          <t>`FST-610`</t>
-        </is>
-      </c>
-      <c r="C163" s="20" t="inlineStr">
-        <is>
-          <t>Capstone Project FSTI</t>
-        </is>
-      </c>
-      <c r="D163" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E163" s="20" t="inlineStr">
-        <is>
-          <t>Proyek</t>
-        </is>
-      </c>
-      <c r="F163" s="20" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G163" s="20" t="inlineStr">
-        <is>
-          <t>`STI-523`, $\ge 100\text{ SKS}$</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="16" customHeight="1">
-      <c r="A164" s="21" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B164" s="19" t="inlineStr">
-        <is>
-          <t>`FST-612`</t>
-        </is>
-      </c>
-      <c r="C164" s="19" t="inlineStr">
-        <is>
-          <t>Praktik Kerja Lapangan (PKL)</t>
-        </is>
-      </c>
-      <c r="D164" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E164" s="19" t="inlineStr">
-        <is>
-          <t>Magang</t>
-        </is>
-      </c>
-      <c r="F164" s="19" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G164" s="19" t="inlineStr">
-        <is>
-          <t>$\ge 100\text{ SKS}$</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="16" customHeight="1">
-      <c r="A165" s="22" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="B165" s="20" t="inlineStr">
-        <is>
-          <t>`FST-613`</t>
-        </is>
-      </c>
-      <c r="C165" s="20" t="inlineStr">
-        <is>
-          <t>Pra-Skripsi / Seminar Proposal</t>
-        </is>
-      </c>
-      <c r="D165" s="22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E165" s="20" t="inlineStr">
-        <is>
-          <t>Seminar</t>
-        </is>
-      </c>
-      <c r="F165" s="20" t="inlineStr">
-        <is>
-          <t>FSTI</t>
-        </is>
-      </c>
-      <c r="G165" s="20" t="inlineStr">
-        <is>
-          <t>`FST-611`, $\ge 100\text{ SKS}$</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="16" customHeight="1">
-      <c r="A166" s="21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="B166" s="19" t="inlineStr">
-        <is>
-          <t>`STA/B/C`</t>
-        </is>
-      </c>
-      <c r="C166" s="19" t="inlineStr">
-        <is>
-          <t>**MK Pilihan Peminatan 4**</t>
-        </is>
-      </c>
-      <c r="D166" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E166" s="19" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F166" s="19" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G166" s="19" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="16" customHeight="1">
-      <c r="A167" s="22" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B167" s="20" t="inlineStr">
-        <is>
-          <t>`STA/B/C`</t>
-        </is>
-      </c>
-      <c r="C167" s="20" t="inlineStr">
-        <is>
-          <t>**MK Pilihan Peminatan 5**</t>
-        </is>
-      </c>
-      <c r="D167" s="22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E167" s="20" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F167" s="20" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G167" s="20" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="16" customHeight="1">
-      <c r="A168" s="21" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B168" s="19" t="inlineStr">
-        <is>
-          <t>`STA/B/C`</t>
-        </is>
-      </c>
-      <c r="C168" s="19" t="inlineStr">
-        <is>
-          <t>**MK Pilihan Peminatan 6**</t>
-        </is>
-      </c>
-      <c r="D168" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E168" s="19" t="inlineStr">
-        <is>
-          <t>Elektif</t>
-        </is>
-      </c>
-      <c r="F168" s="19" t="inlineStr">
-        <is>
-          <t>Peminatan</t>
-        </is>
-      </c>
-      <c r="G168" s="19" t="inlineStr">
-        <is>
-          <t>Prasyarat Peminatan</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="16" customHeight="1">
-      <c r="A169" s="20" t="inlineStr">
-        <is>
-          <t>**SUBTOTAL**</t>
-        </is>
-      </c>
-      <c r="B169" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C169" s="20" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 7 (7 MK)**</t>
-        </is>
-      </c>
-      <c r="D169" s="22" t="inlineStr">
-        <is>
-          <t>**20**</t>
-        </is>
-      </c>
-      <c r="E169" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F169" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G169" s="20" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 140 SKS**</t>
         </is>
       </c>
     </row>
@@ -21156,7 +21317,7 @@
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="15" t="inlineStr">
         <is>
-          <t>SEMESTER 8 (6 SKS) — Tahap Penyelesaian Skripsi / Non-Skripsi</t>
+          <t>SEMESTER 6 (19 SKS) — Tahap Spesialisasi Deep Learning, Platform Engineering &amp; MBKM</t>
         </is>
       </c>
       <c r="B171" s="16" t="n"/>
@@ -21206,511 +21367,2136 @@
     <row r="173" ht="16" customHeight="1">
       <c r="A173" s="21" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B173" s="19" t="inlineStr">
         <is>
-          <t>`FST-714`</t>
+          <t>`STI-624`</t>
         </is>
       </c>
       <c r="C173" s="19" t="inlineStr">
         <is>
-          <t>Skripsi / Tugas Akhir</t>
+          <t>Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="D173" s="21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E173" s="19" t="inlineStr">
         <is>
-          <t>Mandiri</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F173" s="19" t="inlineStr">
         <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G173" s="19" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-416`</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="16" customHeight="1">
+      <c r="A174" s="22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B174" s="20" t="inlineStr">
+        <is>
+          <t>`STI-625`</t>
+        </is>
+      </c>
+      <c r="C174" s="20" t="inlineStr">
+        <is>
+          <t>Smart City &amp; Pemerintahan Digital</t>
+        </is>
+      </c>
+      <c r="D174" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E174" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F174" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G174" s="20" t="inlineStr">
+        <is>
+          <t>`STI-521`</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="16" customHeight="1">
+      <c r="A175" s="21" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B175" s="19" t="inlineStr">
+        <is>
+          <t>`STI-626`</t>
+        </is>
+      </c>
+      <c r="C175" s="19" t="inlineStr">
+        <is>
+          <t>Deep Learning &amp; Neural Networks</t>
+        </is>
+      </c>
+      <c r="D175" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E175" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F175" s="19" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G175" s="19" t="inlineStr">
+        <is>
+          <t>`STI-413`</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="16" customHeight="1">
+      <c r="A176" s="22" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B176" s="20" t="inlineStr">
+        <is>
+          <t>`STI-627`</t>
+        </is>
+      </c>
+      <c r="C176" s="20" t="inlineStr">
+        <is>
+          <t>Digital Platform Engineering</t>
+        </is>
+      </c>
+      <c r="D176" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E176" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F176" s="20" t="inlineStr">
+        <is>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G176" s="20" t="inlineStr">
+        <is>
+          <t>`STI-416`</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="16" customHeight="1">
+      <c r="A177" s="21" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B177" s="19" t="inlineStr">
+        <is>
+          <t>`FST-611`</t>
+        </is>
+      </c>
+      <c r="C177" s="19" t="inlineStr">
+        <is>
+          <t>Metodologi Penelitian</t>
+        </is>
+      </c>
+      <c r="D177" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E177" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F177" s="19" t="inlineStr">
+        <is>
           <t>FSTI</t>
         </is>
       </c>
-      <c r="G173" s="19" t="inlineStr">
-        <is>
-          <t>`FST-613`, $\ge 120\text{ SKS}$</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="16" customHeight="1">
-      <c r="A174" s="20" t="inlineStr">
+      <c r="G177" s="19" t="inlineStr">
+        <is>
+          <t>$\ge 76\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="16" customHeight="1">
+      <c r="A178" s="22" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B178" s="20" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C178" s="20" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 2**</t>
+        </is>
+      </c>
+      <c r="D178" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E178" s="20" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F178" s="20" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G178" s="20" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="16" customHeight="1">
+      <c r="A179" s="21" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B179" s="19" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C179" s="19" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 3**</t>
+        </is>
+      </c>
+      <c r="D179" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E179" s="19" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F179" s="19" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G179" s="19" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="16" customHeight="1">
+      <c r="A180" s="20" t="inlineStr">
         <is>
           <t>**SUBTOTAL**</t>
         </is>
       </c>
-      <c r="B174" s="22" t="inlineStr">
+      <c r="B180" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C174" s="20" t="inlineStr">
-        <is>
-          <t>**Total SKS Semester 8 (1 MK)**</t>
-        </is>
-      </c>
-      <c r="D174" s="22" t="inlineStr">
-        <is>
-          <t>**6**</t>
-        </is>
-      </c>
-      <c r="E174" s="20" t="inlineStr">
+      <c r="C180" s="20" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 6 (7 MK)**</t>
+        </is>
+      </c>
+      <c r="D180" s="22" t="inlineStr">
+        <is>
+          <t>**19**</t>
+        </is>
+      </c>
+      <c r="E180" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F174" s="20" t="inlineStr">
+      <c r="F180" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G174" s="20" t="inlineStr">
-        <is>
-          <t>**Kumulatif: 146 SKS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="175"/>
-    <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="15" t="inlineStr">
-        <is>
-          <t>3.1 REKAPITULASI &amp; MATRIKS KALKULASI SKS AKUMULATIF SEMESTER 1 – 8</t>
-        </is>
-      </c>
-      <c r="B176" s="16" t="n"/>
-      <c r="C176" s="16" t="n"/>
-      <c r="D176" s="16" t="n"/>
-      <c r="E176" s="16" t="n"/>
-      <c r="F176" s="17" t="n"/>
-    </row>
-    <row r="177" ht="26" customHeight="1">
-      <c r="A177" s="18" t="inlineStr">
-        <is>
-          <t>Semester</t>
-        </is>
-      </c>
-      <c r="B177" s="18" t="inlineStr">
-        <is>
-          <t>Jumlah MK</t>
-        </is>
-      </c>
-      <c r="C177" s="18" t="inlineStr">
-        <is>
-          <t>Beban SKS</t>
-        </is>
-      </c>
-      <c r="D177" s="18" t="inlineStr">
-        <is>
-          <t>SKS Kumulatif</t>
-        </is>
-      </c>
-      <c r="E177" s="18" t="inlineStr">
-        <is>
-          <t>Persentase</t>
-        </is>
-      </c>
-      <c r="F177" s="18" t="inlineStr">
-        <is>
-          <t>Tahapan Akademik &amp; Karakteristik</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="16" customHeight="1">
-      <c r="A178" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 1**</t>
-        </is>
-      </c>
-      <c r="B178" s="21" t="inlineStr">
-        <is>
-          <t>8 MK</t>
-        </is>
-      </c>
-      <c r="C178" s="21" t="inlineStr">
-        <is>
-          <t>19 SKS</t>
-        </is>
-      </c>
-      <c r="D178" s="21" t="inlineStr">
-        <is>
-          <t>19 SKS</t>
-        </is>
-      </c>
-      <c r="E178" s="19" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="F178" s="19" t="inlineStr">
-        <is>
-          <t>Tahap Fondasi Sains, Algoritma &amp; Logika</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="16" customHeight="1">
-      <c r="A179" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 2**</t>
-        </is>
-      </c>
-      <c r="B179" s="22" t="inlineStr">
-        <is>
-          <t>8 MK</t>
-        </is>
-      </c>
-      <c r="C179" s="22" t="inlineStr">
-        <is>
-          <t>20 SKS</t>
-        </is>
-      </c>
-      <c r="D179" s="22" t="inlineStr">
-        <is>
-          <t>39 SKS</t>
-        </is>
-      </c>
-      <c r="E179" s="20" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="F179" s="20" t="inlineStr">
-        <is>
-          <t>Tahap Fondasi Data, Matdis &amp; OOP</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="16" customHeight="1">
-      <c r="A180" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 3**</t>
-        </is>
-      </c>
-      <c r="B180" s="21" t="inlineStr">
-        <is>
-          <t>7 MK</t>
-        </is>
-      </c>
-      <c r="C180" s="21" t="inlineStr">
-        <is>
-          <t>20 SKS</t>
-        </is>
-      </c>
-      <c r="D180" s="21" t="inlineStr">
-        <is>
-          <t>59 SKS</t>
-        </is>
-      </c>
-      <c r="E180" s="19" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="F180" s="19" t="inlineStr">
-        <is>
-          <t>Tahap Penguatan Core RPL, OS &amp; Jaringan</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="16" customHeight="1">
-      <c r="A181" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 4**</t>
-        </is>
-      </c>
-      <c r="B181" s="22" t="inlineStr">
-        <is>
-          <t>8 MK</t>
-        </is>
-      </c>
-      <c r="C181" s="22" t="inlineStr">
-        <is>
-          <t>21 SKS</t>
-        </is>
-      </c>
-      <c r="D181" s="22" t="inlineStr">
-        <is>
-          <t>80 SKS</t>
-        </is>
-      </c>
-      <c r="E181" s="20" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="F181" s="20" t="inlineStr">
-        <is>
-          <t>Tahap Penguatan Core AI/ML, NLP &amp; Cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="16" customHeight="1">
-      <c r="A182" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 5**</t>
-        </is>
-      </c>
-      <c r="B182" s="21" t="inlineStr">
-        <is>
-          <t>7 MK</t>
-        </is>
-      </c>
-      <c r="C182" s="21" t="inlineStr">
-        <is>
-          <t>21 SKS</t>
-        </is>
-      </c>
-      <c r="D182" s="21" t="inlineStr">
-        <is>
-          <t>101 SKS</t>
-        </is>
-      </c>
-      <c r="E182" s="19" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="F182" s="19" t="inlineStr">
-        <is>
-          <t>Tahap Spesialisasi Keamanan Lanjut &amp; IoT</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="16" customHeight="1">
-      <c r="A183" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 6**</t>
-        </is>
-      </c>
-      <c r="B183" s="22" t="inlineStr">
-        <is>
-          <t>7 MK</t>
-        </is>
-      </c>
-      <c r="C183" s="22" t="inlineStr">
-        <is>
-          <t>19 SKS</t>
-        </is>
-      </c>
-      <c r="D183" s="22" t="inlineStr">
-        <is>
-          <t>120 SKS</t>
-        </is>
-      </c>
-      <c r="E183" s="20" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="F183" s="20" t="inlineStr">
-        <is>
-          <t>Tahap Spesialisasi Deep Learning &amp; Platform Eng</t>
+      <c r="G180" s="20" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 120 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="181"/>
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 7 (20 SKS) — Tahap Integrasi Capstone, PKL &amp; Pra-Skripsi</t>
+        </is>
+      </c>
+      <c r="B182" s="16" t="n"/>
+      <c r="C182" s="16" t="n"/>
+      <c r="D182" s="16" t="n"/>
+      <c r="E182" s="16" t="n"/>
+      <c r="F182" s="16" t="n"/>
+      <c r="G182" s="17" t="n"/>
+    </row>
+    <row r="183" ht="26" customHeight="1">
+      <c r="A183" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B183" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C183" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D183" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E183" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F183" s="18" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G183" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
         </is>
       </c>
     </row>
     <row r="184" ht="16" customHeight="1">
-      <c r="A184" s="19" t="inlineStr">
-        <is>
-          <t>**Sem 7**</t>
-        </is>
-      </c>
-      <c r="B184" s="21" t="inlineStr">
-        <is>
-          <t>7 MK</t>
-        </is>
-      </c>
-      <c r="C184" s="21" t="inlineStr">
-        <is>
-          <t>20 SKS</t>
+      <c r="A184" s="21" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B184" s="19" t="inlineStr">
+        <is>
+          <t>`STI-728`</t>
+        </is>
+      </c>
+      <c r="C184" s="19" t="inlineStr">
+        <is>
+          <t>Inovasi Teknologi dan Startup Digital</t>
         </is>
       </c>
       <c r="D184" s="21" t="inlineStr">
         <is>
-          <t>140 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E184" s="19" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>+P</t>
         </is>
       </c>
       <c r="F184" s="19" t="inlineStr">
         <is>
-          <t>Tahap Integrasi Capstone, PKL &amp; Sempro</t>
+          <t>Core STI</t>
+        </is>
+      </c>
+      <c r="G184" s="19" t="inlineStr">
+        <is>
+          <t>`STI-627`, `MKU-204`</t>
         </is>
       </c>
     </row>
     <row r="185" ht="16" customHeight="1">
-      <c r="A185" s="20" t="inlineStr">
-        <is>
-          <t>**Sem 8**</t>
-        </is>
-      </c>
-      <c r="B185" s="22" t="inlineStr">
-        <is>
-          <t>1 MK</t>
-        </is>
-      </c>
-      <c r="C185" s="22" t="inlineStr">
-        <is>
-          <t>6 SKS</t>
+      <c r="A185" s="22" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B185" s="20" t="inlineStr">
+        <is>
+          <t>`FST-610`</t>
+        </is>
+      </c>
+      <c r="C185" s="20" t="inlineStr">
+        <is>
+          <t>Capstone Project FSTI</t>
         </is>
       </c>
       <c r="D185" s="22" t="inlineStr">
         <is>
-          <t>146 SKS</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E185" s="20" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>Proyek</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
         <is>
-          <t>Tahap Penyelesaian Skripsi / Non-Skripsi</t>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G185" s="20" t="inlineStr">
+        <is>
+          <t>`STI-523`, $\ge 100\text{ SKS}$</t>
         </is>
       </c>
     </row>
     <row r="186" ht="16" customHeight="1">
-      <c r="A186" s="19" t="inlineStr">
-        <is>
-          <t>**TOTAL**</t>
+      <c r="A186" s="21" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="B186" s="19" t="inlineStr">
         <is>
-          <t>**55 MK**</t>
+          <t>`FST-612`</t>
         </is>
       </c>
       <c r="C186" s="19" t="inlineStr">
         <is>
-          <t>**146 SKS**</t>
-        </is>
-      </c>
-      <c r="D186" s="19" t="inlineStr">
-        <is>
-          <t>**146 SKS**</t>
+          <t>Praktik Kerja Lapangan (PKL)</t>
+        </is>
+      </c>
+      <c r="D186" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="E186" s="19" t="inlineStr">
         <is>
-          <t>**100,0%**</t>
+          <t>Magang</t>
         </is>
       </c>
       <c r="F186" s="19" t="inlineStr">
         <is>
-          <t>**Paket Lulus Tepat Waktu (4 Tahun)**</t>
-        </is>
-      </c>
-    </row>
-    <row r="187"/>
-    <row r="188" ht="20" customHeight="1">
-      <c r="A188" s="15" t="inlineStr">
-        <is>
-          <t>3 PEMINATAN SPESIALISASI KEAHLIAN SISTEKIN</t>
-        </is>
-      </c>
-      <c r="B188" s="16" t="n"/>
-      <c r="C188" s="16" t="n"/>
-      <c r="D188" s="16" t="n"/>
-      <c r="E188" s="16" t="n"/>
-      <c r="F188" s="17" t="n"/>
-    </row>
-    <row r="189" ht="26" customHeight="1">
-      <c r="A189" s="18" t="inlineStr">
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G186" s="19" t="inlineStr">
+        <is>
+          <t>$\ge 100\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="16" customHeight="1">
+      <c r="A187" s="22" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B187" s="20" t="inlineStr">
+        <is>
+          <t>`FST-613`</t>
+        </is>
+      </c>
+      <c r="C187" s="20" t="inlineStr">
+        <is>
+          <t>Pra-Skripsi / Seminar Proposal</t>
+        </is>
+      </c>
+      <c r="D187" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E187" s="20" t="inlineStr">
+        <is>
+          <t>Seminar</t>
+        </is>
+      </c>
+      <c r="F187" s="20" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G187" s="20" t="inlineStr">
+        <is>
+          <t>`FST-611`, $\ge 100\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="16" customHeight="1">
+      <c r="A188" s="21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B188" s="19" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C188" s="19" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 4**</t>
+        </is>
+      </c>
+      <c r="D188" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E188" s="19" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F188" s="19" t="inlineStr">
         <is>
           <t>Peminatan</t>
         </is>
       </c>
-      <c r="B189" s="18" t="inlineStr">
-        <is>
-          <t>Basis Profil (PL)</t>
-        </is>
-      </c>
-      <c r="C189" s="18" t="inlineStr">
-        <is>
-          <t>Mata Kuliah Pilihan (@ 3 SKS)</t>
+      <c r="G188" s="19" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="16" customHeight="1">
+      <c r="A189" s="22" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B189" s="20" t="inlineStr">
+        <is>
+          <t>`STA/B/C`</t>
+        </is>
+      </c>
+      <c r="C189" s="20" t="inlineStr">
+        <is>
+          <t>**MK Pilihan Peminatan 5**</t>
+        </is>
+      </c>
+      <c r="D189" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E189" s="20" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F189" s="20" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G189" s="20" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
         </is>
       </c>
     </row>
     <row r="190" ht="16" customHeight="1">
-      <c r="A190" s="19" t="inlineStr">
-        <is>
-          <t>**P1: Integrated Smart Systems** *(Flagship)*</t>
+      <c r="A190" s="21" t="inlineStr">
+        <is>
+          <t>52</t>
         </is>
       </c>
       <c r="B190" s="19" t="inlineStr">
         <is>
-          <t>**PL-1:** Intelligent IS &amp; Data/AI Engineer</t>
+          <t>`STA/B/C`</t>
         </is>
       </c>
       <c r="C190" s="19" t="inlineStr">
         <is>
-          <t>1. `STA-01` Decision Support Systems (+P, Sem 5)&lt;br&gt;2. `STA-02` Computational Methods &amp; Numerics (+P, Sem 6)&lt;br&gt;3. `STA-03` Intelligent Agent Systems (+P, Sem 6)&lt;br&gt;4. `STA-04` MLOps and AI Pipeline (+P, Sem 7)&lt;br&gt;5. `STA-05` Conversational AI &amp; Assistant (+P, Sem 7)&lt;br&gt;6. `STA-06` Smart Surveillance &amp; IoT Analytics (+P, Sem 7)</t>
+          <t>**MK Pilihan Peminatan 6**</t>
+        </is>
+      </c>
+      <c r="D190" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E190" s="19" t="inlineStr">
+        <is>
+          <t>Elektif</t>
+        </is>
+      </c>
+      <c r="F190" s="19" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="G190" s="19" t="inlineStr">
+        <is>
+          <t>Prasyarat Peminatan</t>
         </is>
       </c>
     </row>
     <row r="191" ht="16" customHeight="1">
       <c r="A191" s="20" t="inlineStr">
         <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B191" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C191" s="20" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 7 (7 MK)**</t>
+        </is>
+      </c>
+      <c r="D191" s="22" t="inlineStr">
+        <is>
+          <t>**20**</t>
+        </is>
+      </c>
+      <c r="E191" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F191" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G191" s="20" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 140 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="192"/>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="15" t="inlineStr">
+        <is>
+          <t>SEMESTER 8 (6 SKS) — Tahap Penyelesaian Skripsi / Non-Skripsi</t>
+        </is>
+      </c>
+      <c r="B193" s="16" t="n"/>
+      <c r="C193" s="16" t="n"/>
+      <c r="D193" s="16" t="n"/>
+      <c r="E193" s="16" t="n"/>
+      <c r="F193" s="16" t="n"/>
+      <c r="G193" s="17" t="n"/>
+    </row>
+    <row r="194" ht="26" customHeight="1">
+      <c r="A194" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B194" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C194" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D194" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E194" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F194" s="18" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="G194" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="16" customHeight="1">
+      <c r="A195" s="21" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B195" s="19" t="inlineStr">
+        <is>
+          <t>`FST-714`</t>
+        </is>
+      </c>
+      <c r="C195" s="19" t="inlineStr">
+        <is>
+          <t>Skripsi / Tugas Akhir</t>
+        </is>
+      </c>
+      <c r="D195" s="21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E195" s="19" t="inlineStr">
+        <is>
+          <t>Mandiri</t>
+        </is>
+      </c>
+      <c r="F195" s="19" t="inlineStr">
+        <is>
+          <t>FSTI</t>
+        </is>
+      </c>
+      <c r="G195" s="19" t="inlineStr">
+        <is>
+          <t>`FST-613`, $\ge 120\text{ SKS}$</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="16" customHeight="1">
+      <c r="A196" s="20" t="inlineStr">
+        <is>
+          <t>**SUBTOTAL**</t>
+        </is>
+      </c>
+      <c r="B196" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C196" s="20" t="inlineStr">
+        <is>
+          <t>**Total SKS Semester 8 (1 MK)**</t>
+        </is>
+      </c>
+      <c r="D196" s="22" t="inlineStr">
+        <is>
+          <t>**6**</t>
+        </is>
+      </c>
+      <c r="E196" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F196" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G196" s="20" t="inlineStr">
+        <is>
+          <t>**Kumulatif: 146 SKS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="197"/>
+    <row r="198" ht="20" customHeight="1">
+      <c r="A198" s="15" t="inlineStr">
+        <is>
+          <t>3.1 REKAPITULASI &amp; MATRIKS KALKULASI SKS AKUMULATIF SEMESTER 1 – 8</t>
+        </is>
+      </c>
+      <c r="B198" s="16" t="n"/>
+      <c r="C198" s="16" t="n"/>
+      <c r="D198" s="16" t="n"/>
+      <c r="E198" s="16" t="n"/>
+      <c r="F198" s="17" t="n"/>
+    </row>
+    <row r="199" ht="26" customHeight="1">
+      <c r="A199" s="18" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="B199" s="18" t="inlineStr">
+        <is>
+          <t>Jumlah MK</t>
+        </is>
+      </c>
+      <c r="C199" s="18" t="inlineStr">
+        <is>
+          <t>Beban SKS</t>
+        </is>
+      </c>
+      <c r="D199" s="18" t="inlineStr">
+        <is>
+          <t>SKS Kumulatif</t>
+        </is>
+      </c>
+      <c r="E199" s="18" t="inlineStr">
+        <is>
+          <t>Persentase</t>
+        </is>
+      </c>
+      <c r="F199" s="18" t="inlineStr">
+        <is>
+          <t>Tahapan Akademik &amp; Karakteristik</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="16" customHeight="1">
+      <c r="A200" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 1**</t>
+        </is>
+      </c>
+      <c r="B200" s="21" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="C200" s="21" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="D200" s="21" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="E200" s="19" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="F200" s="19" t="inlineStr">
+        <is>
+          <t>Tahap Fondasi Sains, Algoritma &amp; Logika</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="16" customHeight="1">
+      <c r="A201" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 2**</t>
+        </is>
+      </c>
+      <c r="B201" s="22" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="C201" s="22" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="D201" s="22" t="inlineStr">
+        <is>
+          <t>39 SKS</t>
+        </is>
+      </c>
+      <c r="E201" s="20" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="F201" s="20" t="inlineStr">
+        <is>
+          <t>Tahap Fondasi Data, Matdis &amp; OOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="16" customHeight="1">
+      <c r="A202" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 3**</t>
+        </is>
+      </c>
+      <c r="B202" s="21" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="C202" s="21" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="D202" s="21" t="inlineStr">
+        <is>
+          <t>59 SKS</t>
+        </is>
+      </c>
+      <c r="E202" s="19" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="F202" s="19" t="inlineStr">
+        <is>
+          <t>Tahap Penguatan Core RPL, OS &amp; Jaringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="16" customHeight="1">
+      <c r="A203" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 4**</t>
+        </is>
+      </c>
+      <c r="B203" s="22" t="inlineStr">
+        <is>
+          <t>8 MK</t>
+        </is>
+      </c>
+      <c r="C203" s="22" t="inlineStr">
+        <is>
+          <t>21 SKS</t>
+        </is>
+      </c>
+      <c r="D203" s="22" t="inlineStr">
+        <is>
+          <t>80 SKS</t>
+        </is>
+      </c>
+      <c r="E203" s="20" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="F203" s="20" t="inlineStr">
+        <is>
+          <t>Tahap Penguatan Core AI/ML, NLP &amp; Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="16" customHeight="1">
+      <c r="A204" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 5**</t>
+        </is>
+      </c>
+      <c r="B204" s="21" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="C204" s="21" t="inlineStr">
+        <is>
+          <t>21 SKS</t>
+        </is>
+      </c>
+      <c r="D204" s="21" t="inlineStr">
+        <is>
+          <t>101 SKS</t>
+        </is>
+      </c>
+      <c r="E204" s="19" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="F204" s="19" t="inlineStr">
+        <is>
+          <t>Tahap Spesialisasi Keamanan Lanjut &amp; IoT</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="16" customHeight="1">
+      <c r="A205" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 6**</t>
+        </is>
+      </c>
+      <c r="B205" s="22" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="C205" s="22" t="inlineStr">
+        <is>
+          <t>19 SKS</t>
+        </is>
+      </c>
+      <c r="D205" s="22" t="inlineStr">
+        <is>
+          <t>120 SKS</t>
+        </is>
+      </c>
+      <c r="E205" s="20" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="F205" s="20" t="inlineStr">
+        <is>
+          <t>Tahap Spesialisasi Deep Learning &amp; Platform Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="16" customHeight="1">
+      <c r="A206" s="19" t="inlineStr">
+        <is>
+          <t>**Sem 7**</t>
+        </is>
+      </c>
+      <c r="B206" s="21" t="inlineStr">
+        <is>
+          <t>7 MK</t>
+        </is>
+      </c>
+      <c r="C206" s="21" t="inlineStr">
+        <is>
+          <t>20 SKS</t>
+        </is>
+      </c>
+      <c r="D206" s="21" t="inlineStr">
+        <is>
+          <t>140 SKS</t>
+        </is>
+      </c>
+      <c r="E206" s="19" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="F206" s="19" t="inlineStr">
+        <is>
+          <t>Tahap Integrasi Capstone, PKL &amp; Sempro</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="16" customHeight="1">
+      <c r="A207" s="20" t="inlineStr">
+        <is>
+          <t>**Sem 8**</t>
+        </is>
+      </c>
+      <c r="B207" s="22" t="inlineStr">
+        <is>
+          <t>1 MK</t>
+        </is>
+      </c>
+      <c r="C207" s="22" t="inlineStr">
+        <is>
+          <t>6 SKS</t>
+        </is>
+      </c>
+      <c r="D207" s="22" t="inlineStr">
+        <is>
+          <t>146 SKS</t>
+        </is>
+      </c>
+      <c r="E207" s="20" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="F207" s="20" t="inlineStr">
+        <is>
+          <t>Tahap Penyelesaian Skripsi / Non-Skripsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="16" customHeight="1">
+      <c r="A208" s="19" t="inlineStr">
+        <is>
+          <t>**TOTAL**</t>
+        </is>
+      </c>
+      <c r="B208" s="19" t="inlineStr">
+        <is>
+          <t>**55 MK**</t>
+        </is>
+      </c>
+      <c r="C208" s="19" t="inlineStr">
+        <is>
+          <t>**146 SKS**</t>
+        </is>
+      </c>
+      <c r="D208" s="19" t="inlineStr">
+        <is>
+          <t>**146 SKS**</t>
+        </is>
+      </c>
+      <c r="E208" s="19" t="inlineStr">
+        <is>
+          <t>**100,0%**</t>
+        </is>
+      </c>
+      <c r="F208" s="19" t="inlineStr">
+        <is>
+          <t>**Paket Lulus Tepat Waktu (4 Tahun)**</t>
+        </is>
+      </c>
+    </row>
+    <row r="209"/>
+    <row r="210" ht="20" customHeight="1">
+      <c r="A210" s="15" t="inlineStr">
+        <is>
+          <t>3 PEMINATAN SPESIALISASI KEAHLIAN SISTEKIN</t>
+        </is>
+      </c>
+      <c r="B210" s="16" t="n"/>
+      <c r="C210" s="16" t="n"/>
+      <c r="D210" s="16" t="n"/>
+      <c r="E210" s="16" t="n"/>
+      <c r="F210" s="17" t="n"/>
+    </row>
+    <row r="211" ht="26" customHeight="1">
+      <c r="A211" s="18" t="inlineStr">
+        <is>
+          <t>Peminatan</t>
+        </is>
+      </c>
+      <c r="B211" s="18" t="inlineStr">
+        <is>
+          <t>Basis Profil (PL)</t>
+        </is>
+      </c>
+      <c r="C211" s="18" t="inlineStr">
+        <is>
+          <t>Mata Kuliah Pilihan (@ 3 SKS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="16" customHeight="1">
+      <c r="A212" s="19" t="inlineStr">
+        <is>
+          <t>**P1: Integrated Smart Systems** *(Flagship)*</t>
+        </is>
+      </c>
+      <c r="B212" s="19" t="inlineStr">
+        <is>
+          <t>**PL-1:** Intelligent IS &amp; Data/AI Engineer</t>
+        </is>
+      </c>
+      <c r="C212" s="19" t="inlineStr">
+        <is>
+          <t>1. `STA-01` Decision Support Systems (+P, Sem 5)&lt;br&gt;2. `STA-02` Computational Methods &amp; Numerics (+P, Sem 6)&lt;br&gt;3. `STA-03` Intelligent Agent Systems (+P, Sem 6)&lt;br&gt;4. `STA-04` MLOps and AI Pipeline (+P, Sem 7)&lt;br&gt;5. `STA-05` Conversational AI &amp; Assistant (+P, Sem 7)&lt;br&gt;6. `STA-06` Smart Surveillance &amp; IoT Analytics (+P, Sem 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="16" customHeight="1">
+      <c r="A213" s="20" t="inlineStr">
+        <is>
           <t>**P2: Cloud Infrastructure &amp; Cybersecurity** *(Volume)*</t>
         </is>
       </c>
-      <c r="B191" s="20" t="inlineStr">
+      <c r="B213" s="20" t="inlineStr">
         <is>
           <t>**PL-2:** Cloud, Cyber &amp; Smart Systems Integrator</t>
         </is>
       </c>
-      <c r="C191" s="20" t="inlineStr">
+      <c r="C213" s="20" t="inlineStr">
         <is>
           <t>1. `STB-01` Network Security &amp; Digital Forensics (+P, Sem 5)&lt;br&gt;2. `STB-02` Cloud Architecture &amp; DevOps (+P, Sem 6)&lt;br&gt;3. `STB-03` Cybersecurity Risk Management (Teori, Sem 6)&lt;br&gt;4. `STB-04` IT Governance &amp; Compliance COBIT 2019 (Teori, Sem 7)&lt;br&gt;5. `STB-05` IT Service Management ITIL 4 (Teori, Sem 7)&lt;br&gt;6. `STB-06` Enterprise Architecture TOGAF (Teori, Sem 7)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="16" customHeight="1">
-      <c r="A192" s="19" t="inlineStr">
+    <row r="214" ht="16" customHeight="1">
+      <c r="A214" s="19" t="inlineStr">
         <is>
           <t>**P3: Digital Platform Engineering** *(Niche &amp; Techno)*</t>
         </is>
       </c>
-      <c r="B192" s="19" t="inlineStr">
+      <c r="B214" s="19" t="inlineStr">
         <is>
           <t>**PL-3:** UI/UX Designer &amp; Platform Engineer</t>
         </is>
       </c>
-      <c r="C192" s="19" t="inlineStr">
+      <c r="C214" s="19" t="inlineStr">
         <is>
           <t>1. `STC-01` UX Research &amp; Design (+P, Sem 5)&lt;br&gt;2. `STC-02` Rekayasa &amp; Otomasi Proses Bisnis (+P, Sem 6)&lt;br&gt;3. `STC-03` Rekayasa Aplikasi Industri Vertikal (+P, Sem 6)&lt;br&gt;4. `STC-04` Immersive Media &amp; XR Development (+P, Sem 7)&lt;br&gt;5. `STC-05` SaaS Architecture &amp; Multi-Tenancy (+P, Sem 7)&lt;br&gt;6. `STC-06` Digital Product Management (Teori, Sem 7)</t>
         </is>
       </c>
     </row>
+    <row r="215"/>
+    <row r="216" ht="20" customHeight="1">
+      <c r="A216" s="15" t="inlineStr">
+        <is>
+          <t>4.1 PEMINATAN 1: INTEGRATED SMART SYSTEMS (FLAGSHIP — 6 MK / 18 SKS)</t>
+        </is>
+      </c>
+      <c r="B216" s="16" t="n"/>
+      <c r="C216" s="16" t="n"/>
+      <c r="D216" s="16" t="n"/>
+      <c r="E216" s="16" t="n"/>
+      <c r="F216" s="16" t="n"/>
+      <c r="G216" s="16" t="n"/>
+      <c r="H216" s="17" t="n"/>
+    </row>
+    <row r="217" ht="26" customHeight="1">
+      <c r="A217" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B217" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C217" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D217" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E217" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F217" s="18" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="G217" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat Akademik</t>
+        </is>
+      </c>
+      <c r="H217" s="18" t="inlineStr">
+        <is>
+          <t>Bahan Kajian Utama</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="16" customHeight="1">
+      <c r="A218" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B218" s="21" t="inlineStr">
+        <is>
+          <t>`STA-01`</t>
+        </is>
+      </c>
+      <c r="C218" s="19" t="inlineStr">
+        <is>
+          <t>Decision Support Systems</t>
+        </is>
+      </c>
+      <c r="D218" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E218" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F218" s="19" t="inlineStr">
+        <is>
+          <t>Sem 5</t>
+        </is>
+      </c>
+      <c r="G218" s="19" t="inlineStr">
+        <is>
+          <t>`STI-307` Sistem Cerdas</t>
+        </is>
+      </c>
+      <c r="H218" s="19" t="inlineStr">
+        <is>
+          <t>BK-IS17 Business Analytics, AHP/TOPSIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="16" customHeight="1">
+      <c r="A219" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B219" s="22" t="inlineStr">
+        <is>
+          <t>`STA-02`</t>
+        </is>
+      </c>
+      <c r="C219" s="20" t="inlineStr">
+        <is>
+          <t>Computational Methods and Numerics</t>
+        </is>
+      </c>
+      <c r="D219" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E219" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F219" s="20" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G219" s="20" t="inlineStr">
+        <is>
+          <t>`STI-102`, `STI-205` Aljabar Linear</t>
+        </is>
+      </c>
+      <c r="H219" s="20" t="inlineStr">
+        <is>
+          <t>BK-IS10 / BK-IT01 Komputasi Saintifik</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="16" customHeight="1">
+      <c r="A220" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B220" s="21" t="inlineStr">
+        <is>
+          <t>`STA-03`</t>
+        </is>
+      </c>
+      <c r="C220" s="19" t="inlineStr">
+        <is>
+          <t>Intelligent Agent Systems</t>
+        </is>
+      </c>
+      <c r="D220" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E220" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F220" s="19" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G220" s="19" t="inlineStr">
+        <is>
+          <t>`STI-307` Sistem Cerdas</t>
+        </is>
+      </c>
+      <c r="H220" s="19" t="inlineStr">
+        <is>
+          <t>BK-IT02 Multi-Agent Systems, Reinforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="16" customHeight="1">
+      <c r="A221" s="22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B221" s="22" t="inlineStr">
+        <is>
+          <t>`STA-04`</t>
+        </is>
+      </c>
+      <c r="C221" s="20" t="inlineStr">
+        <is>
+          <t>MLOps and AI Pipeline</t>
+        </is>
+      </c>
+      <c r="D221" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E221" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F221" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G221" s="20" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-624` Integrasi AI</t>
+        </is>
+      </c>
+      <c r="H221" s="20" t="inlineStr">
+        <is>
+          <t>BK-IS18 Machine Learning Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="16" customHeight="1">
+      <c r="A222" s="21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B222" s="21" t="inlineStr">
+        <is>
+          <t>`STA-05`</t>
+        </is>
+      </c>
+      <c r="C222" s="19" t="inlineStr">
+        <is>
+          <t>Conversational AI and Intelligent Assistant</t>
+        </is>
+      </c>
+      <c r="D222" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E222" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F222" s="19" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G222" s="19" t="inlineStr">
+        <is>
+          <t>`STI-413`, `STI-416` Web Back End</t>
+        </is>
+      </c>
+      <c r="H222" s="19" t="inlineStr">
+        <is>
+          <t>BK-IT02 LLM, RAG Architecture, Prompt Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="16" customHeight="1">
+      <c r="A223" s="22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B223" s="22" t="inlineStr">
+        <is>
+          <t>`STA-06`</t>
+        </is>
+      </c>
+      <c r="C223" s="20" t="inlineStr">
+        <is>
+          <t>Smart Surveillance and IoT Analytics</t>
+        </is>
+      </c>
+      <c r="D223" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E223" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F223" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G223" s="20" t="inlineStr">
+        <is>
+          <t>`STI-626`, `STI-521` IoT</t>
+        </is>
+      </c>
+      <c r="H223" s="20" t="inlineStr">
+        <is>
+          <t>BK-IT02 Video Analytics, Edge AI, Vision</t>
+        </is>
+      </c>
+    </row>
+    <row r="224"/>
+    <row r="225" ht="20" customHeight="1">
+      <c r="A225" s="15" t="inlineStr">
+        <is>
+          <t>4.2 PEMINATAN 2: CLOUD INFRASTRUCTURE &amp; CYBERSECURITY (VOLUME — 6 MK / 18 SKS)</t>
+        </is>
+      </c>
+      <c r="B225" s="16" t="n"/>
+      <c r="C225" s="16" t="n"/>
+      <c r="D225" s="16" t="n"/>
+      <c r="E225" s="16" t="n"/>
+      <c r="F225" s="16" t="n"/>
+      <c r="G225" s="16" t="n"/>
+      <c r="H225" s="17" t="n"/>
+    </row>
+    <row r="226" ht="26" customHeight="1">
+      <c r="A226" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B226" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C226" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D226" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E226" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F226" s="18" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="G226" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat Akademik</t>
+        </is>
+      </c>
+      <c r="H226" s="18" t="inlineStr">
+        <is>
+          <t>Bahan Kajian Utama</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="16" customHeight="1">
+      <c r="A227" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B227" s="21" t="inlineStr">
+        <is>
+          <t>`STB-01`</t>
+        </is>
+      </c>
+      <c r="C227" s="19" t="inlineStr">
+        <is>
+          <t>Network Security and Digital Forensics</t>
+        </is>
+      </c>
+      <c r="D227" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E227" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F227" s="19" t="inlineStr">
+        <is>
+          <t>Sem 5</t>
+        </is>
+      </c>
+      <c r="G227" s="19" t="inlineStr">
+        <is>
+          <t>`STI-312`, `STI-418` Dasar Keamanan</t>
+        </is>
+      </c>
+      <c r="H227" s="19" t="inlineStr">
+        <is>
+          <t>BK-IT06 Cyber Defense, Forensik Jaringan</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="16" customHeight="1">
+      <c r="A228" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B228" s="22" t="inlineStr">
+        <is>
+          <t>`STB-02`</t>
+        </is>
+      </c>
+      <c r="C228" s="20" t="inlineStr">
+        <is>
+          <t>Cloud Architecture &amp; DevOps</t>
+        </is>
+      </c>
+      <c r="D228" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E228" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F228" s="20" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G228" s="20" t="inlineStr">
+        <is>
+          <t>`STI-417` Komputasi Awan</t>
+        </is>
+      </c>
+      <c r="H228" s="20" t="inlineStr">
+        <is>
+          <t>BK-IT05 Cloud Systems, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="16" customHeight="1">
+      <c r="A229" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B229" s="21" t="inlineStr">
+        <is>
+          <t>`STB-03`</t>
+        </is>
+      </c>
+      <c r="C229" s="19" t="inlineStr">
+        <is>
+          <t>Cybersecurity Risk Management</t>
+        </is>
+      </c>
+      <c r="D229" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E229" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F229" s="19" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G229" s="19" t="inlineStr">
+        <is>
+          <t>`STI-418` Dasar Keamanan Informasi</t>
+        </is>
+      </c>
+      <c r="H229" s="19" t="inlineStr">
+        <is>
+          <t>BK-IS06 Risk Management, ISO 27005, NIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="16" customHeight="1">
+      <c r="A230" s="22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B230" s="22" t="inlineStr">
+        <is>
+          <t>`STB-04`</t>
+        </is>
+      </c>
+      <c r="C230" s="20" t="inlineStr">
+        <is>
+          <t>IT Governance &amp; Compliance (COBIT 2019)</t>
+        </is>
+      </c>
+      <c r="D230" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E230" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F230" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G230" s="20" t="inlineStr">
+        <is>
+          <t>`STI-101` Pengantar Sistem &amp; TI</t>
+        </is>
+      </c>
+      <c r="H230" s="20" t="inlineStr">
+        <is>
+          <t>BK-IS07 IT Governance, COBIT 2019 Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="16" customHeight="1">
+      <c r="A231" s="21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B231" s="21" t="inlineStr">
+        <is>
+          <t>`STB-05`</t>
+        </is>
+      </c>
+      <c r="C231" s="19" t="inlineStr">
+        <is>
+          <t>IT Service Management (ITIL 4)</t>
+        </is>
+      </c>
+      <c r="D231" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E231" s="19" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F231" s="19" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G231" s="19" t="inlineStr">
+        <is>
+          <t>`STI-101` Pengantar Sistem &amp; TI</t>
+        </is>
+      </c>
+      <c r="H231" s="19" t="inlineStr">
+        <is>
+          <t>BK-IS08 Service Management, ITIL 4 Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="16" customHeight="1">
+      <c r="A232" s="22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B232" s="22" t="inlineStr">
+        <is>
+          <t>`STB-06`</t>
+        </is>
+      </c>
+      <c r="C232" s="20" t="inlineStr">
+        <is>
+          <t>Enterprise Architecture (TOGAF)</t>
+        </is>
+      </c>
+      <c r="D232" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E232" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F232" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G232" s="20" t="inlineStr">
+        <is>
+          <t>`STI-306` Analisis &amp; Perancangan SI</t>
+        </is>
+      </c>
+      <c r="H232" s="20" t="inlineStr">
+        <is>
+          <t>BK-IS04 Enterprise Architecture, TOGAF Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="233"/>
+    <row r="234" ht="20" customHeight="1">
+      <c r="A234" s="15" t="inlineStr">
+        <is>
+          <t>4.3 PEMINATAN 3: DIGITAL PLATFORM ENGINEERING (NICHE &amp; TECHNO — 6 MK / 18 SKS)</t>
+        </is>
+      </c>
+      <c r="B234" s="16" t="n"/>
+      <c r="C234" s="16" t="n"/>
+      <c r="D234" s="16" t="n"/>
+      <c r="E234" s="16" t="n"/>
+      <c r="F234" s="16" t="n"/>
+      <c r="G234" s="16" t="n"/>
+      <c r="H234" s="17" t="n"/>
+    </row>
+    <row r="235" ht="26" customHeight="1">
+      <c r="A235" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B235" s="18" t="inlineStr">
+        <is>
+          <t>Kode MK</t>
+        </is>
+      </c>
+      <c r="C235" s="18" t="inlineStr">
+        <is>
+          <t>Nama Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="D235" s="18" t="inlineStr">
+        <is>
+          <t>SKS</t>
+        </is>
+      </c>
+      <c r="E235" s="18" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F235" s="18" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="G235" s="18" t="inlineStr">
+        <is>
+          <t>Prasyarat Akademik</t>
+        </is>
+      </c>
+      <c r="H235" s="18" t="inlineStr">
+        <is>
+          <t>Bahan Kajian Utama</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="16" customHeight="1">
+      <c r="A236" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B236" s="21" t="inlineStr">
+        <is>
+          <t>`STC-01`</t>
+        </is>
+      </c>
+      <c r="C236" s="19" t="inlineStr">
+        <is>
+          <t>User Experience Research &amp; Design</t>
+        </is>
+      </c>
+      <c r="D236" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E236" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F236" s="19" t="inlineStr">
+        <is>
+          <t>Sem 5</t>
+        </is>
+      </c>
+      <c r="G236" s="19" t="inlineStr">
+        <is>
+          <t>`STI-308` UI/UX Design &amp; Prototyping</t>
+        </is>
+      </c>
+      <c r="H236" s="19" t="inlineStr">
+        <is>
+          <t>BK-IS13 Human-Centered Design, Usability</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="16" customHeight="1">
+      <c r="A237" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B237" s="22" t="inlineStr">
+        <is>
+          <t>`STC-02`</t>
+        </is>
+      </c>
+      <c r="C237" s="20" t="inlineStr">
+        <is>
+          <t>Rekayasa &amp; Otomasi Proses Bisnis (BPA)</t>
+        </is>
+      </c>
+      <c r="D237" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E237" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F237" s="20" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G237" s="20" t="inlineStr">
+        <is>
+          <t>`STI-306` Analisis &amp; Perancangan SI</t>
+        </is>
+      </c>
+      <c r="H237" s="20" t="inlineStr">
+        <is>
+          <t>BK-IS09 Business Process, Workflow &amp; RPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="16" customHeight="1">
+      <c r="A238" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B238" s="21" t="inlineStr">
+        <is>
+          <t>`STC-03`</t>
+        </is>
+      </c>
+      <c r="C238" s="19" t="inlineStr">
+        <is>
+          <t>Rekayasa Aplikasi Industri Vertikal (FinTech &amp; EdTech)</t>
+        </is>
+      </c>
+      <c r="D238" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E238" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F238" s="19" t="inlineStr">
+        <is>
+          <t>Sem 6</t>
+        </is>
+      </c>
+      <c r="G238" s="19" t="inlineStr">
+        <is>
+          <t>`STI-416` Web Back End Development</t>
+        </is>
+      </c>
+      <c r="H238" s="19" t="inlineStr">
+        <is>
+          <t>BK-IS05 Application Domains, Microservices</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="16" customHeight="1">
+      <c r="A239" s="22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B239" s="22" t="inlineStr">
+        <is>
+          <t>`STC-04`</t>
+        </is>
+      </c>
+      <c r="C239" s="20" t="inlineStr">
+        <is>
+          <t>Immersive Media &amp; XR Development</t>
+        </is>
+      </c>
+      <c r="D239" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E239" s="20" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F239" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G239" s="20" t="inlineStr">
+        <is>
+          <t>`STI-311` Web Front End Development</t>
+        </is>
+      </c>
+      <c r="H239" s="20" t="inlineStr">
+        <is>
+          <t>BK-IT14 Computer Graphics, Unity/WebXR</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="16" customHeight="1">
+      <c r="A240" s="21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B240" s="21" t="inlineStr">
+        <is>
+          <t>`STC-05`</t>
+        </is>
+      </c>
+      <c r="C240" s="19" t="inlineStr">
+        <is>
+          <t>SaaS Architecture &amp; Multi-Tenancy</t>
+        </is>
+      </c>
+      <c r="D240" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E240" s="19" t="inlineStr">
+        <is>
+          <t>+P</t>
+        </is>
+      </c>
+      <c r="F240" s="19" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G240" s="19" t="inlineStr">
+        <is>
+          <t>`STI-416` Web Back End Development</t>
+        </is>
+      </c>
+      <c r="H240" s="19" t="inlineStr">
+        <is>
+          <t>BK-IT08 Distributed Systems, Multi-Tenancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="16" customHeight="1">
+      <c r="A241" s="22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B241" s="22" t="inlineStr">
+        <is>
+          <t>`STC-06`</t>
+        </is>
+      </c>
+      <c r="C241" s="20" t="inlineStr">
+        <is>
+          <t>Digital Product Management &amp; Agile Practices</t>
+        </is>
+      </c>
+      <c r="D241" s="22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E241" s="20" t="inlineStr">
+        <is>
+          <t>Teori</t>
+        </is>
+      </c>
+      <c r="F241" s="20" t="inlineStr">
+        <is>
+          <t>Sem 7</t>
+        </is>
+      </c>
+      <c r="G241" s="20" t="inlineStr">
+        <is>
+          <t>`STI-523` Manajemen Proyek TI</t>
+        </is>
+      </c>
+      <c r="H241" s="20" t="inlineStr">
+        <is>
+          <t>BK-IS14 Product Management, Scrum, Lean</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="22">
+    <mergeCell ref="A159:G159"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A135:G135"/>
+    <mergeCell ref="A171:G171"/>
+    <mergeCell ref="A198:F198"/>
+    <mergeCell ref="A225:H225"/>
+    <mergeCell ref="A216:H216"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A89:G89"/>
-    <mergeCell ref="A149:G149"/>
+    <mergeCell ref="A111:G111"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A182:G182"/>
     <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A123:G123"/>
+    <mergeCell ref="A146:G146"/>
+    <mergeCell ref="A234:H234"/>
+    <mergeCell ref="A193:G193"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A188:F188"/>
-    <mergeCell ref="A176:F176"/>
-    <mergeCell ref="A101:G101"/>
-    <mergeCell ref="A171:G171"/>
-    <mergeCell ref="A137:G137"/>
-    <mergeCell ref="A160:G160"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A113:G113"/>
-    <mergeCell ref="A77:F77"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
+++ b/KURIKULUM2026_REVISI/MASTER_KURIKULUM_OBE_SISTEKIN_2026.xlsx
@@ -23514,7 +23514,7 @@
   <cols>
     <col width="44.84999999999999" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="33.34999999999999" customWidth="1" min="3" max="3"/>
+    <col width="36.8" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -23627,7 +23627,7 @@
       <c r="B9" s="22" t="inlineStr"/>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>• STI-519 Keamanan Lanjut (3)</t>
+          <t>• STI-626 Deep Learning (+P) (3)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr"/>
